--- a/CEO Review.xlsx
+++ b/CEO Review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://peoplestronghrservices-my.sharepoint.com/personal/baljeet_singh_taggd_in/Documents/Desktop/Clude Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1459" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0136D6A5-674A-4810-8FA2-512D366206E8}"/>
+  <xr:revisionPtr revIDLastSave="1479" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1F8228E-E0C3-4F9A-832E-AFF643A44C06}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F2C8E0B5-D69E-42FC-A0A4-20379F29D696}"/>
   </bookViews>
@@ -4114,7 +4114,7 @@
         <v>43</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>84</v>
@@ -4123,7 +4123,7 @@
         <v>118</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="14">

--- a/CEO Review.xlsx
+++ b/CEO Review.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://peoplestronghrservices-my.sharepoint.com/personal/baljeet_singh_taggd_in/Documents/Desktop/Clude Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1479" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1F8228E-E0C3-4F9A-832E-AFF643A44C06}"/>
+  <xr:revisionPtr revIDLastSave="1591" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A2B0699-1645-445A-BFCA-7793F019BAFC}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F2C8E0B5-D69E-42FC-A0A4-20379F29D696}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Actual" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$BZ$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Actual!$A$2:$O$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$BZ$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="125">
   <si>
     <t>Clients</t>
   </si>
@@ -407,7 +409,16 @@
     <t>New Sales</t>
   </si>
   <si>
-    <t>Nizar</t>
+    <t>Quantiphi</t>
+  </si>
+  <si>
+    <t>Rahul</t>
+  </si>
+  <si>
+    <t>Apr</t>
+  </si>
+  <si>
+    <t>Rev</t>
   </si>
 </sst>
 </file>
@@ -542,7 +553,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -607,6 +618,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -995,71 +1012,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:78" x14ac:dyDescent="0.35">
-      <c r="G1" s="26" t="s">
+      <c r="G1" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="R1" s="26" t="s">
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="R1" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="S1" s="26"/>
-      <c r="T1" s="26"/>
-      <c r="U1" s="26"/>
-      <c r="V1" s="26"/>
-      <c r="W1" s="26"/>
-      <c r="X1" s="26"/>
-      <c r="Y1" s="26"/>
-      <c r="Z1" s="26"/>
-      <c r="AA1" s="26"/>
-      <c r="AC1" s="26" t="s">
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
+      <c r="V1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="28"/>
+      <c r="Y1" s="28"/>
+      <c r="Z1" s="28"/>
+      <c r="AA1" s="28"/>
+      <c r="AC1" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="AD1" s="26"/>
-      <c r="AE1" s="26"/>
-      <c r="AF1" s="26"/>
-      <c r="AG1" s="26"/>
-      <c r="AH1" s="26"/>
-      <c r="AI1" s="26"/>
-      <c r="AJ1" s="26"/>
-      <c r="AK1" s="26"/>
-      <c r="AL1" s="26"/>
-      <c r="AN1" s="26" t="s">
+      <c r="AD1" s="28"/>
+      <c r="AE1" s="28"/>
+      <c r="AF1" s="28"/>
+      <c r="AG1" s="28"/>
+      <c r="AH1" s="28"/>
+      <c r="AI1" s="28"/>
+      <c r="AJ1" s="28"/>
+      <c r="AK1" s="28"/>
+      <c r="AL1" s="28"/>
+      <c r="AN1" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="AO1" s="26"/>
-      <c r="AP1" s="26"/>
-      <c r="AQ1" s="26"/>
-      <c r="AR1" s="26"/>
-      <c r="AS1" s="26"/>
-      <c r="AT1" s="26"/>
-      <c r="AU1" s="26"/>
-      <c r="AV1" s="26"/>
-      <c r="AW1" s="26"/>
-      <c r="AY1" s="27" t="s">
+      <c r="AO1" s="28"/>
+      <c r="AP1" s="28"/>
+      <c r="AQ1" s="28"/>
+      <c r="AR1" s="28"/>
+      <c r="AS1" s="28"/>
+      <c r="AT1" s="28"/>
+      <c r="AU1" s="28"/>
+      <c r="AV1" s="28"/>
+      <c r="AW1" s="28"/>
+      <c r="AY1" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="AZ1" s="27"/>
-      <c r="BA1" s="27"/>
-      <c r="BB1" s="27"/>
-      <c r="BC1" s="27"/>
-      <c r="BD1" s="27"/>
-      <c r="BE1" s="27"/>
-      <c r="BF1" s="27"/>
-      <c r="BG1" s="27"/>
-      <c r="BH1" s="27"/>
-      <c r="BJ1" s="26" t="s">
+      <c r="AZ1" s="29"/>
+      <c r="BA1" s="29"/>
+      <c r="BB1" s="29"/>
+      <c r="BC1" s="29"/>
+      <c r="BD1" s="29"/>
+      <c r="BE1" s="29"/>
+      <c r="BF1" s="29"/>
+      <c r="BG1" s="29"/>
+      <c r="BH1" s="29"/>
+      <c r="BJ1" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="BK1" s="26"/>
-      <c r="BL1" s="26"/>
+      <c r="BK1" s="28"/>
+      <c r="BL1" s="28"/>
       <c r="BN1" s="19" t="s">
         <v>79</v>
       </c>
@@ -1579,11 +1596,11 @@
         <v>0</v>
       </c>
       <c r="AY4" s="17">
-        <f t="shared" ref="AY4:AZ60" si="5">R4+AC4+AN4+G4</f>
+        <f t="shared" ref="AY4:AY60" si="5">R4+AC4+AN4+G4</f>
         <v>20</v>
       </c>
       <c r="AZ4" s="17">
-        <f t="shared" ref="AZ4:AZ59" si="6">S4+AD4+AO4+H4</f>
+        <f t="shared" ref="AZ4:AZ61" si="6">S4+AD4+AO4+H4</f>
         <v>24.876199999999997</v>
       </c>
       <c r="BA4" s="17">
@@ -7473,14 +7490,14 @@
         <v>46</v>
       </c>
       <c r="H38" s="17">
-        <v>46</v>
+        <v>54.4</v>
       </c>
       <c r="I38" s="3">
-        <v>10.783197784832396</v>
+        <v>19.183197784832394</v>
       </c>
       <c r="J38" s="4">
         <f t="shared" si="2"/>
-        <v>0.23441734314853035</v>
+        <v>0.35263231222118374</v>
       </c>
       <c r="K38" s="3">
         <v>100619.43490047885</v>
@@ -7575,15 +7592,15 @@
       </c>
       <c r="AZ38" s="17">
         <f t="shared" si="6"/>
-        <v>232</v>
+        <v>240.4</v>
       </c>
       <c r="BA38" s="17">
         <f t="shared" si="7"/>
-        <v>80.567750474779331</v>
+        <v>88.967750474779336</v>
       </c>
       <c r="BB38" s="4">
         <f t="shared" si="8"/>
-        <v>0.34727478652922128</v>
+        <v>0.37008215671705214</v>
       </c>
       <c r="BC38" s="3">
         <f t="shared" si="10"/>
@@ -11242,16 +11259,16 @@
         <v>120</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E60" s="16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G60" s="23">
         <v>217</v>
@@ -11273,29 +11290,17 @@
         <v>0</v>
       </c>
       <c r="M60" s="17"/>
-      <c r="R60">
-        <v>575.60266666666666</v>
-      </c>
-      <c r="W60">
-        <v>0</v>
-      </c>
       <c r="X60" s="17"/>
-      <c r="AC60">
-        <v>742.6486666666666</v>
-      </c>
       <c r="AH60">
         <v>0</v>
       </c>
       <c r="AI60" s="17"/>
-      <c r="AN60">
-        <v>995.74866666666662</v>
-      </c>
       <c r="AY60" s="17">
         <f t="shared" si="5"/>
-        <v>2531</v>
+        <v>217</v>
       </c>
       <c r="AZ60" s="17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BA60" s="18"/>
@@ -11304,21 +11309,48 @@
       <c r="BH60" s="7"/>
     </row>
     <row r="61" spans="1:78" x14ac:dyDescent="0.35">
+      <c r="A61" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="B61" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="D61" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="E61" s="16" t="s">
+        <v>122</v>
+      </c>
       <c r="G61" s="18"/>
-      <c r="H61" s="18"/>
-      <c r="I61" s="18"/>
+      <c r="H61" s="27">
+        <v>25</v>
+      </c>
+      <c r="I61" s="27">
+        <v>18.829519600000001</v>
+      </c>
+      <c r="J61" s="25">
+        <f>(H61-I61)/H61</f>
+        <v>0.24681921599999995</v>
+      </c>
+      <c r="K61">
+        <v>117684.4975</v>
+      </c>
+      <c r="L61" s="24">
+        <v>5.2</v>
+      </c>
       <c r="R61" s="18"/>
       <c r="S61" s="18"/>
       <c r="T61" s="18"/>
-      <c r="AD61" s="18">
-        <f>SUM(AD3:AD59)</f>
-        <v>3050.4382926999997</v>
-      </c>
-      <c r="AE61" s="18">
-        <f>SUM(AE3:AE59)</f>
-        <v>1111.0013699458748</v>
-      </c>
+      <c r="AD61" s="18"/>
+      <c r="AE61" s="18"/>
       <c r="AO61" s="18"/>
+      <c r="AZ61" s="17">
+        <f t="shared" si="6"/>
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -11331,4 +11363,2266 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97FC45BD-D7D2-468B-B2BF-48180A39FC65}">
+  <dimension ref="A1:O61"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="25.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.36328125" customWidth="1"/>
+    <col min="7" max="7" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="G1" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" s="17">
+        <v>120</v>
+      </c>
+      <c r="H3" s="7">
+        <v>96.630983659997625</v>
+      </c>
+      <c r="I3" s="4">
+        <f>IFERROR(H3/G3,0)</f>
+        <v>0.80525819716664693</v>
+      </c>
+      <c r="J3" s="17">
+        <v>107620.37733721343</v>
+      </c>
+      <c r="K3" s="17">
+        <v>57.333333333333336</v>
+      </c>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" s="17">
+        <v>2.2562000000000002</v>
+      </c>
+      <c r="H4" s="7">
+        <v>-0.17604378797486162</v>
+      </c>
+      <c r="I4" s="4">
+        <f t="shared" ref="I4:I61" si="0">IFERROR(H4/G4,0)</f>
+        <v>-7.8026676701915432E-2</v>
+      </c>
+      <c r="J4" s="17">
+        <v>173405.52273207638</v>
+      </c>
+      <c r="K4" s="17">
+        <v>2</v>
+      </c>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G5" s="17">
+        <v>9.3010766</v>
+      </c>
+      <c r="H5" s="7">
+        <v>3.561191132154701</v>
+      </c>
+      <c r="I5" s="4">
+        <f t="shared" si="0"/>
+        <v>0.3828794542079893</v>
+      </c>
+      <c r="J5" s="17">
+        <v>100967.52669613245</v>
+      </c>
+      <c r="K5" s="17">
+        <v>4</v>
+      </c>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G6" s="17">
+        <v>26.5</v>
+      </c>
+      <c r="H6" s="7">
+        <v>-3.5042859329899017</v>
+      </c>
+      <c r="I6" s="4">
+        <f t="shared" si="0"/>
+        <v>-0.13223720501848685</v>
+      </c>
+      <c r="J6" s="17">
+        <v>110580.54850844618</v>
+      </c>
+      <c r="K6" s="17">
+        <v>15.666666666666666</v>
+      </c>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="17">
+        <v>6.1185</v>
+      </c>
+      <c r="H7" s="7">
+        <v>0.29414927678181019</v>
+      </c>
+      <c r="I7" s="4">
+        <f t="shared" si="0"/>
+        <v>4.8075390501235625E-2</v>
+      </c>
+      <c r="J7" s="17">
+        <v>101311.4009425254</v>
+      </c>
+      <c r="K7" s="17">
+        <v>6</v>
+      </c>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G8" s="17">
+        <v>13.0525</v>
+      </c>
+      <c r="H8" s="7">
+        <v>1.4691666666666663</v>
+      </c>
+      <c r="I8" s="4">
+        <f t="shared" si="0"/>
+        <v>0.112558258315776</v>
+      </c>
+      <c r="J8" s="17">
+        <v>101000</v>
+      </c>
+      <c r="K8" s="17">
+        <v>8.1666666666666661</v>
+      </c>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G9" s="17">
+        <v>6.83</v>
+      </c>
+      <c r="H9" s="7">
+        <v>-0.19260178039615519</v>
+      </c>
+      <c r="I9" s="4">
+        <f t="shared" si="0"/>
+        <v>-2.8199382195630337E-2</v>
+      </c>
+      <c r="J9" s="17">
+        <v>80180.641691213954</v>
+      </c>
+      <c r="K9" s="17">
+        <v>10.666666666666666</v>
+      </c>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G10" s="17">
+        <v>2.7279200000000001</v>
+      </c>
+      <c r="H10" s="7">
+        <v>1.1487128559241577</v>
+      </c>
+      <c r="I10" s="4">
+        <f t="shared" si="0"/>
+        <v>0.42109477401249218</v>
+      </c>
+      <c r="J10" s="17">
+        <v>105409.9872037921</v>
+      </c>
+      <c r="K10" s="17">
+        <v>2</v>
+      </c>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G11" s="17">
+        <v>12.79</v>
+      </c>
+      <c r="H11" s="7">
+        <v>5.5607583716918079</v>
+      </c>
+      <c r="I11" s="4">
+        <f t="shared" si="0"/>
+        <v>0.4347739149094455</v>
+      </c>
+      <c r="J11" s="17">
+        <v>92529.711095863735</v>
+      </c>
+      <c r="K11" s="17">
+        <v>8.6666666666666661</v>
+      </c>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" s="17">
+        <v>181.56917999999999</v>
+      </c>
+      <c r="H12" s="7">
+        <v>60.485020524784211</v>
+      </c>
+      <c r="I12" s="4">
+        <f t="shared" si="0"/>
+        <v>0.33312382930178025</v>
+      </c>
+      <c r="J12" s="17">
+        <v>139210.95651634005</v>
+      </c>
+      <c r="K12" s="17">
+        <v>56.4</v>
+      </c>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13" s="17">
+        <v>3.7850000000000001</v>
+      </c>
+      <c r="H13" s="7">
+        <v>1.8593369920277556</v>
+      </c>
+      <c r="I13" s="4">
+        <f t="shared" si="0"/>
+        <v>0.49123830700865406</v>
+      </c>
+      <c r="J13" s="17">
+        <v>127874.84755439906</v>
+      </c>
+      <c r="K13" s="17">
+        <v>2.4</v>
+      </c>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G14" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="H14" s="7">
+        <v>-0.91500000000000004</v>
+      </c>
+      <c r="I14" s="4">
+        <f t="shared" si="0"/>
+        <v>-1.0166666666666666</v>
+      </c>
+      <c r="J14" s="17">
+        <v>90000</v>
+      </c>
+      <c r="K14" s="17">
+        <v>1.3499999999999999</v>
+      </c>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G15" s="17">
+        <v>0</v>
+      </c>
+      <c r="H15" s="7">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="17">
+        <v>0</v>
+      </c>
+      <c r="K15" s="17">
+        <v>0</v>
+      </c>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" s="17">
+        <v>4.5916899999999998</v>
+      </c>
+      <c r="H16" s="7">
+        <v>1.4324625273205285</v>
+      </c>
+      <c r="I16" s="4">
+        <f t="shared" si="0"/>
+        <v>0.31196847507574088</v>
+      </c>
+      <c r="J16" s="17">
+        <v>84493.658345803764</v>
+      </c>
+      <c r="K16" s="17">
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G17" s="17">
+        <v>119.60778230000001</v>
+      </c>
+      <c r="H17" s="7">
+        <v>45.798046329112786</v>
+      </c>
+      <c r="I17" s="4">
+        <f t="shared" si="0"/>
+        <v>0.38290189357614052</v>
+      </c>
+      <c r="J17" s="17">
+        <v>93889.935253165968</v>
+      </c>
+      <c r="K17" s="17">
+        <v>80.666666666666671</v>
+      </c>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G18" s="17">
+        <v>6.1910834999999995</v>
+      </c>
+      <c r="H18" s="7">
+        <v>12.332741667468573</v>
+      </c>
+      <c r="I18" s="4">
+        <f t="shared" si="0"/>
+        <v>1.9920166910151631</v>
+      </c>
+      <c r="J18" s="17">
+        <v>130642.86165864758</v>
+      </c>
+      <c r="K18" s="17">
+        <v>10</v>
+      </c>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19" s="17">
+        <v>39.987499999999997</v>
+      </c>
+      <c r="H19" s="7">
+        <v>16.605902462209162</v>
+      </c>
+      <c r="I19" s="4">
+        <f t="shared" si="0"/>
+        <v>0.41527733572264242</v>
+      </c>
+      <c r="J19" s="17">
+        <v>98824.569981892113</v>
+      </c>
+      <c r="K19" s="17">
+        <v>12.199999999999998</v>
+      </c>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G20" s="17">
+        <v>6.9908000000000001</v>
+      </c>
+      <c r="H20" s="7">
+        <v>4.9588260938679767</v>
+      </c>
+      <c r="I20" s="4">
+        <f t="shared" si="0"/>
+        <v>0.70933599786404655</v>
+      </c>
+      <c r="J20" s="17">
+        <v>87648.628603046702</v>
+      </c>
+      <c r="K20" s="17">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G21" s="17">
+        <v>26.27983</v>
+      </c>
+      <c r="H21" s="7">
+        <v>3.5382942375971473</v>
+      </c>
+      <c r="I21" s="4">
+        <f t="shared" si="0"/>
+        <v>0.13463916005534082</v>
+      </c>
+      <c r="J21" s="17">
+        <v>92605.584307238096</v>
+      </c>
+      <c r="K21" s="17">
+        <v>35.5</v>
+      </c>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G22" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H22" s="7">
+        <v>0.8944301000144349</v>
+      </c>
+      <c r="I22" s="4">
+        <f t="shared" si="0"/>
+        <v>8.9443010001443479</v>
+      </c>
+      <c r="J22" s="17">
+        <v>103085.48499783476</v>
+      </c>
+      <c r="K22" s="17">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" s="17">
+        <v>0.68445</v>
+      </c>
+      <c r="H23" s="7">
+        <v>-0.20664055542154255</v>
+      </c>
+      <c r="I23" s="4">
+        <f t="shared" si="0"/>
+        <v>-0.30190745185410556</v>
+      </c>
+      <c r="J23" s="17">
+        <v>110145.72220882092</v>
+      </c>
+      <c r="K23" s="17">
+        <v>1</v>
+      </c>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G24" s="17">
+        <v>1.6505700000000001</v>
+      </c>
+      <c r="H24" s="7">
+        <v>-0.80506115618567142</v>
+      </c>
+      <c r="I24" s="4">
+        <f t="shared" si="0"/>
+        <v>-0.48774735769199207</v>
+      </c>
+      <c r="J24" s="17">
+        <v>100838.35645704676</v>
+      </c>
+      <c r="K24" s="17">
+        <v>5</v>
+      </c>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G25" s="17">
+        <v>10.015700000000001</v>
+      </c>
+      <c r="H25" s="7">
+        <v>4.84458093899734</v>
+      </c>
+      <c r="I25" s="4">
+        <f t="shared" si="0"/>
+        <v>0.48369868696120488</v>
+      </c>
+      <c r="J25" s="17">
+        <v>99879.714553386511</v>
+      </c>
+      <c r="K25" s="17">
+        <v>5</v>
+      </c>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G26" s="17">
+        <v>24.223479999999999</v>
+      </c>
+      <c r="H26" s="7">
+        <v>-5.7914111873014162</v>
+      </c>
+      <c r="I26" s="4">
+        <f t="shared" si="0"/>
+        <v>-0.23908254252904276</v>
+      </c>
+      <c r="J26" s="17">
+        <v>117138.77421768615</v>
+      </c>
+      <c r="K26" s="17">
+        <v>18.666666666666668</v>
+      </c>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G27" s="17">
+        <v>0</v>
+      </c>
+      <c r="H27" s="7">
+        <v>-0.43439174266359831</v>
+      </c>
+      <c r="I27" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="17">
+        <v>130317.5227990795</v>
+      </c>
+      <c r="K27" s="17">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="8"/>
+      <c r="O27" s="8"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G28" s="17">
+        <v>10.29</v>
+      </c>
+      <c r="H28" s="7">
+        <v>-7.6009084794700739E-3</v>
+      </c>
+      <c r="I28" s="4">
+        <f t="shared" si="0"/>
+        <v>-7.3866943435083325E-4</v>
+      </c>
+      <c r="J28" s="17">
+        <v>83282.006813596032</v>
+      </c>
+      <c r="K28" s="17">
+        <v>13.333333333333334</v>
+      </c>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G29" s="17">
+        <v>5.4947099999999995</v>
+      </c>
+      <c r="H29" s="7">
+        <v>-0.1393034954768749</v>
+      </c>
+      <c r="I29" s="4">
+        <f t="shared" si="0"/>
+        <v>-2.5352292564461986E-2</v>
+      </c>
+      <c r="J29" s="17">
+        <v>91755.335649669636</v>
+      </c>
+      <c r="K29" s="17">
+        <v>7</v>
+      </c>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="8"/>
+      <c r="O29" s="8"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G30" s="17">
+        <v>0</v>
+      </c>
+      <c r="H30" s="7">
+        <v>0.6</v>
+      </c>
+      <c r="I30" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="17">
+        <v>110000</v>
+      </c>
+      <c r="K30" s="17">
+        <v>0</v>
+      </c>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A31" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G31" s="17">
+        <v>26.5</v>
+      </c>
+      <c r="H31" s="7">
+        <v>-2.604686874742915</v>
+      </c>
+      <c r="I31" s="4">
+        <f t="shared" si="0"/>
+        <v>-9.8290070745015667E-2</v>
+      </c>
+      <c r="J31" s="17">
+        <v>92547.060993046674</v>
+      </c>
+      <c r="K31" s="17">
+        <v>27.666666666666668</v>
+      </c>
+      <c r="L31" s="8"/>
+      <c r="M31" s="8"/>
+      <c r="N31" s="8"/>
+      <c r="O31" s="8"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A32" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G32" s="17">
+        <v>30.8</v>
+      </c>
+      <c r="H32" s="7">
+        <v>14.827293382532636</v>
+      </c>
+      <c r="I32" s="4">
+        <f t="shared" si="0"/>
+        <v>0.48140562930300762</v>
+      </c>
+      <c r="J32" s="17">
+        <v>87949.115935818816</v>
+      </c>
+      <c r="K32" s="17">
+        <v>14.333333333333334</v>
+      </c>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+      <c r="N32" s="8"/>
+      <c r="O32" s="8"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A33" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G33" s="17">
+        <v>0</v>
+      </c>
+      <c r="H33" s="7">
+        <v>-1.2224075445787013</v>
+      </c>
+      <c r="I33" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="17">
+        <v>122240.75445787013</v>
+      </c>
+      <c r="K33" s="17">
+        <v>1</v>
+      </c>
+      <c r="L33" s="8"/>
+      <c r="M33" s="8"/>
+      <c r="N33" s="8"/>
+      <c r="O33" s="8"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A34" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G34" s="17">
+        <v>0</v>
+      </c>
+      <c r="H34" s="7">
+        <v>0</v>
+      </c>
+      <c r="I34" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="17">
+        <v>0</v>
+      </c>
+      <c r="K34" s="17">
+        <v>0</v>
+      </c>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+      <c r="N34" s="8"/>
+      <c r="O34" s="8"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A35" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G35" s="17">
+        <v>3.81</v>
+      </c>
+      <c r="H35" s="7">
+        <v>0.33530240421176227</v>
+      </c>
+      <c r="I35" s="4">
+        <f t="shared" si="0"/>
+        <v>8.8005880370541273E-2</v>
+      </c>
+      <c r="J35" s="17">
+        <v>95201.325533781623</v>
+      </c>
+      <c r="K35" s="17">
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
+      <c r="N35" s="8"/>
+      <c r="O35" s="8"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A36" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G36" s="17">
+        <v>3.6067749999999998</v>
+      </c>
+      <c r="H36" s="7">
+        <v>2.1636641240935273</v>
+      </c>
+      <c r="I36" s="4">
+        <f t="shared" si="0"/>
+        <v>0.59988885475071974</v>
+      </c>
+      <c r="J36" s="17">
+        <v>82348.641423246372</v>
+      </c>
+      <c r="K36" s="17">
+        <v>5.333333333333333</v>
+      </c>
+      <c r="L36" s="8"/>
+      <c r="M36" s="8"/>
+      <c r="N36" s="8"/>
+      <c r="O36" s="8"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A37" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G37" s="17">
+        <v>37.19</v>
+      </c>
+      <c r="H37" s="7">
+        <v>-10.621458196587033</v>
+      </c>
+      <c r="I37" s="4">
+        <f t="shared" si="0"/>
+        <v>-0.28559984395232679</v>
+      </c>
+      <c r="J37" s="17">
+        <v>94388.83163095171</v>
+      </c>
+      <c r="K37" s="17">
+        <v>40.666666666666664</v>
+      </c>
+      <c r="L37" s="8"/>
+      <c r="M37" s="8"/>
+      <c r="N37" s="8"/>
+      <c r="O37" s="8"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A38" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G38" s="17">
+        <v>12</v>
+      </c>
+      <c r="H38" s="7">
+        <v>6.3943992616107979</v>
+      </c>
+      <c r="I38" s="4">
+        <f t="shared" si="0"/>
+        <v>0.53286660513423312</v>
+      </c>
+      <c r="J38" s="17">
+        <v>100619.43490047885</v>
+      </c>
+      <c r="K38" s="17">
+        <v>11.666666666666666</v>
+      </c>
+      <c r="L38" s="8"/>
+      <c r="M38" s="8"/>
+      <c r="N38" s="8"/>
+      <c r="O38" s="8"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G39" s="17">
+        <v>4.83</v>
+      </c>
+      <c r="H39" s="7">
+        <v>2.4016443555995544</v>
+      </c>
+      <c r="I39" s="4">
+        <f t="shared" si="0"/>
+        <v>0.49723485623179181</v>
+      </c>
+      <c r="J39" s="17">
+        <v>93473.032591125986</v>
+      </c>
+      <c r="K39" s="17">
+        <v>3</v>
+      </c>
+      <c r="L39" s="8"/>
+      <c r="M39" s="8"/>
+      <c r="N39" s="8"/>
+      <c r="O39" s="8"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A40" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G40" s="17">
+        <v>3.5616104000000002</v>
+      </c>
+      <c r="H40" s="7">
+        <v>3.0382940431250547</v>
+      </c>
+      <c r="I40" s="4">
+        <f t="shared" si="0"/>
+        <v>0.85306748967406842</v>
+      </c>
+      <c r="J40" s="17">
+        <v>102889.40225520697</v>
+      </c>
+      <c r="K40" s="17">
+        <v>4</v>
+      </c>
+      <c r="L40" s="8"/>
+      <c r="M40" s="8"/>
+      <c r="N40" s="8"/>
+      <c r="O40" s="8"/>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A41" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G41" s="17">
+        <v>0</v>
+      </c>
+      <c r="H41" s="7">
+        <v>0</v>
+      </c>
+      <c r="I41" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J41" s="17">
+        <v>0</v>
+      </c>
+      <c r="K41" s="17">
+        <v>0</v>
+      </c>
+      <c r="L41" s="8"/>
+      <c r="M41" s="8"/>
+      <c r="N41" s="8"/>
+      <c r="O41" s="8"/>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A42" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G42" s="17">
+        <v>10.17</v>
+      </c>
+      <c r="H42" s="7">
+        <v>3.984591770590749</v>
+      </c>
+      <c r="I42" s="4">
+        <f t="shared" si="0"/>
+        <v>0.39179860084471474</v>
+      </c>
+      <c r="J42" s="17">
+        <v>109174.83125485166</v>
+      </c>
+      <c r="K42" s="17">
+        <v>5</v>
+      </c>
+      <c r="L42" s="8"/>
+      <c r="M42" s="8"/>
+      <c r="N42" s="8"/>
+      <c r="O42" s="8"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A43" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G43" s="17">
+        <v>0</v>
+      </c>
+      <c r="H43" s="7">
+        <v>3.3333333333333326E-2</v>
+      </c>
+      <c r="I43" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="17">
+        <v>90000</v>
+      </c>
+      <c r="K43" s="17">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="L43" s="8"/>
+      <c r="M43" s="8"/>
+      <c r="N43" s="8"/>
+      <c r="O43" s="8"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A44" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G44" s="17">
+        <v>2.90625</v>
+      </c>
+      <c r="H44" s="7">
+        <v>1.4333848089524714</v>
+      </c>
+      <c r="I44" s="4">
+        <f t="shared" si="0"/>
+        <v>0.49320767619869987</v>
+      </c>
+      <c r="J44" s="17">
+        <v>112725.33024016366</v>
+      </c>
+      <c r="K44" s="17">
+        <v>4.6000000000000005</v>
+      </c>
+      <c r="L44" s="8"/>
+      <c r="M44" s="8"/>
+      <c r="N44" s="8"/>
+      <c r="O44" s="8"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A45" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G45" s="17">
+        <v>7.97</v>
+      </c>
+      <c r="H45" s="7">
+        <v>4.0882134700977213</v>
+      </c>
+      <c r="I45" s="4">
+        <f t="shared" si="0"/>
+        <v>0.51295024718917459</v>
+      </c>
+      <c r="J45" s="17">
+        <v>115651.32991422365</v>
+      </c>
+      <c r="K45" s="17">
+        <v>4</v>
+      </c>
+      <c r="L45" s="8"/>
+      <c r="M45" s="8"/>
+      <c r="N45" s="8"/>
+      <c r="O45" s="8"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A46" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G46" s="17">
+        <v>10.65</v>
+      </c>
+      <c r="H46" s="7">
+        <v>3.7363008021508812</v>
+      </c>
+      <c r="I46" s="4">
+        <f t="shared" si="0"/>
+        <v>0.35082636639914377</v>
+      </c>
+      <c r="J46" s="17">
+        <v>74953.145229196627</v>
+      </c>
+      <c r="K46" s="17">
+        <v>6.333333333333333</v>
+      </c>
+      <c r="L46" s="8"/>
+      <c r="M46" s="8"/>
+      <c r="N46" s="8"/>
+      <c r="O46" s="8"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A47" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G47" s="17">
+        <v>6.5951000000000004</v>
+      </c>
+      <c r="H47" s="7">
+        <v>0.88921430612099994</v>
+      </c>
+      <c r="I47" s="4">
+        <f t="shared" si="0"/>
+        <v>0.13482954104122757</v>
+      </c>
+      <c r="J47" s="17">
+        <v>108677.95830910001</v>
+      </c>
+      <c r="K47" s="17">
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="L47" s="8"/>
+      <c r="M47" s="8"/>
+      <c r="N47" s="8"/>
+      <c r="O47" s="8"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A48" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G48" s="17">
+        <v>65.400000000000006</v>
+      </c>
+      <c r="H48" s="7">
+        <v>26.472517639262765</v>
+      </c>
+      <c r="I48" s="4">
+        <f t="shared" si="0"/>
+        <v>0.40477855717527161</v>
+      </c>
+      <c r="J48" s="17">
+        <v>104841.14470569149</v>
+      </c>
+      <c r="K48" s="17">
+        <v>24.666666666666668</v>
+      </c>
+      <c r="L48" s="8"/>
+      <c r="M48" s="8"/>
+      <c r="N48" s="8"/>
+      <c r="O48" s="8"/>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A49" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G49" s="17">
+        <v>17</v>
+      </c>
+      <c r="H49" s="7">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="I49" s="4">
+        <f t="shared" si="0"/>
+        <v>0.2829411764705882</v>
+      </c>
+      <c r="J49" s="17">
+        <v>101000</v>
+      </c>
+      <c r="K49" s="17">
+        <v>19</v>
+      </c>
+      <c r="L49" s="8"/>
+      <c r="M49" s="8"/>
+      <c r="N49" s="8"/>
+      <c r="O49" s="8"/>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A50" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G50" s="17">
+        <v>7.9112900000000002</v>
+      </c>
+      <c r="H50" s="7">
+        <v>5.8537633333333341</v>
+      </c>
+      <c r="I50" s="4">
+        <f t="shared" si="0"/>
+        <v>0.73992526292593674</v>
+      </c>
+      <c r="J50" s="17">
+        <v>101000</v>
+      </c>
+      <c r="K50" s="17">
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="L50" s="8"/>
+      <c r="M50" s="8"/>
+      <c r="N50" s="8"/>
+      <c r="O50" s="8"/>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A51" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G51" s="17">
+        <v>0</v>
+      </c>
+      <c r="H51" s="7">
+        <v>-6.3453123695111699</v>
+      </c>
+      <c r="I51" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="17">
+        <v>105755.2061585195</v>
+      </c>
+      <c r="K51" s="17">
+        <v>6</v>
+      </c>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="8"/>
+      <c r="O51" s="8"/>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A52" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G52" s="17">
+        <v>1</v>
+      </c>
+      <c r="H52" s="7">
+        <v>-0.7882832298375444</v>
+      </c>
+      <c r="I52" s="4">
+        <f t="shared" si="0"/>
+        <v>-0.7882832298375444</v>
+      </c>
+      <c r="J52" s="17">
+        <v>139414.16149187722</v>
+      </c>
+      <c r="K52" s="17">
+        <v>2</v>
+      </c>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+      <c r="N52" s="8"/>
+      <c r="O52" s="8"/>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A53" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G53" s="17">
+        <v>0</v>
+      </c>
+      <c r="H53" s="7">
+        <v>0</v>
+      </c>
+      <c r="I53" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="17">
+        <v>121584.75193965515</v>
+      </c>
+      <c r="K53" s="17">
+        <v>0</v>
+      </c>
+      <c r="L53" s="8"/>
+      <c r="M53" s="8"/>
+      <c r="N53" s="8"/>
+      <c r="O53" s="8"/>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A54" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G54" s="17">
+        <v>0</v>
+      </c>
+      <c r="H54" s="7">
+        <v>0</v>
+      </c>
+      <c r="I54" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J54" s="17">
+        <v>0</v>
+      </c>
+      <c r="K54" s="17">
+        <v>0</v>
+      </c>
+      <c r="L54" s="8"/>
+      <c r="M54" s="8"/>
+      <c r="N54" s="8"/>
+      <c r="O54" s="8"/>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A55" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G55" s="17">
+        <v>9</v>
+      </c>
+      <c r="H55" s="7">
+        <v>-6.5757544546004523</v>
+      </c>
+      <c r="I55" s="4">
+        <f t="shared" si="0"/>
+        <v>-0.73063938384449467</v>
+      </c>
+      <c r="J55" s="17">
+        <v>50745.724005939614</v>
+      </c>
+      <c r="K55" s="17">
+        <v>21.333333333333332</v>
+      </c>
+      <c r="L55" s="8"/>
+      <c r="M55" s="8"/>
+      <c r="N55" s="8"/>
+      <c r="O55" s="8"/>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A56" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G56" s="17">
+        <v>2.9410600000000002</v>
+      </c>
+      <c r="H56" s="7">
+        <v>0.44902000000000014</v>
+      </c>
+      <c r="I56" s="4">
+        <f t="shared" si="0"/>
+        <v>0.15267284584469548</v>
+      </c>
+      <c r="J56" s="17">
+        <v>101000</v>
+      </c>
+      <c r="K56" s="17">
+        <v>0.79999999999999993</v>
+      </c>
+      <c r="L56" s="8"/>
+      <c r="M56" s="8"/>
+      <c r="N56" s="8"/>
+      <c r="O56" s="8"/>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A57" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G57" s="17">
+        <v>0</v>
+      </c>
+      <c r="H57" s="7">
+        <v>-1.4939221985593101</v>
+      </c>
+      <c r="I57" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="17">
+        <v>448176.65956779307</v>
+      </c>
+      <c r="K57" s="17">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="L57" s="8"/>
+      <c r="M57" s="8"/>
+      <c r="N57" s="8"/>
+      <c r="O57" s="8"/>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A58" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B58" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C58" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E58" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="G58" s="17">
+        <v>0</v>
+      </c>
+      <c r="H58" s="7">
+        <v>0.28333333333333338</v>
+      </c>
+      <c r="I58" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="17">
+        <v>90000</v>
+      </c>
+      <c r="K58" s="17">
+        <v>1.1666666666666667</v>
+      </c>
+      <c r="L58" s="8"/>
+      <c r="M58" s="8"/>
+      <c r="N58" s="8"/>
+      <c r="O58" s="8"/>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A59" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="B59" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C59" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E59" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="G59" s="17">
+        <v>1.75</v>
+      </c>
+      <c r="H59" s="7">
+        <v>1.24</v>
+      </c>
+      <c r="I59" s="4">
+        <f t="shared" si="0"/>
+        <v>0.70857142857142852</v>
+      </c>
+      <c r="J59" s="17">
+        <v>90000</v>
+      </c>
+      <c r="K59" s="17">
+        <v>0.56666666666666665</v>
+      </c>
+      <c r="L59" s="8"/>
+      <c r="M59" s="8"/>
+      <c r="N59" s="8"/>
+      <c r="O59" s="8"/>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A60" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="B60" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="C60" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E60" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="G60" s="17">
+        <v>0</v>
+      </c>
+      <c r="H60" s="7">
+        <v>0</v>
+      </c>
+      <c r="I60" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J60" s="17">
+        <v>0</v>
+      </c>
+      <c r="K60" s="17">
+        <v>0</v>
+      </c>
+      <c r="L60" s="8"/>
+      <c r="M60" s="8"/>
+      <c r="N60" s="8"/>
+      <c r="O60" s="8"/>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A61" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="B61" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="D61" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="E61" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G61" s="17">
+        <v>0</v>
+      </c>
+      <c r="H61" s="7">
+        <v>0</v>
+      </c>
+      <c r="I61" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J61" s="17">
+        <v>117684.4975</v>
+      </c>
+      <c r="K61" s="17">
+        <v>5.2</v>
+      </c>
+      <c r="L61" s="8"/>
+      <c r="M61" s="8"/>
+      <c r="N61" s="8"/>
+      <c r="O61" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G1:O1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/CEO Review.xlsx
+++ b/CEO Review.xlsx
@@ -8,16 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://peoplestronghrservices-my.sharepoint.com/personal/baljeet_singh_taggd_in/Documents/Desktop/Clude Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1591" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A2B0699-1645-445A-BFCA-7793F019BAFC}"/>
+  <xr:revisionPtr revIDLastSave="1592" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{373BA5BD-E38F-4D82-A3FB-075ACE5C396B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F2C8E0B5-D69E-42FC-A0A4-20379F29D696}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Actual" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Actual!$A$2:$O$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$BZ$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -44,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="123">
   <si>
     <t>Clients</t>
   </si>
@@ -413,12 +411,6 @@
   </si>
   <si>
     <t>Rahul</t>
-  </si>
-  <si>
-    <t>Apr</t>
-  </si>
-  <si>
-    <t>Rev</t>
   </si>
 </sst>
 </file>
@@ -11363,2266 +11355,4 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97FC45BD-D7D2-468B-B2BF-48180A39FC65}">
-  <dimension ref="A1:O61"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="25.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.36328125" customWidth="1"/>
-    <col min="7" max="7" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.7265625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="G1" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G3" s="17">
-        <v>120</v>
-      </c>
-      <c r="H3" s="7">
-        <v>96.630983659997625</v>
-      </c>
-      <c r="I3" s="4">
-        <f>IFERROR(H3/G3,0)</f>
-        <v>0.80525819716664693</v>
-      </c>
-      <c r="J3" s="17">
-        <v>107620.37733721343</v>
-      </c>
-      <c r="K3" s="17">
-        <v>57.333333333333336</v>
-      </c>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="G4" s="17">
-        <v>2.2562000000000002</v>
-      </c>
-      <c r="H4" s="7">
-        <v>-0.17604378797486162</v>
-      </c>
-      <c r="I4" s="4">
-        <f t="shared" ref="I4:I61" si="0">IFERROR(H4/G4,0)</f>
-        <v>-7.8026676701915432E-2</v>
-      </c>
-      <c r="J4" s="17">
-        <v>173405.52273207638</v>
-      </c>
-      <c r="K4" s="17">
-        <v>2</v>
-      </c>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G5" s="17">
-        <v>9.3010766</v>
-      </c>
-      <c r="H5" s="7">
-        <v>3.561191132154701</v>
-      </c>
-      <c r="I5" s="4">
-        <f t="shared" si="0"/>
-        <v>0.3828794542079893</v>
-      </c>
-      <c r="J5" s="17">
-        <v>100967.52669613245</v>
-      </c>
-      <c r="K5" s="17">
-        <v>4</v>
-      </c>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G6" s="17">
-        <v>26.5</v>
-      </c>
-      <c r="H6" s="7">
-        <v>-3.5042859329899017</v>
-      </c>
-      <c r="I6" s="4">
-        <f t="shared" si="0"/>
-        <v>-0.13223720501848685</v>
-      </c>
-      <c r="J6" s="17">
-        <v>110580.54850844618</v>
-      </c>
-      <c r="K6" s="17">
-        <v>15.666666666666666</v>
-      </c>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G7" s="17">
-        <v>6.1185</v>
-      </c>
-      <c r="H7" s="7">
-        <v>0.29414927678181019</v>
-      </c>
-      <c r="I7" s="4">
-        <f t="shared" si="0"/>
-        <v>4.8075390501235625E-2</v>
-      </c>
-      <c r="J7" s="17">
-        <v>101311.4009425254</v>
-      </c>
-      <c r="K7" s="17">
-        <v>6</v>
-      </c>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G8" s="17">
-        <v>13.0525</v>
-      </c>
-      <c r="H8" s="7">
-        <v>1.4691666666666663</v>
-      </c>
-      <c r="I8" s="4">
-        <f t="shared" si="0"/>
-        <v>0.112558258315776</v>
-      </c>
-      <c r="J8" s="17">
-        <v>101000</v>
-      </c>
-      <c r="K8" s="17">
-        <v>8.1666666666666661</v>
-      </c>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G9" s="17">
-        <v>6.83</v>
-      </c>
-      <c r="H9" s="7">
-        <v>-0.19260178039615519</v>
-      </c>
-      <c r="I9" s="4">
-        <f t="shared" si="0"/>
-        <v>-2.8199382195630337E-2</v>
-      </c>
-      <c r="J9" s="17">
-        <v>80180.641691213954</v>
-      </c>
-      <c r="K9" s="17">
-        <v>10.666666666666666</v>
-      </c>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G10" s="17">
-        <v>2.7279200000000001</v>
-      </c>
-      <c r="H10" s="7">
-        <v>1.1487128559241577</v>
-      </c>
-      <c r="I10" s="4">
-        <f t="shared" si="0"/>
-        <v>0.42109477401249218</v>
-      </c>
-      <c r="J10" s="17">
-        <v>105409.9872037921</v>
-      </c>
-      <c r="K10" s="17">
-        <v>2</v>
-      </c>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G11" s="17">
-        <v>12.79</v>
-      </c>
-      <c r="H11" s="7">
-        <v>5.5607583716918079</v>
-      </c>
-      <c r="I11" s="4">
-        <f t="shared" si="0"/>
-        <v>0.4347739149094455</v>
-      </c>
-      <c r="J11" s="17">
-        <v>92529.711095863735</v>
-      </c>
-      <c r="K11" s="17">
-        <v>8.6666666666666661</v>
-      </c>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G12" s="17">
-        <v>181.56917999999999</v>
-      </c>
-      <c r="H12" s="7">
-        <v>60.485020524784211</v>
-      </c>
-      <c r="I12" s="4">
-        <f t="shared" si="0"/>
-        <v>0.33312382930178025</v>
-      </c>
-      <c r="J12" s="17">
-        <v>139210.95651634005</v>
-      </c>
-      <c r="K12" s="17">
-        <v>56.4</v>
-      </c>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G13" s="17">
-        <v>3.7850000000000001</v>
-      </c>
-      <c r="H13" s="7">
-        <v>1.8593369920277556</v>
-      </c>
-      <c r="I13" s="4">
-        <f t="shared" si="0"/>
-        <v>0.49123830700865406</v>
-      </c>
-      <c r="J13" s="17">
-        <v>127874.84755439906</v>
-      </c>
-      <c r="K13" s="17">
-        <v>2.4</v>
-      </c>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="8"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G14" s="17">
-        <v>0.9</v>
-      </c>
-      <c r="H14" s="7">
-        <v>-0.91500000000000004</v>
-      </c>
-      <c r="I14" s="4">
-        <f t="shared" si="0"/>
-        <v>-1.0166666666666666</v>
-      </c>
-      <c r="J14" s="17">
-        <v>90000</v>
-      </c>
-      <c r="K14" s="17">
-        <v>1.3499999999999999</v>
-      </c>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G15" s="17">
-        <v>0</v>
-      </c>
-      <c r="H15" s="7">
-        <v>0</v>
-      </c>
-      <c r="I15" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="17">
-        <v>0</v>
-      </c>
-      <c r="K15" s="17">
-        <v>0</v>
-      </c>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G16" s="17">
-        <v>4.5916899999999998</v>
-      </c>
-      <c r="H16" s="7">
-        <v>1.4324625273205285</v>
-      </c>
-      <c r="I16" s="4">
-        <f t="shared" si="0"/>
-        <v>0.31196847507574088</v>
-      </c>
-      <c r="J16" s="17">
-        <v>84493.658345803764</v>
-      </c>
-      <c r="K16" s="17">
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G17" s="17">
-        <v>119.60778230000001</v>
-      </c>
-      <c r="H17" s="7">
-        <v>45.798046329112786</v>
-      </c>
-      <c r="I17" s="4">
-        <f t="shared" si="0"/>
-        <v>0.38290189357614052</v>
-      </c>
-      <c r="J17" s="17">
-        <v>93889.935253165968</v>
-      </c>
-      <c r="K17" s="17">
-        <v>80.666666666666671</v>
-      </c>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="8"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G18" s="17">
-        <v>6.1910834999999995</v>
-      </c>
-      <c r="H18" s="7">
-        <v>12.332741667468573</v>
-      </c>
-      <c r="I18" s="4">
-        <f t="shared" si="0"/>
-        <v>1.9920166910151631</v>
-      </c>
-      <c r="J18" s="17">
-        <v>130642.86165864758</v>
-      </c>
-      <c r="K18" s="17">
-        <v>10</v>
-      </c>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A19" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="G19" s="17">
-        <v>39.987499999999997</v>
-      </c>
-      <c r="H19" s="7">
-        <v>16.605902462209162</v>
-      </c>
-      <c r="I19" s="4">
-        <f t="shared" si="0"/>
-        <v>0.41527733572264242</v>
-      </c>
-      <c r="J19" s="17">
-        <v>98824.569981892113</v>
-      </c>
-      <c r="K19" s="17">
-        <v>12.199999999999998</v>
-      </c>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-      <c r="N19" s="8"/>
-      <c r="O19" s="8"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G20" s="17">
-        <v>6.9908000000000001</v>
-      </c>
-      <c r="H20" s="7">
-        <v>4.9588260938679767</v>
-      </c>
-      <c r="I20" s="4">
-        <f t="shared" si="0"/>
-        <v>0.70933599786404655</v>
-      </c>
-      <c r="J20" s="17">
-        <v>87648.628603046702</v>
-      </c>
-      <c r="K20" s="17">
-        <v>4.333333333333333</v>
-      </c>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
-      <c r="O20" s="8"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A21" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G21" s="17">
-        <v>26.27983</v>
-      </c>
-      <c r="H21" s="7">
-        <v>3.5382942375971473</v>
-      </c>
-      <c r="I21" s="4">
-        <f t="shared" si="0"/>
-        <v>0.13463916005534082</v>
-      </c>
-      <c r="J21" s="17">
-        <v>92605.584307238096</v>
-      </c>
-      <c r="K21" s="17">
-        <v>35.5</v>
-      </c>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="8"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A22" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G22" s="17">
-        <v>0.1</v>
-      </c>
-      <c r="H22" s="7">
-        <v>0.8944301000144349</v>
-      </c>
-      <c r="I22" s="4">
-        <f t="shared" si="0"/>
-        <v>8.9443010001443479</v>
-      </c>
-      <c r="J22" s="17">
-        <v>103085.48499783476</v>
-      </c>
-      <c r="K22" s="17">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="L22" s="8"/>
-      <c r="M22" s="8"/>
-      <c r="N22" s="8"/>
-      <c r="O22" s="8"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A23" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G23" s="17">
-        <v>0.68445</v>
-      </c>
-      <c r="H23" s="7">
-        <v>-0.20664055542154255</v>
-      </c>
-      <c r="I23" s="4">
-        <f t="shared" si="0"/>
-        <v>-0.30190745185410556</v>
-      </c>
-      <c r="J23" s="17">
-        <v>110145.72220882092</v>
-      </c>
-      <c r="K23" s="17">
-        <v>1</v>
-      </c>
-      <c r="L23" s="8"/>
-      <c r="M23" s="8"/>
-      <c r="N23" s="8"/>
-      <c r="O23" s="8"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A24" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G24" s="17">
-        <v>1.6505700000000001</v>
-      </c>
-      <c r="H24" s="7">
-        <v>-0.80506115618567142</v>
-      </c>
-      <c r="I24" s="4">
-        <f t="shared" si="0"/>
-        <v>-0.48774735769199207</v>
-      </c>
-      <c r="J24" s="17">
-        <v>100838.35645704676</v>
-      </c>
-      <c r="K24" s="17">
-        <v>5</v>
-      </c>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
-      <c r="O24" s="8"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A25" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G25" s="17">
-        <v>10.015700000000001</v>
-      </c>
-      <c r="H25" s="7">
-        <v>4.84458093899734</v>
-      </c>
-      <c r="I25" s="4">
-        <f t="shared" si="0"/>
-        <v>0.48369868696120488</v>
-      </c>
-      <c r="J25" s="17">
-        <v>99879.714553386511</v>
-      </c>
-      <c r="K25" s="17">
-        <v>5</v>
-      </c>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A26" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G26" s="17">
-        <v>24.223479999999999</v>
-      </c>
-      <c r="H26" s="7">
-        <v>-5.7914111873014162</v>
-      </c>
-      <c r="I26" s="4">
-        <f t="shared" si="0"/>
-        <v>-0.23908254252904276</v>
-      </c>
-      <c r="J26" s="17">
-        <v>117138.77421768615</v>
-      </c>
-      <c r="K26" s="17">
-        <v>18.666666666666668</v>
-      </c>
-      <c r="L26" s="8"/>
-      <c r="M26" s="8"/>
-      <c r="N26" s="8"/>
-      <c r="O26" s="8"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A27" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G27" s="17">
-        <v>0</v>
-      </c>
-      <c r="H27" s="7">
-        <v>-0.43439174266359831</v>
-      </c>
-      <c r="I27" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J27" s="17">
-        <v>130317.5227990795</v>
-      </c>
-      <c r="K27" s="17">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="L27" s="8"/>
-      <c r="M27" s="8"/>
-      <c r="N27" s="8"/>
-      <c r="O27" s="8"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A28" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G28" s="17">
-        <v>10.29</v>
-      </c>
-      <c r="H28" s="7">
-        <v>-7.6009084794700739E-3</v>
-      </c>
-      <c r="I28" s="4">
-        <f t="shared" si="0"/>
-        <v>-7.3866943435083325E-4</v>
-      </c>
-      <c r="J28" s="17">
-        <v>83282.006813596032</v>
-      </c>
-      <c r="K28" s="17">
-        <v>13.333333333333334</v>
-      </c>
-      <c r="L28" s="8"/>
-      <c r="M28" s="8"/>
-      <c r="N28" s="8"/>
-      <c r="O28" s="8"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G29" s="17">
-        <v>5.4947099999999995</v>
-      </c>
-      <c r="H29" s="7">
-        <v>-0.1393034954768749</v>
-      </c>
-      <c r="I29" s="4">
-        <f t="shared" si="0"/>
-        <v>-2.5352292564461986E-2</v>
-      </c>
-      <c r="J29" s="17">
-        <v>91755.335649669636</v>
-      </c>
-      <c r="K29" s="17">
-        <v>7</v>
-      </c>
-      <c r="L29" s="8"/>
-      <c r="M29" s="8"/>
-      <c r="N29" s="8"/>
-      <c r="O29" s="8"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A30" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G30" s="17">
-        <v>0</v>
-      </c>
-      <c r="H30" s="7">
-        <v>0.6</v>
-      </c>
-      <c r="I30" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J30" s="17">
-        <v>110000</v>
-      </c>
-      <c r="K30" s="17">
-        <v>0</v>
-      </c>
-      <c r="L30" s="8"/>
-      <c r="M30" s="8"/>
-      <c r="N30" s="8"/>
-      <c r="O30" s="8"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A31" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G31" s="17">
-        <v>26.5</v>
-      </c>
-      <c r="H31" s="7">
-        <v>-2.604686874742915</v>
-      </c>
-      <c r="I31" s="4">
-        <f t="shared" si="0"/>
-        <v>-9.8290070745015667E-2</v>
-      </c>
-      <c r="J31" s="17">
-        <v>92547.060993046674</v>
-      </c>
-      <c r="K31" s="17">
-        <v>27.666666666666668</v>
-      </c>
-      <c r="L31" s="8"/>
-      <c r="M31" s="8"/>
-      <c r="N31" s="8"/>
-      <c r="O31" s="8"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A32" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G32" s="17">
-        <v>30.8</v>
-      </c>
-      <c r="H32" s="7">
-        <v>14.827293382532636</v>
-      </c>
-      <c r="I32" s="4">
-        <f t="shared" si="0"/>
-        <v>0.48140562930300762</v>
-      </c>
-      <c r="J32" s="17">
-        <v>87949.115935818816</v>
-      </c>
-      <c r="K32" s="17">
-        <v>14.333333333333334</v>
-      </c>
-      <c r="L32" s="8"/>
-      <c r="M32" s="8"/>
-      <c r="N32" s="8"/>
-      <c r="O32" s="8"/>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A33" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G33" s="17">
-        <v>0</v>
-      </c>
-      <c r="H33" s="7">
-        <v>-1.2224075445787013</v>
-      </c>
-      <c r="I33" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J33" s="17">
-        <v>122240.75445787013</v>
-      </c>
-      <c r="K33" s="17">
-        <v>1</v>
-      </c>
-      <c r="L33" s="8"/>
-      <c r="M33" s="8"/>
-      <c r="N33" s="8"/>
-      <c r="O33" s="8"/>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A34" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G34" s="17">
-        <v>0</v>
-      </c>
-      <c r="H34" s="7">
-        <v>0</v>
-      </c>
-      <c r="I34" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J34" s="17">
-        <v>0</v>
-      </c>
-      <c r="K34" s="17">
-        <v>0</v>
-      </c>
-      <c r="L34" s="8"/>
-      <c r="M34" s="8"/>
-      <c r="N34" s="8"/>
-      <c r="O34" s="8"/>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A35" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G35" s="17">
-        <v>3.81</v>
-      </c>
-      <c r="H35" s="7">
-        <v>0.33530240421176227</v>
-      </c>
-      <c r="I35" s="4">
-        <f t="shared" si="0"/>
-        <v>8.8005880370541273E-2</v>
-      </c>
-      <c r="J35" s="17">
-        <v>95201.325533781623</v>
-      </c>
-      <c r="K35" s="17">
-        <v>2.3333333333333335</v>
-      </c>
-      <c r="L35" s="8"/>
-      <c r="M35" s="8"/>
-      <c r="N35" s="8"/>
-      <c r="O35" s="8"/>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A36" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G36" s="17">
-        <v>3.6067749999999998</v>
-      </c>
-      <c r="H36" s="7">
-        <v>2.1636641240935273</v>
-      </c>
-      <c r="I36" s="4">
-        <f t="shared" si="0"/>
-        <v>0.59988885475071974</v>
-      </c>
-      <c r="J36" s="17">
-        <v>82348.641423246372</v>
-      </c>
-      <c r="K36" s="17">
-        <v>5.333333333333333</v>
-      </c>
-      <c r="L36" s="8"/>
-      <c r="M36" s="8"/>
-      <c r="N36" s="8"/>
-      <c r="O36" s="8"/>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A37" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G37" s="17">
-        <v>37.19</v>
-      </c>
-      <c r="H37" s="7">
-        <v>-10.621458196587033</v>
-      </c>
-      <c r="I37" s="4">
-        <f t="shared" si="0"/>
-        <v>-0.28559984395232679</v>
-      </c>
-      <c r="J37" s="17">
-        <v>94388.83163095171</v>
-      </c>
-      <c r="K37" s="17">
-        <v>40.666666666666664</v>
-      </c>
-      <c r="L37" s="8"/>
-      <c r="M37" s="8"/>
-      <c r="N37" s="8"/>
-      <c r="O37" s="8"/>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A38" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G38" s="17">
-        <v>12</v>
-      </c>
-      <c r="H38" s="7">
-        <v>6.3943992616107979</v>
-      </c>
-      <c r="I38" s="4">
-        <f t="shared" si="0"/>
-        <v>0.53286660513423312</v>
-      </c>
-      <c r="J38" s="17">
-        <v>100619.43490047885</v>
-      </c>
-      <c r="K38" s="17">
-        <v>11.666666666666666</v>
-      </c>
-      <c r="L38" s="8"/>
-      <c r="M38" s="8"/>
-      <c r="N38" s="8"/>
-      <c r="O38" s="8"/>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G39" s="17">
-        <v>4.83</v>
-      </c>
-      <c r="H39" s="7">
-        <v>2.4016443555995544</v>
-      </c>
-      <c r="I39" s="4">
-        <f t="shared" si="0"/>
-        <v>0.49723485623179181</v>
-      </c>
-      <c r="J39" s="17">
-        <v>93473.032591125986</v>
-      </c>
-      <c r="K39" s="17">
-        <v>3</v>
-      </c>
-      <c r="L39" s="8"/>
-      <c r="M39" s="8"/>
-      <c r="N39" s="8"/>
-      <c r="O39" s="8"/>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A40" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G40" s="17">
-        <v>3.5616104000000002</v>
-      </c>
-      <c r="H40" s="7">
-        <v>3.0382940431250547</v>
-      </c>
-      <c r="I40" s="4">
-        <f t="shared" si="0"/>
-        <v>0.85306748967406842</v>
-      </c>
-      <c r="J40" s="17">
-        <v>102889.40225520697</v>
-      </c>
-      <c r="K40" s="17">
-        <v>4</v>
-      </c>
-      <c r="L40" s="8"/>
-      <c r="M40" s="8"/>
-      <c r="N40" s="8"/>
-      <c r="O40" s="8"/>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A41" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G41" s="17">
-        <v>0</v>
-      </c>
-      <c r="H41" s="7">
-        <v>0</v>
-      </c>
-      <c r="I41" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J41" s="17">
-        <v>0</v>
-      </c>
-      <c r="K41" s="17">
-        <v>0</v>
-      </c>
-      <c r="L41" s="8"/>
-      <c r="M41" s="8"/>
-      <c r="N41" s="8"/>
-      <c r="O41" s="8"/>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A42" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G42" s="17">
-        <v>10.17</v>
-      </c>
-      <c r="H42" s="7">
-        <v>3.984591770590749</v>
-      </c>
-      <c r="I42" s="4">
-        <f t="shared" si="0"/>
-        <v>0.39179860084471474</v>
-      </c>
-      <c r="J42" s="17">
-        <v>109174.83125485166</v>
-      </c>
-      <c r="K42" s="17">
-        <v>5</v>
-      </c>
-      <c r="L42" s="8"/>
-      <c r="M42" s="8"/>
-      <c r="N42" s="8"/>
-      <c r="O42" s="8"/>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A43" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G43" s="17">
-        <v>0</v>
-      </c>
-      <c r="H43" s="7">
-        <v>3.3333333333333326E-2</v>
-      </c>
-      <c r="I43" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J43" s="17">
-        <v>90000</v>
-      </c>
-      <c r="K43" s="17">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="L43" s="8"/>
-      <c r="M43" s="8"/>
-      <c r="N43" s="8"/>
-      <c r="O43" s="8"/>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A44" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G44" s="17">
-        <v>2.90625</v>
-      </c>
-      <c r="H44" s="7">
-        <v>1.4333848089524714</v>
-      </c>
-      <c r="I44" s="4">
-        <f t="shared" si="0"/>
-        <v>0.49320767619869987</v>
-      </c>
-      <c r="J44" s="17">
-        <v>112725.33024016366</v>
-      </c>
-      <c r="K44" s="17">
-        <v>4.6000000000000005</v>
-      </c>
-      <c r="L44" s="8"/>
-      <c r="M44" s="8"/>
-      <c r="N44" s="8"/>
-      <c r="O44" s="8"/>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A45" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G45" s="17">
-        <v>7.97</v>
-      </c>
-      <c r="H45" s="7">
-        <v>4.0882134700977213</v>
-      </c>
-      <c r="I45" s="4">
-        <f t="shared" si="0"/>
-        <v>0.51295024718917459</v>
-      </c>
-      <c r="J45" s="17">
-        <v>115651.32991422365</v>
-      </c>
-      <c r="K45" s="17">
-        <v>4</v>
-      </c>
-      <c r="L45" s="8"/>
-      <c r="M45" s="8"/>
-      <c r="N45" s="8"/>
-      <c r="O45" s="8"/>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A46" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G46" s="17">
-        <v>10.65</v>
-      </c>
-      <c r="H46" s="7">
-        <v>3.7363008021508812</v>
-      </c>
-      <c r="I46" s="4">
-        <f t="shared" si="0"/>
-        <v>0.35082636639914377</v>
-      </c>
-      <c r="J46" s="17">
-        <v>74953.145229196627</v>
-      </c>
-      <c r="K46" s="17">
-        <v>6.333333333333333</v>
-      </c>
-      <c r="L46" s="8"/>
-      <c r="M46" s="8"/>
-      <c r="N46" s="8"/>
-      <c r="O46" s="8"/>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A47" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G47" s="17">
-        <v>6.5951000000000004</v>
-      </c>
-      <c r="H47" s="7">
-        <v>0.88921430612099994</v>
-      </c>
-      <c r="I47" s="4">
-        <f t="shared" si="0"/>
-        <v>0.13482954104122757</v>
-      </c>
-      <c r="J47" s="17">
-        <v>108677.95830910001</v>
-      </c>
-      <c r="K47" s="17">
-        <v>2.3333333333333335</v>
-      </c>
-      <c r="L47" s="8"/>
-      <c r="M47" s="8"/>
-      <c r="N47" s="8"/>
-      <c r="O47" s="8"/>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A48" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="G48" s="17">
-        <v>65.400000000000006</v>
-      </c>
-      <c r="H48" s="7">
-        <v>26.472517639262765</v>
-      </c>
-      <c r="I48" s="4">
-        <f t="shared" si="0"/>
-        <v>0.40477855717527161</v>
-      </c>
-      <c r="J48" s="17">
-        <v>104841.14470569149</v>
-      </c>
-      <c r="K48" s="17">
-        <v>24.666666666666668</v>
-      </c>
-      <c r="L48" s="8"/>
-      <c r="M48" s="8"/>
-      <c r="N48" s="8"/>
-      <c r="O48" s="8"/>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A49" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G49" s="17">
-        <v>17</v>
-      </c>
-      <c r="H49" s="7">
-        <v>4.8099999999999996</v>
-      </c>
-      <c r="I49" s="4">
-        <f t="shared" si="0"/>
-        <v>0.2829411764705882</v>
-      </c>
-      <c r="J49" s="17">
-        <v>101000</v>
-      </c>
-      <c r="K49" s="17">
-        <v>19</v>
-      </c>
-      <c r="L49" s="8"/>
-      <c r="M49" s="8"/>
-      <c r="N49" s="8"/>
-      <c r="O49" s="8"/>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A50" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G50" s="17">
-        <v>7.9112900000000002</v>
-      </c>
-      <c r="H50" s="7">
-        <v>5.8537633333333341</v>
-      </c>
-      <c r="I50" s="4">
-        <f t="shared" si="0"/>
-        <v>0.73992526292593674</v>
-      </c>
-      <c r="J50" s="17">
-        <v>101000</v>
-      </c>
-      <c r="K50" s="17">
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="L50" s="8"/>
-      <c r="M50" s="8"/>
-      <c r="N50" s="8"/>
-      <c r="O50" s="8"/>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A51" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G51" s="17">
-        <v>0</v>
-      </c>
-      <c r="H51" s="7">
-        <v>-6.3453123695111699</v>
-      </c>
-      <c r="I51" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J51" s="17">
-        <v>105755.2061585195</v>
-      </c>
-      <c r="K51" s="17">
-        <v>6</v>
-      </c>
-      <c r="L51" s="8"/>
-      <c r="M51" s="8"/>
-      <c r="N51" s="8"/>
-      <c r="O51" s="8"/>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A52" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G52" s="17">
-        <v>1</v>
-      </c>
-      <c r="H52" s="7">
-        <v>-0.7882832298375444</v>
-      </c>
-      <c r="I52" s="4">
-        <f t="shared" si="0"/>
-        <v>-0.7882832298375444</v>
-      </c>
-      <c r="J52" s="17">
-        <v>139414.16149187722</v>
-      </c>
-      <c r="K52" s="17">
-        <v>2</v>
-      </c>
-      <c r="L52" s="8"/>
-      <c r="M52" s="8"/>
-      <c r="N52" s="8"/>
-      <c r="O52" s="8"/>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A53" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G53" s="17">
-        <v>0</v>
-      </c>
-      <c r="H53" s="7">
-        <v>0</v>
-      </c>
-      <c r="I53" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J53" s="17">
-        <v>121584.75193965515</v>
-      </c>
-      <c r="K53" s="17">
-        <v>0</v>
-      </c>
-      <c r="L53" s="8"/>
-      <c r="M53" s="8"/>
-      <c r="N53" s="8"/>
-      <c r="O53" s="8"/>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A54" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G54" s="17">
-        <v>0</v>
-      </c>
-      <c r="H54" s="7">
-        <v>0</v>
-      </c>
-      <c r="I54" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J54" s="17">
-        <v>0</v>
-      </c>
-      <c r="K54" s="17">
-        <v>0</v>
-      </c>
-      <c r="L54" s="8"/>
-      <c r="M54" s="8"/>
-      <c r="N54" s="8"/>
-      <c r="O54" s="8"/>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A55" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G55" s="17">
-        <v>9</v>
-      </c>
-      <c r="H55" s="7">
-        <v>-6.5757544546004523</v>
-      </c>
-      <c r="I55" s="4">
-        <f t="shared" si="0"/>
-        <v>-0.73063938384449467</v>
-      </c>
-      <c r="J55" s="17">
-        <v>50745.724005939614</v>
-      </c>
-      <c r="K55" s="17">
-        <v>21.333333333333332</v>
-      </c>
-      <c r="L55" s="8"/>
-      <c r="M55" s="8"/>
-      <c r="N55" s="8"/>
-      <c r="O55" s="8"/>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A56" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="G56" s="17">
-        <v>2.9410600000000002</v>
-      </c>
-      <c r="H56" s="7">
-        <v>0.44902000000000014</v>
-      </c>
-      <c r="I56" s="4">
-        <f t="shared" si="0"/>
-        <v>0.15267284584469548</v>
-      </c>
-      <c r="J56" s="17">
-        <v>101000</v>
-      </c>
-      <c r="K56" s="17">
-        <v>0.79999999999999993</v>
-      </c>
-      <c r="L56" s="8"/>
-      <c r="M56" s="8"/>
-      <c r="N56" s="8"/>
-      <c r="O56" s="8"/>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A57" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G57" s="17">
-        <v>0</v>
-      </c>
-      <c r="H57" s="7">
-        <v>-1.4939221985593101</v>
-      </c>
-      <c r="I57" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J57" s="17">
-        <v>448176.65956779307</v>
-      </c>
-      <c r="K57" s="17">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="L57" s="8"/>
-      <c r="M57" s="8"/>
-      <c r="N57" s="8"/>
-      <c r="O57" s="8"/>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A58" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B58" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C58" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E58" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="G58" s="17">
-        <v>0</v>
-      </c>
-      <c r="H58" s="7">
-        <v>0.28333333333333338</v>
-      </c>
-      <c r="I58" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J58" s="17">
-        <v>90000</v>
-      </c>
-      <c r="K58" s="17">
-        <v>1.1666666666666667</v>
-      </c>
-      <c r="L58" s="8"/>
-      <c r="M58" s="8"/>
-      <c r="N58" s="8"/>
-      <c r="O58" s="8"/>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A59" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="B59" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C59" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E59" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="G59" s="17">
-        <v>1.75</v>
-      </c>
-      <c r="H59" s="7">
-        <v>1.24</v>
-      </c>
-      <c r="I59" s="4">
-        <f t="shared" si="0"/>
-        <v>0.70857142857142852</v>
-      </c>
-      <c r="J59" s="17">
-        <v>90000</v>
-      </c>
-      <c r="K59" s="17">
-        <v>0.56666666666666665</v>
-      </c>
-      <c r="L59" s="8"/>
-      <c r="M59" s="8"/>
-      <c r="N59" s="8"/>
-      <c r="O59" s="8"/>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A60" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="B60" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="C60" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E60" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="G60" s="17">
-        <v>0</v>
-      </c>
-      <c r="H60" s="7">
-        <v>0</v>
-      </c>
-      <c r="I60" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J60" s="17">
-        <v>0</v>
-      </c>
-      <c r="K60" s="17">
-        <v>0</v>
-      </c>
-      <c r="L60" s="8"/>
-      <c r="M60" s="8"/>
-      <c r="N60" s="8"/>
-      <c r="O60" s="8"/>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A61" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="B61" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="C61" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="D61" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="E61" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G61" s="17">
-        <v>0</v>
-      </c>
-      <c r="H61" s="7">
-        <v>0</v>
-      </c>
-      <c r="I61" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J61" s="17">
-        <v>117684.4975</v>
-      </c>
-      <c r="K61" s="17">
-        <v>5.2</v>
-      </c>
-      <c r="L61" s="8"/>
-      <c r="M61" s="8"/>
-      <c r="N61" s="8"/>
-      <c r="O61" s="8"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="G1:O1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/CEO Review.xlsx
+++ b/CEO Review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://peoplestronghrservices-my.sharepoint.com/personal/baljeet_singh_taggd_in/Documents/Desktop/Clude Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1592" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{373BA5BD-E38F-4D82-A3FB-075ACE5C396B}"/>
+  <xr:revisionPtr revIDLastSave="1602" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77DFA558-16B7-47FD-8E57-582AD4DDD0AE}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F2C8E0B5-D69E-42FC-A0A4-20379F29D696}"/>
   </bookViews>
@@ -545,7 +545,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -622,6 +622,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -11282,14 +11291,26 @@
         <v>0</v>
       </c>
       <c r="M60" s="17"/>
+      <c r="R60" s="30">
+        <f>506+12</f>
+        <v>518</v>
+      </c>
       <c r="X60" s="17"/>
+      <c r="AC60" s="31">
+        <f>759+12</f>
+        <v>771</v>
+      </c>
       <c r="AH60">
         <v>0</v>
       </c>
       <c r="AI60" s="17"/>
+      <c r="AN60" s="32">
+        <f>1013+12</f>
+        <v>1025</v>
+      </c>
       <c r="AY60" s="17">
         <f t="shared" si="5"/>
-        <v>217</v>
+        <v>2531</v>
       </c>
       <c r="AZ60" s="17">
         <f t="shared" si="6"/>

--- a/CEO Review.xlsx
+++ b/CEO Review.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://peoplestronghrservices-my.sharepoint.com/personal/baljeet_singh_taggd_in/Documents/Desktop/Clude Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1602" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77DFA558-16B7-47FD-8E57-582AD4DDD0AE}"/>
+  <xr:revisionPtr revIDLastSave="1701" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AFE4DC0-9F73-4A3F-A057-2DAE547ABBB7}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F2C8E0B5-D69E-42FC-A0A4-20379F29D696}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{F2C8E0B5-D69E-42FC-A0A4-20379F29D696}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Actual" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Actual!$A$2:$AL$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$BZ$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="128">
   <si>
     <t>Clients</t>
   </si>
@@ -412,6 +414,21 @@
   <si>
     <t>Rahul</t>
   </si>
+  <si>
+    <t>Apr</t>
+  </si>
+  <si>
+    <t>Forecast Revenue</t>
+  </si>
+  <si>
+    <t>Actual Revenue</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>June</t>
+  </si>
 </sst>
 </file>
 
@@ -545,7 +562,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -618,19 +635,13 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1013,71 +1024,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:78" x14ac:dyDescent="0.35">
-      <c r="G1" s="28" t="s">
+      <c r="G1" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="R1" s="28" t="s">
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="R1" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
-      <c r="V1" s="28"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="28"/>
-      <c r="AA1" s="28"/>
-      <c r="AC1" s="28" t="s">
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="29"/>
+      <c r="Z1" s="29"/>
+      <c r="AA1" s="29"/>
+      <c r="AC1" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="AD1" s="28"/>
-      <c r="AE1" s="28"/>
-      <c r="AF1" s="28"/>
-      <c r="AG1" s="28"/>
-      <c r="AH1" s="28"/>
-      <c r="AI1" s="28"/>
-      <c r="AJ1" s="28"/>
-      <c r="AK1" s="28"/>
-      <c r="AL1" s="28"/>
-      <c r="AN1" s="28" t="s">
+      <c r="AD1" s="29"/>
+      <c r="AE1" s="29"/>
+      <c r="AF1" s="29"/>
+      <c r="AG1" s="29"/>
+      <c r="AH1" s="29"/>
+      <c r="AI1" s="29"/>
+      <c r="AJ1" s="29"/>
+      <c r="AK1" s="29"/>
+      <c r="AL1" s="29"/>
+      <c r="AN1" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="AO1" s="28"/>
-      <c r="AP1" s="28"/>
-      <c r="AQ1" s="28"/>
-      <c r="AR1" s="28"/>
-      <c r="AS1" s="28"/>
-      <c r="AT1" s="28"/>
-      <c r="AU1" s="28"/>
-      <c r="AV1" s="28"/>
-      <c r="AW1" s="28"/>
-      <c r="AY1" s="29" t="s">
+      <c r="AO1" s="29"/>
+      <c r="AP1" s="29"/>
+      <c r="AQ1" s="29"/>
+      <c r="AR1" s="29"/>
+      <c r="AS1" s="29"/>
+      <c r="AT1" s="29"/>
+      <c r="AU1" s="29"/>
+      <c r="AV1" s="29"/>
+      <c r="AW1" s="29"/>
+      <c r="AY1" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="AZ1" s="29"/>
-      <c r="BA1" s="29"/>
-      <c r="BB1" s="29"/>
-      <c r="BC1" s="29"/>
-      <c r="BD1" s="29"/>
-      <c r="BE1" s="29"/>
-      <c r="BF1" s="29"/>
-      <c r="BG1" s="29"/>
-      <c r="BH1" s="29"/>
-      <c r="BJ1" s="28" t="s">
+      <c r="AZ1" s="30"/>
+      <c r="BA1" s="30"/>
+      <c r="BB1" s="30"/>
+      <c r="BC1" s="30"/>
+      <c r="BD1" s="30"/>
+      <c r="BE1" s="30"/>
+      <c r="BF1" s="30"/>
+      <c r="BG1" s="30"/>
+      <c r="BH1" s="30"/>
+      <c r="BJ1" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="BK1" s="28"/>
-      <c r="BL1" s="28"/>
+      <c r="BK1" s="29"/>
+      <c r="BL1" s="29"/>
       <c r="BN1" s="19" t="s">
         <v>79</v>
       </c>
@@ -11291,12 +11302,12 @@
         <v>0</v>
       </c>
       <c r="M60" s="17"/>
-      <c r="R60" s="30">
+      <c r="R60" s="28">
         <f>506+12</f>
         <v>518</v>
       </c>
       <c r="X60" s="17"/>
-      <c r="AC60" s="31">
+      <c r="AC60" s="16">
         <f>759+12</f>
         <v>771</v>
       </c>
@@ -11304,7 +11315,7 @@
         <v>0</v>
       </c>
       <c r="AI60" s="17"/>
-      <c r="AN60" s="32">
+      <c r="AN60" s="24">
         <f>1013+12</f>
         <v>1025</v>
       </c>
@@ -11376,4 +11387,3923 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62BD0EA2-02E9-43B0-A368-1C9D568EE9C9}">
+  <dimension ref="A1:AL61"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="25.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.08984375" customWidth="1"/>
+    <col min="7" max="7" width="15.7265625" customWidth="1"/>
+    <col min="8" max="8" width="13.90625" customWidth="1"/>
+    <col min="9" max="16" width="8.7265625" customWidth="1"/>
+    <col min="18" max="18" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="G1" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="R1" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="29"/>
+      <c r="Z1" s="29"/>
+      <c r="AA1" s="29"/>
+      <c r="AC1" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="AD1" s="29"/>
+      <c r="AE1" s="29"/>
+      <c r="AF1" s="29"/>
+      <c r="AG1" s="29"/>
+      <c r="AH1" s="29"/>
+      <c r="AI1" s="29"/>
+      <c r="AJ1" s="29"/>
+      <c r="AK1" s="29"/>
+      <c r="AL1" s="29"/>
+    </row>
+    <row r="2" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI2" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AJ2" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="AK2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL2" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" s="14">
+        <v>120</v>
+      </c>
+      <c r="H3" s="17">
+        <v>120</v>
+      </c>
+      <c r="I3" s="3">
+        <v>96.630983659997625</v>
+      </c>
+      <c r="J3" s="4">
+        <f>IFERROR(I3/H3,0)</f>
+        <v>0.80525819716664693</v>
+      </c>
+      <c r="K3" s="3"/>
+      <c r="L3" s="17">
+        <v>57.333333333333336</v>
+      </c>
+      <c r="M3" s="17"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="7">
+        <v>4.3498168498168504</v>
+      </c>
+      <c r="R3" s="14">
+        <v>167</v>
+      </c>
+      <c r="S3" s="17"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="17"/>
+      <c r="X3" s="17"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
+      <c r="AA3" s="7"/>
+      <c r="AC3" s="14">
+        <v>188</v>
+      </c>
+      <c r="AD3" s="17"/>
+      <c r="AE3" s="3"/>
+      <c r="AF3" s="4"/>
+      <c r="AG3" s="3"/>
+      <c r="AH3" s="17"/>
+      <c r="AI3" s="17"/>
+      <c r="AJ3" s="6"/>
+      <c r="AK3" s="6"/>
+      <c r="AL3" s="7"/>
+    </row>
+    <row r="4" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" s="14">
+        <v>2.4</v>
+      </c>
+      <c r="H4" s="17">
+        <v>2.2562000000000002</v>
+      </c>
+      <c r="I4" s="3">
+        <v>-0.17604378797486162</v>
+      </c>
+      <c r="J4" s="4">
+        <f t="shared" ref="J4:J61" si="0">IFERROR(I4/H4,0)</f>
+        <v>-7.8026676701915432E-2</v>
+      </c>
+      <c r="K4" s="3"/>
+      <c r="L4" s="17">
+        <v>2</v>
+      </c>
+      <c r="M4" s="17"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="7">
+        <v>0</v>
+      </c>
+      <c r="R4" s="14">
+        <v>6.6</v>
+      </c>
+      <c r="S4" s="17"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="17"/>
+      <c r="X4" s="17"/>
+      <c r="Y4" s="6"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="7"/>
+      <c r="AC4" s="14">
+        <v>1.02</v>
+      </c>
+      <c r="AD4" s="17"/>
+      <c r="AE4" s="3"/>
+      <c r="AF4" s="4"/>
+      <c r="AG4" s="3"/>
+      <c r="AH4" s="17"/>
+      <c r="AI4" s="17"/>
+      <c r="AJ4" s="6"/>
+      <c r="AK4" s="3"/>
+      <c r="AL4" s="7"/>
+    </row>
+    <row r="5" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G5" s="14">
+        <v>7.5</v>
+      </c>
+      <c r="H5" s="17">
+        <v>9.3010766</v>
+      </c>
+      <c r="I5" s="3">
+        <v>3.561191132154701</v>
+      </c>
+      <c r="J5" s="4">
+        <f t="shared" si="0"/>
+        <v>0.3828794542079893</v>
+      </c>
+      <c r="K5" s="3"/>
+      <c r="L5" s="17">
+        <v>4</v>
+      </c>
+      <c r="M5" s="17"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="7">
+        <v>2.5332973999999999</v>
+      </c>
+      <c r="R5" s="14">
+        <v>7.9985999999999997</v>
+      </c>
+      <c r="S5" s="17"/>
+      <c r="T5" s="3"/>
+      <c r="U5" s="4"/>
+      <c r="V5" s="3"/>
+      <c r="W5" s="17"/>
+      <c r="X5" s="17"/>
+      <c r="Y5" s="6"/>
+      <c r="Z5" s="3"/>
+      <c r="AA5" s="7"/>
+      <c r="AC5" s="14">
+        <v>5.5</v>
+      </c>
+      <c r="AD5" s="17"/>
+      <c r="AE5" s="3"/>
+      <c r="AF5" s="4"/>
+      <c r="AG5" s="3"/>
+      <c r="AH5" s="17"/>
+      <c r="AI5" s="17"/>
+      <c r="AJ5" s="6"/>
+      <c r="AK5" s="3"/>
+      <c r="AL5" s="7"/>
+    </row>
+    <row r="6" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G6" s="14">
+        <v>20</v>
+      </c>
+      <c r="H6" s="17">
+        <v>26.5</v>
+      </c>
+      <c r="I6" s="3">
+        <v>-3.5042859329899017</v>
+      </c>
+      <c r="J6" s="4">
+        <f t="shared" si="0"/>
+        <v>-0.13223720501848685</v>
+      </c>
+      <c r="K6" s="3"/>
+      <c r="L6" s="17">
+        <v>15.666666666666666</v>
+      </c>
+      <c r="M6" s="17"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="7">
+        <v>1.3417475728155339</v>
+      </c>
+      <c r="R6" s="14">
+        <v>13.11</v>
+      </c>
+      <c r="S6" s="17"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="4"/>
+      <c r="V6" s="3"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="6"/>
+      <c r="Z6" s="3"/>
+      <c r="AA6" s="7"/>
+      <c r="AC6" s="14">
+        <v>1.85</v>
+      </c>
+      <c r="AD6" s="17"/>
+      <c r="AE6" s="3"/>
+      <c r="AF6" s="4"/>
+      <c r="AG6" s="3"/>
+      <c r="AH6" s="17"/>
+      <c r="AI6" s="17"/>
+      <c r="AJ6" s="6"/>
+      <c r="AK6" s="3"/>
+      <c r="AL6" s="7"/>
+    </row>
+    <row r="7" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="14">
+        <v>6</v>
+      </c>
+      <c r="H7" s="17">
+        <v>6.1185</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0.29414927678181019</v>
+      </c>
+      <c r="J7" s="4">
+        <f t="shared" si="0"/>
+        <v>4.8075390501235625E-2</v>
+      </c>
+      <c r="K7" s="3"/>
+      <c r="L7" s="17">
+        <v>6</v>
+      </c>
+      <c r="M7" s="17"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="7">
+        <v>1.2745666666666666</v>
+      </c>
+      <c r="R7" s="14">
+        <v>6</v>
+      </c>
+      <c r="S7" s="17"/>
+      <c r="T7" s="3"/>
+      <c r="U7" s="4"/>
+      <c r="V7" s="3"/>
+      <c r="W7" s="17"/>
+      <c r="X7" s="17"/>
+      <c r="Y7" s="6"/>
+      <c r="Z7" s="3"/>
+      <c r="AA7" s="7"/>
+      <c r="AC7" s="14">
+        <v>7</v>
+      </c>
+      <c r="AD7" s="17"/>
+      <c r="AE7" s="3"/>
+      <c r="AF7" s="4"/>
+      <c r="AG7" s="3"/>
+      <c r="AH7" s="17"/>
+      <c r="AI7" s="17"/>
+      <c r="AJ7" s="6"/>
+      <c r="AK7" s="3"/>
+      <c r="AL7" s="7"/>
+    </row>
+    <row r="8" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G8" s="14">
+        <v>11</v>
+      </c>
+      <c r="H8" s="17">
+        <v>13.0525</v>
+      </c>
+      <c r="I8" s="3">
+        <v>1.4691666666666663</v>
+      </c>
+      <c r="J8" s="4">
+        <f t="shared" si="0"/>
+        <v>0.112558258315776</v>
+      </c>
+      <c r="K8" s="3"/>
+      <c r="L8" s="17">
+        <v>8.1666666666666661</v>
+      </c>
+      <c r="M8" s="17"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="7">
+        <v>1.2146874999999999</v>
+      </c>
+      <c r="R8" s="14">
+        <v>9.6</v>
+      </c>
+      <c r="S8" s="17"/>
+      <c r="T8" s="3"/>
+      <c r="U8" s="4"/>
+      <c r="V8" s="3"/>
+      <c r="W8" s="17"/>
+      <c r="X8" s="17"/>
+      <c r="Y8" s="6"/>
+      <c r="Z8" s="3"/>
+      <c r="AA8" s="7"/>
+      <c r="AC8" s="14">
+        <v>6.5</v>
+      </c>
+      <c r="AD8" s="17"/>
+      <c r="AE8" s="3"/>
+      <c r="AF8" s="4"/>
+      <c r="AG8" s="3"/>
+      <c r="AH8" s="17"/>
+      <c r="AI8" s="17"/>
+      <c r="AJ8" s="6"/>
+      <c r="AK8" s="3"/>
+      <c r="AL8" s="7"/>
+    </row>
+    <row r="9" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G9" s="14">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="H9" s="17">
+        <v>6.83</v>
+      </c>
+      <c r="I9" s="3">
+        <v>-0.19260178039615519</v>
+      </c>
+      <c r="J9" s="4">
+        <f t="shared" si="0"/>
+        <v>-2.8199382195630337E-2</v>
+      </c>
+      <c r="K9" s="3"/>
+      <c r="L9" s="17">
+        <v>10.666666666666666</v>
+      </c>
+      <c r="M9" s="17"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="7">
+        <v>0.83599999999999997</v>
+      </c>
+      <c r="R9" s="14">
+        <v>9</v>
+      </c>
+      <c r="S9" s="17"/>
+      <c r="T9" s="3"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="3"/>
+      <c r="W9" s="17"/>
+      <c r="X9" s="17"/>
+      <c r="Y9" s="6"/>
+      <c r="Z9" s="3"/>
+      <c r="AA9" s="7"/>
+      <c r="AC9" s="14">
+        <v>9.25</v>
+      </c>
+      <c r="AD9" s="17"/>
+      <c r="AE9" s="3"/>
+      <c r="AF9" s="4"/>
+      <c r="AG9" s="3"/>
+      <c r="AH9" s="17"/>
+      <c r="AI9" s="17"/>
+      <c r="AJ9" s="6"/>
+      <c r="AK9" s="3"/>
+      <c r="AL9" s="7"/>
+    </row>
+    <row r="10" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G10" s="14">
+        <v>4</v>
+      </c>
+      <c r="H10" s="17">
+        <v>2.7279200000000001</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1.1487128559241577</v>
+      </c>
+      <c r="J10" s="4">
+        <f t="shared" si="0"/>
+        <v>0.42109477401249218</v>
+      </c>
+      <c r="K10" s="3"/>
+      <c r="L10" s="17">
+        <v>2</v>
+      </c>
+      <c r="M10" s="17"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="7">
+        <v>1.6284562999999999</v>
+      </c>
+      <c r="R10" s="14">
+        <v>2.7114332000000001</v>
+      </c>
+      <c r="S10" s="17"/>
+      <c r="T10" s="3"/>
+      <c r="U10" s="4"/>
+      <c r="V10" s="3"/>
+      <c r="W10" s="17"/>
+      <c r="X10" s="17"/>
+      <c r="Y10" s="6"/>
+      <c r="Z10" s="3"/>
+      <c r="AA10" s="7"/>
+      <c r="AC10" s="14">
+        <v>4.3313845999999998</v>
+      </c>
+      <c r="AD10" s="17"/>
+      <c r="AE10" s="3"/>
+      <c r="AF10" s="4"/>
+      <c r="AG10" s="3"/>
+      <c r="AH10" s="17"/>
+      <c r="AI10" s="17"/>
+      <c r="AJ10" s="6"/>
+      <c r="AK10" s="3"/>
+      <c r="AL10" s="7"/>
+    </row>
+    <row r="11" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G11" s="14">
+        <v>14.3</v>
+      </c>
+      <c r="H11" s="17">
+        <v>12.79</v>
+      </c>
+      <c r="I11" s="3">
+        <v>5.5607583716918079</v>
+      </c>
+      <c r="J11" s="4">
+        <f t="shared" si="0"/>
+        <v>0.4347739149094455</v>
+      </c>
+      <c r="K11" s="3"/>
+      <c r="L11" s="17">
+        <v>8.6666666666666661</v>
+      </c>
+      <c r="M11" s="17"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="7">
+        <v>1.8106666666666664</v>
+      </c>
+      <c r="R11" s="14">
+        <v>13.649999999999999</v>
+      </c>
+      <c r="S11" s="17"/>
+      <c r="T11" s="3"/>
+      <c r="U11" s="4"/>
+      <c r="V11" s="3"/>
+      <c r="W11" s="17"/>
+      <c r="X11" s="17"/>
+      <c r="Y11" s="6"/>
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="7"/>
+      <c r="AC11" s="14">
+        <v>14.3</v>
+      </c>
+      <c r="AD11" s="17"/>
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="4"/>
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="17"/>
+      <c r="AI11" s="17"/>
+      <c r="AJ11" s="6"/>
+      <c r="AK11" s="3"/>
+      <c r="AL11" s="7"/>
+    </row>
+    <row r="12" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" s="14">
+        <v>139</v>
+      </c>
+      <c r="H12" s="17">
+        <v>181.56917999999999</v>
+      </c>
+      <c r="I12" s="3">
+        <v>60.485020524784211</v>
+      </c>
+      <c r="J12" s="4">
+        <f t="shared" si="0"/>
+        <v>0.33312382930178025</v>
+      </c>
+      <c r="K12" s="3"/>
+      <c r="L12" s="17">
+        <v>56.4</v>
+      </c>
+      <c r="M12" s="17"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="7">
+        <v>3.8186813186813189</v>
+      </c>
+      <c r="R12" s="14">
+        <v>117.71541000000001</v>
+      </c>
+      <c r="S12" s="17"/>
+      <c r="T12" s="3"/>
+      <c r="U12" s="4"/>
+      <c r="V12" s="3"/>
+      <c r="W12" s="17"/>
+      <c r="X12" s="17"/>
+      <c r="Y12" s="6"/>
+      <c r="Z12" s="3"/>
+      <c r="AA12" s="7"/>
+      <c r="AC12" s="14">
+        <v>117.71541000000001</v>
+      </c>
+      <c r="AD12" s="17"/>
+      <c r="AE12" s="3"/>
+      <c r="AF12" s="4"/>
+      <c r="AG12" s="3"/>
+      <c r="AH12" s="17"/>
+      <c r="AI12" s="17"/>
+      <c r="AJ12" s="6"/>
+      <c r="AK12" s="3"/>
+      <c r="AL12" s="7"/>
+    </row>
+    <row r="13" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13" s="14">
+        <v>4</v>
+      </c>
+      <c r="H13" s="17">
+        <v>3.7850000000000001</v>
+      </c>
+      <c r="I13" s="3">
+        <v>1.8593369920277556</v>
+      </c>
+      <c r="J13" s="4">
+        <f t="shared" si="0"/>
+        <v>0.49123830700865406</v>
+      </c>
+      <c r="K13" s="3"/>
+      <c r="L13" s="17">
+        <v>2.4</v>
+      </c>
+      <c r="M13" s="17"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="7">
+        <v>4.9283333333333337</v>
+      </c>
+      <c r="R13" s="14">
+        <v>5</v>
+      </c>
+      <c r="S13" s="17"/>
+      <c r="T13" s="3"/>
+      <c r="U13" s="4"/>
+      <c r="V13" s="3"/>
+      <c r="W13" s="17"/>
+      <c r="X13" s="17"/>
+      <c r="Y13" s="6"/>
+      <c r="Z13" s="3"/>
+      <c r="AA13" s="7"/>
+      <c r="AC13" s="14">
+        <v>6</v>
+      </c>
+      <c r="AD13" s="17"/>
+      <c r="AE13" s="3"/>
+      <c r="AF13" s="4"/>
+      <c r="AG13" s="3"/>
+      <c r="AH13" s="17"/>
+      <c r="AI13" s="17"/>
+      <c r="AJ13" s="6"/>
+      <c r="AK13" s="3"/>
+      <c r="AL13" s="7"/>
+    </row>
+    <row r="14" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G14" s="14">
+        <v>3</v>
+      </c>
+      <c r="H14" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-0.91500000000000004</v>
+      </c>
+      <c r="J14" s="4">
+        <f t="shared" si="0"/>
+        <v>-1.0166666666666666</v>
+      </c>
+      <c r="K14" s="3"/>
+      <c r="L14" s="17">
+        <v>1.3499999999999999</v>
+      </c>
+      <c r="M14" s="17"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="R14" s="14">
+        <v>0</v>
+      </c>
+      <c r="S14" s="17"/>
+      <c r="T14" s="3"/>
+      <c r="U14" s="4"/>
+      <c r="V14" s="3"/>
+      <c r="W14" s="17"/>
+      <c r="X14" s="17"/>
+      <c r="Y14" s="6"/>
+      <c r="Z14" s="3"/>
+      <c r="AA14" s="7"/>
+      <c r="AC14" s="14">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="17"/>
+      <c r="AE14" s="3"/>
+      <c r="AF14" s="4"/>
+      <c r="AG14" s="3"/>
+      <c r="AH14" s="17"/>
+      <c r="AI14" s="17"/>
+      <c r="AJ14" s="6"/>
+      <c r="AK14" s="3"/>
+      <c r="AL14" s="7"/>
+    </row>
+    <row r="15" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G15" s="14">
+        <v>0</v>
+      </c>
+      <c r="H15" s="17">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="3"/>
+      <c r="L15" s="17">
+        <v>0</v>
+      </c>
+      <c r="M15" s="17"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="7">
+        <v>0</v>
+      </c>
+      <c r="R15" s="14">
+        <v>0</v>
+      </c>
+      <c r="S15" s="17"/>
+      <c r="T15" s="3"/>
+      <c r="U15" s="4"/>
+      <c r="V15" s="3"/>
+      <c r="W15" s="17"/>
+      <c r="X15" s="17"/>
+      <c r="Y15" s="6"/>
+      <c r="Z15" s="3"/>
+      <c r="AA15" s="7"/>
+      <c r="AC15" s="14">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="17"/>
+      <c r="AE15" s="3"/>
+      <c r="AF15" s="4"/>
+      <c r="AG15" s="3"/>
+      <c r="AH15" s="17"/>
+      <c r="AI15" s="17"/>
+      <c r="AJ15" s="6"/>
+      <c r="AK15" s="3"/>
+      <c r="AL15" s="7"/>
+    </row>
+    <row r="16" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" s="14">
+        <v>3</v>
+      </c>
+      <c r="H16" s="17">
+        <v>4.5916899999999998</v>
+      </c>
+      <c r="I16" s="3">
+        <v>1.4324625273205285</v>
+      </c>
+      <c r="J16" s="4">
+        <f t="shared" si="0"/>
+        <v>0.31196847507574088</v>
+      </c>
+      <c r="K16" s="3"/>
+      <c r="L16" s="17">
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="M16" s="17"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="7">
+        <v>2.2652816666666666</v>
+      </c>
+      <c r="R16" s="14">
+        <v>4</v>
+      </c>
+      <c r="S16" s="17"/>
+      <c r="T16" s="3"/>
+      <c r="U16" s="4"/>
+      <c r="V16" s="3"/>
+      <c r="W16" s="17"/>
+      <c r="X16" s="17"/>
+      <c r="Y16" s="6"/>
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="7"/>
+      <c r="AC16" s="14">
+        <v>5</v>
+      </c>
+      <c r="AD16" s="17"/>
+      <c r="AE16" s="3"/>
+      <c r="AF16" s="4"/>
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="17"/>
+      <c r="AI16" s="17"/>
+      <c r="AJ16" s="6"/>
+      <c r="AK16" s="3"/>
+      <c r="AL16" s="7"/>
+    </row>
+    <row r="17" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G17" s="14">
+        <v>129</v>
+      </c>
+      <c r="H17" s="17">
+        <v>119.60778230000001</v>
+      </c>
+      <c r="I17" s="3">
+        <v>45.798046329112786</v>
+      </c>
+      <c r="J17" s="4">
+        <f t="shared" si="0"/>
+        <v>0.38290189357614052</v>
+      </c>
+      <c r="K17" s="3"/>
+      <c r="L17" s="17">
+        <v>80.666666666666671</v>
+      </c>
+      <c r="M17" s="17"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="3"/>
+      <c r="P17" s="7">
+        <v>1.8414534459595959</v>
+      </c>
+      <c r="R17" s="14">
+        <v>121</v>
+      </c>
+      <c r="S17" s="17"/>
+      <c r="T17" s="3"/>
+      <c r="U17" s="4"/>
+      <c r="V17" s="3"/>
+      <c r="W17" s="17"/>
+      <c r="X17" s="17"/>
+      <c r="Y17" s="6"/>
+      <c r="Z17" s="3"/>
+      <c r="AA17" s="7"/>
+      <c r="AC17" s="14">
+        <v>124</v>
+      </c>
+      <c r="AD17" s="17"/>
+      <c r="AE17" s="3"/>
+      <c r="AF17" s="4"/>
+      <c r="AG17" s="3"/>
+      <c r="AH17" s="17"/>
+      <c r="AI17" s="17"/>
+      <c r="AJ17" s="6"/>
+      <c r="AK17" s="3"/>
+      <c r="AL17" s="7"/>
+    </row>
+    <row r="18" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="H18" s="17">
+        <v>6.1910834999999995</v>
+      </c>
+      <c r="I18" s="3">
+        <v>12.332741667468573</v>
+      </c>
+      <c r="J18" s="4">
+        <f t="shared" si="0"/>
+        <v>1.9920166910151631</v>
+      </c>
+      <c r="K18" s="3"/>
+      <c r="L18" s="17">
+        <v>10</v>
+      </c>
+      <c r="M18" s="17"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="7">
+        <v>8.4656759444444436</v>
+      </c>
+      <c r="R18" s="14">
+        <v>25</v>
+      </c>
+      <c r="S18" s="17"/>
+      <c r="T18" s="3"/>
+      <c r="U18" s="4"/>
+      <c r="V18" s="3"/>
+      <c r="W18" s="17"/>
+      <c r="X18" s="17"/>
+      <c r="Y18" s="6"/>
+      <c r="Z18" s="3"/>
+      <c r="AA18" s="7"/>
+      <c r="AC18" s="14">
+        <v>45</v>
+      </c>
+      <c r="AD18" s="17"/>
+      <c r="AE18" s="3"/>
+      <c r="AF18" s="4"/>
+      <c r="AG18" s="3"/>
+      <c r="AH18" s="17"/>
+      <c r="AI18" s="17"/>
+      <c r="AJ18" s="6"/>
+      <c r="AK18" s="3"/>
+      <c r="AL18" s="7"/>
+    </row>
+    <row r="19" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19" s="14">
+        <v>23</v>
+      </c>
+      <c r="H19" s="17">
+        <v>39.987499999999997</v>
+      </c>
+      <c r="I19" s="3">
+        <v>16.605902462209162</v>
+      </c>
+      <c r="J19" s="4">
+        <f t="shared" si="0"/>
+        <v>0.41527733572264242</v>
+      </c>
+      <c r="K19" s="3"/>
+      <c r="L19" s="17">
+        <v>12.199999999999998</v>
+      </c>
+      <c r="M19" s="17"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="7">
+        <v>2.86625</v>
+      </c>
+      <c r="R19" s="14">
+        <v>23</v>
+      </c>
+      <c r="S19" s="17"/>
+      <c r="T19" s="3"/>
+      <c r="U19" s="4"/>
+      <c r="V19" s="3"/>
+      <c r="W19" s="17"/>
+      <c r="X19" s="17"/>
+      <c r="Y19" s="6"/>
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="7"/>
+      <c r="AC19" s="14">
+        <v>23</v>
+      </c>
+      <c r="AD19" s="17"/>
+      <c r="AE19" s="3"/>
+      <c r="AF19" s="4"/>
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="17"/>
+      <c r="AI19" s="17"/>
+      <c r="AJ19" s="6"/>
+      <c r="AK19" s="3"/>
+      <c r="AL19" s="7"/>
+    </row>
+    <row r="20" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G20" s="14">
+        <v>7</v>
+      </c>
+      <c r="H20" s="17">
+        <v>6.9908000000000001</v>
+      </c>
+      <c r="I20" s="3">
+        <v>4.9588260938679767</v>
+      </c>
+      <c r="J20" s="4">
+        <f t="shared" si="0"/>
+        <v>0.70933599786404655</v>
+      </c>
+      <c r="K20" s="3"/>
+      <c r="L20" s="17">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="M20" s="17"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="7">
+        <v>2.5019809523809524</v>
+      </c>
+      <c r="R20" s="14">
+        <v>12.190000000000001</v>
+      </c>
+      <c r="S20" s="17"/>
+      <c r="T20" s="3"/>
+      <c r="U20" s="4"/>
+      <c r="V20" s="3"/>
+      <c r="W20" s="17"/>
+      <c r="X20" s="17"/>
+      <c r="Y20" s="6"/>
+      <c r="Z20" s="3"/>
+      <c r="AA20" s="7"/>
+      <c r="AC20" s="14">
+        <v>7.09</v>
+      </c>
+      <c r="AD20" s="17"/>
+      <c r="AE20" s="3"/>
+      <c r="AF20" s="4"/>
+      <c r="AG20" s="3"/>
+      <c r="AH20" s="17"/>
+      <c r="AI20" s="17"/>
+      <c r="AJ20" s="6"/>
+      <c r="AK20" s="3"/>
+      <c r="AL20" s="7"/>
+    </row>
+    <row r="21" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G21" s="14">
+        <v>30</v>
+      </c>
+      <c r="H21" s="17">
+        <v>26.27983</v>
+      </c>
+      <c r="I21" s="3">
+        <v>3.5382942375971473</v>
+      </c>
+      <c r="J21" s="4">
+        <f t="shared" si="0"/>
+        <v>0.13463916005534082</v>
+      </c>
+      <c r="K21" s="3"/>
+      <c r="L21" s="17">
+        <v>35.5</v>
+      </c>
+      <c r="M21" s="17"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="3"/>
+      <c r="P21" s="7">
+        <v>1.0554572946859904</v>
+      </c>
+      <c r="R21" s="14">
+        <v>34.880000000000003</v>
+      </c>
+      <c r="S21" s="17"/>
+      <c r="T21" s="3"/>
+      <c r="U21" s="4"/>
+      <c r="V21" s="3"/>
+      <c r="W21" s="17"/>
+      <c r="X21" s="17"/>
+      <c r="Y21" s="6"/>
+      <c r="Z21" s="3"/>
+      <c r="AA21" s="7"/>
+      <c r="AC21" s="14">
+        <v>48.080000000000005</v>
+      </c>
+      <c r="AD21" s="17"/>
+      <c r="AE21" s="3"/>
+      <c r="AF21" s="4"/>
+      <c r="AG21" s="3"/>
+      <c r="AH21" s="17"/>
+      <c r="AI21" s="17"/>
+      <c r="AJ21" s="6"/>
+      <c r="AK21" s="3"/>
+      <c r="AL21" s="7"/>
+    </row>
+    <row r="22" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G22" s="14">
+        <v>0</v>
+      </c>
+      <c r="H22" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0.8944301000144349</v>
+      </c>
+      <c r="J22" s="4">
+        <f t="shared" si="0"/>
+        <v>8.9443010001443479</v>
+      </c>
+      <c r="K22" s="3"/>
+      <c r="L22" s="17">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="M22" s="17"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="7">
+        <v>0</v>
+      </c>
+      <c r="R22" s="14">
+        <v>2.4849999999999999</v>
+      </c>
+      <c r="S22" s="17"/>
+      <c r="T22" s="3"/>
+      <c r="U22" s="4"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="17"/>
+      <c r="X22" s="17"/>
+      <c r="Y22" s="6"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="7"/>
+      <c r="AC22" s="14">
+        <v>2.16</v>
+      </c>
+      <c r="AD22" s="17"/>
+      <c r="AE22" s="3"/>
+      <c r="AF22" s="4"/>
+      <c r="AG22" s="3"/>
+      <c r="AH22" s="17"/>
+      <c r="AI22" s="17"/>
+      <c r="AJ22" s="6"/>
+      <c r="AK22" s="3"/>
+      <c r="AL22" s="7"/>
+    </row>
+    <row r="23" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="H23" s="17">
+        <v>0.68445</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-0.20664055542154255</v>
+      </c>
+      <c r="J23" s="4">
+        <f t="shared" si="0"/>
+        <v>-0.30190745185410556</v>
+      </c>
+      <c r="K23" s="3"/>
+      <c r="L23" s="17">
+        <v>1</v>
+      </c>
+      <c r="M23" s="17"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="7">
+        <v>0.8948166666666667</v>
+      </c>
+      <c r="R23" s="14">
+        <v>1</v>
+      </c>
+      <c r="S23" s="17"/>
+      <c r="T23" s="3"/>
+      <c r="U23" s="4"/>
+      <c r="V23" s="3"/>
+      <c r="W23" s="17"/>
+      <c r="X23" s="17"/>
+      <c r="Y23" s="6"/>
+      <c r="Z23" s="3"/>
+      <c r="AA23" s="7"/>
+      <c r="AC23" s="14">
+        <v>1</v>
+      </c>
+      <c r="AD23" s="17"/>
+      <c r="AE23" s="3"/>
+      <c r="AF23" s="4"/>
+      <c r="AG23" s="3"/>
+      <c r="AH23" s="17"/>
+      <c r="AI23" s="17"/>
+      <c r="AJ23" s="6"/>
+      <c r="AK23" s="3"/>
+      <c r="AL23" s="7"/>
+    </row>
+    <row r="24" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G24" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="H24" s="17">
+        <v>1.6505700000000001</v>
+      </c>
+      <c r="I24" s="3">
+        <v>-0.80506115618567142</v>
+      </c>
+      <c r="J24" s="4">
+        <f t="shared" si="0"/>
+        <v>-0.48774735769199207</v>
+      </c>
+      <c r="K24" s="3"/>
+      <c r="L24" s="17">
+        <v>5</v>
+      </c>
+      <c r="M24" s="17"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="7">
+        <v>1.3667279569892472</v>
+      </c>
+      <c r="R24" s="14">
+        <v>2.8</v>
+      </c>
+      <c r="S24" s="17"/>
+      <c r="T24" s="3"/>
+      <c r="U24" s="4"/>
+      <c r="V24" s="3"/>
+      <c r="W24" s="17"/>
+      <c r="X24" s="17"/>
+      <c r="Y24" s="6"/>
+      <c r="Z24" s="3"/>
+      <c r="AA24" s="7"/>
+      <c r="AC24" s="14">
+        <v>8.26</v>
+      </c>
+      <c r="AD24" s="17"/>
+      <c r="AE24" s="3"/>
+      <c r="AF24" s="4"/>
+      <c r="AG24" s="3"/>
+      <c r="AH24" s="17"/>
+      <c r="AI24" s="17"/>
+      <c r="AJ24" s="6"/>
+      <c r="AK24" s="3"/>
+      <c r="AL24" s="7"/>
+    </row>
+    <row r="25" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G25" s="14">
+        <v>7</v>
+      </c>
+      <c r="H25" s="17">
+        <v>10.015700000000001</v>
+      </c>
+      <c r="I25" s="3">
+        <v>4.84458093899734</v>
+      </c>
+      <c r="J25" s="4">
+        <f t="shared" si="0"/>
+        <v>0.48369868696120488</v>
+      </c>
+      <c r="K25" s="3"/>
+      <c r="L25" s="17">
+        <v>5</v>
+      </c>
+      <c r="M25" s="17"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="7">
+        <v>2.4596416666666667</v>
+      </c>
+      <c r="R25" s="14">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="S25" s="17"/>
+      <c r="T25" s="3"/>
+      <c r="U25" s="4"/>
+      <c r="V25" s="3"/>
+      <c r="W25" s="17"/>
+      <c r="X25" s="17"/>
+      <c r="Y25" s="6"/>
+      <c r="Z25" s="3"/>
+      <c r="AA25" s="7"/>
+      <c r="AC25" s="14">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="AD25" s="17"/>
+      <c r="AE25" s="3"/>
+      <c r="AF25" s="4"/>
+      <c r="AG25" s="3"/>
+      <c r="AH25" s="17"/>
+      <c r="AI25" s="17"/>
+      <c r="AJ25" s="6"/>
+      <c r="AK25" s="3"/>
+      <c r="AL25" s="7"/>
+    </row>
+    <row r="26" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G26" s="14">
+        <v>16</v>
+      </c>
+      <c r="H26" s="17">
+        <v>24.223479999999999</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-5.7914111873014162</v>
+      </c>
+      <c r="J26" s="4">
+        <f t="shared" si="0"/>
+        <v>-0.23908254252904276</v>
+      </c>
+      <c r="K26" s="3"/>
+      <c r="L26" s="17">
+        <v>18.666666666666668</v>
+      </c>
+      <c r="M26" s="17"/>
+      <c r="N26" s="6"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="7">
+        <v>0.94555843137254891</v>
+      </c>
+      <c r="R26" s="14">
+        <v>12</v>
+      </c>
+      <c r="S26" s="17"/>
+      <c r="T26" s="3"/>
+      <c r="U26" s="4"/>
+      <c r="V26" s="3"/>
+      <c r="W26" s="17"/>
+      <c r="X26" s="17"/>
+      <c r="Y26" s="6"/>
+      <c r="Z26" s="3"/>
+      <c r="AA26" s="7"/>
+      <c r="AC26" s="14">
+        <v>12</v>
+      </c>
+      <c r="AD26" s="17"/>
+      <c r="AE26" s="3"/>
+      <c r="AF26" s="4"/>
+      <c r="AG26" s="3"/>
+      <c r="AH26" s="17"/>
+      <c r="AI26" s="17"/>
+      <c r="AJ26" s="6"/>
+      <c r="AK26" s="3"/>
+      <c r="AL26" s="7"/>
+    </row>
+    <row r="27" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G27" s="14">
+        <v>0</v>
+      </c>
+      <c r="H27" s="17">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-0.43439174266359831</v>
+      </c>
+      <c r="J27" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="3"/>
+      <c r="L27" s="17">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="M27" s="17"/>
+      <c r="N27" s="6"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="7">
+        <v>0</v>
+      </c>
+      <c r="R27" s="14">
+        <v>0</v>
+      </c>
+      <c r="S27" s="17"/>
+      <c r="T27" s="3"/>
+      <c r="U27" s="4"/>
+      <c r="V27" s="3"/>
+      <c r="W27" s="17"/>
+      <c r="X27" s="17"/>
+      <c r="Y27" s="6"/>
+      <c r="Z27" s="3"/>
+      <c r="AA27" s="7"/>
+      <c r="AC27" s="14">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="17"/>
+      <c r="AE27" s="3"/>
+      <c r="AF27" s="4"/>
+      <c r="AG27" s="3"/>
+      <c r="AH27" s="17"/>
+      <c r="AI27" s="17"/>
+      <c r="AJ27" s="6"/>
+      <c r="AK27" s="3"/>
+      <c r="AL27" s="7"/>
+    </row>
+    <row r="28" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G28" s="14">
+        <v>14</v>
+      </c>
+      <c r="H28" s="17">
+        <v>10.29</v>
+      </c>
+      <c r="I28" s="3">
+        <v>-7.6009084794700739E-3</v>
+      </c>
+      <c r="J28" s="4">
+        <f t="shared" si="0"/>
+        <v>-7.3866943435083325E-4</v>
+      </c>
+      <c r="K28" s="3"/>
+      <c r="L28" s="17">
+        <v>13.333333333333334</v>
+      </c>
+      <c r="M28" s="17"/>
+      <c r="N28" s="6"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="7">
+        <v>0.98200589970501451</v>
+      </c>
+      <c r="R28" s="14">
+        <v>14.4</v>
+      </c>
+      <c r="S28" s="17"/>
+      <c r="T28" s="3"/>
+      <c r="U28" s="4"/>
+      <c r="V28" s="3"/>
+      <c r="W28" s="17"/>
+      <c r="X28" s="17"/>
+      <c r="Y28" s="6"/>
+      <c r="Z28" s="3"/>
+      <c r="AA28" s="7"/>
+      <c r="AC28" s="14">
+        <v>8.6</v>
+      </c>
+      <c r="AD28" s="17"/>
+      <c r="AE28" s="3"/>
+      <c r="AF28" s="4"/>
+      <c r="AG28" s="3"/>
+      <c r="AH28" s="17"/>
+      <c r="AI28" s="17"/>
+      <c r="AJ28" s="6"/>
+      <c r="AK28" s="3"/>
+      <c r="AL28" s="7"/>
+    </row>
+    <row r="29" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G29" s="14">
+        <v>7.1</v>
+      </c>
+      <c r="H29" s="17">
+        <v>5.4947099999999995</v>
+      </c>
+      <c r="I29" s="3">
+        <v>-0.1393034954768749</v>
+      </c>
+      <c r="J29" s="4">
+        <f t="shared" si="0"/>
+        <v>-2.5352292564461986E-2</v>
+      </c>
+      <c r="K29" s="3"/>
+      <c r="L29" s="17">
+        <v>7</v>
+      </c>
+      <c r="M29" s="17"/>
+      <c r="N29" s="6"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="7">
+        <v>1.0472616666666665</v>
+      </c>
+      <c r="R29" s="14">
+        <v>6.48</v>
+      </c>
+      <c r="S29" s="17"/>
+      <c r="T29" s="3"/>
+      <c r="U29" s="4"/>
+      <c r="V29" s="3"/>
+      <c r="W29" s="17"/>
+      <c r="X29" s="17"/>
+      <c r="Y29" s="6"/>
+      <c r="Z29" s="3"/>
+      <c r="AA29" s="7"/>
+      <c r="AC29" s="14">
+        <v>6.8759999999999994</v>
+      </c>
+      <c r="AD29" s="17"/>
+      <c r="AE29" s="3"/>
+      <c r="AF29" s="4"/>
+      <c r="AG29" s="3"/>
+      <c r="AH29" s="17"/>
+      <c r="AI29" s="17"/>
+      <c r="AJ29" s="6"/>
+      <c r="AK29" s="3"/>
+      <c r="AL29" s="7"/>
+    </row>
+    <row r="30" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G30" s="14">
+        <v>0</v>
+      </c>
+      <c r="H30" s="17">
+        <v>0</v>
+      </c>
+      <c r="I30" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="J30" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="3"/>
+      <c r="L30" s="17">
+        <v>0</v>
+      </c>
+      <c r="M30" s="17"/>
+      <c r="N30" s="6"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="7">
+        <v>0</v>
+      </c>
+      <c r="R30" s="14">
+        <v>0</v>
+      </c>
+      <c r="S30" s="17"/>
+      <c r="T30" s="3"/>
+      <c r="U30" s="4"/>
+      <c r="V30" s="3"/>
+      <c r="W30" s="17"/>
+      <c r="X30" s="17"/>
+      <c r="Y30" s="6"/>
+      <c r="Z30" s="3"/>
+      <c r="AA30" s="7"/>
+      <c r="AC30" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="AD30" s="17"/>
+      <c r="AE30" s="3"/>
+      <c r="AF30" s="4"/>
+      <c r="AG30" s="3"/>
+      <c r="AH30" s="17"/>
+      <c r="AI30" s="17"/>
+      <c r="AJ30" s="6"/>
+      <c r="AK30" s="3"/>
+      <c r="AL30" s="7"/>
+    </row>
+    <row r="31" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A31" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G31" s="14">
+        <v>23</v>
+      </c>
+      <c r="H31" s="17">
+        <v>26.5</v>
+      </c>
+      <c r="I31" s="3">
+        <v>-2.604686874742915</v>
+      </c>
+      <c r="J31" s="4">
+        <f t="shared" si="0"/>
+        <v>-9.8290070745015667E-2</v>
+      </c>
+      <c r="K31" s="3"/>
+      <c r="L31" s="17">
+        <v>27.666666666666668</v>
+      </c>
+      <c r="M31" s="17"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="7">
+        <v>0.97046413502109707</v>
+      </c>
+      <c r="R31" s="14">
+        <v>28.8</v>
+      </c>
+      <c r="S31" s="17"/>
+      <c r="T31" s="3"/>
+      <c r="U31" s="4"/>
+      <c r="V31" s="3"/>
+      <c r="W31" s="17"/>
+      <c r="X31" s="17"/>
+      <c r="Y31" s="6"/>
+      <c r="Z31" s="3"/>
+      <c r="AA31" s="7"/>
+      <c r="AC31" s="14">
+        <v>13.7</v>
+      </c>
+      <c r="AD31" s="17"/>
+      <c r="AE31" s="3"/>
+      <c r="AF31" s="4"/>
+      <c r="AG31" s="3"/>
+      <c r="AH31" s="17"/>
+      <c r="AI31" s="17"/>
+      <c r="AJ31" s="6"/>
+      <c r="AK31" s="3"/>
+      <c r="AL31" s="7"/>
+    </row>
+    <row r="32" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A32" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G32" s="14">
+        <v>20.8</v>
+      </c>
+      <c r="H32" s="17">
+        <v>30.8</v>
+      </c>
+      <c r="I32" s="3">
+        <v>14.827293382532636</v>
+      </c>
+      <c r="J32" s="4">
+        <f t="shared" si="0"/>
+        <v>0.48140562930300762</v>
+      </c>
+      <c r="K32" s="3"/>
+      <c r="L32" s="17">
+        <v>14.333333333333334</v>
+      </c>
+      <c r="M32" s="17"/>
+      <c r="N32" s="6"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="7">
+        <v>2.1102564102564103</v>
+      </c>
+      <c r="R32" s="14">
+        <v>28.75</v>
+      </c>
+      <c r="S32" s="17"/>
+      <c r="T32" s="3"/>
+      <c r="U32" s="4"/>
+      <c r="V32" s="3"/>
+      <c r="W32" s="17"/>
+      <c r="X32" s="17"/>
+      <c r="Y32" s="6"/>
+      <c r="Z32" s="3"/>
+      <c r="AA32" s="7"/>
+      <c r="AC32" s="14">
+        <v>22.75</v>
+      </c>
+      <c r="AD32" s="17"/>
+      <c r="AE32" s="3"/>
+      <c r="AF32" s="4"/>
+      <c r="AG32" s="3"/>
+      <c r="AH32" s="17"/>
+      <c r="AI32" s="17"/>
+      <c r="AJ32" s="6"/>
+      <c r="AK32" s="3"/>
+      <c r="AL32" s="7"/>
+    </row>
+    <row r="33" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A33" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G33" s="14">
+        <v>0</v>
+      </c>
+      <c r="H33" s="17">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-1.2224075445787013</v>
+      </c>
+      <c r="J33" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="3"/>
+      <c r="L33" s="17">
+        <v>1</v>
+      </c>
+      <c r="M33" s="17"/>
+      <c r="N33" s="6"/>
+      <c r="O33" s="3"/>
+      <c r="P33" s="7">
+        <v>0</v>
+      </c>
+      <c r="R33" s="14">
+        <v>0</v>
+      </c>
+      <c r="S33" s="17"/>
+      <c r="T33" s="3"/>
+      <c r="U33" s="4"/>
+      <c r="V33" s="3"/>
+      <c r="W33" s="17"/>
+      <c r="X33" s="17"/>
+      <c r="Y33" s="6"/>
+      <c r="Z33" s="3"/>
+      <c r="AA33" s="7"/>
+      <c r="AC33" s="14">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="17"/>
+      <c r="AE33" s="3"/>
+      <c r="AF33" s="4"/>
+      <c r="AG33" s="3"/>
+      <c r="AH33" s="17"/>
+      <c r="AI33" s="17"/>
+      <c r="AJ33" s="6"/>
+      <c r="AK33" s="3"/>
+      <c r="AL33" s="7"/>
+    </row>
+    <row r="34" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A34" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G34" s="14">
+        <v>0</v>
+      </c>
+      <c r="H34" s="17">
+        <v>0</v>
+      </c>
+      <c r="I34" s="3">
+        <v>0</v>
+      </c>
+      <c r="J34" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="3"/>
+      <c r="L34" s="17">
+        <v>0</v>
+      </c>
+      <c r="M34" s="17"/>
+      <c r="N34" s="6"/>
+      <c r="O34" s="3"/>
+      <c r="P34" s="7">
+        <v>0</v>
+      </c>
+      <c r="R34" s="14">
+        <v>0</v>
+      </c>
+      <c r="S34" s="17"/>
+      <c r="T34" s="3"/>
+      <c r="U34" s="4"/>
+      <c r="V34" s="3"/>
+      <c r="W34" s="17"/>
+      <c r="X34" s="17"/>
+      <c r="Y34" s="6"/>
+      <c r="Z34" s="3"/>
+      <c r="AA34" s="7"/>
+      <c r="AC34" s="14">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="17"/>
+      <c r="AE34" s="3"/>
+      <c r="AF34" s="4"/>
+      <c r="AG34" s="3"/>
+      <c r="AH34" s="17"/>
+      <c r="AI34" s="17"/>
+      <c r="AJ34" s="6"/>
+      <c r="AK34" s="3"/>
+      <c r="AL34" s="7"/>
+    </row>
+    <row r="35" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A35" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G35" s="14">
+        <v>4</v>
+      </c>
+      <c r="H35" s="17">
+        <v>3.81</v>
+      </c>
+      <c r="I35" s="3">
+        <v>0.33530240421176227</v>
+      </c>
+      <c r="J35" s="4">
+        <f t="shared" si="0"/>
+        <v>8.8005880370541273E-2</v>
+      </c>
+      <c r="K35" s="3"/>
+      <c r="L35" s="17">
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="M35" s="17"/>
+      <c r="N35" s="6"/>
+      <c r="O35" s="3"/>
+      <c r="P35" s="7">
+        <v>1.2174603174603174</v>
+      </c>
+      <c r="R35" s="14">
+        <v>2.7</v>
+      </c>
+      <c r="S35" s="17"/>
+      <c r="T35" s="3"/>
+      <c r="U35" s="4"/>
+      <c r="V35" s="3"/>
+      <c r="W35" s="17"/>
+      <c r="X35" s="17"/>
+      <c r="Y35" s="6"/>
+      <c r="Z35" s="3"/>
+      <c r="AA35" s="7"/>
+      <c r="AC35" s="14">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="AD35" s="17"/>
+      <c r="AE35" s="3"/>
+      <c r="AF35" s="4"/>
+      <c r="AG35" s="3"/>
+      <c r="AH35" s="17"/>
+      <c r="AI35" s="17"/>
+      <c r="AJ35" s="6"/>
+      <c r="AK35" s="3"/>
+      <c r="AL35" s="7"/>
+    </row>
+    <row r="36" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A36" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G36" s="14">
+        <v>8</v>
+      </c>
+      <c r="H36" s="17">
+        <v>3.6067749999999998</v>
+      </c>
+      <c r="I36" s="3">
+        <v>2.1636641240935273</v>
+      </c>
+      <c r="J36" s="4">
+        <f t="shared" si="0"/>
+        <v>0.59988885475071974</v>
+      </c>
+      <c r="K36" s="3"/>
+      <c r="L36" s="17">
+        <v>5.333333333333333</v>
+      </c>
+      <c r="M36" s="17"/>
+      <c r="N36" s="6"/>
+      <c r="O36" s="3"/>
+      <c r="P36" s="7">
+        <v>1.6388979166666668</v>
+      </c>
+      <c r="R36" s="14">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="S36" s="17"/>
+      <c r="T36" s="3"/>
+      <c r="U36" s="4"/>
+      <c r="V36" s="3"/>
+      <c r="W36" s="17"/>
+      <c r="X36" s="17"/>
+      <c r="Y36" s="6"/>
+      <c r="Z36" s="3"/>
+      <c r="AA36" s="7"/>
+      <c r="AC36" s="14">
+        <v>7.76</v>
+      </c>
+      <c r="AD36" s="17"/>
+      <c r="AE36" s="3"/>
+      <c r="AF36" s="4"/>
+      <c r="AG36" s="3"/>
+      <c r="AH36" s="17"/>
+      <c r="AI36" s="17"/>
+      <c r="AJ36" s="6"/>
+      <c r="AK36" s="3"/>
+      <c r="AL36" s="7"/>
+    </row>
+    <row r="37" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A37" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G37" s="14">
+        <v>31</v>
+      </c>
+      <c r="H37" s="17">
+        <v>37.19</v>
+      </c>
+      <c r="I37" s="3">
+        <v>-10.621458196587033</v>
+      </c>
+      <c r="J37" s="4">
+        <f t="shared" si="0"/>
+        <v>-0.28559984395232679</v>
+      </c>
+      <c r="K37" s="3"/>
+      <c r="L37" s="17">
+        <v>40.666666666666664</v>
+      </c>
+      <c r="M37" s="17"/>
+      <c r="N37" s="6"/>
+      <c r="O37" s="3"/>
+      <c r="P37" s="7">
+        <v>1.6331372549019607</v>
+      </c>
+      <c r="R37" s="14">
+        <v>24.3</v>
+      </c>
+      <c r="S37" s="17"/>
+      <c r="T37" s="3"/>
+      <c r="U37" s="4"/>
+      <c r="V37" s="3"/>
+      <c r="W37" s="17"/>
+      <c r="X37" s="17"/>
+      <c r="Y37" s="6"/>
+      <c r="Z37" s="3"/>
+      <c r="AA37" s="7"/>
+      <c r="AC37" s="14">
+        <v>21.8</v>
+      </c>
+      <c r="AD37" s="17"/>
+      <c r="AE37" s="3"/>
+      <c r="AF37" s="4"/>
+      <c r="AG37" s="3"/>
+      <c r="AH37" s="17"/>
+      <c r="AI37" s="17"/>
+      <c r="AJ37" s="6"/>
+      <c r="AK37" s="3"/>
+      <c r="AL37" s="7"/>
+    </row>
+    <row r="38" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A38" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G38" s="14">
+        <v>12</v>
+      </c>
+      <c r="H38" s="17">
+        <v>12</v>
+      </c>
+      <c r="I38" s="3">
+        <v>6.3943992616107979</v>
+      </c>
+      <c r="J38" s="4">
+        <f t="shared" si="0"/>
+        <v>0.53286660513423312</v>
+      </c>
+      <c r="K38" s="3"/>
+      <c r="L38" s="17">
+        <v>11.666666666666666</v>
+      </c>
+      <c r="M38" s="17"/>
+      <c r="N38" s="6"/>
+      <c r="O38" s="3"/>
+      <c r="P38" s="7">
+        <v>2.1904761904761907</v>
+      </c>
+      <c r="R38" s="14">
+        <v>18</v>
+      </c>
+      <c r="S38" s="17"/>
+      <c r="T38" s="3"/>
+      <c r="U38" s="4"/>
+      <c r="V38" s="3"/>
+      <c r="W38" s="17"/>
+      <c r="X38" s="17"/>
+      <c r="Y38" s="6"/>
+      <c r="Z38" s="3"/>
+      <c r="AA38" s="7"/>
+      <c r="AC38" s="14">
+        <v>24.4</v>
+      </c>
+      <c r="AD38" s="17"/>
+      <c r="AE38" s="3"/>
+      <c r="AF38" s="4"/>
+      <c r="AG38" s="3"/>
+      <c r="AH38" s="17"/>
+      <c r="AI38" s="17"/>
+      <c r="AJ38" s="6"/>
+      <c r="AK38" s="3"/>
+      <c r="AL38" s="7"/>
+    </row>
+    <row r="39" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G39" s="14">
+        <v>3.4</v>
+      </c>
+      <c r="H39" s="17">
+        <v>4.83</v>
+      </c>
+      <c r="I39" s="3">
+        <v>2.4016443555995544</v>
+      </c>
+      <c r="J39" s="4">
+        <f t="shared" si="0"/>
+        <v>0.49723485623179181</v>
+      </c>
+      <c r="K39" s="3"/>
+      <c r="L39" s="17">
+        <v>3</v>
+      </c>
+      <c r="M39" s="17"/>
+      <c r="N39" s="6"/>
+      <c r="O39" s="3"/>
+      <c r="P39" s="7">
+        <v>2.6029176666666669</v>
+      </c>
+      <c r="R39" s="14">
+        <v>7.3425019999999996</v>
+      </c>
+      <c r="S39" s="17"/>
+      <c r="T39" s="3"/>
+      <c r="U39" s="4"/>
+      <c r="V39" s="3"/>
+      <c r="W39" s="17"/>
+      <c r="X39" s="17"/>
+      <c r="Y39" s="6"/>
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="7"/>
+      <c r="AC39" s="14">
+        <v>3.4450040000000004</v>
+      </c>
+      <c r="AD39" s="17"/>
+      <c r="AE39" s="3"/>
+      <c r="AF39" s="4"/>
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="17"/>
+      <c r="AI39" s="17"/>
+      <c r="AJ39" s="6"/>
+      <c r="AK39" s="3"/>
+      <c r="AL39" s="7"/>
+    </row>
+    <row r="40" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A40" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G40" s="14">
+        <v>3.6</v>
+      </c>
+      <c r="H40" s="17">
+        <v>3.5616104000000002</v>
+      </c>
+      <c r="I40" s="3">
+        <v>3.0382940431250547</v>
+      </c>
+      <c r="J40" s="4">
+        <f t="shared" si="0"/>
+        <v>0.85306748967406842</v>
+      </c>
+      <c r="K40" s="3"/>
+      <c r="L40" s="17">
+        <v>4</v>
+      </c>
+      <c r="M40" s="17"/>
+      <c r="N40" s="6"/>
+      <c r="O40" s="3"/>
+      <c r="P40" s="7">
+        <v>2.3077000430107528</v>
+      </c>
+      <c r="R40" s="14">
+        <v>8.6</v>
+      </c>
+      <c r="S40" s="17"/>
+      <c r="T40" s="3"/>
+      <c r="U40" s="4"/>
+      <c r="V40" s="3"/>
+      <c r="W40" s="17"/>
+      <c r="X40" s="17"/>
+      <c r="Y40" s="6"/>
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="7"/>
+      <c r="AC40" s="14">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="AD40" s="17"/>
+      <c r="AE40" s="3"/>
+      <c r="AF40" s="4"/>
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="17"/>
+      <c r="AI40" s="17"/>
+      <c r="AJ40" s="6"/>
+      <c r="AK40" s="3"/>
+      <c r="AL40" s="7"/>
+    </row>
+    <row r="41" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A41" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G41" s="14">
+        <v>0</v>
+      </c>
+      <c r="H41" s="17">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3">
+        <v>0</v>
+      </c>
+      <c r="J41" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K41" s="3"/>
+      <c r="L41" s="17">
+        <v>0</v>
+      </c>
+      <c r="M41" s="17"/>
+      <c r="N41" s="6"/>
+      <c r="O41" s="3"/>
+      <c r="P41" s="7">
+        <v>0</v>
+      </c>
+      <c r="R41" s="14">
+        <v>0</v>
+      </c>
+      <c r="S41" s="17"/>
+      <c r="T41" s="3"/>
+      <c r="U41" s="4"/>
+      <c r="V41" s="3"/>
+      <c r="W41" s="17"/>
+      <c r="X41" s="17"/>
+      <c r="Y41" s="6"/>
+      <c r="Z41" s="3"/>
+      <c r="AA41" s="7"/>
+      <c r="AC41" s="14">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="17"/>
+      <c r="AE41" s="3"/>
+      <c r="AF41" s="4"/>
+      <c r="AG41" s="3"/>
+      <c r="AH41" s="17"/>
+      <c r="AI41" s="17"/>
+      <c r="AJ41" s="6"/>
+      <c r="AK41" s="3"/>
+      <c r="AL41" s="7"/>
+    </row>
+    <row r="42" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A42" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G42" s="14">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="H42" s="17">
+        <v>10.17</v>
+      </c>
+      <c r="I42" s="3">
+        <v>3.984591770590749</v>
+      </c>
+      <c r="J42" s="4">
+        <f t="shared" si="0"/>
+        <v>0.39179860084471474</v>
+      </c>
+      <c r="K42" s="3"/>
+      <c r="L42" s="17">
+        <v>5</v>
+      </c>
+      <c r="M42" s="17"/>
+      <c r="N42" s="6"/>
+      <c r="O42" s="3"/>
+      <c r="P42" s="7">
+        <v>2.9510416666666659</v>
+      </c>
+      <c r="R42" s="14">
+        <v>10.02</v>
+      </c>
+      <c r="S42" s="17"/>
+      <c r="T42" s="3"/>
+      <c r="U42" s="4"/>
+      <c r="V42" s="3"/>
+      <c r="W42" s="17"/>
+      <c r="X42" s="17"/>
+      <c r="Y42" s="6"/>
+      <c r="Z42" s="3"/>
+      <c r="AA42" s="7"/>
+      <c r="AC42" s="14">
+        <v>8.14</v>
+      </c>
+      <c r="AD42" s="17"/>
+      <c r="AE42" s="3"/>
+      <c r="AF42" s="4"/>
+      <c r="AG42" s="3"/>
+      <c r="AH42" s="17"/>
+      <c r="AI42" s="17"/>
+      <c r="AJ42" s="6"/>
+      <c r="AK42" s="3"/>
+      <c r="AL42" s="7"/>
+    </row>
+    <row r="43" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A43" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G43" s="14">
+        <v>0</v>
+      </c>
+      <c r="H43" s="17">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3">
+        <v>3.3333333333333326E-2</v>
+      </c>
+      <c r="J43" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="3"/>
+      <c r="L43" s="17">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="M43" s="17"/>
+      <c r="N43" s="6"/>
+      <c r="O43" s="3"/>
+      <c r="P43" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="R43" s="14">
+        <v>0</v>
+      </c>
+      <c r="S43" s="17"/>
+      <c r="T43" s="3"/>
+      <c r="U43" s="4"/>
+      <c r="V43" s="3"/>
+      <c r="W43" s="17"/>
+      <c r="X43" s="17"/>
+      <c r="Y43" s="6"/>
+      <c r="Z43" s="3"/>
+      <c r="AA43" s="7"/>
+      <c r="AC43" s="14">
+        <v>1</v>
+      </c>
+      <c r="AD43" s="17"/>
+      <c r="AE43" s="3"/>
+      <c r="AF43" s="4"/>
+      <c r="AG43" s="3"/>
+      <c r="AH43" s="17"/>
+      <c r="AI43" s="17"/>
+      <c r="AJ43" s="6"/>
+      <c r="AK43" s="3"/>
+      <c r="AL43" s="7"/>
+    </row>
+    <row r="44" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A44" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G44" s="14">
+        <v>3.3</v>
+      </c>
+      <c r="H44" s="17">
+        <v>2.90625</v>
+      </c>
+      <c r="I44" s="3">
+        <v>1.4333848089524714</v>
+      </c>
+      <c r="J44" s="4">
+        <f t="shared" si="0"/>
+        <v>0.49320767619869987</v>
+      </c>
+      <c r="K44" s="3"/>
+      <c r="L44" s="17">
+        <v>4.6000000000000005</v>
+      </c>
+      <c r="M44" s="17"/>
+      <c r="N44" s="6"/>
+      <c r="O44" s="3"/>
+      <c r="P44" s="7">
+        <v>2.2062499999999998</v>
+      </c>
+      <c r="R44" s="14">
+        <v>7.95</v>
+      </c>
+      <c r="S44" s="17"/>
+      <c r="T44" s="3"/>
+      <c r="U44" s="4"/>
+      <c r="V44" s="3"/>
+      <c r="W44" s="17"/>
+      <c r="X44" s="17"/>
+      <c r="Y44" s="6"/>
+      <c r="Z44" s="3"/>
+      <c r="AA44" s="7"/>
+      <c r="AC44" s="14">
+        <v>9</v>
+      </c>
+      <c r="AD44" s="17"/>
+      <c r="AE44" s="3"/>
+      <c r="AF44" s="4"/>
+      <c r="AG44" s="3"/>
+      <c r="AH44" s="17"/>
+      <c r="AI44" s="17"/>
+      <c r="AJ44" s="6"/>
+      <c r="AK44" s="3"/>
+      <c r="AL44" s="7"/>
+    </row>
+    <row r="45" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A45" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G45" s="14">
+        <v>9</v>
+      </c>
+      <c r="H45" s="17">
+        <v>7.97</v>
+      </c>
+      <c r="I45" s="3">
+        <v>4.0882134700977213</v>
+      </c>
+      <c r="J45" s="4">
+        <f t="shared" si="0"/>
+        <v>0.51295024718917459</v>
+      </c>
+      <c r="K45" s="3"/>
+      <c r="L45" s="17">
+        <v>4</v>
+      </c>
+      <c r="M45" s="17"/>
+      <c r="N45" s="6"/>
+      <c r="O45" s="3"/>
+      <c r="P45" s="7">
+        <v>2.9047555555555555</v>
+      </c>
+      <c r="R45" s="14">
+        <v>9.0863999999999994</v>
+      </c>
+      <c r="S45" s="17"/>
+      <c r="T45" s="3"/>
+      <c r="U45" s="4"/>
+      <c r="V45" s="3"/>
+      <c r="W45" s="17"/>
+      <c r="X45" s="17"/>
+      <c r="Y45" s="6"/>
+      <c r="Z45" s="3"/>
+      <c r="AA45" s="7"/>
+      <c r="AC45" s="14">
+        <v>9.0863999999999994</v>
+      </c>
+      <c r="AD45" s="17"/>
+      <c r="AE45" s="3"/>
+      <c r="AF45" s="4"/>
+      <c r="AG45" s="3"/>
+      <c r="AH45" s="17"/>
+      <c r="AI45" s="17"/>
+      <c r="AJ45" s="6"/>
+      <c r="AK45" s="3"/>
+      <c r="AL45" s="7"/>
+    </row>
+    <row r="46" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A46" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G46" s="14">
+        <v>6.5</v>
+      </c>
+      <c r="H46" s="17">
+        <v>10.65</v>
+      </c>
+      <c r="I46" s="3">
+        <v>3.7363008021508812</v>
+      </c>
+      <c r="J46" s="4">
+        <f t="shared" si="0"/>
+        <v>0.35082636639914377</v>
+      </c>
+      <c r="K46" s="3"/>
+      <c r="L46" s="17">
+        <v>6.333333333333333</v>
+      </c>
+      <c r="M46" s="17"/>
+      <c r="N46" s="6"/>
+      <c r="O46" s="3"/>
+      <c r="P46" s="7">
+        <v>1.6966666666666668</v>
+      </c>
+      <c r="R46" s="14">
+        <v>8.4</v>
+      </c>
+      <c r="S46" s="17"/>
+      <c r="T46" s="3"/>
+      <c r="U46" s="4"/>
+      <c r="V46" s="3"/>
+      <c r="W46" s="17"/>
+      <c r="X46" s="17"/>
+      <c r="Y46" s="6"/>
+      <c r="Z46" s="3"/>
+      <c r="AA46" s="7"/>
+      <c r="AC46" s="14">
+        <v>6.4</v>
+      </c>
+      <c r="AD46" s="17"/>
+      <c r="AE46" s="3"/>
+      <c r="AF46" s="4"/>
+      <c r="AG46" s="3"/>
+      <c r="AH46" s="17"/>
+      <c r="AI46" s="17"/>
+      <c r="AJ46" s="6"/>
+      <c r="AK46" s="3"/>
+      <c r="AL46" s="7"/>
+    </row>
+    <row r="47" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A47" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G47" s="14">
+        <v>6.4</v>
+      </c>
+      <c r="H47" s="17">
+        <v>6.5951000000000004</v>
+      </c>
+      <c r="I47" s="3">
+        <v>0.88921430612099994</v>
+      </c>
+      <c r="J47" s="4">
+        <f t="shared" si="0"/>
+        <v>0.13482954104122757</v>
+      </c>
+      <c r="K47" s="3"/>
+      <c r="L47" s="17">
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="M47" s="17"/>
+      <c r="N47" s="6"/>
+      <c r="O47" s="3"/>
+      <c r="P47" s="7">
+        <v>1.7125166666666667</v>
+      </c>
+      <c r="R47" s="14">
+        <v>2.33</v>
+      </c>
+      <c r="S47" s="17"/>
+      <c r="T47" s="3"/>
+      <c r="U47" s="4"/>
+      <c r="V47" s="3"/>
+      <c r="W47" s="17"/>
+      <c r="X47" s="17"/>
+      <c r="Y47" s="6"/>
+      <c r="Z47" s="3"/>
+      <c r="AA47" s="7"/>
+      <c r="AC47" s="14">
+        <v>1.35</v>
+      </c>
+      <c r="AD47" s="17"/>
+      <c r="AE47" s="3"/>
+      <c r="AF47" s="4"/>
+      <c r="AG47" s="3"/>
+      <c r="AH47" s="17"/>
+      <c r="AI47" s="17"/>
+      <c r="AJ47" s="6"/>
+      <c r="AK47" s="3"/>
+      <c r="AL47" s="7"/>
+    </row>
+    <row r="48" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A48" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G48" s="14">
+        <v>45.8</v>
+      </c>
+      <c r="H48" s="17">
+        <v>65.400000000000006</v>
+      </c>
+      <c r="I48" s="3">
+        <v>26.472517639262765</v>
+      </c>
+      <c r="J48" s="4">
+        <f t="shared" si="0"/>
+        <v>0.40477855717527161</v>
+      </c>
+      <c r="K48" s="3"/>
+      <c r="L48" s="17">
+        <v>24.666666666666668</v>
+      </c>
+      <c r="M48" s="17"/>
+      <c r="N48" s="6"/>
+      <c r="O48" s="3"/>
+      <c r="P48" s="7">
+        <v>2.7543859649122808</v>
+      </c>
+      <c r="R48" s="14">
+        <v>45.8</v>
+      </c>
+      <c r="S48" s="17"/>
+      <c r="T48" s="3"/>
+      <c r="U48" s="4"/>
+      <c r="V48" s="3"/>
+      <c r="W48" s="17"/>
+      <c r="X48" s="17"/>
+      <c r="Y48" s="6"/>
+      <c r="Z48" s="3"/>
+      <c r="AA48" s="7"/>
+      <c r="AC48" s="14">
+        <v>45.8</v>
+      </c>
+      <c r="AD48" s="17"/>
+      <c r="AE48" s="3"/>
+      <c r="AF48" s="4"/>
+      <c r="AG48" s="3"/>
+      <c r="AH48" s="17"/>
+      <c r="AI48" s="17"/>
+      <c r="AJ48" s="6"/>
+      <c r="AK48" s="3"/>
+      <c r="AL48" s="7"/>
+    </row>
+    <row r="49" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A49" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G49" s="14">
+        <v>18</v>
+      </c>
+      <c r="H49" s="17">
+        <v>17</v>
+      </c>
+      <c r="I49" s="3">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="J49" s="4">
+        <f t="shared" si="0"/>
+        <v>0.2829411764705882</v>
+      </c>
+      <c r="K49" s="3"/>
+      <c r="L49" s="17">
+        <v>19</v>
+      </c>
+      <c r="M49" s="17"/>
+      <c r="N49" s="6"/>
+      <c r="O49" s="3"/>
+      <c r="P49" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="R49" s="14">
+        <v>25</v>
+      </c>
+      <c r="S49" s="17"/>
+      <c r="T49" s="3"/>
+      <c r="U49" s="4"/>
+      <c r="V49" s="3"/>
+      <c r="W49" s="17"/>
+      <c r="X49" s="17"/>
+      <c r="Y49" s="6"/>
+      <c r="Z49" s="3"/>
+      <c r="AA49" s="7"/>
+      <c r="AC49" s="14">
+        <v>30</v>
+      </c>
+      <c r="AD49" s="17"/>
+      <c r="AE49" s="3"/>
+      <c r="AF49" s="4"/>
+      <c r="AG49" s="3"/>
+      <c r="AH49" s="17"/>
+      <c r="AI49" s="17"/>
+      <c r="AJ49" s="6"/>
+      <c r="AK49" s="3"/>
+      <c r="AL49" s="7"/>
+    </row>
+    <row r="50" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A50" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G50" s="14">
+        <v>8.9</v>
+      </c>
+      <c r="H50" s="17">
+        <v>7.9112900000000002</v>
+      </c>
+      <c r="I50" s="3">
+        <v>5.8537633333333341</v>
+      </c>
+      <c r="J50" s="4">
+        <f t="shared" si="0"/>
+        <v>0.73992526292593674</v>
+      </c>
+      <c r="K50" s="3"/>
+      <c r="L50" s="17">
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="M50" s="17"/>
+      <c r="N50" s="6"/>
+      <c r="O50" s="3"/>
+      <c r="P50" s="7">
+        <v>7.2004300000000008</v>
+      </c>
+      <c r="R50" s="14">
+        <v>10.32</v>
+      </c>
+      <c r="S50" s="17"/>
+      <c r="T50" s="3"/>
+      <c r="U50" s="4"/>
+      <c r="V50" s="3"/>
+      <c r="W50" s="17"/>
+      <c r="X50" s="17"/>
+      <c r="Y50" s="6"/>
+      <c r="Z50" s="3"/>
+      <c r="AA50" s="7"/>
+      <c r="AC50" s="14">
+        <v>3.37</v>
+      </c>
+      <c r="AD50" s="17"/>
+      <c r="AE50" s="3"/>
+      <c r="AF50" s="4"/>
+      <c r="AG50" s="3"/>
+      <c r="AH50" s="17"/>
+      <c r="AI50" s="17"/>
+      <c r="AJ50" s="6"/>
+      <c r="AK50" s="3"/>
+      <c r="AL50" s="7"/>
+    </row>
+    <row r="51" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A51" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G51" s="14">
+        <v>8</v>
+      </c>
+      <c r="H51" s="17">
+        <v>0</v>
+      </c>
+      <c r="I51" s="3">
+        <v>-6.3453123695111699</v>
+      </c>
+      <c r="J51" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="3"/>
+      <c r="L51" s="17">
+        <v>6</v>
+      </c>
+      <c r="M51" s="17"/>
+      <c r="N51" s="6"/>
+      <c r="O51" s="3"/>
+      <c r="P51" s="7">
+        <v>0</v>
+      </c>
+      <c r="R51" s="14">
+        <v>0</v>
+      </c>
+      <c r="S51" s="17"/>
+      <c r="T51" s="3"/>
+      <c r="U51" s="4"/>
+      <c r="V51" s="3"/>
+      <c r="W51" s="17"/>
+      <c r="X51" s="17"/>
+      <c r="Y51" s="6"/>
+      <c r="Z51" s="3"/>
+      <c r="AA51" s="7"/>
+      <c r="AC51" s="14">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="17"/>
+      <c r="AE51" s="3"/>
+      <c r="AF51" s="4"/>
+      <c r="AG51" s="3"/>
+      <c r="AH51" s="17"/>
+      <c r="AI51" s="17"/>
+      <c r="AJ51" s="6"/>
+      <c r="AK51" s="3"/>
+      <c r="AL51" s="7"/>
+    </row>
+    <row r="52" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A52" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G52" s="14">
+        <v>0.6</v>
+      </c>
+      <c r="H52" s="17">
+        <v>1</v>
+      </c>
+      <c r="I52" s="3">
+        <v>-0.7882832298375444</v>
+      </c>
+      <c r="J52" s="4">
+        <f t="shared" si="0"/>
+        <v>-0.7882832298375444</v>
+      </c>
+      <c r="K52" s="3"/>
+      <c r="L52" s="17">
+        <v>2</v>
+      </c>
+      <c r="M52" s="17"/>
+      <c r="N52" s="6"/>
+      <c r="O52" s="3"/>
+      <c r="P52" s="7">
+        <v>2</v>
+      </c>
+      <c r="R52" s="14">
+        <v>0</v>
+      </c>
+      <c r="S52" s="17"/>
+      <c r="T52" s="3"/>
+      <c r="U52" s="4"/>
+      <c r="V52" s="3"/>
+      <c r="W52" s="17"/>
+      <c r="X52" s="17"/>
+      <c r="Y52" s="6"/>
+      <c r="Z52" s="3"/>
+      <c r="AA52" s="7"/>
+      <c r="AC52" s="14">
+        <v>5</v>
+      </c>
+      <c r="AD52" s="17"/>
+      <c r="AE52" s="3"/>
+      <c r="AF52" s="4"/>
+      <c r="AG52" s="3"/>
+      <c r="AH52" s="17"/>
+      <c r="AI52" s="17"/>
+      <c r="AJ52" s="6"/>
+      <c r="AK52" s="3"/>
+      <c r="AL52" s="7"/>
+    </row>
+    <row r="53" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A53" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G53" s="14">
+        <v>0</v>
+      </c>
+      <c r="H53" s="17">
+        <v>0</v>
+      </c>
+      <c r="I53" s="3">
+        <v>0</v>
+      </c>
+      <c r="J53" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="3"/>
+      <c r="L53" s="17">
+        <v>0</v>
+      </c>
+      <c r="M53" s="17"/>
+      <c r="N53" s="6"/>
+      <c r="O53" s="3"/>
+      <c r="P53" s="7">
+        <v>0</v>
+      </c>
+      <c r="R53" s="14">
+        <v>0</v>
+      </c>
+      <c r="S53" s="17"/>
+      <c r="T53" s="3"/>
+      <c r="U53" s="4"/>
+      <c r="V53" s="3"/>
+      <c r="W53" s="17"/>
+      <c r="X53" s="17"/>
+      <c r="Y53" s="6"/>
+      <c r="Z53" s="3"/>
+      <c r="AA53" s="7"/>
+      <c r="AC53" s="14">
+        <v>0</v>
+      </c>
+      <c r="AD53" s="17"/>
+      <c r="AE53" s="3"/>
+      <c r="AF53" s="4"/>
+      <c r="AG53" s="3"/>
+      <c r="AH53" s="17"/>
+      <c r="AI53" s="17"/>
+      <c r="AJ53" s="6"/>
+      <c r="AK53" s="3"/>
+      <c r="AL53" s="7"/>
+    </row>
+    <row r="54" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A54" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G54" s="14">
+        <v>0</v>
+      </c>
+      <c r="H54" s="17">
+        <v>0</v>
+      </c>
+      <c r="I54" s="3">
+        <v>0</v>
+      </c>
+      <c r="J54" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="3"/>
+      <c r="L54" s="17">
+        <v>0</v>
+      </c>
+      <c r="M54" s="17"/>
+      <c r="N54" s="6"/>
+      <c r="O54" s="3"/>
+      <c r="P54" s="7">
+        <v>0</v>
+      </c>
+      <c r="R54" s="14">
+        <v>0</v>
+      </c>
+      <c r="S54" s="17"/>
+      <c r="T54" s="3"/>
+      <c r="U54" s="4"/>
+      <c r="V54" s="3"/>
+      <c r="W54" s="17"/>
+      <c r="X54" s="17"/>
+      <c r="Y54" s="6"/>
+      <c r="Z54" s="3"/>
+      <c r="AA54" s="7"/>
+      <c r="AC54" s="14">
+        <v>0</v>
+      </c>
+      <c r="AD54" s="17"/>
+      <c r="AE54" s="3"/>
+      <c r="AF54" s="4"/>
+      <c r="AG54" s="3"/>
+      <c r="AH54" s="17"/>
+      <c r="AI54" s="17"/>
+      <c r="AJ54" s="6"/>
+      <c r="AK54" s="3"/>
+      <c r="AL54" s="7"/>
+    </row>
+    <row r="55" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A55" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G55" s="14">
+        <v>4</v>
+      </c>
+      <c r="H55" s="17">
+        <v>9</v>
+      </c>
+      <c r="I55" s="3">
+        <v>-6.5757544546004523</v>
+      </c>
+      <c r="J55" s="4">
+        <f t="shared" si="0"/>
+        <v>-0.73063938384449467</v>
+      </c>
+      <c r="K55" s="3"/>
+      <c r="L55" s="17">
+        <v>21.333333333333332</v>
+      </c>
+      <c r="M55" s="17"/>
+      <c r="N55" s="6"/>
+      <c r="O55" s="3"/>
+      <c r="P55" s="7">
+        <v>0.21039603960396042</v>
+      </c>
+      <c r="R55" s="14">
+        <v>2.25</v>
+      </c>
+      <c r="S55" s="17"/>
+      <c r="T55" s="3"/>
+      <c r="U55" s="4"/>
+      <c r="V55" s="3"/>
+      <c r="W55" s="17"/>
+      <c r="X55" s="17"/>
+      <c r="Y55" s="6"/>
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="7"/>
+      <c r="AC55" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="AD55" s="17"/>
+      <c r="AE55" s="3"/>
+      <c r="AF55" s="4"/>
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="17"/>
+      <c r="AI55" s="17"/>
+      <c r="AJ55" s="6"/>
+      <c r="AK55" s="3"/>
+      <c r="AL55" s="7"/>
+    </row>
+    <row r="56" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A56" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G56" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="H56" s="17">
+        <v>2.9410600000000002</v>
+      </c>
+      <c r="I56" s="3">
+        <v>0.44902000000000014</v>
+      </c>
+      <c r="J56" s="4">
+        <f t="shared" si="0"/>
+        <v>0.15267284584469548</v>
+      </c>
+      <c r="K56" s="3"/>
+      <c r="L56" s="17">
+        <v>0.79999999999999993</v>
+      </c>
+      <c r="M56" s="17"/>
+      <c r="N56" s="6"/>
+      <c r="O56" s="3"/>
+      <c r="P56" s="7">
+        <v>0</v>
+      </c>
+      <c r="R56" s="14">
+        <v>0.83</v>
+      </c>
+      <c r="S56" s="17"/>
+      <c r="T56" s="3"/>
+      <c r="U56" s="4"/>
+      <c r="V56" s="3"/>
+      <c r="W56" s="17"/>
+      <c r="X56" s="17"/>
+      <c r="Y56" s="6"/>
+      <c r="Z56" s="3"/>
+      <c r="AA56" s="7"/>
+      <c r="AC56" s="14">
+        <v>0</v>
+      </c>
+      <c r="AD56" s="17"/>
+      <c r="AE56" s="3"/>
+      <c r="AF56" s="4"/>
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="17"/>
+      <c r="AI56" s="17"/>
+      <c r="AJ56" s="6"/>
+      <c r="AK56" s="3"/>
+      <c r="AL56" s="7"/>
+    </row>
+    <row r="57" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A57" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G57" s="14">
+        <v>0</v>
+      </c>
+      <c r="H57" s="17">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3">
+        <v>-1.4939221985593101</v>
+      </c>
+      <c r="J57" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="3"/>
+      <c r="L57" s="17">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="M57" s="17"/>
+      <c r="N57" s="6"/>
+      <c r="O57" s="3"/>
+      <c r="P57" s="7">
+        <v>0</v>
+      </c>
+      <c r="R57" s="14">
+        <v>0</v>
+      </c>
+      <c r="S57" s="17"/>
+      <c r="T57" s="3"/>
+      <c r="U57" s="4"/>
+      <c r="V57" s="3"/>
+      <c r="W57" s="17"/>
+      <c r="X57" s="17"/>
+      <c r="Y57" s="6"/>
+      <c r="Z57" s="3"/>
+      <c r="AA57" s="7"/>
+      <c r="AC57" s="14">
+        <v>0</v>
+      </c>
+      <c r="AD57" s="17"/>
+      <c r="AE57" s="3"/>
+      <c r="AF57" s="4"/>
+      <c r="AG57" s="3"/>
+      <c r="AH57" s="17"/>
+      <c r="AI57" s="17"/>
+      <c r="AJ57" s="6"/>
+      <c r="AK57" s="3"/>
+      <c r="AL57" s="7"/>
+    </row>
+    <row r="58" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A58" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B58" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C58" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E58" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="G58" s="14">
+        <v>0</v>
+      </c>
+      <c r="H58" s="17">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0.28333333333333338</v>
+      </c>
+      <c r="J58" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="3"/>
+      <c r="L58" s="17">
+        <v>1.1666666666666667</v>
+      </c>
+      <c r="M58" s="17"/>
+      <c r="N58" s="6"/>
+      <c r="O58" s="3"/>
+      <c r="P58" s="7">
+        <v>0.38095238095238093</v>
+      </c>
+      <c r="R58" s="3">
+        <v>2</v>
+      </c>
+      <c r="S58" s="17"/>
+      <c r="T58" s="3"/>
+      <c r="U58" s="4"/>
+      <c r="V58" s="3"/>
+      <c r="W58" s="17"/>
+      <c r="X58" s="17"/>
+      <c r="Y58" s="6"/>
+      <c r="Z58" s="3"/>
+      <c r="AA58" s="7"/>
+      <c r="AC58" s="14">
+        <v>2</v>
+      </c>
+      <c r="AD58" s="17"/>
+      <c r="AE58" s="3"/>
+      <c r="AF58" s="4"/>
+      <c r="AG58" s="3"/>
+      <c r="AH58" s="17"/>
+      <c r="AI58" s="17"/>
+      <c r="AJ58" s="6"/>
+      <c r="AK58" s="3"/>
+      <c r="AL58" s="7"/>
+    </row>
+    <row r="59" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A59" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="B59" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C59" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E59" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="G59" s="14">
+        <v>0</v>
+      </c>
+      <c r="H59" s="17">
+        <v>1.75</v>
+      </c>
+      <c r="I59" s="3">
+        <v>1.24</v>
+      </c>
+      <c r="J59" s="4">
+        <f t="shared" si="0"/>
+        <v>0.70857142857142852</v>
+      </c>
+      <c r="K59" s="3"/>
+      <c r="L59" s="17">
+        <v>0.56666666666666665</v>
+      </c>
+      <c r="M59" s="17"/>
+      <c r="N59" s="6"/>
+      <c r="O59" s="3"/>
+      <c r="P59" s="7">
+        <v>1.2500000000000002</v>
+      </c>
+      <c r="R59" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="S59" s="17"/>
+      <c r="T59" s="3"/>
+      <c r="U59" s="4"/>
+      <c r="V59" s="3"/>
+      <c r="W59" s="17"/>
+      <c r="X59" s="17"/>
+      <c r="Y59" s="6"/>
+      <c r="Z59" s="3"/>
+      <c r="AA59" s="7"/>
+      <c r="AC59" s="14">
+        <v>1.75</v>
+      </c>
+      <c r="AD59" s="17"/>
+      <c r="AE59" s="3"/>
+      <c r="AF59" s="4"/>
+      <c r="AG59" s="3"/>
+      <c r="AH59" s="17"/>
+      <c r="AI59" s="17"/>
+      <c r="AJ59" s="6"/>
+      <c r="AK59" s="3"/>
+      <c r="AL59" s="7"/>
+    </row>
+    <row r="60" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A60" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="B60" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="C60" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E60" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="G60" s="14">
+        <v>0</v>
+      </c>
+      <c r="H60" s="17">
+        <v>0</v>
+      </c>
+      <c r="I60" s="3">
+        <v>0</v>
+      </c>
+      <c r="J60" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K60" s="16"/>
+      <c r="L60" s="24">
+        <v>0</v>
+      </c>
+      <c r="M60" s="17"/>
+      <c r="R60" s="23">
+        <v>0</v>
+      </c>
+      <c r="S60" s="17"/>
+      <c r="T60" s="3"/>
+      <c r="U60" s="4"/>
+      <c r="V60" s="16"/>
+      <c r="W60" s="24"/>
+      <c r="X60" s="17"/>
+      <c r="AC60" s="14">
+        <v>0</v>
+      </c>
+      <c r="AD60" s="17"/>
+      <c r="AE60" s="3"/>
+      <c r="AF60" s="4"/>
+      <c r="AG60" s="16"/>
+      <c r="AH60" s="24"/>
+      <c r="AI60" s="17"/>
+    </row>
+    <row r="61" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A61" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="B61" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="D61" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="E61" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G61" s="14">
+        <v>0</v>
+      </c>
+      <c r="H61" s="17">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L61" s="24">
+        <v>5.2</v>
+      </c>
+      <c r="R61" s="18">
+        <v>12.5</v>
+      </c>
+      <c r="S61" s="17"/>
+      <c r="T61" s="3"/>
+      <c r="U61" s="4"/>
+      <c r="W61" s="24"/>
+      <c r="AC61" s="14">
+        <v>12.5</v>
+      </c>
+      <c r="AD61" s="17"/>
+      <c r="AE61" s="3"/>
+      <c r="AF61" s="4"/>
+      <c r="AH61" s="24"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="G1:P1"/>
+    <mergeCell ref="R1:AA1"/>
+    <mergeCell ref="AC1:AL1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/CEO Review.xlsx
+++ b/CEO Review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://peoplestronghrservices-my.sharepoint.com/personal/baljeet_singh_taggd_in/Documents/Desktop/Clude Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1701" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AFE4DC0-9F73-4A3F-A057-2DAE547ABBB7}"/>
+  <xr:revisionPtr revIDLastSave="1809" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82084BC5-C749-4248-AEA7-38FBCBD28A37}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{F2C8E0B5-D69E-42FC-A0A4-20379F29D696}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Actual" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Actual!$A$2:$AL$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Actual!$A$2:$AO$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$BZ$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="129">
   <si>
     <t>Clients</t>
   </si>
@@ -418,9 +418,6 @@
     <t>Apr</t>
   </si>
   <si>
-    <t>Forecast Revenue</t>
-  </si>
-  <si>
     <t>Actual Revenue</t>
   </si>
   <si>
@@ -428,6 +425,12 @@
   </si>
   <si>
     <t>June</t>
+  </si>
+  <si>
+    <t>Unbilled</t>
+  </si>
+  <si>
+    <t>Budget Revenue</t>
   </si>
 </sst>
 </file>
@@ -11391,21 +11394,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62BD0EA2-02E9-43B0-A368-1C9D568EE9C9}">
-  <dimension ref="A1:AL61"/>
+  <dimension ref="A1:AO61"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="0" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="0" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="5.08984375" customWidth="1"/>
     <col min="7" max="7" width="15.7265625" customWidth="1"/>
     <col min="8" max="8" width="13.90625" customWidth="1"/>
-    <col min="9" max="16" width="8.7265625" customWidth="1"/>
-    <col min="18" max="18" width="15.7265625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="8.7265625" customWidth="1"/>
+    <col min="14" max="14" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="8.7265625" customWidth="1"/>
+    <col min="19" max="19" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="15.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:41" x14ac:dyDescent="0.35">
       <c r="G1" s="29" t="s">
         <v>123</v>
       </c>
@@ -11418,10 +11425,10 @@
       <c r="N1" s="29"/>
       <c r="O1" s="29"/>
       <c r="P1" s="29"/>
-      <c r="R1" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="S1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="S1" s="29" t="s">
+        <v>125</v>
+      </c>
       <c r="T1" s="29"/>
       <c r="U1" s="29"/>
       <c r="V1" s="29"/>
@@ -11430,11 +11437,11 @@
       <c r="Y1" s="29"/>
       <c r="Z1" s="29"/>
       <c r="AA1" s="29"/>
-      <c r="AC1" s="29" t="s">
-        <v>127</v>
-      </c>
-      <c r="AD1" s="29"/>
-      <c r="AE1" s="29"/>
+      <c r="AB1" s="29"/>
+      <c r="AC1" s="29"/>
+      <c r="AE1" s="29" t="s">
+        <v>126</v>
+      </c>
       <c r="AF1" s="29"/>
       <c r="AG1" s="29"/>
       <c r="AH1" s="29"/>
@@ -11442,8 +11449,11 @@
       <c r="AJ1" s="29"/>
       <c r="AK1" s="29"/>
       <c r="AL1" s="29"/>
+      <c r="AM1" s="29"/>
+      <c r="AN1" s="29"/>
+      <c r="AO1" s="29"/>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -11460,10 +11470,10 @@
         <v>1</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>125</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>26</v>
@@ -11487,70 +11497,79 @@
         <v>34</v>
       </c>
       <c r="P2" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="S2" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="T2" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="S2" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="T2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="Y2" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AB2" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="AC2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AE2" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF2" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="AD2" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AG2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AH2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AG2" s="1" t="s">
+      <c r="AI2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="AJ2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AI2" s="1" t="s">
+      <c r="AK2" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="AJ2" s="1" t="s">
+      <c r="AL2" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="AK2" s="1" t="s">
+      <c r="AM2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AL2" s="1" t="s">
+      <c r="AN2" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="AO2" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -11586,35 +11605,44 @@
       <c r="M3" s="17"/>
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
-      <c r="P3" s="7">
+      <c r="P3" s="6">
+        <v>120</v>
+      </c>
+      <c r="Q3" s="7">
         <v>4.3498168498168504</v>
       </c>
-      <c r="R3" s="14">
+      <c r="S3" s="14">
         <v>167</v>
       </c>
-      <c r="S3" s="17"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="4"/>
-      <c r="V3" s="3"/>
-      <c r="W3" s="17"/>
+      <c r="T3" s="17">
+        <v>167</v>
+      </c>
+      <c r="U3" s="3"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="3"/>
       <c r="X3" s="17"/>
-      <c r="Y3" s="6"/>
+      <c r="Y3" s="17"/>
       <c r="Z3" s="6"/>
-      <c r="AA3" s="7"/>
-      <c r="AC3" s="14">
+      <c r="AA3" s="6"/>
+      <c r="AB3" s="6"/>
+      <c r="AC3" s="7"/>
+      <c r="AE3" s="14">
         <v>188</v>
       </c>
-      <c r="AD3" s="17"/>
-      <c r="AE3" s="3"/>
-      <c r="AF3" s="4"/>
+      <c r="AF3" s="17">
+        <v>188</v>
+      </c>
       <c r="AG3" s="3"/>
-      <c r="AH3" s="17"/>
-      <c r="AI3" s="17"/>
-      <c r="AJ3" s="6"/>
-      <c r="AK3" s="6"/>
-      <c r="AL3" s="7"/>
+      <c r="AH3" s="4"/>
+      <c r="AI3" s="3"/>
+      <c r="AJ3" s="17"/>
+      <c r="AK3" s="17"/>
+      <c r="AL3" s="6"/>
+      <c r="AM3" s="6"/>
+      <c r="AN3" s="6"/>
+      <c r="AO3" s="7"/>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>60</v>
       </c>
@@ -11631,7 +11659,7 @@
         <v>69</v>
       </c>
       <c r="G4" s="14">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="H4" s="17">
         <v>2.2562000000000002</v>
@@ -11650,35 +11678,44 @@
       <c r="M4" s="17"/>
       <c r="N4" s="6"/>
       <c r="O4" s="3"/>
-      <c r="P4" s="7">
-        <v>0</v>
-      </c>
-      <c r="R4" s="14">
+      <c r="P4" s="3">
+        <v>2.25</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>0</v>
+      </c>
+      <c r="S4" s="14">
+        <v>2</v>
+      </c>
+      <c r="T4" s="17">
         <v>6.6</v>
       </c>
-      <c r="S4" s="17"/>
-      <c r="T4" s="3"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="3"/>
-      <c r="W4" s="17"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="3"/>
       <c r="X4" s="17"/>
-      <c r="Y4" s="6"/>
-      <c r="Z4" s="3"/>
-      <c r="AA4" s="7"/>
-      <c r="AC4" s="14">
+      <c r="Y4" s="17"/>
+      <c r="Z4" s="6"/>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="7"/>
+      <c r="AE4" s="14">
+        <v>2</v>
+      </c>
+      <c r="AF4" s="17">
         <v>1.02</v>
       </c>
-      <c r="AD4" s="17"/>
-      <c r="AE4" s="3"/>
-      <c r="AF4" s="4"/>
       <c r="AG4" s="3"/>
-      <c r="AH4" s="17"/>
-      <c r="AI4" s="17"/>
-      <c r="AJ4" s="6"/>
-      <c r="AK4" s="3"/>
-      <c r="AL4" s="7"/>
+      <c r="AH4" s="4"/>
+      <c r="AI4" s="3"/>
+      <c r="AJ4" s="17"/>
+      <c r="AK4" s="17"/>
+      <c r="AL4" s="6"/>
+      <c r="AM4" s="3"/>
+      <c r="AN4" s="3"/>
+      <c r="AO4" s="7"/>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
@@ -11695,7 +11732,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="14">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="H5" s="17">
         <v>9.3010766</v>
@@ -11714,35 +11751,42 @@
       <c r="M5" s="17"/>
       <c r="N5" s="6"/>
       <c r="O5" s="3"/>
-      <c r="P5" s="7">
+      <c r="P5" s="3"/>
+      <c r="Q5" s="7">
         <v>2.5332973999999999</v>
       </c>
-      <c r="R5" s="14">
+      <c r="S5" s="14">
+        <v>8</v>
+      </c>
+      <c r="T5" s="17">
         <v>7.9985999999999997</v>
       </c>
-      <c r="S5" s="17"/>
-      <c r="T5" s="3"/>
-      <c r="U5" s="4"/>
-      <c r="V5" s="3"/>
-      <c r="W5" s="17"/>
+      <c r="U5" s="3"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="3"/>
       <c r="X5" s="17"/>
-      <c r="Y5" s="6"/>
-      <c r="Z5" s="3"/>
-      <c r="AA5" s="7"/>
-      <c r="AC5" s="14">
+      <c r="Y5" s="17"/>
+      <c r="Z5" s="6"/>
+      <c r="AA5" s="3"/>
+      <c r="AB5" s="3"/>
+      <c r="AC5" s="7"/>
+      <c r="AE5" s="14">
+        <v>8</v>
+      </c>
+      <c r="AF5" s="17">
         <v>5.5</v>
       </c>
-      <c r="AD5" s="17"/>
-      <c r="AE5" s="3"/>
-      <c r="AF5" s="4"/>
       <c r="AG5" s="3"/>
-      <c r="AH5" s="17"/>
-      <c r="AI5" s="17"/>
-      <c r="AJ5" s="6"/>
-      <c r="AK5" s="3"/>
-      <c r="AL5" s="7"/>
+      <c r="AH5" s="4"/>
+      <c r="AI5" s="3"/>
+      <c r="AJ5" s="17"/>
+      <c r="AK5" s="17"/>
+      <c r="AL5" s="6"/>
+      <c r="AM5" s="3"/>
+      <c r="AN5" s="3"/>
+      <c r="AO5" s="7"/>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>37</v>
       </c>
@@ -11778,35 +11822,44 @@
       <c r="M6" s="17"/>
       <c r="N6" s="6"/>
       <c r="O6" s="3"/>
-      <c r="P6" s="7">
+      <c r="P6" s="3">
+        <v>26.5</v>
+      </c>
+      <c r="Q6" s="7">
         <v>1.3417475728155339</v>
       </c>
-      <c r="R6" s="14">
+      <c r="S6" s="14">
+        <v>17</v>
+      </c>
+      <c r="T6" s="17">
         <v>13.11</v>
       </c>
-      <c r="S6" s="17"/>
-      <c r="T6" s="3"/>
-      <c r="U6" s="4"/>
-      <c r="V6" s="3"/>
-      <c r="W6" s="17"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="4"/>
+      <c r="W6" s="3"/>
       <c r="X6" s="17"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="3"/>
-      <c r="AA6" s="7"/>
-      <c r="AC6" s="14">
+      <c r="Y6" s="17"/>
+      <c r="Z6" s="6"/>
+      <c r="AA6" s="3"/>
+      <c r="AB6" s="3"/>
+      <c r="AC6" s="7"/>
+      <c r="AE6" s="14">
+        <v>19</v>
+      </c>
+      <c r="AF6" s="17">
         <v>1.85</v>
       </c>
-      <c r="AD6" s="17"/>
-      <c r="AE6" s="3"/>
-      <c r="AF6" s="4"/>
       <c r="AG6" s="3"/>
-      <c r="AH6" s="17"/>
-      <c r="AI6" s="17"/>
-      <c r="AJ6" s="6"/>
-      <c r="AK6" s="3"/>
-      <c r="AL6" s="7"/>
+      <c r="AH6" s="4"/>
+      <c r="AI6" s="3"/>
+      <c r="AJ6" s="17"/>
+      <c r="AK6" s="17"/>
+      <c r="AL6" s="6"/>
+      <c r="AM6" s="3"/>
+      <c r="AN6" s="3"/>
+      <c r="AO6" s="7"/>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>38</v>
       </c>
@@ -11823,7 +11876,7 @@
         <v>71</v>
       </c>
       <c r="G7" s="14">
-        <v>6</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="H7" s="17">
         <v>6.1185</v>
@@ -11842,35 +11895,44 @@
       <c r="M7" s="17"/>
       <c r="N7" s="6"/>
       <c r="O7" s="3"/>
-      <c r="P7" s="7">
+      <c r="P7" s="3">
+        <v>6.11</v>
+      </c>
+      <c r="Q7" s="7">
         <v>1.2745666666666666</v>
       </c>
-      <c r="R7" s="14">
+      <c r="S7" s="14">
+        <v>9.6</v>
+      </c>
+      <c r="T7" s="17">
         <v>6</v>
       </c>
-      <c r="S7" s="17"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="4"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="17"/>
+      <c r="U7" s="3"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="3"/>
       <c r="X7" s="17"/>
-      <c r="Y7" s="6"/>
-      <c r="Z7" s="3"/>
-      <c r="AA7" s="7"/>
-      <c r="AC7" s="14">
+      <c r="Y7" s="17"/>
+      <c r="Z7" s="6"/>
+      <c r="AA7" s="3"/>
+      <c r="AB7" s="3"/>
+      <c r="AC7" s="7"/>
+      <c r="AE7" s="14">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="AF7" s="17">
         <v>7</v>
       </c>
-      <c r="AD7" s="17"/>
-      <c r="AE7" s="3"/>
-      <c r="AF7" s="4"/>
       <c r="AG7" s="3"/>
-      <c r="AH7" s="17"/>
-      <c r="AI7" s="17"/>
-      <c r="AJ7" s="6"/>
-      <c r="AK7" s="3"/>
-      <c r="AL7" s="7"/>
+      <c r="AH7" s="4"/>
+      <c r="AI7" s="3"/>
+      <c r="AJ7" s="17"/>
+      <c r="AK7" s="17"/>
+      <c r="AL7" s="6"/>
+      <c r="AM7" s="3"/>
+      <c r="AN7" s="3"/>
+      <c r="AO7" s="7"/>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>39</v>
       </c>
@@ -11906,35 +11968,44 @@
       <c r="M8" s="17"/>
       <c r="N8" s="6"/>
       <c r="O8" s="3"/>
-      <c r="P8" s="7">
+      <c r="P8" s="3">
+        <v>13.05</v>
+      </c>
+      <c r="Q8" s="7">
         <v>1.2146874999999999</v>
       </c>
-      <c r="R8" s="14">
+      <c r="S8" s="14">
+        <v>11</v>
+      </c>
+      <c r="T8" s="17">
         <v>9.6</v>
       </c>
-      <c r="S8" s="17"/>
-      <c r="T8" s="3"/>
-      <c r="U8" s="4"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="17"/>
+      <c r="U8" s="3"/>
+      <c r="V8" s="4"/>
+      <c r="W8" s="3"/>
       <c r="X8" s="17"/>
-      <c r="Y8" s="6"/>
-      <c r="Z8" s="3"/>
-      <c r="AA8" s="7"/>
-      <c r="AC8" s="14">
+      <c r="Y8" s="17"/>
+      <c r="Z8" s="6"/>
+      <c r="AA8" s="3"/>
+      <c r="AB8" s="3"/>
+      <c r="AC8" s="7"/>
+      <c r="AE8" s="14">
+        <v>11</v>
+      </c>
+      <c r="AF8" s="17">
         <v>6.5</v>
       </c>
-      <c r="AD8" s="17"/>
-      <c r="AE8" s="3"/>
-      <c r="AF8" s="4"/>
       <c r="AG8" s="3"/>
-      <c r="AH8" s="17"/>
-      <c r="AI8" s="17"/>
-      <c r="AJ8" s="6"/>
-      <c r="AK8" s="3"/>
-      <c r="AL8" s="7"/>
+      <c r="AH8" s="4"/>
+      <c r="AI8" s="3"/>
+      <c r="AJ8" s="17"/>
+      <c r="AK8" s="17"/>
+      <c r="AL8" s="6"/>
+      <c r="AM8" s="3"/>
+      <c r="AN8" s="3"/>
+      <c r="AO8" s="7"/>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -11951,7 +12022,7 @@
         <v>2</v>
       </c>
       <c r="G9" s="14">
-        <v>8.3000000000000007</v>
+        <v>17.25</v>
       </c>
       <c r="H9" s="17">
         <v>6.83</v>
@@ -11970,35 +12041,44 @@
       <c r="M9" s="17"/>
       <c r="N9" s="6"/>
       <c r="O9" s="3"/>
-      <c r="P9" s="7">
+      <c r="P9" s="3">
+        <v>4.58</v>
+      </c>
+      <c r="Q9" s="7">
         <v>0.83599999999999997</v>
       </c>
-      <c r="R9" s="14">
+      <c r="S9" s="14">
+        <v>17.25</v>
+      </c>
+      <c r="T9" s="17">
         <v>9</v>
       </c>
-      <c r="S9" s="17"/>
-      <c r="T9" s="3"/>
-      <c r="U9" s="4"/>
-      <c r="V9" s="3"/>
-      <c r="W9" s="17"/>
+      <c r="U9" s="3"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="3"/>
       <c r="X9" s="17"/>
-      <c r="Y9" s="6"/>
-      <c r="Z9" s="3"/>
-      <c r="AA9" s="7"/>
-      <c r="AC9" s="14">
+      <c r="Y9" s="17"/>
+      <c r="Z9" s="6"/>
+      <c r="AA9" s="3"/>
+      <c r="AB9" s="3"/>
+      <c r="AC9" s="7"/>
+      <c r="AE9" s="14">
+        <v>17.25</v>
+      </c>
+      <c r="AF9" s="17">
         <v>9.25</v>
       </c>
-      <c r="AD9" s="17"/>
-      <c r="AE9" s="3"/>
-      <c r="AF9" s="4"/>
       <c r="AG9" s="3"/>
-      <c r="AH9" s="17"/>
-      <c r="AI9" s="17"/>
-      <c r="AJ9" s="6"/>
-      <c r="AK9" s="3"/>
-      <c r="AL9" s="7"/>
+      <c r="AH9" s="4"/>
+      <c r="AI9" s="3"/>
+      <c r="AJ9" s="17"/>
+      <c r="AK9" s="17"/>
+      <c r="AL9" s="6"/>
+      <c r="AM9" s="3"/>
+      <c r="AN9" s="3"/>
+      <c r="AO9" s="7"/>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>4</v>
       </c>
@@ -12015,7 +12095,7 @@
         <v>2</v>
       </c>
       <c r="G10" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H10" s="17">
         <v>2.7279200000000001</v>
@@ -12034,35 +12114,42 @@
       <c r="M10" s="17"/>
       <c r="N10" s="6"/>
       <c r="O10" s="3"/>
-      <c r="P10" s="7">
+      <c r="P10" s="3"/>
+      <c r="Q10" s="7">
         <v>1.6284562999999999</v>
       </c>
-      <c r="R10" s="14">
+      <c r="S10" s="14">
+        <v>3</v>
+      </c>
+      <c r="T10" s="17">
         <v>2.7114332000000001</v>
       </c>
-      <c r="S10" s="17"/>
-      <c r="T10" s="3"/>
-      <c r="U10" s="4"/>
-      <c r="V10" s="3"/>
-      <c r="W10" s="17"/>
+      <c r="U10" s="3"/>
+      <c r="V10" s="4"/>
+      <c r="W10" s="3"/>
       <c r="X10" s="17"/>
-      <c r="Y10" s="6"/>
-      <c r="Z10" s="3"/>
-      <c r="AA10" s="7"/>
-      <c r="AC10" s="14">
+      <c r="Y10" s="17"/>
+      <c r="Z10" s="6"/>
+      <c r="AA10" s="3"/>
+      <c r="AB10" s="3"/>
+      <c r="AC10" s="7"/>
+      <c r="AE10" s="14">
+        <v>4</v>
+      </c>
+      <c r="AF10" s="17">
         <v>4.3313845999999998</v>
       </c>
-      <c r="AD10" s="17"/>
-      <c r="AE10" s="3"/>
-      <c r="AF10" s="4"/>
       <c r="AG10" s="3"/>
-      <c r="AH10" s="17"/>
-      <c r="AI10" s="17"/>
-      <c r="AJ10" s="6"/>
-      <c r="AK10" s="3"/>
-      <c r="AL10" s="7"/>
+      <c r="AH10" s="4"/>
+      <c r="AI10" s="3"/>
+      <c r="AJ10" s="17"/>
+      <c r="AK10" s="17"/>
+      <c r="AL10" s="6"/>
+      <c r="AM10" s="3"/>
+      <c r="AN10" s="3"/>
+      <c r="AO10" s="7"/>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
@@ -12079,7 +12166,7 @@
         <v>2</v>
       </c>
       <c r="G11" s="14">
-        <v>14.3</v>
+        <v>17.166666666666668</v>
       </c>
       <c r="H11" s="17">
         <v>12.79</v>
@@ -12098,35 +12185,44 @@
       <c r="M11" s="17"/>
       <c r="N11" s="6"/>
       <c r="O11" s="3"/>
-      <c r="P11" s="7">
+      <c r="P11" s="3">
+        <v>12.79</v>
+      </c>
+      <c r="Q11" s="7">
         <v>1.8106666666666664</v>
       </c>
-      <c r="R11" s="14">
+      <c r="S11" s="14">
+        <v>17.166666666666668</v>
+      </c>
+      <c r="T11" s="17">
         <v>13.649999999999999</v>
       </c>
-      <c r="S11" s="17"/>
-      <c r="T11" s="3"/>
-      <c r="U11" s="4"/>
-      <c r="V11" s="3"/>
-      <c r="W11" s="17"/>
+      <c r="U11" s="3"/>
+      <c r="V11" s="4"/>
+      <c r="W11" s="3"/>
       <c r="X11" s="17"/>
-      <c r="Y11" s="6"/>
-      <c r="Z11" s="3"/>
-      <c r="AA11" s="7"/>
-      <c r="AC11" s="14">
+      <c r="Y11" s="17"/>
+      <c r="Z11" s="6"/>
+      <c r="AA11" s="3"/>
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="7"/>
+      <c r="AE11" s="14">
+        <v>17.166666666666668</v>
+      </c>
+      <c r="AF11" s="17">
         <v>14.3</v>
       </c>
-      <c r="AD11" s="17"/>
-      <c r="AE11" s="3"/>
-      <c r="AF11" s="4"/>
       <c r="AG11" s="3"/>
-      <c r="AH11" s="17"/>
-      <c r="AI11" s="17"/>
-      <c r="AJ11" s="6"/>
-      <c r="AK11" s="3"/>
-      <c r="AL11" s="7"/>
+      <c r="AH11" s="4"/>
+      <c r="AI11" s="3"/>
+      <c r="AJ11" s="17"/>
+      <c r="AK11" s="17"/>
+      <c r="AL11" s="6"/>
+      <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
+      <c r="AO11" s="7"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>40</v>
       </c>
@@ -12143,7 +12239,7 @@
         <v>72</v>
       </c>
       <c r="G12" s="14">
-        <v>139</v>
+        <v>113.10139199999999</v>
       </c>
       <c r="H12" s="17">
         <v>181.56917999999999</v>
@@ -12162,35 +12258,42 @@
       <c r="M12" s="17"/>
       <c r="N12" s="6"/>
       <c r="O12" s="3"/>
-      <c r="P12" s="7">
+      <c r="P12" s="3"/>
+      <c r="Q12" s="7">
         <v>3.8186813186813189</v>
       </c>
-      <c r="R12" s="14">
+      <c r="S12" s="14">
+        <v>113.10139199999999</v>
+      </c>
+      <c r="T12" s="17">
         <v>117.71541000000001</v>
       </c>
-      <c r="S12" s="17"/>
-      <c r="T12" s="3"/>
-      <c r="U12" s="4"/>
-      <c r="V12" s="3"/>
-      <c r="W12" s="17"/>
+      <c r="U12" s="3"/>
+      <c r="V12" s="4"/>
+      <c r="W12" s="3"/>
       <c r="X12" s="17"/>
-      <c r="Y12" s="6"/>
-      <c r="Z12" s="3"/>
-      <c r="AA12" s="7"/>
-      <c r="AC12" s="14">
+      <c r="Y12" s="17"/>
+      <c r="Z12" s="6"/>
+      <c r="AA12" s="3"/>
+      <c r="AB12" s="3"/>
+      <c r="AC12" s="7"/>
+      <c r="AE12" s="14">
+        <v>103.101392</v>
+      </c>
+      <c r="AF12" s="17">
         <v>117.71541000000001</v>
       </c>
-      <c r="AD12" s="17"/>
-      <c r="AE12" s="3"/>
-      <c r="AF12" s="4"/>
       <c r="AG12" s="3"/>
-      <c r="AH12" s="17"/>
-      <c r="AI12" s="17"/>
-      <c r="AJ12" s="6"/>
-      <c r="AK12" s="3"/>
-      <c r="AL12" s="7"/>
+      <c r="AH12" s="4"/>
+      <c r="AI12" s="3"/>
+      <c r="AJ12" s="17"/>
+      <c r="AK12" s="17"/>
+      <c r="AL12" s="6"/>
+      <c r="AM12" s="3"/>
+      <c r="AN12" s="3"/>
+      <c r="AO12" s="7"/>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>41</v>
       </c>
@@ -12207,7 +12310,7 @@
         <v>71</v>
       </c>
       <c r="G13" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H13" s="17">
         <v>3.7850000000000001</v>
@@ -12226,35 +12329,44 @@
       <c r="M13" s="17"/>
       <c r="N13" s="6"/>
       <c r="O13" s="3"/>
-      <c r="P13" s="7">
+      <c r="P13" s="3">
+        <v>3.78</v>
+      </c>
+      <c r="Q13" s="7">
         <v>4.9283333333333337</v>
       </c>
-      <c r="R13" s="14">
+      <c r="S13" s="14">
+        <v>9</v>
+      </c>
+      <c r="T13" s="17">
         <v>5</v>
       </c>
-      <c r="S13" s="17"/>
-      <c r="T13" s="3"/>
-      <c r="U13" s="4"/>
-      <c r="V13" s="3"/>
-      <c r="W13" s="17"/>
+      <c r="U13" s="3"/>
+      <c r="V13" s="4"/>
+      <c r="W13" s="3"/>
       <c r="X13" s="17"/>
-      <c r="Y13" s="6"/>
-      <c r="Z13" s="3"/>
-      <c r="AA13" s="7"/>
-      <c r="AC13" s="14">
+      <c r="Y13" s="17"/>
+      <c r="Z13" s="6"/>
+      <c r="AA13" s="3"/>
+      <c r="AB13" s="3"/>
+      <c r="AC13" s="7"/>
+      <c r="AE13" s="14">
+        <v>9</v>
+      </c>
+      <c r="AF13" s="17">
         <v>6</v>
       </c>
-      <c r="AD13" s="17"/>
-      <c r="AE13" s="3"/>
-      <c r="AF13" s="4"/>
       <c r="AG13" s="3"/>
-      <c r="AH13" s="17"/>
-      <c r="AI13" s="17"/>
-      <c r="AJ13" s="6"/>
-      <c r="AK13" s="3"/>
-      <c r="AL13" s="7"/>
+      <c r="AH13" s="4"/>
+      <c r="AI13" s="3"/>
+      <c r="AJ13" s="17"/>
+      <c r="AK13" s="17"/>
+      <c r="AL13" s="6"/>
+      <c r="AM13" s="3"/>
+      <c r="AN13" s="3"/>
+      <c r="AO13" s="7"/>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
@@ -12271,7 +12383,7 @@
         <v>2</v>
       </c>
       <c r="G14" s="14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H14" s="17">
         <v>0.9</v>
@@ -12290,35 +12402,44 @@
       <c r="M14" s="17"/>
       <c r="N14" s="6"/>
       <c r="O14" s="3"/>
-      <c r="P14" s="7">
+      <c r="P14" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="Q14" s="7">
         <v>0.1</v>
       </c>
-      <c r="R14" s="14">
-        <v>0</v>
-      </c>
-      <c r="S14" s="17"/>
-      <c r="T14" s="3"/>
-      <c r="U14" s="4"/>
-      <c r="V14" s="3"/>
-      <c r="W14" s="17"/>
+      <c r="S14" s="14">
+        <v>0</v>
+      </c>
+      <c r="T14" s="17">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3"/>
+      <c r="V14" s="4"/>
+      <c r="W14" s="3"/>
       <c r="X14" s="17"/>
-      <c r="Y14" s="6"/>
-      <c r="Z14" s="3"/>
-      <c r="AA14" s="7"/>
-      <c r="AC14" s="14">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="17"/>
-      <c r="AE14" s="3"/>
-      <c r="AF14" s="4"/>
+      <c r="Y14" s="17"/>
+      <c r="Z14" s="6"/>
+      <c r="AA14" s="3"/>
+      <c r="AB14" s="3"/>
+      <c r="AC14" s="7"/>
+      <c r="AE14" s="14">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="17">
+        <v>0</v>
+      </c>
       <c r="AG14" s="3"/>
-      <c r="AH14" s="17"/>
-      <c r="AI14" s="17"/>
-      <c r="AJ14" s="6"/>
-      <c r="AK14" s="3"/>
-      <c r="AL14" s="7"/>
+      <c r="AH14" s="4"/>
+      <c r="AI14" s="3"/>
+      <c r="AJ14" s="17"/>
+      <c r="AK14" s="17"/>
+      <c r="AL14" s="6"/>
+      <c r="AM14" s="3"/>
+      <c r="AN14" s="3"/>
+      <c r="AO14" s="7"/>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>23</v>
       </c>
@@ -12354,35 +12475,42 @@
       <c r="M15" s="17"/>
       <c r="N15" s="6"/>
       <c r="O15" s="3"/>
-      <c r="P15" s="7">
-        <v>0</v>
-      </c>
-      <c r="R15" s="14">
-        <v>0</v>
-      </c>
-      <c r="S15" s="17"/>
-      <c r="T15" s="3"/>
-      <c r="U15" s="4"/>
-      <c r="V15" s="3"/>
-      <c r="W15" s="17"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="7">
+        <v>0</v>
+      </c>
+      <c r="S15" s="14">
+        <v>0</v>
+      </c>
+      <c r="T15" s="17">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3"/>
+      <c r="V15" s="4"/>
+      <c r="W15" s="3"/>
       <c r="X15" s="17"/>
-      <c r="Y15" s="6"/>
-      <c r="Z15" s="3"/>
-      <c r="AA15" s="7"/>
-      <c r="AC15" s="14">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="17"/>
-      <c r="AE15" s="3"/>
-      <c r="AF15" s="4"/>
+      <c r="Y15" s="17"/>
+      <c r="Z15" s="6"/>
+      <c r="AA15" s="3"/>
+      <c r="AB15" s="3"/>
+      <c r="AC15" s="7"/>
+      <c r="AE15" s="14">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="17">
+        <v>0</v>
+      </c>
       <c r="AG15" s="3"/>
-      <c r="AH15" s="17"/>
-      <c r="AI15" s="17"/>
-      <c r="AJ15" s="6"/>
-      <c r="AK15" s="3"/>
-      <c r="AL15" s="7"/>
+      <c r="AH15" s="4"/>
+      <c r="AI15" s="3"/>
+      <c r="AJ15" s="17"/>
+      <c r="AK15" s="17"/>
+      <c r="AL15" s="6"/>
+      <c r="AM15" s="3"/>
+      <c r="AN15" s="3"/>
+      <c r="AO15" s="7"/>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>42</v>
       </c>
@@ -12418,35 +12546,42 @@
       <c r="M16" s="17"/>
       <c r="N16" s="6"/>
       <c r="O16" s="3"/>
-      <c r="P16" s="7">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="7">
         <v>2.2652816666666666</v>
       </c>
-      <c r="R16" s="14">
+      <c r="S16" s="14">
         <v>4</v>
       </c>
-      <c r="S16" s="17"/>
-      <c r="T16" s="3"/>
-      <c r="U16" s="4"/>
-      <c r="V16" s="3"/>
-      <c r="W16" s="17"/>
+      <c r="T16" s="17">
+        <v>4</v>
+      </c>
+      <c r="U16" s="3"/>
+      <c r="V16" s="4"/>
+      <c r="W16" s="3"/>
       <c r="X16" s="17"/>
-      <c r="Y16" s="6"/>
-      <c r="Z16" s="3"/>
-      <c r="AA16" s="7"/>
-      <c r="AC16" s="14">
+      <c r="Y16" s="17"/>
+      <c r="Z16" s="6"/>
+      <c r="AA16" s="3"/>
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="7"/>
+      <c r="AE16" s="14">
         <v>5</v>
       </c>
-      <c r="AD16" s="17"/>
-      <c r="AE16" s="3"/>
-      <c r="AF16" s="4"/>
+      <c r="AF16" s="17">
+        <v>5</v>
+      </c>
       <c r="AG16" s="3"/>
-      <c r="AH16" s="17"/>
-      <c r="AI16" s="17"/>
-      <c r="AJ16" s="6"/>
-      <c r="AK16" s="3"/>
-      <c r="AL16" s="7"/>
+      <c r="AH16" s="4"/>
+      <c r="AI16" s="3"/>
+      <c r="AJ16" s="17"/>
+      <c r="AK16" s="17"/>
+      <c r="AL16" s="6"/>
+      <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
+      <c r="AO16" s="7"/>
     </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>10</v>
       </c>
@@ -12463,7 +12598,7 @@
         <v>2</v>
       </c>
       <c r="G17" s="14">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="H17" s="17">
         <v>119.60778230000001</v>
@@ -12482,35 +12617,42 @@
       <c r="M17" s="17"/>
       <c r="N17" s="6"/>
       <c r="O17" s="3"/>
-      <c r="P17" s="7">
+      <c r="P17" s="3"/>
+      <c r="Q17" s="7">
         <v>1.8414534459595959</v>
       </c>
-      <c r="R17" s="14">
+      <c r="S17" s="14">
+        <v>100</v>
+      </c>
+      <c r="T17" s="17">
         <v>121</v>
       </c>
-      <c r="S17" s="17"/>
-      <c r="T17" s="3"/>
-      <c r="U17" s="4"/>
-      <c r="V17" s="3"/>
-      <c r="W17" s="17"/>
+      <c r="U17" s="3"/>
+      <c r="V17" s="4"/>
+      <c r="W17" s="3"/>
       <c r="X17" s="17"/>
-      <c r="Y17" s="6"/>
-      <c r="Z17" s="3"/>
-      <c r="AA17" s="7"/>
-      <c r="AC17" s="14">
+      <c r="Y17" s="17"/>
+      <c r="Z17" s="6"/>
+      <c r="AA17" s="3"/>
+      <c r="AB17" s="3"/>
+      <c r="AC17" s="7"/>
+      <c r="AE17" s="14">
+        <v>100</v>
+      </c>
+      <c r="AF17" s="17">
         <v>124</v>
       </c>
-      <c r="AD17" s="17"/>
-      <c r="AE17" s="3"/>
-      <c r="AF17" s="4"/>
       <c r="AG17" s="3"/>
-      <c r="AH17" s="17"/>
-      <c r="AI17" s="17"/>
-      <c r="AJ17" s="6"/>
-      <c r="AK17" s="3"/>
-      <c r="AL17" s="7"/>
+      <c r="AH17" s="4"/>
+      <c r="AI17" s="3"/>
+      <c r="AJ17" s="17"/>
+      <c r="AK17" s="17"/>
+      <c r="AL17" s="6"/>
+      <c r="AM17" s="3"/>
+      <c r="AN17" s="3"/>
+      <c r="AO17" s="7"/>
     </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -12527,7 +12669,7 @@
         <v>2</v>
       </c>
       <c r="G18" s="14">
-        <v>0.2</v>
+        <v>20</v>
       </c>
       <c r="H18" s="17">
         <v>6.1910834999999995</v>
@@ -12546,35 +12688,42 @@
       <c r="M18" s="17"/>
       <c r="N18" s="6"/>
       <c r="O18" s="3"/>
-      <c r="P18" s="7">
+      <c r="P18" s="3"/>
+      <c r="Q18" s="7">
         <v>8.4656759444444436</v>
       </c>
-      <c r="R18" s="14">
+      <c r="S18" s="14">
+        <v>20</v>
+      </c>
+      <c r="T18" s="17">
         <v>25</v>
       </c>
-      <c r="S18" s="17"/>
-      <c r="T18" s="3"/>
-      <c r="U18" s="4"/>
-      <c r="V18" s="3"/>
-      <c r="W18" s="17"/>
+      <c r="U18" s="3"/>
+      <c r="V18" s="4"/>
+      <c r="W18" s="3"/>
       <c r="X18" s="17"/>
-      <c r="Y18" s="6"/>
-      <c r="Z18" s="3"/>
-      <c r="AA18" s="7"/>
-      <c r="AC18" s="14">
+      <c r="Y18" s="17"/>
+      <c r="Z18" s="6"/>
+      <c r="AA18" s="3"/>
+      <c r="AB18" s="3"/>
+      <c r="AC18" s="7"/>
+      <c r="AE18" s="14">
+        <v>30</v>
+      </c>
+      <c r="AF18" s="17">
         <v>45</v>
       </c>
-      <c r="AD18" s="17"/>
-      <c r="AE18" s="3"/>
-      <c r="AF18" s="4"/>
       <c r="AG18" s="3"/>
-      <c r="AH18" s="17"/>
-      <c r="AI18" s="17"/>
-      <c r="AJ18" s="6"/>
-      <c r="AK18" s="3"/>
-      <c r="AL18" s="7"/>
+      <c r="AH18" s="4"/>
+      <c r="AI18" s="3"/>
+      <c r="AJ18" s="17"/>
+      <c r="AK18" s="17"/>
+      <c r="AL18" s="6"/>
+      <c r="AM18" s="3"/>
+      <c r="AN18" s="3"/>
+      <c r="AO18" s="7"/>
     </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>43</v>
       </c>
@@ -12591,7 +12740,7 @@
         <v>73</v>
       </c>
       <c r="G19" s="14">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H19" s="17">
         <v>39.987499999999997</v>
@@ -12610,35 +12759,44 @@
       <c r="M19" s="17"/>
       <c r="N19" s="6"/>
       <c r="O19" s="3"/>
-      <c r="P19" s="7">
+      <c r="P19" s="3">
+        <v>40</v>
+      </c>
+      <c r="Q19" s="7">
         <v>2.86625</v>
       </c>
-      <c r="R19" s="14">
+      <c r="S19" s="14">
+        <v>60</v>
+      </c>
+      <c r="T19" s="17">
         <v>23</v>
       </c>
-      <c r="S19" s="17"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="4"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="17"/>
+      <c r="U19" s="3"/>
+      <c r="V19" s="4"/>
+      <c r="W19" s="3"/>
       <c r="X19" s="17"/>
-      <c r="Y19" s="6"/>
-      <c r="Z19" s="3"/>
-      <c r="AA19" s="7"/>
-      <c r="AC19" s="14">
+      <c r="Y19" s="17"/>
+      <c r="Z19" s="6"/>
+      <c r="AA19" s="3"/>
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="7"/>
+      <c r="AE19" s="14">
+        <v>50</v>
+      </c>
+      <c r="AF19" s="17">
         <v>23</v>
       </c>
-      <c r="AD19" s="17"/>
-      <c r="AE19" s="3"/>
-      <c r="AF19" s="4"/>
       <c r="AG19" s="3"/>
-      <c r="AH19" s="17"/>
-      <c r="AI19" s="17"/>
-      <c r="AJ19" s="6"/>
-      <c r="AK19" s="3"/>
-      <c r="AL19" s="7"/>
+      <c r="AH19" s="4"/>
+      <c r="AI19" s="3"/>
+      <c r="AJ19" s="17"/>
+      <c r="AK19" s="17"/>
+      <c r="AL19" s="6"/>
+      <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
+      <c r="AO19" s="7"/>
     </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>11</v>
       </c>
@@ -12655,7 +12813,7 @@
         <v>2</v>
       </c>
       <c r="G20" s="14">
-        <v>7</v>
+        <v>6.703333333333334</v>
       </c>
       <c r="H20" s="17">
         <v>6.9908000000000001</v>
@@ -12674,35 +12832,44 @@
       <c r="M20" s="17"/>
       <c r="N20" s="6"/>
       <c r="O20" s="3"/>
-      <c r="P20" s="7">
+      <c r="P20" s="3">
+        <v>6.99</v>
+      </c>
+      <c r="Q20" s="7">
         <v>2.5019809523809524</v>
       </c>
-      <c r="R20" s="14">
+      <c r="S20" s="14">
+        <v>6.703333333333334</v>
+      </c>
+      <c r="T20" s="17">
         <v>12.190000000000001</v>
       </c>
-      <c r="S20" s="17"/>
-      <c r="T20" s="3"/>
-      <c r="U20" s="4"/>
-      <c r="V20" s="3"/>
-      <c r="W20" s="17"/>
+      <c r="U20" s="3"/>
+      <c r="V20" s="4"/>
+      <c r="W20" s="3"/>
       <c r="X20" s="17"/>
-      <c r="Y20" s="6"/>
-      <c r="Z20" s="3"/>
-      <c r="AA20" s="7"/>
-      <c r="AC20" s="14">
+      <c r="Y20" s="17"/>
+      <c r="Z20" s="6"/>
+      <c r="AA20" s="3"/>
+      <c r="AB20" s="3"/>
+      <c r="AC20" s="7"/>
+      <c r="AE20" s="14">
+        <v>6.703333333333334</v>
+      </c>
+      <c r="AF20" s="17">
         <v>7.09</v>
       </c>
-      <c r="AD20" s="17"/>
-      <c r="AE20" s="3"/>
-      <c r="AF20" s="4"/>
       <c r="AG20" s="3"/>
-      <c r="AH20" s="17"/>
-      <c r="AI20" s="17"/>
-      <c r="AJ20" s="6"/>
-      <c r="AK20" s="3"/>
-      <c r="AL20" s="7"/>
+      <c r="AH20" s="4"/>
+      <c r="AI20" s="3"/>
+      <c r="AJ20" s="17"/>
+      <c r="AK20" s="17"/>
+      <c r="AL20" s="6"/>
+      <c r="AM20" s="3"/>
+      <c r="AN20" s="3"/>
+      <c r="AO20" s="7"/>
     </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>12</v>
       </c>
@@ -12738,35 +12905,44 @@
       <c r="M21" s="17"/>
       <c r="N21" s="6"/>
       <c r="O21" s="3"/>
-      <c r="P21" s="7">
+      <c r="P21" s="3">
+        <v>26.27</v>
+      </c>
+      <c r="Q21" s="7">
         <v>1.0554572946859904</v>
       </c>
-      <c r="R21" s="14">
+      <c r="S21" s="14">
+        <v>30</v>
+      </c>
+      <c r="T21" s="17">
         <v>34.880000000000003</v>
       </c>
-      <c r="S21" s="17"/>
-      <c r="T21" s="3"/>
-      <c r="U21" s="4"/>
-      <c r="V21" s="3"/>
-      <c r="W21" s="17"/>
+      <c r="U21" s="3"/>
+      <c r="V21" s="4"/>
+      <c r="W21" s="3"/>
       <c r="X21" s="17"/>
-      <c r="Y21" s="6"/>
-      <c r="Z21" s="3"/>
-      <c r="AA21" s="7"/>
-      <c r="AC21" s="14">
+      <c r="Y21" s="17"/>
+      <c r="Z21" s="6"/>
+      <c r="AA21" s="3"/>
+      <c r="AB21" s="3"/>
+      <c r="AC21" s="7"/>
+      <c r="AE21" s="14">
+        <v>30</v>
+      </c>
+      <c r="AF21" s="17">
         <v>48.080000000000005</v>
       </c>
-      <c r="AD21" s="17"/>
-      <c r="AE21" s="3"/>
-      <c r="AF21" s="4"/>
       <c r="AG21" s="3"/>
-      <c r="AH21" s="17"/>
-      <c r="AI21" s="17"/>
-      <c r="AJ21" s="6"/>
-      <c r="AK21" s="3"/>
-      <c r="AL21" s="7"/>
+      <c r="AH21" s="4"/>
+      <c r="AI21" s="3"/>
+      <c r="AJ21" s="17"/>
+      <c r="AK21" s="17"/>
+      <c r="AL21" s="6"/>
+      <c r="AM21" s="3"/>
+      <c r="AN21" s="3"/>
+      <c r="AO21" s="7"/>
     </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>22</v>
       </c>
@@ -12783,7 +12959,7 @@
         <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H22" s="17">
         <v>0.1</v>
@@ -12802,35 +12978,45 @@
       <c r="M22" s="17"/>
       <c r="N22" s="6"/>
       <c r="O22" s="3"/>
-      <c r="P22" s="7">
-        <v>0</v>
-      </c>
-      <c r="R22" s="14">
+      <c r="P22" s="3">
+        <f>10000/100000</f>
+        <v>0.1</v>
+      </c>
+      <c r="Q22" s="7">
+        <v>0</v>
+      </c>
+      <c r="S22" s="14">
+        <v>5</v>
+      </c>
+      <c r="T22" s="17">
         <v>2.4849999999999999</v>
       </c>
-      <c r="S22" s="17"/>
-      <c r="T22" s="3"/>
-      <c r="U22" s="4"/>
-      <c r="V22" s="3"/>
-      <c r="W22" s="17"/>
+      <c r="U22" s="3"/>
+      <c r="V22" s="4"/>
+      <c r="W22" s="3"/>
       <c r="X22" s="17"/>
-      <c r="Y22" s="6"/>
-      <c r="Z22" s="3"/>
-      <c r="AA22" s="7"/>
-      <c r="AC22" s="14">
+      <c r="Y22" s="17"/>
+      <c r="Z22" s="6"/>
+      <c r="AA22" s="3"/>
+      <c r="AB22" s="3"/>
+      <c r="AC22" s="7"/>
+      <c r="AE22" s="14">
+        <v>5</v>
+      </c>
+      <c r="AF22" s="17">
         <v>2.16</v>
       </c>
-      <c r="AD22" s="17"/>
-      <c r="AE22" s="3"/>
-      <c r="AF22" s="4"/>
       <c r="AG22" s="3"/>
-      <c r="AH22" s="17"/>
-      <c r="AI22" s="17"/>
-      <c r="AJ22" s="6"/>
-      <c r="AK22" s="3"/>
-      <c r="AL22" s="7"/>
+      <c r="AH22" s="4"/>
+      <c r="AI22" s="3"/>
+      <c r="AJ22" s="17"/>
+      <c r="AK22" s="17"/>
+      <c r="AL22" s="6"/>
+      <c r="AM22" s="3"/>
+      <c r="AN22" s="3"/>
+      <c r="AO22" s="7"/>
     </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>44</v>
       </c>
@@ -12847,7 +13033,7 @@
         <v>71</v>
       </c>
       <c r="G23" s="14">
-        <v>1.2</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="H23" s="17">
         <v>0.68445</v>
@@ -12866,35 +13052,44 @@
       <c r="M23" s="17"/>
       <c r="N23" s="6"/>
       <c r="O23" s="3"/>
-      <c r="P23" s="7">
+      <c r="P23" s="3">
+        <v>0.68</v>
+      </c>
+      <c r="Q23" s="7">
         <v>0.8948166666666667</v>
       </c>
-      <c r="R23" s="14">
+      <c r="S23" s="14">
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="T23" s="17">
         <v>1</v>
       </c>
-      <c r="S23" s="17"/>
-      <c r="T23" s="3"/>
-      <c r="U23" s="4"/>
-      <c r="V23" s="3"/>
-      <c r="W23" s="17"/>
+      <c r="U23" s="3"/>
+      <c r="V23" s="4"/>
+      <c r="W23" s="3"/>
       <c r="X23" s="17"/>
-      <c r="Y23" s="6"/>
-      <c r="Z23" s="3"/>
-      <c r="AA23" s="7"/>
-      <c r="AC23" s="14">
+      <c r="Y23" s="17"/>
+      <c r="Z23" s="6"/>
+      <c r="AA23" s="3"/>
+      <c r="AB23" s="3"/>
+      <c r="AC23" s="7"/>
+      <c r="AE23" s="14">
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="AF23" s="17">
         <v>1</v>
       </c>
-      <c r="AD23" s="17"/>
-      <c r="AE23" s="3"/>
-      <c r="AF23" s="4"/>
       <c r="AG23" s="3"/>
-      <c r="AH23" s="17"/>
-      <c r="AI23" s="17"/>
-      <c r="AJ23" s="6"/>
-      <c r="AK23" s="3"/>
-      <c r="AL23" s="7"/>
+      <c r="AH23" s="4"/>
+      <c r="AI23" s="3"/>
+      <c r="AJ23" s="17"/>
+      <c r="AK23" s="17"/>
+      <c r="AL23" s="6"/>
+      <c r="AM23" s="3"/>
+      <c r="AN23" s="3"/>
+      <c r="AO23" s="7"/>
     </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>45</v>
       </c>
@@ -12911,7 +13106,7 @@
         <v>95</v>
       </c>
       <c r="G24" s="14">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="H24" s="17">
         <v>1.6505700000000001</v>
@@ -12930,35 +13125,42 @@
       <c r="M24" s="17"/>
       <c r="N24" s="6"/>
       <c r="O24" s="3"/>
-      <c r="P24" s="7">
+      <c r="P24" s="3"/>
+      <c r="Q24" s="7">
         <v>1.3667279569892472</v>
       </c>
-      <c r="R24" s="14">
+      <c r="S24" s="14">
+        <v>11</v>
+      </c>
+      <c r="T24" s="17">
         <v>2.8</v>
       </c>
-      <c r="S24" s="17"/>
-      <c r="T24" s="3"/>
-      <c r="U24" s="4"/>
-      <c r="V24" s="3"/>
-      <c r="W24" s="17"/>
+      <c r="U24" s="3"/>
+      <c r="V24" s="4"/>
+      <c r="W24" s="3"/>
       <c r="X24" s="17"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="3"/>
-      <c r="AA24" s="7"/>
-      <c r="AC24" s="14">
+      <c r="Y24" s="17"/>
+      <c r="Z24" s="6"/>
+      <c r="AA24" s="3"/>
+      <c r="AB24" s="3"/>
+      <c r="AC24" s="7"/>
+      <c r="AE24" s="14">
+        <v>11</v>
+      </c>
+      <c r="AF24" s="17">
         <v>8.26</v>
       </c>
-      <c r="AD24" s="17"/>
-      <c r="AE24" s="3"/>
-      <c r="AF24" s="4"/>
       <c r="AG24" s="3"/>
-      <c r="AH24" s="17"/>
-      <c r="AI24" s="17"/>
-      <c r="AJ24" s="6"/>
-      <c r="AK24" s="3"/>
-      <c r="AL24" s="7"/>
+      <c r="AH24" s="4"/>
+      <c r="AI24" s="3"/>
+      <c r="AJ24" s="17"/>
+      <c r="AK24" s="17"/>
+      <c r="AL24" s="6"/>
+      <c r="AM24" s="3"/>
+      <c r="AN24" s="3"/>
+      <c r="AO24" s="7"/>
     </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>3</v>
       </c>
@@ -12994,35 +13196,42 @@
       <c r="M25" s="17"/>
       <c r="N25" s="6"/>
       <c r="O25" s="3"/>
-      <c r="P25" s="7">
+      <c r="P25" s="3"/>
+      <c r="Q25" s="7">
         <v>2.4596416666666667</v>
       </c>
-      <c r="R25" s="14">
+      <c r="S25" s="14">
+        <v>7</v>
+      </c>
+      <c r="T25" s="17">
         <v>9.8000000000000007</v>
       </c>
-      <c r="S25" s="17"/>
-      <c r="T25" s="3"/>
-      <c r="U25" s="4"/>
-      <c r="V25" s="3"/>
-      <c r="W25" s="17"/>
+      <c r="U25" s="3"/>
+      <c r="V25" s="4"/>
+      <c r="W25" s="3"/>
       <c r="X25" s="17"/>
-      <c r="Y25" s="6"/>
-      <c r="Z25" s="3"/>
-      <c r="AA25" s="7"/>
-      <c r="AC25" s="14">
+      <c r="Y25" s="17"/>
+      <c r="Z25" s="6"/>
+      <c r="AA25" s="3"/>
+      <c r="AB25" s="3"/>
+      <c r="AC25" s="7"/>
+      <c r="AE25" s="14">
+        <v>7</v>
+      </c>
+      <c r="AF25" s="17">
         <v>9.6999999999999993</v>
       </c>
-      <c r="AD25" s="17"/>
-      <c r="AE25" s="3"/>
-      <c r="AF25" s="4"/>
       <c r="AG25" s="3"/>
-      <c r="AH25" s="17"/>
-      <c r="AI25" s="17"/>
-      <c r="AJ25" s="6"/>
-      <c r="AK25" s="3"/>
-      <c r="AL25" s="7"/>
+      <c r="AH25" s="4"/>
+      <c r="AI25" s="3"/>
+      <c r="AJ25" s="17"/>
+      <c r="AK25" s="17"/>
+      <c r="AL25" s="6"/>
+      <c r="AM25" s="3"/>
+      <c r="AN25" s="3"/>
+      <c r="AO25" s="7"/>
     </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>46</v>
       </c>
@@ -13058,35 +13267,44 @@
       <c r="M26" s="17"/>
       <c r="N26" s="6"/>
       <c r="O26" s="3"/>
-      <c r="P26" s="7">
+      <c r="P26" s="3">
+        <v>24.22</v>
+      </c>
+      <c r="Q26" s="7">
         <v>0.94555843137254891</v>
       </c>
-      <c r="R26" s="14">
+      <c r="S26" s="14">
+        <v>16</v>
+      </c>
+      <c r="T26" s="17">
         <v>12</v>
       </c>
-      <c r="S26" s="17"/>
-      <c r="T26" s="3"/>
-      <c r="U26" s="4"/>
-      <c r="V26" s="3"/>
-      <c r="W26" s="17"/>
+      <c r="U26" s="3"/>
+      <c r="V26" s="4"/>
+      <c r="W26" s="3"/>
       <c r="X26" s="17"/>
-      <c r="Y26" s="6"/>
-      <c r="Z26" s="3"/>
-      <c r="AA26" s="7"/>
-      <c r="AC26" s="14">
+      <c r="Y26" s="17"/>
+      <c r="Z26" s="6"/>
+      <c r="AA26" s="3"/>
+      <c r="AB26" s="3"/>
+      <c r="AC26" s="7"/>
+      <c r="AE26" s="14">
+        <v>16</v>
+      </c>
+      <c r="AF26" s="17">
         <v>12</v>
       </c>
-      <c r="AD26" s="17"/>
-      <c r="AE26" s="3"/>
-      <c r="AF26" s="4"/>
       <c r="AG26" s="3"/>
-      <c r="AH26" s="17"/>
-      <c r="AI26" s="17"/>
-      <c r="AJ26" s="6"/>
-      <c r="AK26" s="3"/>
-      <c r="AL26" s="7"/>
+      <c r="AH26" s="4"/>
+      <c r="AI26" s="3"/>
+      <c r="AJ26" s="17"/>
+      <c r="AK26" s="17"/>
+      <c r="AL26" s="6"/>
+      <c r="AM26" s="3"/>
+      <c r="AN26" s="3"/>
+      <c r="AO26" s="7"/>
     </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>63</v>
       </c>
@@ -13122,35 +13340,42 @@
       <c r="M27" s="17"/>
       <c r="N27" s="6"/>
       <c r="O27" s="3"/>
-      <c r="P27" s="7">
-        <v>0</v>
-      </c>
-      <c r="R27" s="14">
-        <v>0</v>
-      </c>
-      <c r="S27" s="17"/>
-      <c r="T27" s="3"/>
-      <c r="U27" s="4"/>
-      <c r="V27" s="3"/>
-      <c r="W27" s="17"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="7">
+        <v>0</v>
+      </c>
+      <c r="S27" s="14">
+        <v>15</v>
+      </c>
+      <c r="T27" s="17">
+        <v>0</v>
+      </c>
+      <c r="U27" s="3"/>
+      <c r="V27" s="4"/>
+      <c r="W27" s="3"/>
       <c r="X27" s="17"/>
-      <c r="Y27" s="6"/>
-      <c r="Z27" s="3"/>
-      <c r="AA27" s="7"/>
-      <c r="AC27" s="14">
-        <v>0</v>
-      </c>
-      <c r="AD27" s="17"/>
-      <c r="AE27" s="3"/>
-      <c r="AF27" s="4"/>
+      <c r="Y27" s="17"/>
+      <c r="Z27" s="6"/>
+      <c r="AA27" s="3"/>
+      <c r="AB27" s="3"/>
+      <c r="AC27" s="7"/>
+      <c r="AE27" s="14">
+        <v>3</v>
+      </c>
+      <c r="AF27" s="17">
+        <v>0</v>
+      </c>
       <c r="AG27" s="3"/>
-      <c r="AH27" s="17"/>
-      <c r="AI27" s="17"/>
-      <c r="AJ27" s="6"/>
-      <c r="AK27" s="3"/>
-      <c r="AL27" s="7"/>
+      <c r="AH27" s="4"/>
+      <c r="AI27" s="3"/>
+      <c r="AJ27" s="17"/>
+      <c r="AK27" s="17"/>
+      <c r="AL27" s="6"/>
+      <c r="AM27" s="3"/>
+      <c r="AN27" s="3"/>
+      <c r="AO27" s="7"/>
     </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>47</v>
       </c>
@@ -13167,7 +13392,7 @@
         <v>95</v>
       </c>
       <c r="G28" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H28" s="17">
         <v>10.29</v>
@@ -13186,35 +13411,42 @@
       <c r="M28" s="17"/>
       <c r="N28" s="6"/>
       <c r="O28" s="3"/>
-      <c r="P28" s="7">
+      <c r="P28" s="3"/>
+      <c r="Q28" s="7">
         <v>0.98200589970501451</v>
       </c>
-      <c r="R28" s="14">
+      <c r="S28" s="14">
+        <v>9</v>
+      </c>
+      <c r="T28" s="17">
         <v>14.4</v>
       </c>
-      <c r="S28" s="17"/>
-      <c r="T28" s="3"/>
-      <c r="U28" s="4"/>
-      <c r="V28" s="3"/>
-      <c r="W28" s="17"/>
+      <c r="U28" s="3"/>
+      <c r="V28" s="4"/>
+      <c r="W28" s="3"/>
       <c r="X28" s="17"/>
-      <c r="Y28" s="6"/>
-      <c r="Z28" s="3"/>
-      <c r="AA28" s="7"/>
-      <c r="AC28" s="14">
+      <c r="Y28" s="17"/>
+      <c r="Z28" s="6"/>
+      <c r="AA28" s="3"/>
+      <c r="AB28" s="3"/>
+      <c r="AC28" s="7"/>
+      <c r="AE28" s="14">
+        <v>12</v>
+      </c>
+      <c r="AF28" s="17">
         <v>8.6</v>
       </c>
-      <c r="AD28" s="17"/>
-      <c r="AE28" s="3"/>
-      <c r="AF28" s="4"/>
       <c r="AG28" s="3"/>
-      <c r="AH28" s="17"/>
-      <c r="AI28" s="17"/>
-      <c r="AJ28" s="6"/>
-      <c r="AK28" s="3"/>
-      <c r="AL28" s="7"/>
+      <c r="AH28" s="4"/>
+      <c r="AI28" s="3"/>
+      <c r="AJ28" s="17"/>
+      <c r="AK28" s="17"/>
+      <c r="AL28" s="6"/>
+      <c r="AM28" s="3"/>
+      <c r="AN28" s="3"/>
+      <c r="AO28" s="7"/>
     </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>5</v>
       </c>
@@ -13231,7 +13463,7 @@
         <v>2</v>
       </c>
       <c r="G29" s="14">
-        <v>7.1</v>
+        <v>4</v>
       </c>
       <c r="H29" s="17">
         <v>5.4947099999999995</v>
@@ -13250,35 +13482,44 @@
       <c r="M29" s="17"/>
       <c r="N29" s="6"/>
       <c r="O29" s="3"/>
-      <c r="P29" s="7">
+      <c r="P29" s="3">
+        <v>5.49</v>
+      </c>
+      <c r="Q29" s="7">
         <v>1.0472616666666665</v>
       </c>
-      <c r="R29" s="14">
+      <c r="S29" s="14">
+        <v>4</v>
+      </c>
+      <c r="T29" s="17">
         <v>6.48</v>
       </c>
-      <c r="S29" s="17"/>
-      <c r="T29" s="3"/>
-      <c r="U29" s="4"/>
-      <c r="V29" s="3"/>
-      <c r="W29" s="17"/>
+      <c r="U29" s="3"/>
+      <c r="V29" s="4"/>
+      <c r="W29" s="3"/>
       <c r="X29" s="17"/>
-      <c r="Y29" s="6"/>
-      <c r="Z29" s="3"/>
-      <c r="AA29" s="7"/>
-      <c r="AC29" s="14">
+      <c r="Y29" s="17"/>
+      <c r="Z29" s="6"/>
+      <c r="AA29" s="3"/>
+      <c r="AB29" s="3"/>
+      <c r="AC29" s="7"/>
+      <c r="AE29" s="14">
+        <v>4</v>
+      </c>
+      <c r="AF29" s="17">
         <v>6.8759999999999994</v>
       </c>
-      <c r="AD29" s="17"/>
-      <c r="AE29" s="3"/>
-      <c r="AF29" s="4"/>
       <c r="AG29" s="3"/>
-      <c r="AH29" s="17"/>
-      <c r="AI29" s="17"/>
-      <c r="AJ29" s="6"/>
-      <c r="AK29" s="3"/>
-      <c r="AL29" s="7"/>
+      <c r="AH29" s="4"/>
+      <c r="AI29" s="3"/>
+      <c r="AJ29" s="17"/>
+      <c r="AK29" s="17"/>
+      <c r="AL29" s="6"/>
+      <c r="AM29" s="3"/>
+      <c r="AN29" s="3"/>
+      <c r="AO29" s="7"/>
     </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>21</v>
       </c>
@@ -13314,35 +13555,42 @@
       <c r="M30" s="17"/>
       <c r="N30" s="6"/>
       <c r="O30" s="3"/>
-      <c r="P30" s="7">
-        <v>0</v>
-      </c>
-      <c r="R30" s="14">
-        <v>0</v>
-      </c>
-      <c r="S30" s="17"/>
-      <c r="T30" s="3"/>
-      <c r="U30" s="4"/>
-      <c r="V30" s="3"/>
-      <c r="W30" s="17"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="7">
+        <v>0</v>
+      </c>
+      <c r="S30" s="14">
+        <v>0</v>
+      </c>
+      <c r="T30" s="17">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3"/>
+      <c r="V30" s="4"/>
+      <c r="W30" s="3"/>
       <c r="X30" s="17"/>
-      <c r="Y30" s="6"/>
-      <c r="Z30" s="3"/>
-      <c r="AA30" s="7"/>
-      <c r="AC30" s="14">
+      <c r="Y30" s="17"/>
+      <c r="Z30" s="6"/>
+      <c r="AA30" s="3"/>
+      <c r="AB30" s="3"/>
+      <c r="AC30" s="7"/>
+      <c r="AE30" s="14">
+        <v>3</v>
+      </c>
+      <c r="AF30" s="17">
         <v>1.8</v>
       </c>
-      <c r="AD30" s="17"/>
-      <c r="AE30" s="3"/>
-      <c r="AF30" s="4"/>
       <c r="AG30" s="3"/>
-      <c r="AH30" s="17"/>
-      <c r="AI30" s="17"/>
-      <c r="AJ30" s="6"/>
-      <c r="AK30" s="3"/>
-      <c r="AL30" s="7"/>
+      <c r="AH30" s="4"/>
+      <c r="AI30" s="3"/>
+      <c r="AJ30" s="17"/>
+      <c r="AK30" s="17"/>
+      <c r="AL30" s="6"/>
+      <c r="AM30" s="3"/>
+      <c r="AN30" s="3"/>
+      <c r="AO30" s="7"/>
     </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>48</v>
       </c>
@@ -13359,7 +13607,7 @@
         <v>95</v>
       </c>
       <c r="G31" s="14">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H31" s="17">
         <v>26.5</v>
@@ -13378,35 +13626,44 @@
       <c r="M31" s="17"/>
       <c r="N31" s="6"/>
       <c r="O31" s="3"/>
-      <c r="P31" s="7">
+      <c r="P31" s="3">
+        <v>26.5</v>
+      </c>
+      <c r="Q31" s="7">
         <v>0.97046413502109707</v>
       </c>
-      <c r="R31" s="14">
+      <c r="S31" s="14">
+        <v>35</v>
+      </c>
+      <c r="T31" s="17">
         <v>28.8</v>
       </c>
-      <c r="S31" s="17"/>
-      <c r="T31" s="3"/>
-      <c r="U31" s="4"/>
-      <c r="V31" s="3"/>
-      <c r="W31" s="17"/>
+      <c r="U31" s="3"/>
+      <c r="V31" s="4"/>
+      <c r="W31" s="3"/>
       <c r="X31" s="17"/>
-      <c r="Y31" s="6"/>
-      <c r="Z31" s="3"/>
-      <c r="AA31" s="7"/>
-      <c r="AC31" s="14">
+      <c r="Y31" s="17"/>
+      <c r="Z31" s="6"/>
+      <c r="AA31" s="3"/>
+      <c r="AB31" s="3"/>
+      <c r="AC31" s="7"/>
+      <c r="AE31" s="14">
+        <v>30</v>
+      </c>
+      <c r="AF31" s="17">
         <v>13.7</v>
       </c>
-      <c r="AD31" s="17"/>
-      <c r="AE31" s="3"/>
-      <c r="AF31" s="4"/>
       <c r="AG31" s="3"/>
-      <c r="AH31" s="17"/>
-      <c r="AI31" s="17"/>
-      <c r="AJ31" s="6"/>
-      <c r="AK31" s="3"/>
-      <c r="AL31" s="7"/>
+      <c r="AH31" s="4"/>
+      <c r="AI31" s="3"/>
+      <c r="AJ31" s="17"/>
+      <c r="AK31" s="17"/>
+      <c r="AL31" s="6"/>
+      <c r="AM31" s="3"/>
+      <c r="AN31" s="3"/>
+      <c r="AO31" s="7"/>
     </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>14</v>
       </c>
@@ -13423,7 +13680,7 @@
         <v>2</v>
       </c>
       <c r="G32" s="14">
-        <v>20.8</v>
+        <v>20.91</v>
       </c>
       <c r="H32" s="17">
         <v>30.8</v>
@@ -13442,35 +13699,44 @@
       <c r="M32" s="17"/>
       <c r="N32" s="6"/>
       <c r="O32" s="3"/>
-      <c r="P32" s="7">
+      <c r="P32" s="3">
+        <v>30.8</v>
+      </c>
+      <c r="Q32" s="7">
         <v>2.1102564102564103</v>
       </c>
-      <c r="R32" s="14">
+      <c r="S32" s="14">
+        <v>20.91</v>
+      </c>
+      <c r="T32" s="17">
         <v>28.75</v>
       </c>
-      <c r="S32" s="17"/>
-      <c r="T32" s="3"/>
-      <c r="U32" s="4"/>
-      <c r="V32" s="3"/>
-      <c r="W32" s="17"/>
+      <c r="U32" s="3"/>
+      <c r="V32" s="4"/>
+      <c r="W32" s="3"/>
       <c r="X32" s="17"/>
-      <c r="Y32" s="6"/>
-      <c r="Z32" s="3"/>
-      <c r="AA32" s="7"/>
-      <c r="AC32" s="14">
+      <c r="Y32" s="17"/>
+      <c r="Z32" s="6"/>
+      <c r="AA32" s="3"/>
+      <c r="AB32" s="3"/>
+      <c r="AC32" s="7"/>
+      <c r="AE32" s="14">
+        <v>20.91</v>
+      </c>
+      <c r="AF32" s="17">
         <v>22.75</v>
       </c>
-      <c r="AD32" s="17"/>
-      <c r="AE32" s="3"/>
-      <c r="AF32" s="4"/>
       <c r="AG32" s="3"/>
-      <c r="AH32" s="17"/>
-      <c r="AI32" s="17"/>
-      <c r="AJ32" s="6"/>
-      <c r="AK32" s="3"/>
-      <c r="AL32" s="7"/>
+      <c r="AH32" s="4"/>
+      <c r="AI32" s="3"/>
+      <c r="AJ32" s="17"/>
+      <c r="AK32" s="17"/>
+      <c r="AL32" s="6"/>
+      <c r="AM32" s="3"/>
+      <c r="AN32" s="3"/>
+      <c r="AO32" s="7"/>
     </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>15</v>
       </c>
@@ -13487,7 +13753,7 @@
         <v>2</v>
       </c>
       <c r="G33" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" s="17">
         <v>0</v>
@@ -13506,35 +13772,42 @@
       <c r="M33" s="17"/>
       <c r="N33" s="6"/>
       <c r="O33" s="3"/>
-      <c r="P33" s="7">
-        <v>0</v>
-      </c>
-      <c r="R33" s="14">
-        <v>0</v>
-      </c>
-      <c r="S33" s="17"/>
-      <c r="T33" s="3"/>
-      <c r="U33" s="4"/>
-      <c r="V33" s="3"/>
-      <c r="W33" s="17"/>
+      <c r="P33" s="3"/>
+      <c r="Q33" s="7">
+        <v>0</v>
+      </c>
+      <c r="S33" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="T33" s="17">
+        <v>0</v>
+      </c>
+      <c r="U33" s="3"/>
+      <c r="V33" s="4"/>
+      <c r="W33" s="3"/>
       <c r="X33" s="17"/>
-      <c r="Y33" s="6"/>
-      <c r="Z33" s="3"/>
-      <c r="AA33" s="7"/>
-      <c r="AC33" s="14">
-        <v>0</v>
-      </c>
-      <c r="AD33" s="17"/>
-      <c r="AE33" s="3"/>
-      <c r="AF33" s="4"/>
+      <c r="Y33" s="17"/>
+      <c r="Z33" s="6"/>
+      <c r="AA33" s="3"/>
+      <c r="AB33" s="3"/>
+      <c r="AC33" s="7"/>
+      <c r="AE33" s="14">
+        <v>1</v>
+      </c>
+      <c r="AF33" s="17">
+        <v>0</v>
+      </c>
       <c r="AG33" s="3"/>
-      <c r="AH33" s="17"/>
-      <c r="AI33" s="17"/>
-      <c r="AJ33" s="6"/>
-      <c r="AK33" s="3"/>
-      <c r="AL33" s="7"/>
+      <c r="AH33" s="4"/>
+      <c r="AI33" s="3"/>
+      <c r="AJ33" s="17"/>
+      <c r="AK33" s="17"/>
+      <c r="AL33" s="6"/>
+      <c r="AM33" s="3"/>
+      <c r="AN33" s="3"/>
+      <c r="AO33" s="7"/>
     </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>16</v>
       </c>
@@ -13570,35 +13843,42 @@
       <c r="M34" s="17"/>
       <c r="N34" s="6"/>
       <c r="O34" s="3"/>
-      <c r="P34" s="7">
-        <v>0</v>
-      </c>
-      <c r="R34" s="14">
-        <v>0</v>
-      </c>
-      <c r="S34" s="17"/>
-      <c r="T34" s="3"/>
-      <c r="U34" s="4"/>
-      <c r="V34" s="3"/>
-      <c r="W34" s="17"/>
+      <c r="P34" s="3"/>
+      <c r="Q34" s="7">
+        <v>0</v>
+      </c>
+      <c r="S34" s="14">
+        <v>0</v>
+      </c>
+      <c r="T34" s="17">
+        <v>0</v>
+      </c>
+      <c r="U34" s="3"/>
+      <c r="V34" s="4"/>
+      <c r="W34" s="3"/>
       <c r="X34" s="17"/>
-      <c r="Y34" s="6"/>
-      <c r="Z34" s="3"/>
-      <c r="AA34" s="7"/>
-      <c r="AC34" s="14">
-        <v>0</v>
-      </c>
-      <c r="AD34" s="17"/>
-      <c r="AE34" s="3"/>
-      <c r="AF34" s="4"/>
+      <c r="Y34" s="17"/>
+      <c r="Z34" s="6"/>
+      <c r="AA34" s="3"/>
+      <c r="AB34" s="3"/>
+      <c r="AC34" s="7"/>
+      <c r="AE34" s="14">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="17">
+        <v>0</v>
+      </c>
       <c r="AG34" s="3"/>
-      <c r="AH34" s="17"/>
-      <c r="AI34" s="17"/>
-      <c r="AJ34" s="6"/>
-      <c r="AK34" s="3"/>
-      <c r="AL34" s="7"/>
+      <c r="AH34" s="4"/>
+      <c r="AI34" s="3"/>
+      <c r="AJ34" s="17"/>
+      <c r="AK34" s="17"/>
+      <c r="AL34" s="6"/>
+      <c r="AM34" s="3"/>
+      <c r="AN34" s="3"/>
+      <c r="AO34" s="7"/>
     </row>
-    <row r="35" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>49</v>
       </c>
@@ -13615,7 +13895,7 @@
         <v>2</v>
       </c>
       <c r="G35" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H35" s="17">
         <v>3.81</v>
@@ -13634,35 +13914,42 @@
       <c r="M35" s="17"/>
       <c r="N35" s="6"/>
       <c r="O35" s="3"/>
-      <c r="P35" s="7">
+      <c r="P35" s="3"/>
+      <c r="Q35" s="7">
         <v>1.2174603174603174</v>
       </c>
-      <c r="R35" s="14">
+      <c r="S35" s="14">
+        <v>2.6</v>
+      </c>
+      <c r="T35" s="17">
         <v>2.7</v>
       </c>
-      <c r="S35" s="17"/>
-      <c r="T35" s="3"/>
-      <c r="U35" s="4"/>
-      <c r="V35" s="3"/>
-      <c r="W35" s="17"/>
+      <c r="U35" s="3"/>
+      <c r="V35" s="4"/>
+      <c r="W35" s="3"/>
       <c r="X35" s="17"/>
-      <c r="Y35" s="6"/>
-      <c r="Z35" s="3"/>
-      <c r="AA35" s="7"/>
-      <c r="AC35" s="14">
+      <c r="Y35" s="17"/>
+      <c r="Z35" s="6"/>
+      <c r="AA35" s="3"/>
+      <c r="AB35" s="3"/>
+      <c r="AC35" s="7"/>
+      <c r="AE35" s="14">
+        <v>3</v>
+      </c>
+      <c r="AF35" s="17">
         <v>1.1599999999999999</v>
       </c>
-      <c r="AD35" s="17"/>
-      <c r="AE35" s="3"/>
-      <c r="AF35" s="4"/>
       <c r="AG35" s="3"/>
-      <c r="AH35" s="17"/>
-      <c r="AI35" s="17"/>
-      <c r="AJ35" s="6"/>
-      <c r="AK35" s="3"/>
-      <c r="AL35" s="7"/>
+      <c r="AH35" s="4"/>
+      <c r="AI35" s="3"/>
+      <c r="AJ35" s="17"/>
+      <c r="AK35" s="17"/>
+      <c r="AL35" s="6"/>
+      <c r="AM35" s="3"/>
+      <c r="AN35" s="3"/>
+      <c r="AO35" s="7"/>
     </row>
-    <row r="36" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
         <v>17</v>
       </c>
@@ -13679,7 +13966,7 @@
         <v>2</v>
       </c>
       <c r="G36" s="14">
-        <v>8</v>
+        <v>7.87</v>
       </c>
       <c r="H36" s="17">
         <v>3.6067749999999998</v>
@@ -13698,35 +13985,44 @@
       <c r="M36" s="17"/>
       <c r="N36" s="6"/>
       <c r="O36" s="3"/>
-      <c r="P36" s="7">
+      <c r="P36" s="3">
+        <v>3.6</v>
+      </c>
+      <c r="Q36" s="7">
         <v>1.6388979166666668</v>
       </c>
-      <c r="R36" s="14">
+      <c r="S36" s="14">
+        <v>7.87</v>
+      </c>
+      <c r="T36" s="17">
         <v>8.3000000000000007</v>
       </c>
-      <c r="S36" s="17"/>
-      <c r="T36" s="3"/>
-      <c r="U36" s="4"/>
-      <c r="V36" s="3"/>
-      <c r="W36" s="17"/>
+      <c r="U36" s="3"/>
+      <c r="V36" s="4"/>
+      <c r="W36" s="3"/>
       <c r="X36" s="17"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="3"/>
-      <c r="AA36" s="7"/>
-      <c r="AC36" s="14">
+      <c r="Y36" s="17"/>
+      <c r="Z36" s="6"/>
+      <c r="AA36" s="3"/>
+      <c r="AB36" s="3"/>
+      <c r="AC36" s="7"/>
+      <c r="AE36" s="14">
+        <v>7.87</v>
+      </c>
+      <c r="AF36" s="17">
         <v>7.76</v>
       </c>
-      <c r="AD36" s="17"/>
-      <c r="AE36" s="3"/>
-      <c r="AF36" s="4"/>
       <c r="AG36" s="3"/>
-      <c r="AH36" s="17"/>
-      <c r="AI36" s="17"/>
-      <c r="AJ36" s="6"/>
-      <c r="AK36" s="3"/>
-      <c r="AL36" s="7"/>
+      <c r="AH36" s="4"/>
+      <c r="AI36" s="3"/>
+      <c r="AJ36" s="17"/>
+      <c r="AK36" s="17"/>
+      <c r="AL36" s="6"/>
+      <c r="AM36" s="3"/>
+      <c r="AN36" s="3"/>
+      <c r="AO36" s="7"/>
     </row>
-    <row r="37" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>18</v>
       </c>
@@ -13743,7 +14039,7 @@
         <v>2</v>
       </c>
       <c r="G37" s="14">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="H37" s="17">
         <v>37.19</v>
@@ -13762,35 +14058,44 @@
       <c r="M37" s="17"/>
       <c r="N37" s="6"/>
       <c r="O37" s="3"/>
-      <c r="P37" s="7">
+      <c r="P37" s="3">
+        <v>37.19</v>
+      </c>
+      <c r="Q37" s="7">
         <v>1.6331372549019607</v>
       </c>
-      <c r="R37" s="14">
+      <c r="S37" s="14">
+        <v>36</v>
+      </c>
+      <c r="T37" s="17">
         <v>24.3</v>
       </c>
-      <c r="S37" s="17"/>
-      <c r="T37" s="3"/>
-      <c r="U37" s="4"/>
-      <c r="V37" s="3"/>
-      <c r="W37" s="17"/>
+      <c r="U37" s="3"/>
+      <c r="V37" s="4"/>
+      <c r="W37" s="3"/>
       <c r="X37" s="17"/>
-      <c r="Y37" s="6"/>
-      <c r="Z37" s="3"/>
-      <c r="AA37" s="7"/>
-      <c r="AC37" s="14">
+      <c r="Y37" s="17"/>
+      <c r="Z37" s="6"/>
+      <c r="AA37" s="3"/>
+      <c r="AB37" s="3"/>
+      <c r="AC37" s="7"/>
+      <c r="AE37" s="14">
+        <v>36</v>
+      </c>
+      <c r="AF37" s="17">
         <v>21.8</v>
       </c>
-      <c r="AD37" s="17"/>
-      <c r="AE37" s="3"/>
-      <c r="AF37" s="4"/>
       <c r="AG37" s="3"/>
-      <c r="AH37" s="17"/>
-      <c r="AI37" s="17"/>
-      <c r="AJ37" s="6"/>
-      <c r="AK37" s="3"/>
-      <c r="AL37" s="7"/>
+      <c r="AH37" s="4"/>
+      <c r="AI37" s="3"/>
+      <c r="AJ37" s="17"/>
+      <c r="AK37" s="17"/>
+      <c r="AL37" s="6"/>
+      <c r="AM37" s="3"/>
+      <c r="AN37" s="3"/>
+      <c r="AO37" s="7"/>
     </row>
-    <row r="38" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
         <v>50</v>
       </c>
@@ -13807,7 +14112,7 @@
         <v>71</v>
       </c>
       <c r="G38" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H38" s="17">
         <v>12</v>
@@ -13826,35 +14131,42 @@
       <c r="M38" s="17"/>
       <c r="N38" s="6"/>
       <c r="O38" s="3"/>
-      <c r="P38" s="7">
+      <c r="P38" s="3"/>
+      <c r="Q38" s="7">
         <v>2.1904761904761907</v>
       </c>
-      <c r="R38" s="14">
+      <c r="S38" s="14">
+        <v>15</v>
+      </c>
+      <c r="T38" s="17">
         <v>18</v>
       </c>
-      <c r="S38" s="17"/>
-      <c r="T38" s="3"/>
-      <c r="U38" s="4"/>
-      <c r="V38" s="3"/>
-      <c r="W38" s="17"/>
+      <c r="U38" s="3"/>
+      <c r="V38" s="4"/>
+      <c r="W38" s="3"/>
       <c r="X38" s="17"/>
-      <c r="Y38" s="6"/>
-      <c r="Z38" s="3"/>
-      <c r="AA38" s="7"/>
-      <c r="AC38" s="14">
+      <c r="Y38" s="17"/>
+      <c r="Z38" s="6"/>
+      <c r="AA38" s="3"/>
+      <c r="AB38" s="3"/>
+      <c r="AC38" s="7"/>
+      <c r="AE38" s="14">
+        <v>17</v>
+      </c>
+      <c r="AF38" s="17">
         <v>24.4</v>
       </c>
-      <c r="AD38" s="17"/>
-      <c r="AE38" s="3"/>
-      <c r="AF38" s="4"/>
       <c r="AG38" s="3"/>
-      <c r="AH38" s="17"/>
-      <c r="AI38" s="17"/>
-      <c r="AJ38" s="6"/>
-      <c r="AK38" s="3"/>
-      <c r="AL38" s="7"/>
+      <c r="AH38" s="4"/>
+      <c r="AI38" s="3"/>
+      <c r="AJ38" s="17"/>
+      <c r="AK38" s="17"/>
+      <c r="AL38" s="6"/>
+      <c r="AM38" s="3"/>
+      <c r="AN38" s="3"/>
+      <c r="AO38" s="7"/>
     </row>
-    <row r="39" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>6</v>
       </c>
@@ -13871,7 +14183,7 @@
         <v>2</v>
       </c>
       <c r="G39" s="14">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="H39" s="17">
         <v>4.83</v>
@@ -13890,35 +14202,42 @@
       <c r="M39" s="17"/>
       <c r="N39" s="6"/>
       <c r="O39" s="3"/>
-      <c r="P39" s="7">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="7">
         <v>2.6029176666666669</v>
       </c>
-      <c r="R39" s="14">
+      <c r="S39" s="14">
+        <v>5</v>
+      </c>
+      <c r="T39" s="17">
         <v>7.3425019999999996</v>
       </c>
-      <c r="S39" s="17"/>
-      <c r="T39" s="3"/>
-      <c r="U39" s="4"/>
-      <c r="V39" s="3"/>
-      <c r="W39" s="17"/>
+      <c r="U39" s="3"/>
+      <c r="V39" s="4"/>
+      <c r="W39" s="3"/>
       <c r="X39" s="17"/>
-      <c r="Y39" s="6"/>
-      <c r="Z39" s="3"/>
-      <c r="AA39" s="7"/>
-      <c r="AC39" s="14">
+      <c r="Y39" s="17"/>
+      <c r="Z39" s="6"/>
+      <c r="AA39" s="3"/>
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="7"/>
+      <c r="AE39" s="14">
+        <v>5.5</v>
+      </c>
+      <c r="AF39" s="17">
         <v>3.4450040000000004</v>
       </c>
-      <c r="AD39" s="17"/>
-      <c r="AE39" s="3"/>
-      <c r="AF39" s="4"/>
       <c r="AG39" s="3"/>
-      <c r="AH39" s="17"/>
-      <c r="AI39" s="17"/>
-      <c r="AJ39" s="6"/>
-      <c r="AK39" s="3"/>
-      <c r="AL39" s="7"/>
+      <c r="AH39" s="4"/>
+      <c r="AI39" s="3"/>
+      <c r="AJ39" s="17"/>
+      <c r="AK39" s="17"/>
+      <c r="AL39" s="6"/>
+      <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
+      <c r="AO39" s="7"/>
     </row>
-    <row r="40" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
         <v>51</v>
       </c>
@@ -13935,7 +14254,7 @@
         <v>95</v>
       </c>
       <c r="G40" s="14">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="H40" s="17">
         <v>3.5616104000000002</v>
@@ -13954,35 +14273,42 @@
       <c r="M40" s="17"/>
       <c r="N40" s="6"/>
       <c r="O40" s="3"/>
-      <c r="P40" s="7">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="7">
         <v>2.3077000430107528</v>
       </c>
-      <c r="R40" s="14">
+      <c r="S40" s="14">
+        <v>4</v>
+      </c>
+      <c r="T40" s="17">
         <v>8.6</v>
       </c>
-      <c r="S40" s="17"/>
-      <c r="T40" s="3"/>
-      <c r="U40" s="4"/>
-      <c r="V40" s="3"/>
-      <c r="W40" s="17"/>
+      <c r="U40" s="3"/>
+      <c r="V40" s="4"/>
+      <c r="W40" s="3"/>
       <c r="X40" s="17"/>
-      <c r="Y40" s="6"/>
-      <c r="Z40" s="3"/>
-      <c r="AA40" s="7"/>
-      <c r="AC40" s="14">
+      <c r="Y40" s="17"/>
+      <c r="Z40" s="6"/>
+      <c r="AA40" s="3"/>
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="7"/>
+      <c r="AE40" s="14">
+        <v>5</v>
+      </c>
+      <c r="AF40" s="17">
         <v>9.3000000000000007</v>
       </c>
-      <c r="AD40" s="17"/>
-      <c r="AE40" s="3"/>
-      <c r="AF40" s="4"/>
       <c r="AG40" s="3"/>
-      <c r="AH40" s="17"/>
-      <c r="AI40" s="17"/>
-      <c r="AJ40" s="6"/>
-      <c r="AK40" s="3"/>
-      <c r="AL40" s="7"/>
+      <c r="AH40" s="4"/>
+      <c r="AI40" s="3"/>
+      <c r="AJ40" s="17"/>
+      <c r="AK40" s="17"/>
+      <c r="AL40" s="6"/>
+      <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
+      <c r="AO40" s="7"/>
     </row>
-    <row r="41" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>64</v>
       </c>
@@ -14018,35 +14344,42 @@
       <c r="M41" s="17"/>
       <c r="N41" s="6"/>
       <c r="O41" s="3"/>
-      <c r="P41" s="7">
-        <v>0</v>
-      </c>
-      <c r="R41" s="14">
-        <v>0</v>
-      </c>
-      <c r="S41" s="17"/>
-      <c r="T41" s="3"/>
-      <c r="U41" s="4"/>
-      <c r="V41" s="3"/>
-      <c r="W41" s="17"/>
+      <c r="P41" s="3"/>
+      <c r="Q41" s="7">
+        <v>0</v>
+      </c>
+      <c r="S41" s="14">
+        <v>0</v>
+      </c>
+      <c r="T41" s="17">
+        <v>0</v>
+      </c>
+      <c r="U41" s="3"/>
+      <c r="V41" s="4"/>
+      <c r="W41" s="3"/>
       <c r="X41" s="17"/>
-      <c r="Y41" s="6"/>
-      <c r="Z41" s="3"/>
-      <c r="AA41" s="7"/>
-      <c r="AC41" s="14">
-        <v>0</v>
-      </c>
-      <c r="AD41" s="17"/>
-      <c r="AE41" s="3"/>
-      <c r="AF41" s="4"/>
+      <c r="Y41" s="17"/>
+      <c r="Z41" s="6"/>
+      <c r="AA41" s="3"/>
+      <c r="AB41" s="3"/>
+      <c r="AC41" s="7"/>
+      <c r="AE41" s="14">
+        <v>0</v>
+      </c>
+      <c r="AF41" s="17">
+        <v>0</v>
+      </c>
       <c r="AG41" s="3"/>
-      <c r="AH41" s="17"/>
-      <c r="AI41" s="17"/>
-      <c r="AJ41" s="6"/>
-      <c r="AK41" s="3"/>
-      <c r="AL41" s="7"/>
+      <c r="AH41" s="4"/>
+      <c r="AI41" s="3"/>
+      <c r="AJ41" s="17"/>
+      <c r="AK41" s="17"/>
+      <c r="AL41" s="6"/>
+      <c r="AM41" s="3"/>
+      <c r="AN41" s="3"/>
+      <c r="AO41" s="7"/>
     </row>
-    <row r="42" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
         <v>52</v>
       </c>
@@ -14063,7 +14396,7 @@
         <v>95</v>
       </c>
       <c r="G42" s="14">
-        <v>10.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="H42" s="17">
         <v>10.17</v>
@@ -14082,35 +14415,44 @@
       <c r="M42" s="17"/>
       <c r="N42" s="6"/>
       <c r="O42" s="3"/>
-      <c r="P42" s="7">
+      <c r="P42" s="3">
+        <v>10.17</v>
+      </c>
+      <c r="Q42" s="7">
         <v>2.9510416666666659</v>
       </c>
-      <c r="R42" s="14">
+      <c r="S42" s="14">
+        <v>9.5</v>
+      </c>
+      <c r="T42" s="17">
         <v>10.02</v>
       </c>
-      <c r="S42" s="17"/>
-      <c r="T42" s="3"/>
-      <c r="U42" s="4"/>
-      <c r="V42" s="3"/>
-      <c r="W42" s="17"/>
+      <c r="U42" s="3"/>
+      <c r="V42" s="4"/>
+      <c r="W42" s="3"/>
       <c r="X42" s="17"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="3"/>
-      <c r="AA42" s="7"/>
-      <c r="AC42" s="14">
+      <c r="Y42" s="17"/>
+      <c r="Z42" s="6"/>
+      <c r="AA42" s="3"/>
+      <c r="AB42" s="3"/>
+      <c r="AC42" s="7"/>
+      <c r="AE42" s="14">
+        <v>9.5</v>
+      </c>
+      <c r="AF42" s="17">
         <v>8.14</v>
       </c>
-      <c r="AD42" s="17"/>
-      <c r="AE42" s="3"/>
-      <c r="AF42" s="4"/>
       <c r="AG42" s="3"/>
-      <c r="AH42" s="17"/>
-      <c r="AI42" s="17"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="3"/>
-      <c r="AL42" s="7"/>
+      <c r="AH42" s="4"/>
+      <c r="AI42" s="3"/>
+      <c r="AJ42" s="17"/>
+      <c r="AK42" s="17"/>
+      <c r="AL42" s="6"/>
+      <c r="AM42" s="3"/>
+      <c r="AN42" s="3"/>
+      <c r="AO42" s="7"/>
     </row>
-    <row r="43" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
         <v>53</v>
       </c>
@@ -14146,35 +14488,42 @@
       <c r="M43" s="17"/>
       <c r="N43" s="6"/>
       <c r="O43" s="3"/>
-      <c r="P43" s="7">
+      <c r="P43" s="3"/>
+      <c r="Q43" s="7">
         <v>0.33333333333333331</v>
       </c>
-      <c r="R43" s="14">
-        <v>0</v>
-      </c>
-      <c r="S43" s="17"/>
-      <c r="T43" s="3"/>
-      <c r="U43" s="4"/>
-      <c r="V43" s="3"/>
-      <c r="W43" s="17"/>
+      <c r="S43" s="14">
+        <v>0</v>
+      </c>
+      <c r="T43" s="17">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3"/>
+      <c r="V43" s="4"/>
+      <c r="W43" s="3"/>
       <c r="X43" s="17"/>
-      <c r="Y43" s="6"/>
-      <c r="Z43" s="3"/>
-      <c r="AA43" s="7"/>
-      <c r="AC43" s="14">
+      <c r="Y43" s="17"/>
+      <c r="Z43" s="6"/>
+      <c r="AA43" s="3"/>
+      <c r="AB43" s="3"/>
+      <c r="AC43" s="7"/>
+      <c r="AE43" s="14">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="17">
         <v>1</v>
       </c>
-      <c r="AD43" s="17"/>
-      <c r="AE43" s="3"/>
-      <c r="AF43" s="4"/>
       <c r="AG43" s="3"/>
-      <c r="AH43" s="17"/>
-      <c r="AI43" s="17"/>
-      <c r="AJ43" s="6"/>
-      <c r="AK43" s="3"/>
-      <c r="AL43" s="7"/>
+      <c r="AH43" s="4"/>
+      <c r="AI43" s="3"/>
+      <c r="AJ43" s="17"/>
+      <c r="AK43" s="17"/>
+      <c r="AL43" s="6"/>
+      <c r="AM43" s="3"/>
+      <c r="AN43" s="3"/>
+      <c r="AO43" s="7"/>
     </row>
-    <row r="44" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
         <v>54</v>
       </c>
@@ -14191,7 +14540,7 @@
         <v>71</v>
       </c>
       <c r="G44" s="14">
-        <v>3.3</v>
+        <v>7</v>
       </c>
       <c r="H44" s="17">
         <v>2.90625</v>
@@ -14210,35 +14559,44 @@
       <c r="M44" s="17"/>
       <c r="N44" s="6"/>
       <c r="O44" s="3"/>
-      <c r="P44" s="7">
+      <c r="P44" s="3">
+        <v>2.9</v>
+      </c>
+      <c r="Q44" s="7">
         <v>2.2062499999999998</v>
       </c>
-      <c r="R44" s="14">
+      <c r="S44" s="14">
+        <v>7</v>
+      </c>
+      <c r="T44" s="17">
         <v>7.95</v>
       </c>
-      <c r="S44" s="17"/>
-      <c r="T44" s="3"/>
-      <c r="U44" s="4"/>
-      <c r="V44" s="3"/>
-      <c r="W44" s="17"/>
+      <c r="U44" s="3"/>
+      <c r="V44" s="4"/>
+      <c r="W44" s="3"/>
       <c r="X44" s="17"/>
-      <c r="Y44" s="6"/>
-      <c r="Z44" s="3"/>
-      <c r="AA44" s="7"/>
-      <c r="AC44" s="14">
+      <c r="Y44" s="17"/>
+      <c r="Z44" s="6"/>
+      <c r="AA44" s="3"/>
+      <c r="AB44" s="3"/>
+      <c r="AC44" s="7"/>
+      <c r="AE44" s="14">
+        <v>6</v>
+      </c>
+      <c r="AF44" s="17">
         <v>9</v>
       </c>
-      <c r="AD44" s="17"/>
-      <c r="AE44" s="3"/>
-      <c r="AF44" s="4"/>
       <c r="AG44" s="3"/>
-      <c r="AH44" s="17"/>
-      <c r="AI44" s="17"/>
-      <c r="AJ44" s="6"/>
-      <c r="AK44" s="3"/>
-      <c r="AL44" s="7"/>
+      <c r="AH44" s="4"/>
+      <c r="AI44" s="3"/>
+      <c r="AJ44" s="17"/>
+      <c r="AK44" s="17"/>
+      <c r="AL44" s="6"/>
+      <c r="AM44" s="3"/>
+      <c r="AN44" s="3"/>
+      <c r="AO44" s="7"/>
     </row>
-    <row r="45" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>55</v>
       </c>
@@ -14255,7 +14613,7 @@
         <v>71</v>
       </c>
       <c r="G45" s="14">
-        <v>9</v>
+        <v>11.1936</v>
       </c>
       <c r="H45" s="17">
         <v>7.97</v>
@@ -14274,35 +14632,44 @@
       <c r="M45" s="17"/>
       <c r="N45" s="6"/>
       <c r="O45" s="3"/>
-      <c r="P45" s="7">
+      <c r="P45" s="3">
+        <v>7.97</v>
+      </c>
+      <c r="Q45" s="7">
         <v>2.9047555555555555</v>
       </c>
-      <c r="R45" s="14">
+      <c r="S45" s="14">
+        <v>11.1936</v>
+      </c>
+      <c r="T45" s="17">
         <v>9.0863999999999994</v>
       </c>
-      <c r="S45" s="17"/>
-      <c r="T45" s="3"/>
-      <c r="U45" s="4"/>
-      <c r="V45" s="3"/>
-      <c r="W45" s="17"/>
+      <c r="U45" s="3"/>
+      <c r="V45" s="4"/>
+      <c r="W45" s="3"/>
       <c r="X45" s="17"/>
-      <c r="Y45" s="6"/>
-      <c r="Z45" s="3"/>
-      <c r="AA45" s="7"/>
-      <c r="AC45" s="14">
+      <c r="Y45" s="17"/>
+      <c r="Z45" s="6"/>
+      <c r="AA45" s="3"/>
+      <c r="AB45" s="3"/>
+      <c r="AC45" s="7"/>
+      <c r="AE45" s="14">
+        <v>11.1936</v>
+      </c>
+      <c r="AF45" s="17">
         <v>9.0863999999999994</v>
       </c>
-      <c r="AD45" s="17"/>
-      <c r="AE45" s="3"/>
-      <c r="AF45" s="4"/>
       <c r="AG45" s="3"/>
-      <c r="AH45" s="17"/>
-      <c r="AI45" s="17"/>
-      <c r="AJ45" s="6"/>
-      <c r="AK45" s="3"/>
-      <c r="AL45" s="7"/>
+      <c r="AH45" s="4"/>
+      <c r="AI45" s="3"/>
+      <c r="AJ45" s="17"/>
+      <c r="AK45" s="17"/>
+      <c r="AL45" s="6"/>
+      <c r="AM45" s="3"/>
+      <c r="AN45" s="3"/>
+      <c r="AO45" s="7"/>
     </row>
-    <row r="46" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>56</v>
       </c>
@@ -14319,7 +14686,7 @@
         <v>2</v>
       </c>
       <c r="G46" s="14">
-        <v>6.5</v>
+        <v>6.3666666666666663</v>
       </c>
       <c r="H46" s="17">
         <v>10.65</v>
@@ -14338,35 +14705,44 @@
       <c r="M46" s="17"/>
       <c r="N46" s="6"/>
       <c r="O46" s="3"/>
-      <c r="P46" s="7">
+      <c r="P46" s="3">
+        <v>10.65</v>
+      </c>
+      <c r="Q46" s="7">
         <v>1.6966666666666668</v>
       </c>
-      <c r="R46" s="14">
+      <c r="S46" s="14">
+        <v>6.3666666666666663</v>
+      </c>
+      <c r="T46" s="17">
         <v>8.4</v>
       </c>
-      <c r="S46" s="17"/>
-      <c r="T46" s="3"/>
-      <c r="U46" s="4"/>
-      <c r="V46" s="3"/>
-      <c r="W46" s="17"/>
+      <c r="U46" s="3"/>
+      <c r="V46" s="4"/>
+      <c r="W46" s="3"/>
       <c r="X46" s="17"/>
-      <c r="Y46" s="6"/>
-      <c r="Z46" s="3"/>
-      <c r="AA46" s="7"/>
-      <c r="AC46" s="14">
+      <c r="Y46" s="17"/>
+      <c r="Z46" s="6"/>
+      <c r="AA46" s="3"/>
+      <c r="AB46" s="3"/>
+      <c r="AC46" s="7"/>
+      <c r="AE46" s="14">
+        <v>6.3666666666666663</v>
+      </c>
+      <c r="AF46" s="17">
         <v>6.4</v>
       </c>
-      <c r="AD46" s="17"/>
-      <c r="AE46" s="3"/>
-      <c r="AF46" s="4"/>
       <c r="AG46" s="3"/>
-      <c r="AH46" s="17"/>
-      <c r="AI46" s="17"/>
-      <c r="AJ46" s="6"/>
-      <c r="AK46" s="3"/>
-      <c r="AL46" s="7"/>
+      <c r="AH46" s="4"/>
+      <c r="AI46" s="3"/>
+      <c r="AJ46" s="17"/>
+      <c r="AK46" s="17"/>
+      <c r="AL46" s="6"/>
+      <c r="AM46" s="3"/>
+      <c r="AN46" s="3"/>
+      <c r="AO46" s="7"/>
     </row>
-    <row r="47" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
         <v>57</v>
       </c>
@@ -14383,7 +14759,7 @@
         <v>2</v>
       </c>
       <c r="G47" s="14">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="H47" s="17">
         <v>6.5951000000000004</v>
@@ -14402,35 +14778,42 @@
       <c r="M47" s="17"/>
       <c r="N47" s="6"/>
       <c r="O47" s="3"/>
-      <c r="P47" s="7">
+      <c r="P47" s="3"/>
+      <c r="Q47" s="7">
         <v>1.7125166666666667</v>
       </c>
-      <c r="R47" s="14">
+      <c r="S47" s="14">
+        <v>4</v>
+      </c>
+      <c r="T47" s="17">
         <v>2.33</v>
       </c>
-      <c r="S47" s="17"/>
-      <c r="T47" s="3"/>
-      <c r="U47" s="4"/>
-      <c r="V47" s="3"/>
-      <c r="W47" s="17"/>
+      <c r="U47" s="3"/>
+      <c r="V47" s="4"/>
+      <c r="W47" s="3"/>
       <c r="X47" s="17"/>
-      <c r="Y47" s="6"/>
-      <c r="Z47" s="3"/>
-      <c r="AA47" s="7"/>
-      <c r="AC47" s="14">
+      <c r="Y47" s="17"/>
+      <c r="Z47" s="6"/>
+      <c r="AA47" s="3"/>
+      <c r="AB47" s="3"/>
+      <c r="AC47" s="7"/>
+      <c r="AE47" s="14">
+        <v>4</v>
+      </c>
+      <c r="AF47" s="17">
         <v>1.35</v>
       </c>
-      <c r="AD47" s="17"/>
-      <c r="AE47" s="3"/>
-      <c r="AF47" s="4"/>
       <c r="AG47" s="3"/>
-      <c r="AH47" s="17"/>
-      <c r="AI47" s="17"/>
-      <c r="AJ47" s="6"/>
-      <c r="AK47" s="3"/>
-      <c r="AL47" s="7"/>
+      <c r="AH47" s="4"/>
+      <c r="AI47" s="3"/>
+      <c r="AJ47" s="17"/>
+      <c r="AK47" s="17"/>
+      <c r="AL47" s="6"/>
+      <c r="AM47" s="3"/>
+      <c r="AN47" s="3"/>
+      <c r="AO47" s="7"/>
     </row>
-    <row r="48" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
         <v>58</v>
       </c>
@@ -14447,7 +14830,7 @@
         <v>73</v>
       </c>
       <c r="G48" s="14">
-        <v>45.8</v>
+        <v>45.833333333333336</v>
       </c>
       <c r="H48" s="17">
         <v>65.400000000000006</v>
@@ -14466,35 +14849,44 @@
       <c r="M48" s="17"/>
       <c r="N48" s="6"/>
       <c r="O48" s="3"/>
-      <c r="P48" s="7">
+      <c r="P48" s="3">
+        <v>50</v>
+      </c>
+      <c r="Q48" s="7">
         <v>2.7543859649122808</v>
       </c>
-      <c r="R48" s="14">
+      <c r="S48" s="14">
+        <v>45.833333333333336</v>
+      </c>
+      <c r="T48" s="17">
         <v>45.8</v>
       </c>
-      <c r="S48" s="17"/>
-      <c r="T48" s="3"/>
-      <c r="U48" s="4"/>
-      <c r="V48" s="3"/>
-      <c r="W48" s="17"/>
+      <c r="U48" s="3"/>
+      <c r="V48" s="4"/>
+      <c r="W48" s="3"/>
       <c r="X48" s="17"/>
-      <c r="Y48" s="6"/>
-      <c r="Z48" s="3"/>
-      <c r="AA48" s="7"/>
-      <c r="AC48" s="14">
+      <c r="Y48" s="17"/>
+      <c r="Z48" s="6"/>
+      <c r="AA48" s="3"/>
+      <c r="AB48" s="3"/>
+      <c r="AC48" s="7"/>
+      <c r="AE48" s="14">
+        <v>45.833333333333336</v>
+      </c>
+      <c r="AF48" s="17">
         <v>45.8</v>
       </c>
-      <c r="AD48" s="17"/>
-      <c r="AE48" s="3"/>
-      <c r="AF48" s="4"/>
       <c r="AG48" s="3"/>
-      <c r="AH48" s="17"/>
-      <c r="AI48" s="17"/>
-      <c r="AJ48" s="6"/>
-      <c r="AK48" s="3"/>
-      <c r="AL48" s="7"/>
+      <c r="AH48" s="4"/>
+      <c r="AI48" s="3"/>
+      <c r="AJ48" s="17"/>
+      <c r="AK48" s="17"/>
+      <c r="AL48" s="6"/>
+      <c r="AM48" s="3"/>
+      <c r="AN48" s="3"/>
+      <c r="AO48" s="7"/>
     </row>
-    <row r="49" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
         <v>59</v>
       </c>
@@ -14511,7 +14903,7 @@
         <v>2</v>
       </c>
       <c r="G49" s="14">
-        <v>18</v>
+        <v>17.509999999999998</v>
       </c>
       <c r="H49" s="17">
         <v>17</v>
@@ -14530,35 +14922,44 @@
       <c r="M49" s="17"/>
       <c r="N49" s="6"/>
       <c r="O49" s="3"/>
-      <c r="P49" s="7">
+      <c r="P49" s="3">
+        <v>17</v>
+      </c>
+      <c r="Q49" s="7">
         <v>1.5</v>
       </c>
-      <c r="R49" s="14">
+      <c r="S49" s="14">
+        <v>30.29</v>
+      </c>
+      <c r="T49" s="17">
         <v>25</v>
       </c>
-      <c r="S49" s="17"/>
-      <c r="T49" s="3"/>
-      <c r="U49" s="4"/>
-      <c r="V49" s="3"/>
-      <c r="W49" s="17"/>
+      <c r="U49" s="3"/>
+      <c r="V49" s="4"/>
+      <c r="W49" s="3"/>
       <c r="X49" s="17"/>
-      <c r="Y49" s="6"/>
-      <c r="Z49" s="3"/>
-      <c r="AA49" s="7"/>
-      <c r="AC49" s="14">
+      <c r="Y49" s="17"/>
+      <c r="Z49" s="6"/>
+      <c r="AA49" s="3"/>
+      <c r="AB49" s="3"/>
+      <c r="AC49" s="7"/>
+      <c r="AE49" s="14">
+        <v>33.83</v>
+      </c>
+      <c r="AF49" s="17">
         <v>30</v>
       </c>
-      <c r="AD49" s="17"/>
-      <c r="AE49" s="3"/>
-      <c r="AF49" s="4"/>
       <c r="AG49" s="3"/>
-      <c r="AH49" s="17"/>
-      <c r="AI49" s="17"/>
-      <c r="AJ49" s="6"/>
-      <c r="AK49" s="3"/>
-      <c r="AL49" s="7"/>
+      <c r="AH49" s="4"/>
+      <c r="AI49" s="3"/>
+      <c r="AJ49" s="17"/>
+      <c r="AK49" s="17"/>
+      <c r="AL49" s="6"/>
+      <c r="AM49" s="3"/>
+      <c r="AN49" s="3"/>
+      <c r="AO49" s="7"/>
     </row>
-    <row r="50" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
         <v>85</v>
       </c>
@@ -14575,7 +14976,7 @@
         <v>95</v>
       </c>
       <c r="G50" s="14">
-        <v>8.9</v>
+        <v>7.25</v>
       </c>
       <c r="H50" s="17">
         <v>7.9112900000000002</v>
@@ -14594,35 +14995,42 @@
       <c r="M50" s="17"/>
       <c r="N50" s="6"/>
       <c r="O50" s="3"/>
-      <c r="P50" s="7">
+      <c r="P50" s="3"/>
+      <c r="Q50" s="7">
         <v>7.2004300000000008</v>
       </c>
-      <c r="R50" s="14">
+      <c r="S50" s="14">
+        <v>7.25</v>
+      </c>
+      <c r="T50" s="17">
         <v>10.32</v>
       </c>
-      <c r="S50" s="17"/>
-      <c r="T50" s="3"/>
-      <c r="U50" s="4"/>
-      <c r="V50" s="3"/>
-      <c r="W50" s="17"/>
+      <c r="U50" s="3"/>
+      <c r="V50" s="4"/>
+      <c r="W50" s="3"/>
       <c r="X50" s="17"/>
-      <c r="Y50" s="6"/>
-      <c r="Z50" s="3"/>
-      <c r="AA50" s="7"/>
-      <c r="AC50" s="14">
+      <c r="Y50" s="17"/>
+      <c r="Z50" s="6"/>
+      <c r="AA50" s="3"/>
+      <c r="AB50" s="3"/>
+      <c r="AC50" s="7"/>
+      <c r="AE50" s="14">
+        <v>7.25</v>
+      </c>
+      <c r="AF50" s="17">
         <v>3.37</v>
       </c>
-      <c r="AD50" s="17"/>
-      <c r="AE50" s="3"/>
-      <c r="AF50" s="4"/>
       <c r="AG50" s="3"/>
-      <c r="AH50" s="17"/>
-      <c r="AI50" s="17"/>
-      <c r="AJ50" s="6"/>
-      <c r="AK50" s="3"/>
-      <c r="AL50" s="7"/>
+      <c r="AH50" s="4"/>
+      <c r="AI50" s="3"/>
+      <c r="AJ50" s="17"/>
+      <c r="AK50" s="17"/>
+      <c r="AL50" s="6"/>
+      <c r="AM50" s="3"/>
+      <c r="AN50" s="3"/>
+      <c r="AO50" s="7"/>
     </row>
-    <row r="51" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
         <v>30</v>
       </c>
@@ -14639,7 +15047,7 @@
         <v>2</v>
       </c>
       <c r="G51" s="14">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="H51" s="17">
         <v>0</v>
@@ -14658,35 +15066,42 @@
       <c r="M51" s="17"/>
       <c r="N51" s="6"/>
       <c r="O51" s="3"/>
-      <c r="P51" s="7">
-        <v>0</v>
-      </c>
-      <c r="R51" s="14">
-        <v>0</v>
-      </c>
-      <c r="S51" s="17"/>
-      <c r="T51" s="3"/>
-      <c r="U51" s="4"/>
-      <c r="V51" s="3"/>
-      <c r="W51" s="17"/>
+      <c r="P51" s="3"/>
+      <c r="Q51" s="7">
+        <v>0</v>
+      </c>
+      <c r="S51" s="14">
+        <v>19</v>
+      </c>
+      <c r="T51" s="17">
+        <v>0</v>
+      </c>
+      <c r="U51" s="3"/>
+      <c r="V51" s="4"/>
+      <c r="W51" s="3"/>
       <c r="X51" s="17"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="3"/>
-      <c r="AA51" s="7"/>
-      <c r="AC51" s="14">
-        <v>0</v>
-      </c>
-      <c r="AD51" s="17"/>
-      <c r="AE51" s="3"/>
-      <c r="AF51" s="4"/>
+      <c r="Y51" s="17"/>
+      <c r="Z51" s="6"/>
+      <c r="AA51" s="3"/>
+      <c r="AB51" s="3"/>
+      <c r="AC51" s="7"/>
+      <c r="AE51" s="14">
+        <v>19</v>
+      </c>
+      <c r="AF51" s="17">
+        <v>0</v>
+      </c>
       <c r="AG51" s="3"/>
-      <c r="AH51" s="17"/>
-      <c r="AI51" s="17"/>
-      <c r="AJ51" s="6"/>
-      <c r="AK51" s="3"/>
-      <c r="AL51" s="7"/>
+      <c r="AH51" s="4"/>
+      <c r="AI51" s="3"/>
+      <c r="AJ51" s="17"/>
+      <c r="AK51" s="17"/>
+      <c r="AL51" s="6"/>
+      <c r="AM51" s="3"/>
+      <c r="AN51" s="3"/>
+      <c r="AO51" s="7"/>
     </row>
-    <row r="52" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
         <v>19</v>
       </c>
@@ -14703,7 +15118,7 @@
         <v>2</v>
       </c>
       <c r="G52" s="14">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="H52" s="17">
         <v>1</v>
@@ -14722,35 +15137,42 @@
       <c r="M52" s="17"/>
       <c r="N52" s="6"/>
       <c r="O52" s="3"/>
-      <c r="P52" s="7">
+      <c r="P52" s="3"/>
+      <c r="Q52" s="7">
         <v>2</v>
       </c>
-      <c r="R52" s="14">
-        <v>0</v>
-      </c>
-      <c r="S52" s="17"/>
-      <c r="T52" s="3"/>
-      <c r="U52" s="4"/>
-      <c r="V52" s="3"/>
-      <c r="W52" s="17"/>
+      <c r="S52" s="14">
+        <v>2</v>
+      </c>
+      <c r="T52" s="17">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3"/>
+      <c r="V52" s="4"/>
+      <c r="W52" s="3"/>
       <c r="X52" s="17"/>
-      <c r="Y52" s="6"/>
-      <c r="Z52" s="3"/>
-      <c r="AA52" s="7"/>
-      <c r="AC52" s="14">
+      <c r="Y52" s="17"/>
+      <c r="Z52" s="6"/>
+      <c r="AA52" s="3"/>
+      <c r="AB52" s="3"/>
+      <c r="AC52" s="7"/>
+      <c r="AE52" s="14">
         <v>5</v>
       </c>
-      <c r="AD52" s="17"/>
-      <c r="AE52" s="3"/>
-      <c r="AF52" s="4"/>
+      <c r="AF52" s="17">
+        <v>5</v>
+      </c>
       <c r="AG52" s="3"/>
-      <c r="AH52" s="17"/>
-      <c r="AI52" s="17"/>
-      <c r="AJ52" s="6"/>
-      <c r="AK52" s="3"/>
-      <c r="AL52" s="7"/>
+      <c r="AH52" s="4"/>
+      <c r="AI52" s="3"/>
+      <c r="AJ52" s="17"/>
+      <c r="AK52" s="17"/>
+      <c r="AL52" s="6"/>
+      <c r="AM52" s="3"/>
+      <c r="AN52" s="3"/>
+      <c r="AO52" s="7"/>
     </row>
-    <row r="53" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
         <v>61</v>
       </c>
@@ -14786,35 +15208,42 @@
       <c r="M53" s="17"/>
       <c r="N53" s="6"/>
       <c r="O53" s="3"/>
-      <c r="P53" s="7">
-        <v>0</v>
-      </c>
-      <c r="R53" s="14">
-        <v>0</v>
-      </c>
-      <c r="S53" s="17"/>
-      <c r="T53" s="3"/>
-      <c r="U53" s="4"/>
-      <c r="V53" s="3"/>
-      <c r="W53" s="17"/>
+      <c r="P53" s="3"/>
+      <c r="Q53" s="7">
+        <v>0</v>
+      </c>
+      <c r="S53" s="14">
+        <v>0</v>
+      </c>
+      <c r="T53" s="17">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3"/>
+      <c r="V53" s="4"/>
+      <c r="W53" s="3"/>
       <c r="X53" s="17"/>
-      <c r="Y53" s="6"/>
-      <c r="Z53" s="3"/>
-      <c r="AA53" s="7"/>
-      <c r="AC53" s="14">
-        <v>0</v>
-      </c>
-      <c r="AD53" s="17"/>
-      <c r="AE53" s="3"/>
-      <c r="AF53" s="4"/>
+      <c r="Y53" s="17"/>
+      <c r="Z53" s="6"/>
+      <c r="AA53" s="3"/>
+      <c r="AB53" s="3"/>
+      <c r="AC53" s="7"/>
+      <c r="AE53" s="14">
+        <v>1</v>
+      </c>
+      <c r="AF53" s="17">
+        <v>0</v>
+      </c>
       <c r="AG53" s="3"/>
-      <c r="AH53" s="17"/>
-      <c r="AI53" s="17"/>
-      <c r="AJ53" s="6"/>
-      <c r="AK53" s="3"/>
-      <c r="AL53" s="7"/>
+      <c r="AH53" s="4"/>
+      <c r="AI53" s="3"/>
+      <c r="AJ53" s="17"/>
+      <c r="AK53" s="17"/>
+      <c r="AL53" s="6"/>
+      <c r="AM53" s="3"/>
+      <c r="AN53" s="3"/>
+      <c r="AO53" s="7"/>
     </row>
-    <row r="54" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
         <v>62</v>
       </c>
@@ -14850,35 +15279,42 @@
       <c r="M54" s="17"/>
       <c r="N54" s="6"/>
       <c r="O54" s="3"/>
-      <c r="P54" s="7">
-        <v>0</v>
-      </c>
-      <c r="R54" s="14">
-        <v>0</v>
-      </c>
-      <c r="S54" s="17"/>
-      <c r="T54" s="3"/>
-      <c r="U54" s="4"/>
-      <c r="V54" s="3"/>
-      <c r="W54" s="17"/>
+      <c r="P54" s="3"/>
+      <c r="Q54" s="7">
+        <v>0</v>
+      </c>
+      <c r="S54" s="14">
+        <v>0</v>
+      </c>
+      <c r="T54" s="17">
+        <v>0</v>
+      </c>
+      <c r="U54" s="3"/>
+      <c r="V54" s="4"/>
+      <c r="W54" s="3"/>
       <c r="X54" s="17"/>
-      <c r="Y54" s="6"/>
-      <c r="Z54" s="3"/>
-      <c r="AA54" s="7"/>
-      <c r="AC54" s="14">
-        <v>0</v>
-      </c>
-      <c r="AD54" s="17"/>
-      <c r="AE54" s="3"/>
-      <c r="AF54" s="4"/>
+      <c r="Y54" s="17"/>
+      <c r="Z54" s="6"/>
+      <c r="AA54" s="3"/>
+      <c r="AB54" s="3"/>
+      <c r="AC54" s="7"/>
+      <c r="AE54" s="14">
+        <v>0</v>
+      </c>
+      <c r="AF54" s="17">
+        <v>0</v>
+      </c>
       <c r="AG54" s="3"/>
-      <c r="AH54" s="17"/>
-      <c r="AI54" s="17"/>
-      <c r="AJ54" s="6"/>
-      <c r="AK54" s="3"/>
-      <c r="AL54" s="7"/>
+      <c r="AH54" s="4"/>
+      <c r="AI54" s="3"/>
+      <c r="AJ54" s="17"/>
+      <c r="AK54" s="17"/>
+      <c r="AL54" s="6"/>
+      <c r="AM54" s="3"/>
+      <c r="AN54" s="3"/>
+      <c r="AO54" s="7"/>
     </row>
-    <row r="55" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
         <v>65</v>
       </c>
@@ -14895,7 +15331,7 @@
         <v>95</v>
       </c>
       <c r="G55" s="14">
-        <v>4</v>
+        <v>9.6731800000000003</v>
       </c>
       <c r="H55" s="17">
         <v>9</v>
@@ -14914,35 +15350,42 @@
       <c r="M55" s="17"/>
       <c r="N55" s="6"/>
       <c r="O55" s="3"/>
-      <c r="P55" s="7">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="7">
         <v>0.21039603960396042</v>
       </c>
-      <c r="R55" s="14">
+      <c r="S55" s="14">
+        <v>11.291679999999999</v>
+      </c>
+      <c r="T55" s="17">
         <v>2.25</v>
       </c>
-      <c r="S55" s="17"/>
-      <c r="T55" s="3"/>
-      <c r="U55" s="4"/>
-      <c r="V55" s="3"/>
-      <c r="W55" s="17"/>
+      <c r="U55" s="3"/>
+      <c r="V55" s="4"/>
+      <c r="W55" s="3"/>
       <c r="X55" s="17"/>
-      <c r="Y55" s="6"/>
-      <c r="Z55" s="3"/>
-      <c r="AA55" s="7"/>
-      <c r="AC55" s="14">
+      <c r="Y55" s="17"/>
+      <c r="Z55" s="6"/>
+      <c r="AA55" s="3"/>
+      <c r="AB55" s="3"/>
+      <c r="AC55" s="7"/>
+      <c r="AE55" s="14">
+        <v>39.549320000000002</v>
+      </c>
+      <c r="AF55" s="17">
         <v>1.5</v>
       </c>
-      <c r="AD55" s="17"/>
-      <c r="AE55" s="3"/>
-      <c r="AF55" s="4"/>
       <c r="AG55" s="3"/>
-      <c r="AH55" s="17"/>
-      <c r="AI55" s="17"/>
-      <c r="AJ55" s="6"/>
-      <c r="AK55" s="3"/>
-      <c r="AL55" s="7"/>
+      <c r="AH55" s="4"/>
+      <c r="AI55" s="3"/>
+      <c r="AJ55" s="17"/>
+      <c r="AK55" s="17"/>
+      <c r="AL55" s="6"/>
+      <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
+      <c r="AO55" s="7"/>
     </row>
-    <row r="56" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
         <v>66</v>
       </c>
@@ -14959,7 +15402,7 @@
         <v>66</v>
       </c>
       <c r="G56" s="14">
-        <v>1.5</v>
+        <v>6.3891</v>
       </c>
       <c r="H56" s="17">
         <v>2.9410600000000002</v>
@@ -14978,35 +15421,42 @@
       <c r="M56" s="17"/>
       <c r="N56" s="6"/>
       <c r="O56" s="3"/>
-      <c r="P56" s="7">
-        <v>0</v>
-      </c>
-      <c r="R56" s="14">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="7">
+        <v>0</v>
+      </c>
+      <c r="S56" s="14">
+        <v>23.275400000000001</v>
+      </c>
+      <c r="T56" s="17">
         <v>0.83</v>
       </c>
-      <c r="S56" s="17"/>
-      <c r="T56" s="3"/>
-      <c r="U56" s="4"/>
-      <c r="V56" s="3"/>
-      <c r="W56" s="17"/>
+      <c r="U56" s="3"/>
+      <c r="V56" s="4"/>
+      <c r="W56" s="3"/>
       <c r="X56" s="17"/>
-      <c r="Y56" s="6"/>
-      <c r="Z56" s="3"/>
-      <c r="AA56" s="7"/>
-      <c r="AC56" s="14">
-        <v>0</v>
-      </c>
-      <c r="AD56" s="17"/>
-      <c r="AE56" s="3"/>
-      <c r="AF56" s="4"/>
+      <c r="Y56" s="17"/>
+      <c r="Z56" s="6"/>
+      <c r="AA56" s="3"/>
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="7"/>
+      <c r="AE56" s="14">
+        <v>7</v>
+      </c>
+      <c r="AF56" s="17">
+        <v>0</v>
+      </c>
       <c r="AG56" s="3"/>
-      <c r="AH56" s="17"/>
-      <c r="AI56" s="17"/>
-      <c r="AJ56" s="6"/>
-      <c r="AK56" s="3"/>
-      <c r="AL56" s="7"/>
+      <c r="AH56" s="4"/>
+      <c r="AI56" s="3"/>
+      <c r="AJ56" s="17"/>
+      <c r="AK56" s="17"/>
+      <c r="AL56" s="6"/>
+      <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
+      <c r="AO56" s="7"/>
     </row>
-    <row r="57" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
         <v>67</v>
       </c>
@@ -15023,7 +15473,7 @@
         <v>67</v>
       </c>
       <c r="G57" s="14">
-        <v>0</v>
+        <v>4.165</v>
       </c>
       <c r="H57" s="17">
         <v>0</v>
@@ -15042,35 +15492,42 @@
       <c r="M57" s="17"/>
       <c r="N57" s="6"/>
       <c r="O57" s="3"/>
-      <c r="P57" s="7">
-        <v>0</v>
-      </c>
-      <c r="R57" s="14">
-        <v>0</v>
-      </c>
-      <c r="S57" s="17"/>
-      <c r="T57" s="3"/>
-      <c r="U57" s="4"/>
-      <c r="V57" s="3"/>
-      <c r="W57" s="17"/>
+      <c r="P57" s="3"/>
+      <c r="Q57" s="7">
+        <v>0</v>
+      </c>
+      <c r="S57" s="14">
+        <v>5.2478999999999996</v>
+      </c>
+      <c r="T57" s="17">
+        <v>0</v>
+      </c>
+      <c r="U57" s="3"/>
+      <c r="V57" s="4"/>
+      <c r="W57" s="3"/>
       <c r="X57" s="17"/>
-      <c r="Y57" s="6"/>
-      <c r="Z57" s="3"/>
-      <c r="AA57" s="7"/>
-      <c r="AC57" s="14">
-        <v>0</v>
-      </c>
-      <c r="AD57" s="17"/>
-      <c r="AE57" s="3"/>
-      <c r="AF57" s="4"/>
+      <c r="Y57" s="17"/>
+      <c r="Z57" s="6"/>
+      <c r="AA57" s="3"/>
+      <c r="AB57" s="3"/>
+      <c r="AC57" s="7"/>
+      <c r="AE57" s="14">
+        <v>8</v>
+      </c>
+      <c r="AF57" s="17">
+        <v>0</v>
+      </c>
       <c r="AG57" s="3"/>
-      <c r="AH57" s="17"/>
-      <c r="AI57" s="17"/>
-      <c r="AJ57" s="6"/>
-      <c r="AK57" s="3"/>
-      <c r="AL57" s="7"/>
+      <c r="AH57" s="4"/>
+      <c r="AI57" s="3"/>
+      <c r="AJ57" s="17"/>
+      <c r="AK57" s="17"/>
+      <c r="AL57" s="6"/>
+      <c r="AM57" s="3"/>
+      <c r="AN57" s="3"/>
+      <c r="AO57" s="7"/>
     </row>
-    <row r="58" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A58" s="16" t="s">
         <v>96</v>
       </c>
@@ -15106,35 +15563,42 @@
       <c r="M58" s="17"/>
       <c r="N58" s="6"/>
       <c r="O58" s="3"/>
-      <c r="P58" s="7">
+      <c r="P58" s="3"/>
+      <c r="Q58" s="7">
         <v>0.38095238095238093</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="14">
+        <v>0</v>
+      </c>
+      <c r="T58" s="17">
         <v>2</v>
       </c>
-      <c r="S58" s="17"/>
-      <c r="T58" s="3"/>
-      <c r="U58" s="4"/>
-      <c r="V58" s="3"/>
-      <c r="W58" s="17"/>
+      <c r="U58" s="3"/>
+      <c r="V58" s="4"/>
+      <c r="W58" s="3"/>
       <c r="X58" s="17"/>
-      <c r="Y58" s="6"/>
-      <c r="Z58" s="3"/>
-      <c r="AA58" s="7"/>
-      <c r="AC58" s="14">
+      <c r="Y58" s="17"/>
+      <c r="Z58" s="6"/>
+      <c r="AA58" s="3"/>
+      <c r="AB58" s="3"/>
+      <c r="AC58" s="7"/>
+      <c r="AE58" s="14">
+        <v>0</v>
+      </c>
+      <c r="AF58" s="17">
         <v>2</v>
       </c>
-      <c r="AD58" s="17"/>
-      <c r="AE58" s="3"/>
-      <c r="AF58" s="4"/>
       <c r="AG58" s="3"/>
-      <c r="AH58" s="17"/>
-      <c r="AI58" s="17"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="3"/>
-      <c r="AL58" s="7"/>
+      <c r="AH58" s="4"/>
+      <c r="AI58" s="3"/>
+      <c r="AJ58" s="17"/>
+      <c r="AK58" s="17"/>
+      <c r="AL58" s="6"/>
+      <c r="AM58" s="3"/>
+      <c r="AN58" s="3"/>
+      <c r="AO58" s="7"/>
     </row>
-    <row r="59" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A59" s="16" t="s">
         <v>97</v>
       </c>
@@ -15170,35 +15634,44 @@
       <c r="M59" s="17"/>
       <c r="N59" s="6"/>
       <c r="O59" s="3"/>
-      <c r="P59" s="7">
+      <c r="P59" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="Q59" s="7">
         <v>1.2500000000000002</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="14">
+        <v>0</v>
+      </c>
+      <c r="T59" s="17">
         <v>1.75</v>
       </c>
-      <c r="S59" s="17"/>
-      <c r="T59" s="3"/>
-      <c r="U59" s="4"/>
-      <c r="V59" s="3"/>
-      <c r="W59" s="17"/>
+      <c r="U59" s="3"/>
+      <c r="V59" s="4"/>
+      <c r="W59" s="3"/>
       <c r="X59" s="17"/>
-      <c r="Y59" s="6"/>
-      <c r="Z59" s="3"/>
-      <c r="AA59" s="7"/>
-      <c r="AC59" s="14">
+      <c r="Y59" s="17"/>
+      <c r="Z59" s="6"/>
+      <c r="AA59" s="3"/>
+      <c r="AB59" s="3"/>
+      <c r="AC59" s="7"/>
+      <c r="AE59" s="14">
+        <v>0</v>
+      </c>
+      <c r="AF59" s="17">
         <v>1.75</v>
       </c>
-      <c r="AD59" s="17"/>
-      <c r="AE59" s="3"/>
-      <c r="AF59" s="4"/>
       <c r="AG59" s="3"/>
-      <c r="AH59" s="17"/>
-      <c r="AI59" s="17"/>
-      <c r="AJ59" s="6"/>
-      <c r="AK59" s="3"/>
-      <c r="AL59" s="7"/>
+      <c r="AH59" s="4"/>
+      <c r="AI59" s="3"/>
+      <c r="AJ59" s="17"/>
+      <c r="AK59" s="17"/>
+      <c r="AL59" s="6"/>
+      <c r="AM59" s="3"/>
+      <c r="AN59" s="3"/>
+      <c r="AO59" s="7"/>
     </row>
-    <row r="60" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A60" s="16" t="s">
         <v>120</v>
       </c>
@@ -15215,7 +15688,8 @@
         <v>120</v>
       </c>
       <c r="G60" s="14">
-        <v>0</v>
+        <f>217/3</f>
+        <v>72.333333333333329</v>
       </c>
       <c r="H60" s="17">
         <v>0</v>
@@ -15232,26 +15706,30 @@
         <v>0</v>
       </c>
       <c r="M60" s="17"/>
-      <c r="R60" s="23">
-        <v>0</v>
-      </c>
-      <c r="S60" s="17"/>
-      <c r="T60" s="3"/>
-      <c r="U60" s="4"/>
-      <c r="V60" s="16"/>
-      <c r="W60" s="24"/>
-      <c r="X60" s="17"/>
-      <c r="AC60" s="14">
-        <v>0</v>
-      </c>
-      <c r="AD60" s="17"/>
-      <c r="AE60" s="3"/>
-      <c r="AF60" s="4"/>
-      <c r="AG60" s="16"/>
-      <c r="AH60" s="24"/>
-      <c r="AI60" s="17"/>
+      <c r="S60" s="14">
+        <v>72.333333333333329</v>
+      </c>
+      <c r="T60" s="17">
+        <v>0</v>
+      </c>
+      <c r="U60" s="3"/>
+      <c r="V60" s="4"/>
+      <c r="W60" s="16"/>
+      <c r="X60" s="24"/>
+      <c r="Y60" s="17"/>
+      <c r="AE60" s="14">
+        <v>72.3</v>
+      </c>
+      <c r="AF60" s="17">
+        <v>0</v>
+      </c>
+      <c r="AG60" s="3"/>
+      <c r="AH60" s="4"/>
+      <c r="AI60" s="16"/>
+      <c r="AJ60" s="24"/>
+      <c r="AK60" s="17"/>
     </row>
-    <row r="61" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A61" s="16" t="s">
         <v>121</v>
       </c>
@@ -15283,26 +15761,30 @@
       <c r="L61" s="24">
         <v>5.2</v>
       </c>
-      <c r="R61" s="18">
+      <c r="S61" s="14">
+        <v>0</v>
+      </c>
+      <c r="T61" s="17">
         <v>12.5</v>
       </c>
-      <c r="S61" s="17"/>
-      <c r="T61" s="3"/>
-      <c r="U61" s="4"/>
-      <c r="W61" s="24"/>
-      <c r="AC61" s="14">
+      <c r="U61" s="3"/>
+      <c r="V61" s="4"/>
+      <c r="X61" s="24"/>
+      <c r="AE61" s="14">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="17">
         <v>12.5</v>
       </c>
-      <c r="AD61" s="17"/>
-      <c r="AE61" s="3"/>
-      <c r="AF61" s="4"/>
-      <c r="AH61" s="24"/>
+      <c r="AG61" s="3"/>
+      <c r="AH61" s="4"/>
+      <c r="AJ61" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="G1:P1"/>
-    <mergeCell ref="R1:AA1"/>
-    <mergeCell ref="AC1:AL1"/>
+    <mergeCell ref="G1:Q1"/>
+    <mergeCell ref="S1:AC1"/>
+    <mergeCell ref="AE1:AO1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/CEO Review.xlsx
+++ b/CEO Review.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://peoplestronghrservices-my.sharepoint.com/personal/baljeet_singh_taggd_in/Documents/Desktop/Clude Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1809" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82084BC5-C749-4248-AEA7-38FBCBD28A37}"/>
+  <xr:revisionPtr revIDLastSave="1890" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65219F3F-15DC-47EB-9681-BF5DD139218B}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{F2C8E0B5-D69E-42FC-A0A4-20379F29D696}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F2C8E0B5-D69E-42FC-A0A4-20379F29D696}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Actual!$A$2:$AO$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$BZ$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$BZ$62</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="131">
   <si>
     <t>Clients</t>
   </si>
@@ -432,15 +432,20 @@
   <si>
     <t>Budget Revenue</t>
   </si>
+  <si>
+    <t>LAAP India</t>
+  </si>
+  <si>
+    <t>Abhilash Ranjan</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -565,7 +570,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -620,23 +625,14 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -646,6 +642,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -981,7 +983,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DAF86FD-6DF2-4802-8402-DE850AA85999}">
-  <dimension ref="A1:BZ61"/>
+  <dimension ref="A1:BZ62"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.26953125" bestFit="1" customWidth="1"/>
@@ -1027,71 +1029,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:78" x14ac:dyDescent="0.35">
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="R1" s="29" t="s">
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="R1" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="S1" s="29"/>
-      <c r="T1" s="29"/>
-      <c r="U1" s="29"/>
-      <c r="V1" s="29"/>
-      <c r="W1" s="29"/>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="29"/>
-      <c r="AA1" s="29"/>
-      <c r="AC1" s="29" t="s">
+      <c r="S1" s="26"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="26"/>
+      <c r="V1" s="26"/>
+      <c r="W1" s="26"/>
+      <c r="X1" s="26"/>
+      <c r="Y1" s="26"/>
+      <c r="Z1" s="26"/>
+      <c r="AA1" s="26"/>
+      <c r="AC1" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="AD1" s="29"/>
-      <c r="AE1" s="29"/>
-      <c r="AF1" s="29"/>
-      <c r="AG1" s="29"/>
-      <c r="AH1" s="29"/>
-      <c r="AI1" s="29"/>
-      <c r="AJ1" s="29"/>
-      <c r="AK1" s="29"/>
-      <c r="AL1" s="29"/>
-      <c r="AN1" s="29" t="s">
+      <c r="AD1" s="26"/>
+      <c r="AE1" s="26"/>
+      <c r="AF1" s="26"/>
+      <c r="AG1" s="26"/>
+      <c r="AH1" s="26"/>
+      <c r="AI1" s="26"/>
+      <c r="AJ1" s="26"/>
+      <c r="AK1" s="26"/>
+      <c r="AL1" s="26"/>
+      <c r="AN1" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="AO1" s="29"/>
-      <c r="AP1" s="29"/>
-      <c r="AQ1" s="29"/>
-      <c r="AR1" s="29"/>
-      <c r="AS1" s="29"/>
-      <c r="AT1" s="29"/>
-      <c r="AU1" s="29"/>
-      <c r="AV1" s="29"/>
-      <c r="AW1" s="29"/>
-      <c r="AY1" s="30" t="s">
+      <c r="AO1" s="26"/>
+      <c r="AP1" s="26"/>
+      <c r="AQ1" s="26"/>
+      <c r="AR1" s="26"/>
+      <c r="AS1" s="26"/>
+      <c r="AT1" s="26"/>
+      <c r="AU1" s="26"/>
+      <c r="AV1" s="26"/>
+      <c r="AW1" s="26"/>
+      <c r="AY1" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="AZ1" s="30"/>
-      <c r="BA1" s="30"/>
-      <c r="BB1" s="30"/>
-      <c r="BC1" s="30"/>
-      <c r="BD1" s="30"/>
-      <c r="BE1" s="30"/>
-      <c r="BF1" s="30"/>
-      <c r="BG1" s="30"/>
-      <c r="BH1" s="30"/>
-      <c r="BJ1" s="29" t="s">
+      <c r="AZ1" s="27"/>
+      <c r="BA1" s="27"/>
+      <c r="BB1" s="27"/>
+      <c r="BC1" s="27"/>
+      <c r="BD1" s="27"/>
+      <c r="BE1" s="27"/>
+      <c r="BF1" s="27"/>
+      <c r="BG1" s="27"/>
+      <c r="BH1" s="27"/>
+      <c r="BJ1" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="BK1" s="29"/>
-      <c r="BL1" s="29"/>
+      <c r="BK1" s="26"/>
+      <c r="BL1" s="26"/>
       <c r="BN1" s="19" t="s">
         <v>79</v>
       </c>
@@ -1520,7 +1522,7 @@
         <v>-0.52813136392458482</v>
       </c>
       <c r="J4" s="4">
-        <f t="shared" ref="J4:J60" si="2">IFERROR(I4/H4,0)</f>
+        <f t="shared" ref="J4:J61" si="2">IFERROR(I4/H4,0)</f>
         <v>-5.3475158859134571E-2</v>
       </c>
       <c r="K4" s="3">
@@ -1546,7 +1548,7 @@
         <v>-6.4447645003170422</v>
       </c>
       <c r="U4" s="4">
-        <f t="shared" ref="U4:U59" si="3">IFERROR(T4/S4,0)</f>
+        <f t="shared" ref="U4:U62" si="3">IFERROR(T4/S4,0)</f>
         <v>-1.2889529000634083</v>
       </c>
       <c r="V4" s="3">
@@ -1615,15 +1617,15 @@
         <v>20</v>
       </c>
       <c r="AZ4" s="17">
-        <f t="shared" ref="AZ4:AZ61" si="6">S4+AD4+AO4+H4</f>
+        <f t="shared" ref="AZ4:AZ62" si="6">S4+AD4+AO4+H4</f>
         <v>24.876199999999997</v>
       </c>
       <c r="BA4" s="17">
-        <f t="shared" ref="BA4:BA59" si="7">T4+AE4+AP4+I4</f>
+        <f t="shared" ref="BA4:BA62" si="7">T4+AE4+AP4+I4</f>
         <v>-19.862424864875713</v>
       </c>
       <c r="BB4" s="4">
-        <f t="shared" ref="BB4:BB59" si="8">IFERROR(BA4/AZ4,0)</f>
+        <f t="shared" ref="BB4:BB62" si="8">IFERROR(BA4/AZ4,0)</f>
         <v>-0.79845092356853997</v>
       </c>
       <c r="BC4" s="3">
@@ -1689,14 +1691,14 @@
         <v>24</v>
       </c>
       <c r="H5" s="17">
-        <v>22.799676599999998</v>
+        <v>23.299676599999998</v>
       </c>
       <c r="I5" s="3">
-        <v>10.683573396464103</v>
+        <v>11.183573396464103</v>
       </c>
       <c r="J5" s="4">
         <f t="shared" si="2"/>
-        <v>0.46858442704683384</v>
+        <v>0.47998835299130738</v>
       </c>
       <c r="K5" s="3">
         <v>100967.52669613245</v>
@@ -1791,15 +1793,15 @@
       </c>
       <c r="AZ5" s="17">
         <f t="shared" si="6"/>
-        <v>78.799676599999998</v>
+        <v>79.299676599999998</v>
       </c>
       <c r="BA5" s="17">
         <f t="shared" si="7"/>
-        <v>26.700432824795655</v>
+        <v>27.200432824795655</v>
       </c>
       <c r="BB5" s="4">
         <f t="shared" si="8"/>
-        <v>0.33883937062751418</v>
+        <v>0.34300811795234554</v>
       </c>
       <c r="BC5" s="3">
         <f t="shared" si="0"/>
@@ -1866,14 +1868,14 @@
         <v>56</v>
       </c>
       <c r="H6" s="17">
-        <v>41.46</v>
+        <v>79.400000000000006</v>
       </c>
       <c r="I6" s="3">
-        <v>-10.512857798969705</v>
+        <v>27.4271422010303</v>
       </c>
       <c r="J6" s="4">
         <f t="shared" si="2"/>
-        <v>-0.25356627590375552</v>
+        <v>0.34543000253186773</v>
       </c>
       <c r="K6" s="3">
         <v>110580.54850844618</v>
@@ -1968,15 +1970,15 @@
       </c>
       <c r="AZ6" s="17">
         <f t="shared" si="6"/>
-        <v>207.46</v>
+        <v>245.4</v>
       </c>
       <c r="BA6" s="17">
         <f t="shared" si="7"/>
-        <v>-16.023288535569762</v>
+        <v>21.916711464430243</v>
       </c>
       <c r="BB6" s="4">
         <f t="shared" si="8"/>
-        <v>-7.7235556423261159E-2</v>
+        <v>8.9310152666789905E-2</v>
       </c>
       <c r="BC6" s="3">
         <f t="shared" si="0"/>
@@ -2074,14 +2076,14 @@
         <v>27.4</v>
       </c>
       <c r="S7" s="7">
-        <v>27.4</v>
+        <v>19.09</v>
       </c>
       <c r="T7" s="3">
-        <v>7.340342613379967</v>
+        <v>-0.96965738662003176</v>
       </c>
       <c r="U7" s="4">
         <f t="shared" si="3"/>
-        <v>0.26789571581678712</v>
+        <v>-5.0793996156104339E-2</v>
       </c>
       <c r="V7" s="3">
         <v>111442.54103677796</v>
@@ -2150,15 +2152,15 @@
       </c>
       <c r="AZ7" s="17">
         <f t="shared" si="6"/>
-        <v>113.71849999999999</v>
+        <v>105.4085</v>
       </c>
       <c r="BA7" s="17">
         <f t="shared" si="7"/>
-        <v>35.303475670485341</v>
+        <v>26.993475670485338</v>
       </c>
       <c r="BB7" s="4">
         <f t="shared" si="8"/>
-        <v>0.31044619539024293</v>
+        <v>0.25608443029248434</v>
       </c>
       <c r="BC7" s="3">
         <f t="shared" si="0"/>
@@ -2226,14 +2228,14 @@
         <v>33</v>
       </c>
       <c r="H8" s="17">
-        <v>29.1525</v>
+        <v>35.332499999999996</v>
       </c>
       <c r="I8" s="3">
-        <v>4.4074999999999989</v>
+        <v>10.587499999999995</v>
       </c>
       <c r="J8" s="4">
         <f t="shared" si="2"/>
-        <v>0.15118771974959261</v>
+        <v>0.29965329370975718</v>
       </c>
       <c r="K8" s="3">
         <v>101000</v>
@@ -2328,15 +2330,15 @@
       </c>
       <c r="AZ8" s="17">
         <f t="shared" si="6"/>
-        <v>130.85249999999999</v>
+        <v>137.03249999999997</v>
       </c>
       <c r="BA8" s="17">
         <f t="shared" si="7"/>
-        <v>24.448999999999991</v>
+        <v>30.628999999999987</v>
       </c>
       <c r="BB8" s="4">
         <f t="shared" si="8"/>
-        <v>0.18684396553371158</v>
+        <v>0.22351631912137626</v>
       </c>
       <c r="BC8" s="3">
         <f t="shared" si="0"/>
@@ -2401,14 +2403,14 @@
         <v>51.75</v>
       </c>
       <c r="H9" s="17">
-        <v>25.08</v>
+        <v>24.630000000000003</v>
       </c>
       <c r="I9" s="3">
-        <v>-0.5778053411884656</v>
+        <v>-1.0278053411884613</v>
       </c>
       <c r="J9" s="4">
         <f t="shared" si="2"/>
-        <v>-2.3038490478008995E-2</v>
+        <v>-4.1729814908179508E-2</v>
       </c>
       <c r="K9" s="3">
         <v>80180.641691213954</v>
@@ -2503,15 +2505,15 @@
       </c>
       <c r="AZ9" s="17">
         <f t="shared" si="6"/>
-        <v>169.07999999999998</v>
+        <v>168.63</v>
       </c>
       <c r="BA9" s="17">
         <f t="shared" si="7"/>
-        <v>58.751437032889598</v>
+        <v>58.301437032889602</v>
       </c>
       <c r="BB9" s="4">
         <f t="shared" si="8"/>
-        <v>0.34747715302158505</v>
+        <v>0.34573585383911287</v>
       </c>
       <c r="BC9" s="3">
         <f t="shared" si="0"/>
@@ -2580,14 +2582,14 @@
         <v>10</v>
       </c>
       <c r="H10" s="17">
-        <v>9.7707377999999991</v>
+        <v>10.270737799999999</v>
       </c>
       <c r="I10" s="3">
-        <v>3.446138567772473</v>
+        <v>3.946138567772473</v>
       </c>
       <c r="J10" s="4">
         <f t="shared" si="2"/>
-        <v>0.35269993303601632</v>
+        <v>0.38421179126707655</v>
       </c>
       <c r="K10" s="3">
         <v>105409.9872037921</v>
@@ -2682,15 +2684,15 @@
       </c>
       <c r="AZ10" s="17">
         <f t="shared" si="6"/>
-        <v>47.770737799999999</v>
+        <v>48.270737799999999</v>
       </c>
       <c r="BA10" s="17">
         <f t="shared" si="7"/>
-        <v>20.574961101421636</v>
+        <v>21.074961101421636</v>
       </c>
       <c r="BB10" s="4">
         <f t="shared" si="8"/>
-        <v>0.4307021839930979</v>
+        <v>0.43659910873418711</v>
       </c>
       <c r="BC10" s="3">
         <f t="shared" si="0"/>
@@ -2758,14 +2760,14 @@
         <v>51.5</v>
       </c>
       <c r="H11" s="17">
-        <v>40.739999999999995</v>
+        <v>39.39</v>
       </c>
       <c r="I11" s="3">
-        <v>16.682275115075424</v>
+        <v>15.332275115075429</v>
       </c>
       <c r="J11" s="4">
         <f t="shared" si="2"/>
-        <v>0.40948147066949991</v>
+        <v>0.38924283105040441</v>
       </c>
       <c r="K11" s="3">
         <v>92529.711095863735</v>
@@ -2860,15 +2862,15 @@
       </c>
       <c r="AZ11" s="17">
         <f t="shared" si="6"/>
-        <v>184.33999999999997</v>
+        <v>182.99</v>
       </c>
       <c r="BA11" s="17">
         <f t="shared" si="7"/>
-        <v>80.891782994824339</v>
+        <v>79.541782994824345</v>
       </c>
       <c r="BB11" s="4">
         <f t="shared" si="8"/>
-        <v>0.43881839532833</v>
+        <v>0.43467830479711644</v>
       </c>
       <c r="BC11" s="3">
         <f t="shared" si="0"/>
@@ -2936,14 +2938,14 @@
         <v>329.30417599999998</v>
       </c>
       <c r="H12" s="17">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="I12" s="3">
-        <v>181.45506157435264</v>
+        <v>177.45506157435264</v>
       </c>
       <c r="J12" s="4">
         <f t="shared" si="2"/>
-        <v>0.43514403255240441</v>
+        <v>0.42967327257712506</v>
       </c>
       <c r="K12" s="3">
         <v>139210.95651634005</v>
@@ -2962,14 +2964,14 @@
         <v>392.27188129999996</v>
       </c>
       <c r="S12" s="7">
-        <v>392.27188129999996</v>
+        <v>338</v>
       </c>
       <c r="T12" s="3">
-        <v>133.17244903178783</v>
+        <v>78.900567731787874</v>
       </c>
       <c r="U12" s="4">
         <f t="shared" si="3"/>
-        <v>0.33949017347471</v>
+        <v>0.23343363234256767</v>
       </c>
       <c r="V12" s="3">
         <v>153132.05216797406</v>
@@ -3038,15 +3040,15 @@
       </c>
       <c r="AZ12" s="17">
         <f t="shared" si="6"/>
-        <v>1530.8479106999998</v>
+        <v>1472.5760294000002</v>
       </c>
       <c r="BA12" s="17">
         <f t="shared" si="7"/>
-        <v>518.00467546971618</v>
+        <v>459.73279416971627</v>
       </c>
       <c r="BB12" s="4">
         <f t="shared" si="8"/>
-        <v>0.33837762187156262</v>
+        <v>0.31219630429339124</v>
       </c>
       <c r="BC12" s="3">
         <f t="shared" si="0"/>
@@ -3136,14 +3138,14 @@
         <v>27</v>
       </c>
       <c r="S13" s="7">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="T13" s="3">
-        <v>16.872312073691592</v>
+        <v>4.8723120736915924</v>
       </c>
       <c r="U13" s="4">
         <f t="shared" si="3"/>
-        <v>0.6249004471737627</v>
+        <v>0.32482080491277282</v>
       </c>
       <c r="V13" s="3">
         <v>140662.332309839</v>
@@ -3212,15 +3214,15 @@
       </c>
       <c r="AZ13" s="17">
         <f t="shared" si="6"/>
-        <v>84.784999999999997</v>
+        <v>72.784999999999997</v>
       </c>
       <c r="BA13" s="17">
         <f t="shared" si="7"/>
-        <v>45.194947197158044</v>
+        <v>33.194947197158044</v>
       </c>
       <c r="BB13" s="4">
         <f t="shared" si="8"/>
-        <v>0.53305357312210944</v>
+        <v>0.45606851957351163</v>
       </c>
       <c r="BC13" s="3">
         <f t="shared" si="0"/>
@@ -3661,14 +3663,14 @@
         <v>13</v>
       </c>
       <c r="S16" s="7">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T16" s="3">
-        <v>2.7762673401577427</v>
+        <v>-6.2237326598422573</v>
       </c>
       <c r="U16" s="4">
         <f t="shared" si="3"/>
-        <v>0.21355902616598021</v>
+        <v>-1.5559331649605643</v>
       </c>
       <c r="V16" s="3">
         <v>92943.024180384149</v>
@@ -3737,15 +3739,15 @@
       </c>
       <c r="AZ16" s="17">
         <f t="shared" si="6"/>
-        <v>49.59169</v>
+        <v>40.59169</v>
       </c>
       <c r="BA16" s="17">
         <f t="shared" si="7"/>
-        <v>9.6261896024348133</v>
+        <v>0.62618960243481325</v>
       </c>
       <c r="BB16" s="4">
         <f t="shared" si="8"/>
-        <v>0.19410892434669624</v>
+        <v>1.5426546725076321E-2</v>
       </c>
       <c r="BC16" s="3">
         <f t="shared" si="0"/>
@@ -3812,14 +3814,14 @@
         <v>305</v>
       </c>
       <c r="H17" s="17">
-        <v>364.6077823</v>
+        <v>380.6077823</v>
       </c>
       <c r="I17" s="3">
-        <v>137.39413898733835</v>
+        <v>153.39413898733835</v>
       </c>
       <c r="J17" s="4">
         <f t="shared" si="2"/>
-        <v>0.37682722546577513</v>
+        <v>0.40302417901279564</v>
       </c>
       <c r="K17" s="3">
         <v>93889.935253165968</v>
@@ -3914,15 +3916,15 @@
       </c>
       <c r="AZ17" s="17">
         <f t="shared" si="6"/>
-        <v>1444.6077823000001</v>
+        <v>1460.6077823000001</v>
       </c>
       <c r="BA17" s="17">
         <f t="shared" si="7"/>
-        <v>467.58911605555488</v>
+        <v>483.58911605555488</v>
       </c>
       <c r="BB17" s="4">
         <f t="shared" si="8"/>
-        <v>0.32367894025262228</v>
+        <v>0.33108759375090646</v>
       </c>
       <c r="BC17" s="3">
         <f t="shared" si="0"/>
@@ -3990,14 +3992,14 @@
         <v>70</v>
       </c>
       <c r="H18" s="17">
-        <v>76.191083499999991</v>
+        <v>75.491083500000002</v>
       </c>
       <c r="I18" s="3">
-        <v>36.998225002405718</v>
+        <v>36.298225002405729</v>
       </c>
       <c r="J18" s="4">
         <f t="shared" si="2"/>
-        <v>0.48559783248660221</v>
+        <v>0.48082797755056367</v>
       </c>
       <c r="K18" s="3">
         <v>130642.86165864758</v>
@@ -4092,15 +4094,15 @@
       </c>
       <c r="AZ18" s="17">
         <f t="shared" si="6"/>
-        <v>256.19108349999999</v>
+        <v>255.4910835</v>
       </c>
       <c r="BA18" s="17">
         <f t="shared" si="7"/>
-        <v>87.661791960344601</v>
+        <v>86.961791960344613</v>
       </c>
       <c r="BB18" s="4">
         <f t="shared" si="8"/>
-        <v>0.3421734697505372</v>
+        <v>0.34037114238604971</v>
       </c>
       <c r="BC18" s="3">
         <f t="shared" si="0"/>
@@ -4188,14 +4190,14 @@
         <v>150</v>
       </c>
       <c r="S19" s="7">
-        <v>150</v>
+        <v>69</v>
       </c>
       <c r="T19" s="3">
-        <v>110.21322812529024</v>
+        <v>29.213228125290236</v>
       </c>
       <c r="U19" s="4">
         <f t="shared" si="3"/>
-        <v>0.73475485416860165</v>
+        <v>0.42338011775782952</v>
       </c>
       <c r="V19" s="3">
         <v>108707.02698008134</v>
@@ -4264,15 +4266,15 @@
       </c>
       <c r="AZ19" s="17">
         <f t="shared" si="6"/>
-        <v>485.98750000000001</v>
+        <v>404.98750000000001</v>
       </c>
       <c r="BA19" s="17">
         <f t="shared" si="7"/>
-        <v>330.45739176249822</v>
+        <v>249.45739176249822</v>
       </c>
       <c r="BB19" s="4">
         <f t="shared" si="8"/>
-        <v>0.67997096995807138</v>
+        <v>0.61596318840087216</v>
       </c>
       <c r="BC19" s="3">
         <f t="shared" si="0"/>
@@ -4337,14 +4339,14 @@
         <v>20.110000000000003</v>
       </c>
       <c r="H20" s="17">
-        <v>26.270800000000001</v>
+        <v>27.510800000000003</v>
       </c>
       <c r="I20" s="3">
-        <v>14.87647828160393</v>
+        <v>16.116478281603932</v>
       </c>
       <c r="J20" s="4">
         <f t="shared" si="2"/>
-        <v>0.56627427720525947</v>
+        <v>0.58582368675588969</v>
       </c>
       <c r="K20" s="3">
         <v>87648.628603046702</v>
@@ -4363,14 +4365,14 @@
         <v>24.865000000000002</v>
       </c>
       <c r="S20" s="7">
-        <v>24.865000000000002</v>
+        <v>27.864999999999998</v>
       </c>
       <c r="T20" s="3">
-        <v>12.331246109764322</v>
+        <v>15.331246109764319</v>
       </c>
       <c r="U20" s="4">
         <f t="shared" si="3"/>
-        <v>0.49592785480652812</v>
+        <v>0.5501972406159813</v>
       </c>
       <c r="V20" s="3">
         <v>96413.491463351384</v>
@@ -4439,15 +4441,15 @@
       </c>
       <c r="AZ20" s="17">
         <f t="shared" si="6"/>
-        <v>100.48080000000002</v>
+        <v>104.72080000000001</v>
       </c>
       <c r="BA20" s="17">
         <f t="shared" si="7"/>
-        <v>51.485216610896892</v>
+        <v>55.725216610896894</v>
       </c>
       <c r="BB20" s="4">
         <f t="shared" si="8"/>
-        <v>0.51238860171193779</v>
+        <v>0.53213131117119894</v>
       </c>
       <c r="BC20" s="3">
         <f t="shared" si="0"/>
@@ -4516,14 +4518,14 @@
         <v>90</v>
       </c>
       <c r="H21" s="17">
-        <v>109.23983000000001</v>
+        <v>108.03982999999999</v>
       </c>
       <c r="I21" s="3">
-        <v>10.614882712791442</v>
+        <v>9.4148827127914245</v>
       </c>
       <c r="J21" s="4">
         <f t="shared" si="2"/>
-        <v>9.7170443351948105E-2</v>
+        <v>8.7142702027496938E-2</v>
       </c>
       <c r="K21" s="3">
         <v>92605.584307238096</v>
@@ -4618,15 +4620,15 @@
       </c>
       <c r="AZ21" s="17">
         <f t="shared" si="6"/>
-        <v>379.23982999999998</v>
+        <v>378.03982999999999</v>
       </c>
       <c r="BA21" s="17">
         <f t="shared" si="7"/>
-        <v>-44.847443334996896</v>
+        <v>-46.047443334996913</v>
       </c>
       <c r="BB21" s="4">
         <f t="shared" si="8"/>
-        <v>-0.11825615293361169</v>
+        <v>-0.12180579843927269</v>
       </c>
       <c r="BC21" s="3">
         <f t="shared" si="0"/>
@@ -4694,14 +4696,14 @@
         <v>15</v>
       </c>
       <c r="H22" s="17">
-        <v>4.7450000000000001</v>
+        <v>4.6449999999999996</v>
       </c>
       <c r="I22" s="3">
-        <v>2.6832903000433048</v>
+        <v>2.5832903000433043</v>
       </c>
       <c r="J22" s="4">
         <f t="shared" si="2"/>
-        <v>0.56549848262240354</v>
+        <v>0.556144305714382</v>
       </c>
       <c r="K22" s="3">
         <v>103085.48499783476</v>
@@ -4796,15 +4798,15 @@
       </c>
       <c r="AZ22" s="17">
         <f t="shared" si="6"/>
-        <v>79.745000000000005</v>
+        <v>79.644999999999996</v>
       </c>
       <c r="BA22" s="17">
         <f t="shared" si="7"/>
-        <v>70.879648290186211</v>
+        <v>70.779648290186202</v>
       </c>
       <c r="BB22" s="4">
         <f t="shared" si="8"/>
-        <v>0.88882874525282096</v>
+        <v>0.88868916178273849</v>
       </c>
       <c r="BC22" s="3">
         <f t="shared" si="0"/>
@@ -4894,14 +4896,14 @@
         <v>4</v>
       </c>
       <c r="S23" s="7">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="T23" s="3">
-        <v>0.36519116710890964</v>
+        <v>-1.1348088328910904</v>
       </c>
       <c r="U23" s="4">
         <f t="shared" si="3"/>
-        <v>9.1297791777227411E-2</v>
+        <v>-0.45392353315643613</v>
       </c>
       <c r="V23" s="3">
         <v>121160.29442970302</v>
@@ -4970,15 +4972,15 @@
       </c>
       <c r="AZ23" s="17">
         <f t="shared" si="6"/>
-        <v>6.68445</v>
+        <v>5.18445</v>
       </c>
       <c r="BA23" s="17">
         <f t="shared" si="7"/>
-        <v>-7.5243481649378978</v>
+        <v>-9.0243481649378978</v>
       </c>
       <c r="BB23" s="4">
         <f t="shared" si="8"/>
-        <v>-1.125649554553912</v>
+        <v>-1.7406568035062346</v>
       </c>
       <c r="BC23" s="3">
         <f t="shared" si="0"/>
@@ -5048,14 +5050,14 @@
         <v>32</v>
       </c>
       <c r="H24" s="17">
-        <v>12.710570000000001</v>
+        <v>8.9005700000000001</v>
       </c>
       <c r="I24" s="3">
-        <v>-2.4151834685570144</v>
+        <v>-6.2251834685570149</v>
       </c>
       <c r="J24" s="4">
         <f t="shared" si="2"/>
-        <v>-0.19001378132979199</v>
+        <v>-0.69941402276000464</v>
       </c>
       <c r="K24" s="3">
         <v>100838.35645704676</v>
@@ -5150,15 +5152,15 @@
       </c>
       <c r="AZ24" s="17">
         <f t="shared" si="6"/>
-        <v>100.71057</v>
+        <v>96.900570000000002</v>
       </c>
       <c r="BA24" s="17">
         <f t="shared" si="7"/>
-        <v>35.669830085204836</v>
+        <v>31.859830085204841</v>
       </c>
       <c r="BB24" s="4">
         <f t="shared" si="8"/>
-        <v>0.35418159270873789</v>
+        <v>0.32878888210053708</v>
       </c>
       <c r="BC24" s="3">
         <f t="shared" si="0"/>
@@ -5226,14 +5228,14 @@
         <v>21</v>
       </c>
       <c r="H25" s="17">
-        <v>29.515699999999999</v>
+        <v>30.495699999999999</v>
       </c>
       <c r="I25" s="3">
-        <v>14.533742816992021</v>
+        <v>15.513742816992021</v>
       </c>
       <c r="J25" s="4">
         <f t="shared" si="2"/>
-        <v>0.49240718725939148</v>
+        <v>0.5087190265182312</v>
       </c>
       <c r="K25" s="3">
         <v>99879.714553386511</v>
@@ -5328,15 +5330,15 @@
       </c>
       <c r="AZ25" s="17">
         <f t="shared" si="6"/>
-        <v>95.015699999999995</v>
+        <v>95.995699999999999</v>
       </c>
       <c r="BA25" s="17">
         <f t="shared" si="7"/>
-        <v>30.593284113065689</v>
+        <v>31.573284113065689</v>
       </c>
       <c r="BB25" s="4">
         <f t="shared" si="8"/>
-        <v>0.32198135795521887</v>
+        <v>0.32890310829616004</v>
       </c>
       <c r="BC25" s="3">
         <f t="shared" si="0"/>
@@ -5404,14 +5406,14 @@
         <v>48</v>
       </c>
       <c r="H26" s="17">
-        <v>48.223479999999995</v>
+        <v>58.223479999999995</v>
       </c>
       <c r="I26" s="3">
-        <v>-17.374233561904248</v>
+        <v>-7.3742335619042478</v>
       </c>
       <c r="J26" s="4">
         <f t="shared" si="2"/>
-        <v>-0.36028576871483042</v>
+        <v>-0.12665394720316012</v>
       </c>
       <c r="K26" s="3">
         <v>117138.77421768615</v>
@@ -5506,15 +5508,15 @@
       </c>
       <c r="AZ26" s="17">
         <f t="shared" si="6"/>
-        <v>192.22348</v>
+        <v>202.22348</v>
       </c>
       <c r="BA26" s="17">
         <f t="shared" si="7"/>
-        <v>-89.846688316188292</v>
+        <v>-79.846688316188292</v>
       </c>
       <c r="BB26" s="4">
         <f t="shared" si="8"/>
-        <v>-0.46740745884003504</v>
+        <v>-0.39484380506253919</v>
       </c>
       <c r="BC26" s="3">
         <f t="shared" si="0"/>
@@ -5607,14 +5609,14 @@
         <v>4</v>
       </c>
       <c r="S27" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T27" s="3">
-        <v>2.5665072492101251</v>
+        <v>1.5665072492101253</v>
       </c>
       <c r="U27" s="4">
         <f t="shared" si="3"/>
-        <v>0.64162681230253127</v>
+        <v>0.52216908307004173</v>
       </c>
       <c r="V27" s="3">
         <v>143349.27507898747</v>
@@ -5683,15 +5685,15 @@
       </c>
       <c r="AZ27" s="17">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA27" s="17">
         <f t="shared" si="7"/>
-        <v>1.3963465196395803</v>
+        <v>0.39634651963958101</v>
       </c>
       <c r="BB27" s="4">
         <f t="shared" si="8"/>
-        <v>0.19947807423422576</v>
+        <v>6.6057753273263506E-2</v>
       </c>
       <c r="BC27" s="3">
         <f t="shared" si="0"/>
@@ -5753,14 +5755,14 @@
         <v>33</v>
       </c>
       <c r="H28" s="17">
-        <v>33.29</v>
+        <v>33.69</v>
       </c>
       <c r="I28" s="3">
-        <v>-2.2802725438410221E-2</v>
+        <v>0.37719727456158836</v>
       </c>
       <c r="J28" s="4">
         <f t="shared" si="2"/>
-        <v>-6.8497222704746834E-4</v>
+        <v>1.1196119755464185E-2</v>
       </c>
       <c r="K28" s="3">
         <v>83282.006813596032</v>
@@ -5855,15 +5857,15 @@
       </c>
       <c r="AZ28" s="17">
         <f t="shared" si="6"/>
-        <v>179.29</v>
+        <v>179.69</v>
       </c>
       <c r="BA28" s="17">
         <f t="shared" si="7"/>
-        <v>36.044948280614832</v>
+        <v>36.444948280614831</v>
       </c>
       <c r="BB28" s="4">
         <f t="shared" si="8"/>
-        <v>0.20104271448834199</v>
+        <v>0.20282123813576064</v>
       </c>
       <c r="BC28" s="3">
         <f t="shared" si="0"/>
@@ -5927,14 +5929,14 @@
         <v>12</v>
       </c>
       <c r="H29" s="17">
-        <v>18.850709999999999</v>
+        <v>38.650710000000004</v>
       </c>
       <c r="I29" s="3">
-        <v>-0.41791048643062467</v>
+        <v>19.38208951356938</v>
       </c>
       <c r="J29" s="4">
         <f t="shared" si="2"/>
-        <v>-2.2169482551618727E-2</v>
+        <v>0.50146787765527145</v>
       </c>
       <c r="K29" s="3">
         <v>91755.335649669636</v>
@@ -6029,15 +6031,15 @@
       </c>
       <c r="AZ29" s="17">
         <f t="shared" si="6"/>
-        <v>66.850709999999992</v>
+        <v>86.650710000000004</v>
       </c>
       <c r="BA29" s="17">
         <f t="shared" si="7"/>
-        <v>-16.004358091651685</v>
+        <v>3.795641908348319</v>
       </c>
       <c r="BB29" s="4">
         <f t="shared" si="8"/>
-        <v>-0.23940445945378422</v>
+        <v>4.3803933151249641E-2</v>
       </c>
       <c r="BC29" s="3">
         <f t="shared" si="0"/>
@@ -6278,14 +6280,14 @@
         <v>100</v>
       </c>
       <c r="H31" s="17">
-        <v>69</v>
+        <v>83.5</v>
       </c>
       <c r="I31" s="3">
-        <v>-7.8140606242287447</v>
+        <v>6.6859393757712553</v>
       </c>
       <c r="J31" s="4">
         <f t="shared" si="2"/>
-        <v>-0.11324725542360499</v>
+        <v>8.0071130248757547E-2</v>
       </c>
       <c r="K31" s="3">
         <v>92547.060993046674</v>
@@ -6380,15 +6382,15 @@
       </c>
       <c r="AZ31" s="17">
         <f t="shared" si="6"/>
-        <v>449</v>
+        <v>463.5</v>
       </c>
       <c r="BA31" s="17">
         <f t="shared" si="7"/>
-        <v>118.69953931581642</v>
+        <v>133.19953931581642</v>
       </c>
       <c r="BB31" s="4">
         <f t="shared" si="8"/>
-        <v>0.26436423010204102</v>
+        <v>0.28737764685181538</v>
       </c>
       <c r="BC31" s="3">
         <f t="shared" si="0"/>
@@ -6453,14 +6455,14 @@
         <v>62.730000000000004</v>
       </c>
       <c r="H32" s="17">
-        <v>82.3</v>
+        <v>83.07</v>
       </c>
       <c r="I32" s="3">
-        <v>44.481880147597906</v>
+        <v>45.251880147597902</v>
       </c>
       <c r="J32" s="4">
         <f t="shared" si="2"/>
-        <v>0.54048457044468901</v>
+        <v>0.54474395266158548</v>
       </c>
       <c r="K32" s="3">
         <v>87949.115935818816</v>
@@ -6555,15 +6557,15 @@
       </c>
       <c r="AZ32" s="17">
         <f t="shared" si="6"/>
-        <v>265.54000000000002</v>
+        <v>266.31</v>
       </c>
       <c r="BA32" s="17">
         <f t="shared" si="7"/>
-        <v>102.92208463467099</v>
+        <v>103.69208463467099</v>
       </c>
       <c r="BB32" s="4">
         <f t="shared" si="8"/>
-        <v>0.38759540797872633</v>
+        <v>0.38936609453145204</v>
       </c>
       <c r="BC32" s="3">
         <f t="shared" si="0"/>
@@ -6807,14 +6809,14 @@
         <v>0</v>
       </c>
       <c r="H34" s="17">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="I34" s="3">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="J34" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" s="3">
         <v>0</v>
@@ -6909,15 +6911,15 @@
       </c>
       <c r="AZ34" s="17">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="BA34" s="17">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="BB34" s="4">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC34" s="3">
         <f t="shared" si="0"/>
@@ -6979,14 +6981,14 @@
         <v>8.6</v>
       </c>
       <c r="H35" s="17">
-        <v>7.67</v>
+        <v>8.59</v>
       </c>
       <c r="I35" s="3">
-        <v>1.0059072126352868</v>
+        <v>1.9259072126352867</v>
       </c>
       <c r="J35" s="4">
         <f t="shared" si="2"/>
-        <v>0.13114826761868145</v>
+        <v>0.22420340077244316</v>
       </c>
       <c r="K35" s="3">
         <v>95201.325533781623</v>
@@ -7081,18 +7083,18 @@
       </c>
       <c r="AZ35" s="17">
         <f t="shared" si="6"/>
-        <v>40.17</v>
+        <v>41.09</v>
       </c>
       <c r="BA35" s="17">
         <f t="shared" si="7"/>
-        <v>11.514401014331728</v>
+        <v>12.43440101433173</v>
       </c>
       <c r="BB35" s="4">
         <f t="shared" si="8"/>
-        <v>0.28664179771799175</v>
+        <v>0.30261379932664223</v>
       </c>
       <c r="BC35" s="3">
-        <f t="shared" ref="BC35:BC59" si="10">AVERAGE(K35,V35,AG35,AR35)</f>
+        <f t="shared" ref="BC35:BC62" si="10">AVERAGE(K35,V35,AG35,AR35)</f>
         <v>102341.42494881524</v>
       </c>
       <c r="BD35" s="7">
@@ -7153,14 +7155,14 @@
         <v>23.61</v>
       </c>
       <c r="H36" s="17">
-        <v>19.666775000000001</v>
+        <v>11.866775000000001</v>
       </c>
       <c r="I36" s="3">
-        <v>6.4909923722805818</v>
+        <v>-1.3090076277194189</v>
       </c>
       <c r="J36" s="4">
         <f t="shared" si="2"/>
-        <v>0.33004864154293634</v>
+        <v>-0.11030862451840696</v>
       </c>
       <c r="K36" s="3">
         <v>82348.641423246372</v>
@@ -7255,15 +7257,15 @@
       </c>
       <c r="AZ36" s="17">
         <f t="shared" si="6"/>
-        <v>96.375775000000004</v>
+        <v>88.575775000000007</v>
       </c>
       <c r="BA36" s="17">
         <f t="shared" si="7"/>
-        <v>39.71990970080649</v>
+        <v>31.919909700806492</v>
       </c>
       <c r="BB36" s="4">
         <f t="shared" si="8"/>
-        <v>0.41213582667227827</v>
+        <v>0.36036839306013962</v>
       </c>
       <c r="BC36" s="3">
         <f t="shared" si="10"/>
@@ -7331,14 +7333,14 @@
         <v>112</v>
       </c>
       <c r="H37" s="17">
-        <v>83.289999999999992</v>
+        <v>94.38</v>
       </c>
       <c r="I37" s="3">
-        <v>-31.864374589761098</v>
+        <v>-20.774374589761095</v>
       </c>
       <c r="J37" s="4">
         <f t="shared" si="2"/>
-        <v>-0.38257143222188861</v>
+        <v>-0.22011416179022139</v>
       </c>
       <c r="K37" s="3">
         <v>94388.83163095171</v>
@@ -7433,15 +7435,15 @@
       </c>
       <c r="AZ37" s="17">
         <f t="shared" si="6"/>
-        <v>397.28999999999996</v>
+        <v>408.38</v>
       </c>
       <c r="BA37" s="17">
         <f t="shared" si="7"/>
-        <v>-97.873810735972697</v>
+        <v>-86.783810735972693</v>
       </c>
       <c r="BB37" s="4">
         <f t="shared" si="8"/>
-        <v>-0.2463535722922115</v>
+        <v>-0.21250749482338188</v>
       </c>
       <c r="BC37" s="3">
         <f t="shared" si="10"/>
@@ -7531,14 +7533,14 @@
         <v>64</v>
       </c>
       <c r="S38" s="7">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="T38" s="3">
-        <v>25.261517563315643</v>
+        <v>21.261517563315643</v>
       </c>
       <c r="U38" s="4">
         <f t="shared" si="3"/>
-        <v>0.39471121192680692</v>
+        <v>0.35435862605526069</v>
       </c>
       <c r="V38" s="3">
         <v>110681.37839052675</v>
@@ -7607,15 +7609,15 @@
       </c>
       <c r="AZ38" s="17">
         <f t="shared" si="6"/>
-        <v>240.4</v>
+        <v>236.4</v>
       </c>
       <c r="BA38" s="17">
         <f t="shared" si="7"/>
-        <v>88.967750474779336</v>
+        <v>84.967750474779336</v>
       </c>
       <c r="BB38" s="4">
         <f t="shared" si="8"/>
-        <v>0.37008215671705214</v>
+        <v>0.35942364837047097</v>
       </c>
       <c r="BC38" s="3">
         <f t="shared" si="10"/>
@@ -7679,14 +7681,14 @@
         <v>15.5</v>
       </c>
       <c r="H39" s="17">
-        <v>15.617506000000001</v>
+        <v>17.672502000000001</v>
       </c>
       <c r="I39" s="3">
-        <v>7.2049330667986631</v>
+        <v>9.259929066798664</v>
       </c>
       <c r="J39" s="4">
         <f t="shared" si="2"/>
-        <v>0.46133698087253255</v>
+        <v>0.52397385875518154</v>
       </c>
       <c r="K39" s="3">
         <v>93473.032591125986</v>
@@ -7781,15 +7783,15 @@
       </c>
       <c r="AZ39" s="17">
         <f t="shared" si="6"/>
-        <v>65.617506000000006</v>
+        <v>67.672502000000009</v>
       </c>
       <c r="BA39" s="17">
         <f t="shared" si="7"/>
-        <v>29.443442387234239</v>
+        <v>31.498438387234238</v>
       </c>
       <c r="BB39" s="4">
         <f t="shared" si="8"/>
-        <v>0.44871321971966194</v>
+        <v>0.46545402425396115</v>
       </c>
       <c r="BC39" s="3">
         <f t="shared" si="10"/>
@@ -7853,14 +7855,14 @@
         <v>12</v>
       </c>
       <c r="H40" s="17">
-        <v>21.461610400000001</v>
+        <v>19.601610399999998</v>
       </c>
       <c r="I40" s="3">
-        <v>9.1148821293751645</v>
+        <v>7.2548821293751615</v>
       </c>
       <c r="J40" s="4">
         <f t="shared" si="2"/>
-        <v>0.4247063458656003</v>
+        <v>0.37011663742562512</v>
       </c>
       <c r="K40" s="3">
         <v>102889.40225520697</v>
@@ -7955,15 +7957,15 @@
       </c>
       <c r="AZ40" s="17">
         <f t="shared" si="6"/>
-        <v>67.461610399999998</v>
+        <v>65.601610399999998</v>
       </c>
       <c r="BA40" s="17">
         <f t="shared" si="7"/>
-        <v>14.370678836313207</v>
+        <v>12.510678836313204</v>
       </c>
       <c r="BB40" s="4">
         <f t="shared" si="8"/>
-        <v>0.21302009766895821</v>
+        <v>0.19070688600524363</v>
       </c>
       <c r="BC40" s="3">
         <f t="shared" si="10"/>
@@ -8203,14 +8205,14 @@
         <v>28.5</v>
       </c>
       <c r="H42" s="17">
-        <v>28.33</v>
+        <v>30.11</v>
       </c>
       <c r="I42" s="3">
-        <v>11.953775311772247</v>
+        <v>13.733775311772249</v>
       </c>
       <c r="J42" s="4">
         <f t="shared" si="2"/>
-        <v>0.42194759307349977</v>
+        <v>0.45612007013524575</v>
       </c>
       <c r="K42" s="3">
         <v>109174.83125485166</v>
@@ -8305,15 +8307,15 @@
       </c>
       <c r="AZ42" s="17">
         <f t="shared" si="6"/>
-        <v>104.83</v>
+        <v>106.61</v>
       </c>
       <c r="BA42" s="17">
         <f t="shared" si="7"/>
-        <v>34.412233840620672</v>
+        <v>36.192233840620673</v>
       </c>
       <c r="BB42" s="4">
         <f t="shared" si="8"/>
-        <v>0.3282670403569653</v>
+        <v>0.33948254235644565</v>
       </c>
       <c r="BC42" s="3">
         <f t="shared" si="10"/>
@@ -8407,14 +8409,14 @@
         <v>0</v>
       </c>
       <c r="S43" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T43" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U43" s="4">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="3">
         <v>0</v>
@@ -8483,15 +8485,15 @@
       </c>
       <c r="AZ43" s="17">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BA43" s="17">
         <f t="shared" si="7"/>
-        <v>9.9999999999999978E-2</v>
+        <v>3.1</v>
       </c>
       <c r="BB43" s="4">
         <f t="shared" si="8"/>
-        <v>9.9999999999999978E-2</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="BC43" s="3">
         <f t="shared" si="10"/>
@@ -8758,14 +8760,14 @@
         <v>43.296000000000006</v>
       </c>
       <c r="S45" s="7">
-        <v>43.296000000000006</v>
+        <v>30</v>
       </c>
       <c r="T45" s="3">
-        <v>28.030024451322483</v>
+        <v>14.734024451322476</v>
       </c>
       <c r="U45" s="4">
         <f t="shared" si="3"/>
-        <v>0.64740448196883038</v>
+        <v>0.49113414837741587</v>
       </c>
       <c r="V45" s="3">
         <v>127216.46290564603</v>
@@ -8834,15 +8836,15 @@
       </c>
       <c r="AZ45" s="17">
         <f t="shared" si="6"/>
-        <v>156.03080000000003</v>
+        <v>142.73480000000001</v>
       </c>
       <c r="BA45" s="17">
         <f t="shared" si="7"/>
-        <v>96.354713764260623</v>
+        <v>83.058713764260602</v>
       </c>
       <c r="BB45" s="4">
         <f t="shared" si="8"/>
-        <v>0.61753649769315166</v>
+        <v>0.5819093435116075</v>
       </c>
       <c r="BC45" s="3">
         <f t="shared" si="10"/>
@@ -8907,14 +8909,14 @@
         <v>19.099999999999998</v>
       </c>
       <c r="H46" s="17">
-        <v>25.450000000000003</v>
+        <v>24.310000000000002</v>
       </c>
       <c r="I46" s="3">
-        <v>11.208902406452644</v>
+        <v>10.068902406452644</v>
       </c>
       <c r="J46" s="4">
         <f t="shared" si="2"/>
-        <v>0.44042838532230422</v>
+        <v>0.41418767611898982</v>
       </c>
       <c r="K46" s="3">
         <v>74953.145229196627</v>
@@ -8933,14 +8935,14 @@
         <v>20.399999999999999</v>
       </c>
       <c r="S46" s="7">
-        <v>20.399999999999999</v>
+        <v>21.4</v>
       </c>
       <c r="T46" s="3">
-        <v>4.7347926470979029</v>
+        <v>5.7347926470979029</v>
       </c>
       <c r="U46" s="4">
         <f t="shared" si="3"/>
-        <v>0.23209767877930898</v>
+        <v>0.26798096481765904</v>
       </c>
       <c r="V46" s="3">
         <v>82448.459752116294</v>
@@ -9009,15 +9011,15 @@
       </c>
       <c r="AZ46" s="17">
         <f t="shared" si="6"/>
-        <v>87.6</v>
+        <v>87.460000000000008</v>
       </c>
       <c r="BA46" s="17">
         <f t="shared" si="7"/>
-        <v>26.363280347746354</v>
+        <v>26.223280347746353</v>
       </c>
       <c r="BB46" s="4">
         <f t="shared" si="8"/>
-        <v>0.30095068890121413</v>
+        <v>0.29983169846497087</v>
       </c>
       <c r="BC46" s="3">
         <f t="shared" si="10"/>
@@ -9082,14 +9084,14 @@
         <v>12</v>
       </c>
       <c r="H47" s="17">
-        <v>10.2751</v>
+        <v>14.6951</v>
       </c>
       <c r="I47" s="3">
-        <v>2.6676429183629997</v>
+        <v>7.0876429183629996</v>
       </c>
       <c r="J47" s="4">
         <f t="shared" si="2"/>
-        <v>0.25962208819018789</v>
+        <v>0.48231335059734193</v>
       </c>
       <c r="K47" s="3">
         <v>108677.95830910001</v>
@@ -9184,15 +9186,15 @@
       </c>
       <c r="AZ47" s="17">
         <f t="shared" si="6"/>
-        <v>46.275100000000002</v>
+        <v>50.695099999999996</v>
       </c>
       <c r="BA47" s="17">
         <f t="shared" si="7"/>
-        <v>13.563034548960896</v>
+        <v>17.983034548960894</v>
       </c>
       <c r="BB47" s="4">
         <f t="shared" si="8"/>
-        <v>0.29309573720987953</v>
+        <v>0.35472924501501912</v>
       </c>
       <c r="BC47" s="3">
         <f t="shared" si="10"/>
@@ -9611,14 +9613,14 @@
         <v>21.75</v>
       </c>
       <c r="H50" s="17">
-        <v>21.601290000000002</v>
+        <v>22.341290000000001</v>
       </c>
       <c r="I50" s="3">
-        <v>17.561290000000003</v>
+        <v>18.301290000000002</v>
       </c>
       <c r="J50" s="4">
         <f t="shared" si="2"/>
-        <v>0.81297413256337936</v>
+        <v>0.81916890206429449</v>
       </c>
       <c r="K50" s="3">
         <v>101000</v>
@@ -9636,7 +9638,8 @@
       <c r="R50" s="7">
         <v>24.900000000000002</v>
       </c>
-      <c r="S50" s="7">
+      <c r="S50" s="3">
+        <f>R50</f>
         <v>24.900000000000002</v>
       </c>
       <c r="T50" s="3">
@@ -9713,15 +9716,15 @@
       </c>
       <c r="AZ50" s="17">
         <f t="shared" si="6"/>
-        <v>91.951290000000014</v>
+        <v>92.691290000000009</v>
       </c>
       <c r="BA50" s="17">
         <f t="shared" si="7"/>
-        <v>74.57929</v>
+        <v>75.319289999999995</v>
       </c>
       <c r="BB50" s="4">
         <f t="shared" si="8"/>
-        <v>0.81107388487970089</v>
+        <v>0.8125821746574029</v>
       </c>
       <c r="BC50" s="3">
         <f t="shared" si="10"/>
@@ -9809,14 +9812,14 @@
         <v>109.5</v>
       </c>
       <c r="S51" s="7">
-        <v>109.5</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="T51" s="3">
-        <v>88.56046918061314</v>
+        <v>-15.839530819386864</v>
       </c>
       <c r="U51" s="4">
         <f t="shared" si="3"/>
-        <v>0.8087714080421291</v>
+        <v>-3.1057903567425225</v>
       </c>
       <c r="V51" s="3">
         <v>116330.72677437146</v>
@@ -9885,15 +9888,15 @@
       </c>
       <c r="AZ51" s="17">
         <f t="shared" si="6"/>
-        <v>388.5</v>
+        <v>284.10000000000002</v>
       </c>
       <c r="BA51" s="17">
         <f t="shared" si="7"/>
-        <v>306.64547043330589</v>
+        <v>202.24547043330591</v>
       </c>
       <c r="BB51" s="4">
         <f t="shared" si="8"/>
-        <v>0.78930623020155954</v>
+        <v>0.71188127572441362</v>
       </c>
       <c r="BC51" s="3">
         <f t="shared" si="10"/>
@@ -10153,14 +10156,14 @@
         <v>1</v>
       </c>
       <c r="S53" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T53" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U53" s="4">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V53" s="3">
         <v>133743.22713362068</v>
@@ -10229,11 +10232,11 @@
       </c>
       <c r="AZ53" s="17">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA53" s="17">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB53" s="4">
         <f t="shared" si="8"/>
@@ -10471,14 +10474,14 @@
         <v>60.514180000000003</v>
       </c>
       <c r="H55" s="17">
-        <v>12.75</v>
+        <v>32.5</v>
       </c>
       <c r="I55" s="3">
-        <v>-19.727263363801356</v>
+        <v>2.2736636198644078E-2</v>
       </c>
       <c r="J55" s="4">
         <f t="shared" si="2"/>
-        <v>-1.5472363422589299</v>
+        <v>6.9958880611212552E-4</v>
       </c>
       <c r="K55" s="3">
         <v>50745.724005939614</v>
@@ -10573,15 +10576,15 @@
       </c>
       <c r="AZ55" s="17">
         <f t="shared" si="6"/>
-        <v>486.49518</v>
+        <v>506.24518</v>
       </c>
       <c r="BA55" s="17">
         <f t="shared" si="7"/>
-        <v>346.84294753565422</v>
+        <v>366.59294753565422</v>
       </c>
       <c r="BB55" s="4">
         <f t="shared" si="8"/>
-        <v>0.7129422074349312</v>
+        <v>0.72414111189296504</v>
       </c>
       <c r="BC55" s="3">
         <f t="shared" si="10"/>
@@ -10669,14 +10672,14 @@
         <v>24</v>
       </c>
       <c r="S56" s="7">
-        <v>24</v>
+        <v>6.5</v>
       </c>
       <c r="T56" s="3">
-        <v>21.333600000000001</v>
+        <v>3.8336000000000001</v>
       </c>
       <c r="U56" s="4">
         <f t="shared" si="3"/>
-        <v>0.88890000000000002</v>
+        <v>0.58978461538461535</v>
       </c>
       <c r="V56" s="3">
         <v>111100.00000000001</v>
@@ -10745,15 +10748,15 @@
       </c>
       <c r="AZ56" s="17">
         <f t="shared" si="6"/>
-        <v>117.77106000000001</v>
+        <v>100.27106000000001</v>
       </c>
       <c r="BA56" s="17">
         <f t="shared" si="7"/>
-        <v>107.34786</v>
+        <v>89.847859999999997</v>
       </c>
       <c r="BB56" s="4">
         <f t="shared" si="8"/>
-        <v>0.91149608401248994</v>
+        <v>0.89604976750021381</v>
       </c>
       <c r="BC56" s="3">
         <f t="shared" si="10"/>
@@ -10845,14 +10848,14 @@
         <v>64</v>
       </c>
       <c r="S57" s="7">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="T57" s="3">
-        <v>59.070056744754275</v>
+        <v>25.070056744754275</v>
       </c>
       <c r="U57" s="4">
         <f t="shared" si="3"/>
-        <v>0.92296963663678555</v>
+        <v>0.83566855815847585</v>
       </c>
       <c r="V57" s="3">
         <v>492994.3255245724</v>
@@ -10921,15 +10924,15 @@
       </c>
       <c r="AZ57" s="17">
         <f t="shared" si="6"/>
-        <v>332</v>
+        <v>298</v>
       </c>
       <c r="BA57" s="17">
         <f t="shared" si="7"/>
-        <v>312.72840363858489</v>
+        <v>278.72840363858489</v>
       </c>
       <c r="BB57" s="4">
         <f t="shared" si="8"/>
-        <v>0.94195302300778583</v>
+        <v>0.93533021355229828</v>
       </c>
       <c r="BC57" s="3">
         <f t="shared" si="10"/>
@@ -11013,13 +11016,19 @@
       </c>
       <c r="Q58" s="15"/>
       <c r="R58" s="3"/>
-      <c r="S58" s="3"/>
-      <c r="T58" s="3"/>
+      <c r="S58" s="7">
+        <v>23</v>
+      </c>
+      <c r="T58" s="3">
+        <v>23</v>
+      </c>
       <c r="U58" s="4">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="V58" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="V58" s="3">
+        <v>99000.000000000015</v>
+      </c>
       <c r="W58" s="17">
         <v>0</v>
       </c>
@@ -11070,19 +11079,19 @@
       </c>
       <c r="AZ58" s="17">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="BA58" s="17">
         <f t="shared" si="7"/>
-        <v>0.85000000000000009</v>
+        <v>23.85</v>
       </c>
       <c r="BB58" s="4">
         <f t="shared" si="8"/>
-        <v>0.21250000000000002</v>
+        <v>0.88333333333333341</v>
       </c>
       <c r="BC58" s="3">
         <f t="shared" si="10"/>
-        <v>94500</v>
+        <v>96000</v>
       </c>
       <c r="BD58" s="7">
         <f t="shared" si="11"/>
@@ -11162,13 +11171,19 @@
       </c>
       <c r="Q59" s="15"/>
       <c r="R59" s="3"/>
-      <c r="S59" s="3"/>
-      <c r="T59" s="3"/>
+      <c r="S59" s="7">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="T59" s="3">
+        <v>5.0999999999999996</v>
+      </c>
       <c r="U59" s="4">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="V59" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="V59" s="3">
+        <v>99000.000000000015</v>
+      </c>
       <c r="W59" s="17">
         <v>0</v>
       </c>
@@ -11219,19 +11234,19 @@
       </c>
       <c r="AZ59" s="17">
         <f t="shared" si="6"/>
-        <v>5.25</v>
+        <v>10.35</v>
       </c>
       <c r="BA59" s="17">
         <f t="shared" si="7"/>
-        <v>3.7199999999999998</v>
+        <v>8.82</v>
       </c>
       <c r="BB59" s="4">
         <f t="shared" si="8"/>
-        <v>0.70857142857142852</v>
+        <v>0.85217391304347834</v>
       </c>
       <c r="BC59" s="3">
         <f t="shared" si="10"/>
-        <v>94500</v>
+        <v>96000</v>
       </c>
       <c r="BD59" s="7">
         <f t="shared" si="11"/>
@@ -11285,29 +11300,39 @@
       <c r="E60" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="G60" s="23">
+      <c r="G60" s="22">
         <v>217</v>
       </c>
-      <c r="H60" s="24">
-        <v>0</v>
-      </c>
-      <c r="I60" s="16">
-        <v>0</v>
-      </c>
-      <c r="J60" s="25">
+      <c r="H60" s="17">
+        <v>0</v>
+      </c>
+      <c r="I60" s="3">
+        <v>0</v>
+      </c>
+      <c r="J60" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K60" s="16">
-        <v>0</v>
-      </c>
-      <c r="L60" s="24">
+      <c r="K60" s="3">
+        <v>0</v>
+      </c>
+      <c r="L60" s="23">
         <v>0</v>
       </c>
       <c r="M60" s="17"/>
-      <c r="R60" s="28">
-        <f>506+12</f>
-        <v>518</v>
+      <c r="R60" s="25"/>
+      <c r="S60" s="7">
+        <v>0</v>
+      </c>
+      <c r="T60" s="3">
+        <v>0</v>
+      </c>
+      <c r="U60" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V60" s="3">
+        <v>0</v>
       </c>
       <c r="X60" s="17"/>
       <c r="AC60" s="16">
@@ -11318,20 +11343,30 @@
         <v>0</v>
       </c>
       <c r="AI60" s="17"/>
-      <c r="AN60" s="24">
+      <c r="AN60" s="23">
         <f>1013+12</f>
         <v>1025</v>
       </c>
       <c r="AY60" s="17">
         <f t="shared" si="5"/>
-        <v>2531</v>
+        <v>2013</v>
       </c>
       <c r="AZ60" s="17">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BA60" s="18"/>
-      <c r="BB60" s="22"/>
+      <c r="BA60" s="17">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BB60" s="4">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="BC60" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="BD60" s="18"/>
       <c r="BH60" s="7"/>
     </row>
@@ -11345,38 +11380,107 @@
       <c r="C61" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="D61" s="26" t="s">
+      <c r="D61" s="24" t="s">
         <v>118</v>
       </c>
       <c r="E61" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G61" s="18"/>
-      <c r="H61" s="27">
+      <c r="H61" s="17">
         <v>25</v>
       </c>
-      <c r="I61" s="27">
-        <v>18.829519600000001</v>
-      </c>
-      <c r="J61" s="25">
-        <f>(H61-I61)/H61</f>
+      <c r="I61" s="3">
+        <v>6.1704803999999989</v>
+      </c>
+      <c r="J61" s="4">
+        <f t="shared" si="2"/>
         <v>0.24681921599999995</v>
       </c>
-      <c r="K61">
-        <v>117684.4975</v>
-      </c>
-      <c r="L61" s="24">
+      <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="23">
         <v>5.2</v>
       </c>
       <c r="R61" s="18"/>
-      <c r="S61" s="18"/>
-      <c r="T61" s="18"/>
+      <c r="S61" s="7">
+        <v>29.36</v>
+      </c>
+      <c r="T61" s="3">
+        <v>17.598559999999999</v>
+      </c>
+      <c r="U61" s="4">
+        <f t="shared" si="3"/>
+        <v>0.59940599455040866</v>
+      </c>
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
       <c r="AD61" s="18"/>
       <c r="AE61" s="18"/>
       <c r="AO61" s="18"/>
       <c r="AZ61" s="17">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>54.36</v>
+      </c>
+      <c r="BA61" s="17">
+        <f t="shared" si="7"/>
+        <v>23.769040399999998</v>
+      </c>
+      <c r="BB61" s="4">
+        <f t="shared" si="8"/>
+        <v>0.4372523988226637</v>
+      </c>
+      <c r="BC61" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:78" x14ac:dyDescent="0.35">
+      <c r="A62" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="B62" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="C62" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="D62" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="E62" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="S62" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="T62" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="U62" s="4">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AZ62" s="17">
+        <f t="shared" si="6"/>
+        <v>3.2</v>
+      </c>
+      <c r="BA62" s="17">
+        <f t="shared" si="7"/>
+        <v>3.2</v>
+      </c>
+      <c r="BB62" s="4">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="BC62" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -11413,45 +11517,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.35">
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
-      <c r="S1" s="29" t="s">
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="S1" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="T1" s="29"/>
-      <c r="U1" s="29"/>
-      <c r="V1" s="29"/>
-      <c r="W1" s="29"/>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="29"/>
-      <c r="AA1" s="29"/>
-      <c r="AB1" s="29"/>
-      <c r="AC1" s="29"/>
-      <c r="AE1" s="29" t="s">
+      <c r="T1" s="26"/>
+      <c r="U1" s="26"/>
+      <c r="V1" s="26"/>
+      <c r="W1" s="26"/>
+      <c r="X1" s="26"/>
+      <c r="Y1" s="26"/>
+      <c r="Z1" s="26"/>
+      <c r="AA1" s="26"/>
+      <c r="AB1" s="26"/>
+      <c r="AC1" s="26"/>
+      <c r="AE1" s="26" t="s">
         <v>126</v>
       </c>
-      <c r="AF1" s="29"/>
-      <c r="AG1" s="29"/>
-      <c r="AH1" s="29"/>
-      <c r="AI1" s="29"/>
-      <c r="AJ1" s="29"/>
-      <c r="AK1" s="29"/>
-      <c r="AL1" s="29"/>
-      <c r="AM1" s="29"/>
-      <c r="AN1" s="29"/>
-      <c r="AO1" s="29"/>
+      <c r="AF1" s="26"/>
+      <c r="AG1" s="26"/>
+      <c r="AH1" s="26"/>
+      <c r="AI1" s="26"/>
+      <c r="AJ1" s="26"/>
+      <c r="AK1" s="26"/>
+      <c r="AL1" s="26"/>
+      <c r="AM1" s="26"/>
+      <c r="AN1" s="26"/>
+      <c r="AO1" s="26"/>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -15702,7 +15806,7 @@
         <v>0</v>
       </c>
       <c r="K60" s="16"/>
-      <c r="L60" s="24">
+      <c r="L60" s="23">
         <v>0</v>
       </c>
       <c r="M60" s="17"/>
@@ -15715,7 +15819,7 @@
       <c r="U60" s="3"/>
       <c r="V60" s="4"/>
       <c r="W60" s="16"/>
-      <c r="X60" s="24"/>
+      <c r="X60" s="23"/>
       <c r="Y60" s="17"/>
       <c r="AE60" s="14">
         <v>72.3</v>
@@ -15726,7 +15830,7 @@
       <c r="AG60" s="3"/>
       <c r="AH60" s="4"/>
       <c r="AI60" s="16"/>
-      <c r="AJ60" s="24"/>
+      <c r="AJ60" s="23"/>
       <c r="AK60" s="17"/>
     </row>
     <row r="61" spans="1:41" x14ac:dyDescent="0.35">
@@ -15739,7 +15843,7 @@
       <c r="C61" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="D61" s="26" t="s">
+      <c r="D61" s="24" t="s">
         <v>118</v>
       </c>
       <c r="E61" s="16" t="s">
@@ -15758,7 +15862,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L61" s="24">
+      <c r="L61" s="23">
         <v>5.2</v>
       </c>
       <c r="S61" s="14">
@@ -15769,7 +15873,7 @@
       </c>
       <c r="U61" s="3"/>
       <c r="V61" s="4"/>
-      <c r="X61" s="24"/>
+      <c r="X61" s="23"/>
       <c r="AE61" s="14">
         <v>0</v>
       </c>
@@ -15778,7 +15882,7 @@
       </c>
       <c r="AG61" s="3"/>
       <c r="AH61" s="4"/>
-      <c r="AJ61" s="24"/>
+      <c r="AJ61" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/CEO Review.xlsx
+++ b/CEO Review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://peoplestronghrservices-my.sharepoint.com/personal/baljeet_singh_taggd_in/Documents/Desktop/Clude Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1890" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65219F3F-15DC-47EB-9681-BF5DD139218B}"/>
+  <xr:revisionPtr revIDLastSave="1914" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5EAE574-1183-4DAE-9559-528D8495C3FD}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F2C8E0B5-D69E-42FC-A0A4-20379F29D696}"/>
   </bookViews>
@@ -570,7 +570,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -642,12 +642,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1479,7 +1473,6 @@
         <v>100</v>
       </c>
       <c r="BP3">
-        <f>12000000/100000</f>
         <v>120</v>
       </c>
       <c r="BT3" s="5" t="s">
@@ -1654,8 +1647,7 @@
       </c>
       <c r="BN4" s="21"/>
       <c r="BP4">
-        <f>225620/100000</f>
-        <v>2.2562000000000002</v>
+        <v>2.25</v>
       </c>
       <c r="BT4" s="5" t="s">
         <v>101</v>
@@ -1827,9 +1819,6 @@
       <c r="BL5" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="BP5">
-        <v>0</v>
-      </c>
       <c r="BR5">
         <f>531000/100000</f>
         <v>5.31</v>
@@ -2005,11 +1994,9 @@
         <v>100</v>
       </c>
       <c r="BN6" s="21">
-        <f>5066901/100000</f>
-        <v>50.66901</v>
+        <v>50.66</v>
       </c>
       <c r="BP6">
-        <f>2650000/100000</f>
         <v>26.5</v>
       </c>
       <c r="BR6">
@@ -2187,12 +2174,10 @@
         <v>100</v>
       </c>
       <c r="BN7" s="21">
-        <f>5310000/100000</f>
-        <v>53.1</v>
+        <v>39.369999999999997</v>
       </c>
       <c r="BP7">
-        <f>611850/100000</f>
-        <v>6.1185</v>
+        <v>6.11</v>
       </c>
       <c r="BT7" s="5" t="s">
         <v>101</v>
@@ -2366,8 +2351,7 @@
       </c>
       <c r="BN8" s="21"/>
       <c r="BP8">
-        <f>1305250/100000</f>
-        <v>13.0525</v>
+        <v>2.15</v>
       </c>
       <c r="BT8" s="5" t="s">
         <v>101</v>
@@ -2540,10 +2524,6 @@
         <v>100</v>
       </c>
       <c r="BN9" s="21"/>
-      <c r="BP9">
-        <f>458000/100000</f>
-        <v>4.58</v>
-      </c>
       <c r="BR9">
         <f>2553800/100000</f>
         <v>25.538</v>
@@ -2719,9 +2699,6 @@
         <v>100</v>
       </c>
       <c r="BN10" s="21"/>
-      <c r="BP10">
-        <v>0</v>
-      </c>
       <c r="BR10">
         <f>31266/100000</f>
         <v>0.31265999999999999</v>
@@ -2896,13 +2873,9 @@
       <c r="BL11" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="BN11" s="21">
-        <f>1371147/100000</f>
-        <v>13.71147</v>
-      </c>
+      <c r="BN11" s="21"/>
       <c r="BP11">
-        <f>1279000/100000</f>
-        <v>12.79</v>
+        <v>5.23</v>
       </c>
       <c r="BT11" s="5" t="s">
         <v>101</v>
@@ -3075,9 +3048,6 @@
         <v>100</v>
       </c>
       <c r="BN12" s="21"/>
-      <c r="BP12">
-        <v>0</v>
-      </c>
       <c r="BT12" s="5" t="s">
         <v>101</v>
       </c>
@@ -3250,8 +3220,7 @@
       </c>
       <c r="BN13" s="21"/>
       <c r="BP13">
-        <f>378500/100000</f>
-        <v>3.7850000000000001</v>
+        <v>3.78</v>
       </c>
       <c r="BT13" s="5" t="s">
         <v>101</v>
@@ -3423,14 +3392,7 @@
       <c r="BL14" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="BN14" s="21">
-        <f>809775/100000</f>
-        <v>8.0977499999999996</v>
-      </c>
-      <c r="BP14">
-        <f>90000/100000</f>
-        <v>0.9</v>
-      </c>
+      <c r="BN14" s="21"/>
       <c r="BT14" s="5" t="s">
         <v>101</v>
       </c>
@@ -3602,9 +3564,6 @@
         <v>100</v>
       </c>
       <c r="BN15" s="21"/>
-      <c r="BP15">
-        <v>0</v>
-      </c>
       <c r="BT15" s="5" t="s">
         <v>101</v>
       </c>
@@ -3773,13 +3732,7 @@
       <c r="BL16" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="BN16" s="21">
-        <f>12920/100000</f>
-        <v>0.12920000000000001</v>
-      </c>
-      <c r="BP16">
-        <v>0</v>
-      </c>
+      <c r="BN16" s="21"/>
       <c r="BT16" s="5" t="s">
         <v>101</v>
       </c>
@@ -3951,9 +3904,6 @@
         <v>100</v>
       </c>
       <c r="BN17" s="21"/>
-      <c r="BP17">
-        <v>0</v>
-      </c>
       <c r="BR17">
         <f>17110481/100000</f>
         <v>171.10480999999999</v>
@@ -4129,9 +4079,6 @@
         <v>100</v>
       </c>
       <c r="BN18" s="21"/>
-      <c r="BP18">
-        <v>0</v>
-      </c>
       <c r="BT18" s="5" t="s">
         <v>101</v>
       </c>
@@ -4301,10 +4248,6 @@
         <v>100</v>
       </c>
       <c r="BN19" s="21"/>
-      <c r="BP19">
-        <f>3998750/100000</f>
-        <v>39.987499999999997</v>
-      </c>
       <c r="BT19" s="5" t="s">
         <v>101</v>
       </c>
@@ -4476,10 +4419,6 @@
         <v>100</v>
       </c>
       <c r="BN20" s="21"/>
-      <c r="BP20">
-        <f>699080/100000</f>
-        <v>6.9908000000000001</v>
-      </c>
       <c r="BR20">
         <f>3300161/100000</f>
         <v>33.001609999999999</v>
@@ -4654,13 +4593,9 @@
       <c r="BL21" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="BN21" s="21">
-        <f>6916924/100000</f>
-        <v>69.169240000000002</v>
-      </c>
+      <c r="BN21" s="21"/>
       <c r="BP21">
-        <f>2627983/100000</f>
-        <v>26.27983</v>
+        <v>26.27</v>
       </c>
       <c r="BT21" s="5" t="s">
         <v>101</v>
@@ -4834,7 +4769,8 @@
       </c>
       <c r="BN22" s="21"/>
       <c r="BP22">
-        <v>0</v>
+        <f>10000/100000</f>
+        <v>0.1</v>
       </c>
       <c r="BT22" s="5" t="s">
         <v>101</v>
@@ -5007,12 +4943,11 @@
         <v>100</v>
       </c>
       <c r="BN23" s="21">
-        <f>622857.14/100000</f>
-        <v>6.2285713999999999</v>
+        <v>6.22</v>
       </c>
       <c r="BP23">
-        <f>68445/100000</f>
-        <v>0.68445</v>
+        <f>68000/100000</f>
+        <v>0.68</v>
       </c>
       <c r="BR23">
         <f>1692607/100000</f>
@@ -5187,9 +5122,6 @@
         <v>100</v>
       </c>
       <c r="BN24" s="21"/>
-      <c r="BP24">
-        <v>0</v>
-      </c>
       <c r="BR24">
         <f>10643418/100000</f>
         <v>106.43418</v>
@@ -5365,9 +5297,6 @@
         <v>100</v>
       </c>
       <c r="BN25" s="21"/>
-      <c r="BP25">
-        <v>0</v>
-      </c>
       <c r="BR25">
         <f>1952868/100000</f>
         <v>19.528680000000001</v>
@@ -5544,8 +5473,7 @@
       </c>
       <c r="BN26" s="21"/>
       <c r="BP26">
-        <f>2422348/100000</f>
-        <v>24.223479999999999</v>
+        <v>24.22</v>
       </c>
       <c r="BR26">
         <f>5954090/100000</f>
@@ -5720,9 +5648,6 @@
         <v>100</v>
       </c>
       <c r="BN27" s="21"/>
-      <c r="BP27">
-        <v>0</v>
-      </c>
       <c r="BT27" s="5" t="s">
         <v>101</v>
       </c>
@@ -5892,9 +5817,6 @@
         <v>100</v>
       </c>
       <c r="BN28" s="21"/>
-      <c r="BP28">
-        <v>0</v>
-      </c>
       <c r="BT28" s="5" t="s">
         <v>101</v>
       </c>
@@ -6066,10 +5988,6 @@
         <v>100</v>
       </c>
       <c r="BN29" s="21"/>
-      <c r="BP29">
-        <f>549471/100000</f>
-        <v>5.4947100000000004</v>
-      </c>
       <c r="BR29">
         <f>1992034/100000</f>
         <v>19.920339999999999</v>
@@ -6245,9 +6163,6 @@
         <v>100</v>
       </c>
       <c r="BN30" s="21"/>
-      <c r="BP30">
-        <v>0</v>
-      </c>
       <c r="BT30" s="5" t="s">
         <v>101</v>
       </c>
@@ -6417,10 +6332,6 @@
         <v>100</v>
       </c>
       <c r="BN31" s="21"/>
-      <c r="BP31">
-        <f>2650000/100000</f>
-        <v>26.5</v>
-      </c>
       <c r="BT31" s="5" t="s">
         <v>101</v>
       </c>
@@ -6592,12 +6503,7 @@
         <v>100</v>
       </c>
       <c r="BN32" s="21">
-        <f>1675000/100000</f>
         <v>16.75</v>
-      </c>
-      <c r="BP32">
-        <f>3080000/100000</f>
-        <v>30.8</v>
       </c>
       <c r="BT32" s="5" t="s">
         <v>101</v>
@@ -6770,9 +6676,6 @@
         <v>100</v>
       </c>
       <c r="BN33" s="21"/>
-      <c r="BP33">
-        <v>0</v>
-      </c>
       <c r="BR33">
         <f>417121/100000</f>
         <v>4.1712100000000003</v>
@@ -6946,9 +6849,6 @@
         <v>100</v>
       </c>
       <c r="BN34" s="21"/>
-      <c r="BP34">
-        <v>0</v>
-      </c>
       <c r="BT34" s="5" t="s">
         <v>101</v>
       </c>
@@ -7118,9 +7018,6 @@
         <v>100</v>
       </c>
       <c r="BN35" s="21"/>
-      <c r="BP35">
-        <v>0</v>
-      </c>
       <c r="BT35" s="5" t="s">
         <v>101</v>
       </c>
@@ -7291,14 +7188,7 @@
       <c r="BL36" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="BN36" s="21">
-        <f>313160/100000</f>
-        <v>3.1316000000000002</v>
-      </c>
-      <c r="BP36">
-        <f>360677.5/100000</f>
-        <v>3.6067749999999998</v>
-      </c>
+      <c r="BN36" s="21"/>
       <c r="BT36" s="5" t="s">
         <v>101</v>
       </c>
@@ -7470,9 +7360,6 @@
         <v>100</v>
       </c>
       <c r="BN37" s="21"/>
-      <c r="BP37">
-        <v>37.19</v>
-      </c>
       <c r="BT37" s="5" t="s">
         <v>101</v>
       </c>
@@ -7644,9 +7531,6 @@
         <v>100</v>
       </c>
       <c r="BN38" s="21"/>
-      <c r="BP38">
-        <v>0</v>
-      </c>
       <c r="BT38" s="5" t="s">
         <v>101</v>
       </c>
@@ -7818,9 +7702,6 @@
         <v>100</v>
       </c>
       <c r="BN39" s="21"/>
-      <c r="BP39">
-        <v>0</v>
-      </c>
       <c r="BT39" s="5" t="s">
         <v>101</v>
       </c>
@@ -7992,9 +7873,6 @@
         <v>100</v>
       </c>
       <c r="BN40" s="21"/>
-      <c r="BP40">
-        <v>0</v>
-      </c>
       <c r="BR40">
         <f>1677628/100000</f>
         <v>16.77628</v>
@@ -8170,9 +8048,6 @@
         <v>100</v>
       </c>
       <c r="BN41" s="21"/>
-      <c r="BP41">
-        <v>0</v>
-      </c>
       <c r="BT41" s="5" t="s">
         <v>101</v>
       </c>
@@ -8341,14 +8216,7 @@
       <c r="BL42" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="BN42" s="21">
-        <f>422500/100000</f>
-        <v>4.2249999999999996</v>
-      </c>
-      <c r="BP42">
-        <f>1017000/100000</f>
-        <v>10.17</v>
-      </c>
+      <c r="BN42" s="21"/>
       <c r="BT42" s="5" t="s">
         <v>101</v>
       </c>
@@ -8520,9 +8388,6 @@
         <v>100</v>
       </c>
       <c r="BN43" s="21"/>
-      <c r="BP43">
-        <v>0</v>
-      </c>
       <c r="BT43" s="5" t="s">
         <v>101</v>
       </c>
@@ -8692,8 +8557,7 @@
         <v>100</v>
       </c>
       <c r="BN44" s="21">
-        <f>1308437.5/100000</f>
-        <v>13.084375</v>
+        <v>13.08</v>
       </c>
       <c r="BP44">
         <v>2.9</v>
@@ -8871,8 +8735,7 @@
         <v>100</v>
       </c>
       <c r="BN45" s="21">
-        <f>1970400/100000</f>
-        <v>19.704000000000001</v>
+        <v>19.7</v>
       </c>
       <c r="BP45">
         <v>7.97</v>
@@ -9046,10 +8909,6 @@
         <v>100</v>
       </c>
       <c r="BN46" s="21"/>
-      <c r="BP46">
-        <f>1065000/100000</f>
-        <v>10.65</v>
-      </c>
       <c r="BT46" s="5" t="s">
         <v>101</v>
       </c>
@@ -9221,9 +9080,6 @@
         <v>100</v>
       </c>
       <c r="BN47" s="21"/>
-      <c r="BP47">
-        <v>0</v>
-      </c>
       <c r="BT47" s="5" t="s">
         <v>101</v>
       </c>
@@ -9393,11 +9249,9 @@
         <v>100</v>
       </c>
       <c r="BN48" s="21">
-        <f>422210/100000</f>
-        <v>4.2221000000000002</v>
+        <v>4.22</v>
       </c>
       <c r="BP48">
-        <f>5000000/100000</f>
         <v>50</v>
       </c>
       <c r="BR48">
@@ -9574,7 +9428,6 @@
       </c>
       <c r="BN49" s="21"/>
       <c r="BP49">
-        <f>1700000/100000</f>
         <v>17</v>
       </c>
       <c r="BR49">
@@ -9751,9 +9604,6 @@
         <v>100</v>
       </c>
       <c r="BN50" s="21"/>
-      <c r="BP50">
-        <v>0</v>
-      </c>
       <c r="BT50" s="5" t="s">
         <v>101</v>
       </c>
@@ -9923,9 +9773,6 @@
         <v>100</v>
       </c>
       <c r="BN51" s="21"/>
-      <c r="BP51">
-        <v>0</v>
-      </c>
       <c r="BT51" s="5" t="s">
         <v>101</v>
       </c>
@@ -10095,9 +9942,6 @@
         <v>100</v>
       </c>
       <c r="BN52" s="21"/>
-      <c r="BP52">
-        <v>0</v>
-      </c>
       <c r="BT52" s="5" t="s">
         <v>101</v>
       </c>
@@ -10267,9 +10111,6 @@
         <v>100</v>
       </c>
       <c r="BN53" s="21"/>
-      <c r="BP53">
-        <v>0</v>
-      </c>
       <c r="BT53" s="5" t="s">
         <v>101</v>
       </c>
@@ -10439,9 +10280,6 @@
         <v>100</v>
       </c>
       <c r="BN54" s="21"/>
-      <c r="BP54">
-        <v>0</v>
-      </c>
       <c r="BT54" s="5" t="s">
         <v>101</v>
       </c>
@@ -10611,9 +10449,6 @@
         <v>100</v>
       </c>
       <c r="BN55" s="21"/>
-      <c r="BP55">
-        <v>0</v>
-      </c>
       <c r="BT55" s="5" t="s">
         <v>101</v>
       </c>
@@ -10783,9 +10618,6 @@
         <v>100</v>
       </c>
       <c r="BN56" s="21"/>
-      <c r="BP56">
-        <v>0</v>
-      </c>
       <c r="BR56">
         <f>175278/100000</f>
         <v>1.75278</v>
@@ -10959,9 +10791,6 @@
         <v>100</v>
       </c>
       <c r="BN57" s="21"/>
-      <c r="BP57">
-        <v>0</v>
-      </c>
       <c r="BT57" s="5" t="s">
         <v>101</v>
       </c>
@@ -11114,9 +10943,6 @@
         <v>100</v>
       </c>
       <c r="BN58" s="21"/>
-      <c r="BP58">
-        <v>0</v>
-      </c>
       <c r="BT58" s="5" t="s">
         <v>101</v>
       </c>
@@ -11270,7 +11096,6 @@
       </c>
       <c r="BN59" s="21"/>
       <c r="BP59">
-        <f>175000/100000</f>
         <v>1.75</v>
       </c>
       <c r="BT59" s="5" t="s">
@@ -11438,19 +11263,19 @@
       </c>
     </row>
     <row r="62" spans="1:78" x14ac:dyDescent="0.35">
-      <c r="A62" s="28" t="s">
+      <c r="A62" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="B62" s="28" t="s">
+      <c r="B62" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="C62" s="28" t="s">
+      <c r="C62" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="D62" s="29" t="s">
+      <c r="D62" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="E62" s="28" t="s">
+      <c r="E62" s="16" t="s">
         <v>95</v>
       </c>
       <c r="S62" s="3">

--- a/CEO Review.xlsx
+++ b/CEO Review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://peoplestronghrservices-my.sharepoint.com/personal/baljeet_singh_taggd_in/Documents/Desktop/Clude Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1914" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5EAE574-1183-4DAE-9559-528D8495C3FD}"/>
+  <xr:revisionPtr revIDLastSave="1916" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{446B9353-8779-494B-AF09-1A7BF0B565E9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F2C8E0B5-D69E-42FC-A0A4-20379F29D696}"/>
   </bookViews>
@@ -11145,7 +11145,9 @@
         <v>0</v>
       </c>
       <c r="M60" s="17"/>
-      <c r="R60" s="25"/>
+      <c r="R60" s="25">
+        <v>518</v>
+      </c>
       <c r="S60" s="7">
         <v>0</v>
       </c>
@@ -11173,8 +11175,8 @@
         <v>1025</v>
       </c>
       <c r="AY60" s="17">
-        <f t="shared" si="5"/>
-        <v>2013</v>
+        <f>R60+AC60+AN60+G60</f>
+        <v>2531</v>
       </c>
       <c r="AZ60" s="17">
         <f t="shared" si="6"/>

--- a/CEO Review.xlsx
+++ b/CEO Review.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://peoplestronghrservices-my.sharepoint.com/personal/baljeet_singh_taggd_in/Documents/Desktop/Clude Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1916" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{446B9353-8779-494B-AF09-1A7BF0B565E9}"/>
+  <xr:revisionPtr revIDLastSave="1962" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E80E2ED-1B2C-42D3-91FD-00778AD44822}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F2C8E0B5-D69E-42FC-A0A4-20379F29D696}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{F2C8E0B5-D69E-42FC-A0A4-20379F29D696}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Actual" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Actual!$A$2:$AO$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Actual!$A$2:$AO$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$BZ$62</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="131">
   <si>
     <t>Clients</t>
   </si>
@@ -570,7 +570,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -641,6 +641,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1606,7 +1612,7 @@
         <v>0</v>
       </c>
       <c r="AY4" s="17">
-        <f t="shared" ref="AY4:AY60" si="5">R4+AC4+AN4+G4</f>
+        <f t="shared" ref="AY4:AY59" si="5">R4+AC4+AN4+G4</f>
         <v>20</v>
       </c>
       <c r="AZ4" s="17">
@@ -2911,14 +2917,15 @@
         <v>329.30417599999998</v>
       </c>
       <c r="H12" s="17">
-        <v>413</v>
+        <f>413+17</f>
+        <v>430</v>
       </c>
       <c r="I12" s="3">
         <v>177.45506157435264</v>
       </c>
       <c r="J12" s="4">
         <f t="shared" si="2"/>
-        <v>0.42967327257712506</v>
+        <v>0.41268618970779686</v>
       </c>
       <c r="K12" s="3">
         <v>139210.95651634005</v>
@@ -3013,7 +3020,7 @@
       </c>
       <c r="AZ12" s="17">
         <f t="shared" si="6"/>
-        <v>1472.5760294000002</v>
+        <v>1489.5760294000002</v>
       </c>
       <c r="BA12" s="17">
         <f t="shared" si="7"/>
@@ -3021,7 +3028,7 @@
       </c>
       <c r="BB12" s="4">
         <f t="shared" si="8"/>
-        <v>0.31219630429339124</v>
+        <v>0.30863331921022941</v>
       </c>
       <c r="BC12" s="3">
         <f t="shared" si="0"/>
@@ -10868,7 +10875,9 @@
         <v>0</v>
       </c>
       <c r="AC58" s="3"/>
-      <c r="AD58" s="3"/>
+      <c r="AD58" s="3">
+        <v>6</v>
+      </c>
       <c r="AE58" s="3"/>
       <c r="AF58" s="4"/>
       <c r="AG58" s="3"/>
@@ -10882,7 +10891,9 @@
         <v>0</v>
       </c>
       <c r="AN58" s="8"/>
-      <c r="AO58" s="8"/>
+      <c r="AO58" s="8">
+        <v>6</v>
+      </c>
       <c r="AP58" s="17">
         <v>0</v>
       </c>
@@ -10908,7 +10919,7 @@
       </c>
       <c r="AZ58" s="17">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="BA58" s="17">
         <f t="shared" si="7"/>
@@ -10916,7 +10927,7 @@
       </c>
       <c r="BB58" s="4">
         <f t="shared" si="8"/>
-        <v>0.88333333333333341</v>
+        <v>0.61153846153846159</v>
       </c>
       <c r="BC58" s="3">
         <f t="shared" si="10"/>
@@ -11020,7 +11031,9 @@
         <v>0</v>
       </c>
       <c r="AC59" s="3"/>
-      <c r="AD59" s="3"/>
+      <c r="AD59" s="3">
+        <v>5.0999999999999996</v>
+      </c>
       <c r="AE59" s="3"/>
       <c r="AF59" s="4"/>
       <c r="AG59" s="3"/>
@@ -11034,7 +11047,9 @@
         <v>0</v>
       </c>
       <c r="AN59" s="8"/>
-      <c r="AO59" s="8"/>
+      <c r="AO59" s="8">
+        <v>5.0999999999999996</v>
+      </c>
       <c r="AP59" s="17">
         <v>0</v>
       </c>
@@ -11060,7 +11075,7 @@
       </c>
       <c r="AZ59" s="17">
         <f t="shared" si="6"/>
-        <v>10.35</v>
+        <v>20.549999999999997</v>
       </c>
       <c r="BA59" s="17">
         <f t="shared" si="7"/>
@@ -11068,7 +11083,7 @@
       </c>
       <c r="BB59" s="4">
         <f t="shared" si="8"/>
-        <v>0.85217391304347834</v>
+        <v>0.4291970802919709</v>
       </c>
       <c r="BC59" s="3">
         <f t="shared" si="10"/>
@@ -11166,6 +11181,9 @@
         <f>759+12</f>
         <v>771</v>
       </c>
+      <c r="AD60" s="29">
+        <v>0</v>
+      </c>
       <c r="AH60">
         <v>0</v>
       </c>
@@ -11173,6 +11191,9 @@
       <c r="AN60" s="23">
         <f>1013+12</f>
         <v>1025</v>
+      </c>
+      <c r="AO60">
+        <v>0</v>
       </c>
       <c r="AY60" s="17">
         <f>R60+AC60+AN60+G60</f>
@@ -11244,9 +11265,13 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-      <c r="AD61" s="18"/>
+      <c r="AD61" s="18">
+        <v>0</v>
+      </c>
       <c r="AE61" s="18"/>
-      <c r="AO61" s="18"/>
+      <c r="AO61" s="18">
+        <v>0</v>
+      </c>
       <c r="AZ61" s="17">
         <f t="shared" si="6"/>
         <v>54.36</v>
@@ -11280,30 +11305,37 @@
       <c r="E62" s="16" t="s">
         <v>95</v>
       </c>
+      <c r="H62" s="28">
+        <v>3.18</v>
+      </c>
       <c r="S62" s="3">
         <v>3.2</v>
       </c>
-      <c r="T62" s="3">
-        <v>3.2</v>
-      </c>
+      <c r="T62" s="3"/>
       <c r="U62" s="4">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V62" s="3">
         <v>0</v>
       </c>
+      <c r="AD62">
+        <v>3.2</v>
+      </c>
+      <c r="AO62">
+        <v>3.2</v>
+      </c>
       <c r="AZ62" s="17">
-        <f t="shared" si="6"/>
-        <v>3.2</v>
+        <f>S62+AD62+AO62+H62</f>
+        <v>12.780000000000001</v>
       </c>
       <c r="BA62" s="17">
         <f t="shared" si="7"/>
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BB62" s="4">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC62" s="3">
         <f t="shared" si="10"/>
@@ -11325,13 +11357,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62BD0EA2-02E9-43B0-A368-1C9D568EE9C9}">
-  <dimension ref="A1:AO61"/>
+  <dimension ref="A1:AO62"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="0" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="13.54296875" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="0" hidden="1" customWidth="1"/>
+    <col min="2" max="3" width="8.7265625" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" customWidth="1"/>
+    <col min="5" max="5" width="8.7265625" customWidth="1"/>
     <col min="6" max="6" width="5.08984375" customWidth="1"/>
     <col min="7" max="7" width="15.7265625" customWidth="1"/>
     <col min="8" max="8" width="13.90625" customWidth="1"/>
@@ -11690,7 +11722,7 @@
         <v>8</v>
       </c>
       <c r="T5" s="17">
-        <v>7.9985999999999997</v>
+        <v>8.4985999999999997</v>
       </c>
       <c r="U5" s="3"/>
       <c r="V5" s="4"/>
@@ -11763,7 +11795,7 @@
         <v>17</v>
       </c>
       <c r="T6" s="17">
-        <v>13.11</v>
+        <v>17</v>
       </c>
       <c r="U6" s="3"/>
       <c r="V6" s="4"/>
@@ -11778,7 +11810,7 @@
         <v>19</v>
       </c>
       <c r="AF6" s="17">
-        <v>1.85</v>
+        <v>35.9</v>
       </c>
       <c r="AG6" s="3"/>
       <c r="AH6" s="4"/>
@@ -11909,7 +11941,7 @@
         <v>11</v>
       </c>
       <c r="T8" s="17">
-        <v>9.6</v>
+        <v>11.28</v>
       </c>
       <c r="U8" s="3"/>
       <c r="V8" s="4"/>
@@ -11924,7 +11956,7 @@
         <v>11</v>
       </c>
       <c r="AF8" s="17">
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="AG8" s="3"/>
       <c r="AH8" s="4"/>
@@ -11982,7 +12014,7 @@
         <v>17.25</v>
       </c>
       <c r="T9" s="17">
-        <v>9</v>
+        <v>9.0500000000000007</v>
       </c>
       <c r="U9" s="3"/>
       <c r="V9" s="4"/>
@@ -11997,7 +12029,7 @@
         <v>17.25</v>
       </c>
       <c r="AF9" s="17">
-        <v>9.25</v>
+        <v>8.75</v>
       </c>
       <c r="AG9" s="3"/>
       <c r="AH9" s="4"/>
@@ -12053,7 +12085,7 @@
         <v>3</v>
       </c>
       <c r="T10" s="17">
-        <v>2.7114332000000001</v>
+        <v>3.2114332000000001</v>
       </c>
       <c r="U10" s="3"/>
       <c r="V10" s="4"/>
@@ -12126,7 +12158,7 @@
         <v>17.166666666666668</v>
       </c>
       <c r="T11" s="17">
-        <v>13.649999999999999</v>
+        <v>13.3</v>
       </c>
       <c r="U11" s="3"/>
       <c r="V11" s="4"/>
@@ -12141,7 +12173,7 @@
         <v>17.166666666666668</v>
       </c>
       <c r="AF11" s="17">
-        <v>14.3</v>
+        <v>13.3</v>
       </c>
       <c r="AG11" s="3"/>
       <c r="AH11" s="4"/>
@@ -12197,7 +12229,8 @@
         <v>113.10139199999999</v>
       </c>
       <c r="T12" s="17">
-        <v>117.71541000000001</v>
+        <f>115.71541+8</f>
+        <v>123.71541000000001</v>
       </c>
       <c r="U12" s="3"/>
       <c r="V12" s="4"/>
@@ -12212,7 +12245,8 @@
         <v>103.101392</v>
       </c>
       <c r="AF12" s="17">
-        <v>117.71541000000001</v>
+        <f>115.71541+9</f>
+        <v>124.71541000000001</v>
       </c>
       <c r="AG12" s="3"/>
       <c r="AH12" s="4"/>
@@ -12571,7 +12605,7 @@
         <v>100</v>
       </c>
       <c r="AF17" s="17">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="AG17" s="3"/>
       <c r="AH17" s="4"/>
@@ -12627,7 +12661,7 @@
         <v>20</v>
       </c>
       <c r="T18" s="17">
-        <v>25</v>
+        <v>24.3</v>
       </c>
       <c r="U18" s="3"/>
       <c r="V18" s="4"/>
@@ -12773,7 +12807,7 @@
         <v>6.703333333333334</v>
       </c>
       <c r="T20" s="17">
-        <v>12.190000000000001</v>
+        <v>14.080000000000002</v>
       </c>
       <c r="U20" s="3"/>
       <c r="V20" s="4"/>
@@ -12788,7 +12822,7 @@
         <v>6.703333333333334</v>
       </c>
       <c r="AF20" s="17">
-        <v>7.09</v>
+        <v>6.44</v>
       </c>
       <c r="AG20" s="3"/>
       <c r="AH20" s="4"/>
@@ -12846,7 +12880,7 @@
         <v>30</v>
       </c>
       <c r="T21" s="17">
-        <v>34.880000000000003</v>
+        <v>28.880000000000003</v>
       </c>
       <c r="U21" s="3"/>
       <c r="V21" s="4"/>
@@ -12861,7 +12895,7 @@
         <v>30</v>
       </c>
       <c r="AF21" s="17">
-        <v>48.080000000000005</v>
+        <v>52.88</v>
       </c>
       <c r="AG21" s="3"/>
       <c r="AH21" s="4"/>
@@ -12920,7 +12954,7 @@
         <v>5</v>
       </c>
       <c r="T22" s="17">
-        <v>2.4849999999999999</v>
+        <v>2.3849999999999998</v>
       </c>
       <c r="U22" s="3"/>
       <c r="V22" s="4"/>
@@ -13064,7 +13098,7 @@
         <v>11</v>
       </c>
       <c r="T24" s="17">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="U24" s="3"/>
       <c r="V24" s="4"/>
@@ -13079,7 +13113,7 @@
         <v>11</v>
       </c>
       <c r="AF24" s="17">
-        <v>8.26</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="AG24" s="3"/>
       <c r="AH24" s="4"/>
@@ -13135,7 +13169,7 @@
         <v>7</v>
       </c>
       <c r="T25" s="17">
-        <v>9.8000000000000007</v>
+        <v>10.74</v>
       </c>
       <c r="U25" s="3"/>
       <c r="V25" s="4"/>
@@ -13150,7 +13184,7 @@
         <v>7</v>
       </c>
       <c r="AF25" s="17">
-        <v>9.6999999999999993</v>
+        <v>9.74</v>
       </c>
       <c r="AG25" s="3"/>
       <c r="AH25" s="4"/>
@@ -13208,7 +13242,7 @@
         <v>16</v>
       </c>
       <c r="T26" s="17">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="U26" s="3"/>
       <c r="V26" s="4"/>
@@ -13223,7 +13257,7 @@
         <v>16</v>
       </c>
       <c r="AF26" s="17">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AG26" s="3"/>
       <c r="AH26" s="4"/>
@@ -13350,7 +13384,7 @@
         <v>9</v>
       </c>
       <c r="T28" s="17">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="U28" s="3"/>
       <c r="V28" s="4"/>
@@ -13365,7 +13399,7 @@
         <v>12</v>
       </c>
       <c r="AF28" s="17">
-        <v>8.6</v>
+        <v>10.1</v>
       </c>
       <c r="AG28" s="3"/>
       <c r="AH28" s="4"/>
@@ -13438,7 +13472,7 @@
         <v>4</v>
       </c>
       <c r="AF29" s="17">
-        <v>6.8759999999999994</v>
+        <v>26.676000000000002</v>
       </c>
       <c r="AG29" s="3"/>
       <c r="AH29" s="4"/>
@@ -13567,7 +13601,7 @@
         <v>35</v>
       </c>
       <c r="T31" s="17">
-        <v>28.8</v>
+        <v>33</v>
       </c>
       <c r="U31" s="3"/>
       <c r="V31" s="4"/>
@@ -13582,7 +13616,7 @@
         <v>30</v>
       </c>
       <c r="AF31" s="17">
-        <v>13.7</v>
+        <v>24</v>
       </c>
       <c r="AG31" s="3"/>
       <c r="AH31" s="4"/>
@@ -13640,7 +13674,7 @@
         <v>20.91</v>
       </c>
       <c r="T32" s="17">
-        <v>28.75</v>
+        <v>30.77</v>
       </c>
       <c r="U32" s="3"/>
       <c r="V32" s="4"/>
@@ -13655,7 +13689,7 @@
         <v>20.91</v>
       </c>
       <c r="AF32" s="17">
-        <v>22.75</v>
+        <v>21.5</v>
       </c>
       <c r="AG32" s="3"/>
       <c r="AH32" s="4"/>
@@ -13782,7 +13816,7 @@
         <v>0</v>
       </c>
       <c r="T34" s="17">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U34" s="3"/>
       <c r="V34" s="4"/>
@@ -13853,7 +13887,7 @@
         <v>2.6</v>
       </c>
       <c r="T35" s="17">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="U35" s="3"/>
       <c r="V35" s="4"/>
@@ -13868,7 +13902,7 @@
         <v>3</v>
       </c>
       <c r="AF35" s="17">
-        <v>1.1599999999999999</v>
+        <v>2</v>
       </c>
       <c r="AG35" s="3"/>
       <c r="AH35" s="4"/>
@@ -13926,7 +13960,7 @@
         <v>7.87</v>
       </c>
       <c r="T36" s="17">
-        <v>8.3000000000000007</v>
+        <v>4.76</v>
       </c>
       <c r="U36" s="3"/>
       <c r="V36" s="4"/>
@@ -13941,7 +13975,7 @@
         <v>7.87</v>
       </c>
       <c r="AF36" s="17">
-        <v>7.76</v>
+        <v>3.5</v>
       </c>
       <c r="AG36" s="3"/>
       <c r="AH36" s="4"/>
@@ -13999,7 +14033,7 @@
         <v>36</v>
       </c>
       <c r="T37" s="17">
-        <v>24.3</v>
+        <v>27.19</v>
       </c>
       <c r="U37" s="3"/>
       <c r="V37" s="4"/>
@@ -14014,7 +14048,7 @@
         <v>36</v>
       </c>
       <c r="AF37" s="17">
-        <v>21.8</v>
+        <v>30</v>
       </c>
       <c r="AG37" s="3"/>
       <c r="AH37" s="4"/>
@@ -14156,7 +14190,7 @@
         <v>5.5</v>
       </c>
       <c r="AF39" s="17">
-        <v>3.4450040000000004</v>
+        <v>5.5</v>
       </c>
       <c r="AG39" s="3"/>
       <c r="AH39" s="4"/>
@@ -14212,7 +14246,7 @@
         <v>4</v>
       </c>
       <c r="T40" s="17">
-        <v>8.6</v>
+        <v>7.04</v>
       </c>
       <c r="U40" s="3"/>
       <c r="V40" s="4"/>
@@ -14227,7 +14261,7 @@
         <v>5</v>
       </c>
       <c r="AF40" s="17">
-        <v>9.3000000000000007</v>
+        <v>9</v>
       </c>
       <c r="AG40" s="3"/>
       <c r="AH40" s="4"/>
@@ -14356,7 +14390,7 @@
         <v>9.5</v>
       </c>
       <c r="T42" s="17">
-        <v>10.02</v>
+        <v>10.19</v>
       </c>
       <c r="U42" s="3"/>
       <c r="V42" s="4"/>
@@ -14371,7 +14405,7 @@
         <v>9.5</v>
       </c>
       <c r="AF42" s="17">
-        <v>8.14</v>
+        <v>9.75</v>
       </c>
       <c r="AG42" s="3"/>
       <c r="AH42" s="4"/>
@@ -14646,7 +14680,7 @@
         <v>6.3666666666666663</v>
       </c>
       <c r="T46" s="17">
-        <v>8.4</v>
+        <v>8.56</v>
       </c>
       <c r="U46" s="3"/>
       <c r="V46" s="4"/>
@@ -14661,7 +14695,7 @@
         <v>6.3666666666666663</v>
       </c>
       <c r="AF46" s="17">
-        <v>6.4</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="AG46" s="3"/>
       <c r="AH46" s="4"/>
@@ -14717,7 +14751,7 @@
         <v>4</v>
       </c>
       <c r="T47" s="17">
-        <v>2.33</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="U47" s="3"/>
       <c r="V47" s="4"/>
@@ -14732,7 +14766,7 @@
         <v>4</v>
       </c>
       <c r="AF47" s="17">
-        <v>1.35</v>
+        <v>4</v>
       </c>
       <c r="AG47" s="3"/>
       <c r="AH47" s="4"/>
@@ -14934,7 +14968,7 @@
         <v>7.25</v>
       </c>
       <c r="T50" s="17">
-        <v>10.32</v>
+        <v>10.6</v>
       </c>
       <c r="U50" s="3"/>
       <c r="V50" s="4"/>
@@ -14949,7 +14983,7 @@
         <v>7.25</v>
       </c>
       <c r="AF50" s="17">
-        <v>3.37</v>
+        <v>3.83</v>
       </c>
       <c r="AG50" s="3"/>
       <c r="AH50" s="4"/>
@@ -15289,7 +15323,7 @@
         <v>11.291679999999999</v>
       </c>
       <c r="T55" s="17">
-        <v>2.25</v>
+        <v>12.5</v>
       </c>
       <c r="U55" s="3"/>
       <c r="V55" s="4"/>
@@ -15304,7 +15338,7 @@
         <v>39.549320000000002</v>
       </c>
       <c r="AF55" s="17">
-        <v>1.5</v>
+        <v>11</v>
       </c>
       <c r="AG55" s="3"/>
       <c r="AH55" s="4"/>
@@ -15711,6 +15745,29 @@
       <c r="AH61" s="4"/>
       <c r="AJ61" s="23"/>
     </row>
+    <row r="62" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="A62" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="B62" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C62" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="D62" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="E62" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="T62">
+        <v>2.12</v>
+      </c>
+      <c r="AF62" s="17">
+        <v>1.06</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="G1:Q1"/>

--- a/CEO Review.xlsx
+++ b/CEO Review.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://peoplestronghrservices-my.sharepoint.com/personal/baljeet_singh_taggd_in/Documents/Desktop/Clude Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1962" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E80E2ED-1B2C-42D3-91FD-00778AD44822}"/>
+  <xr:revisionPtr revIDLastSave="2035" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B032E314-878D-4D3E-A9EE-790928A3A670}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{F2C8E0B5-D69E-42FC-A0A4-20379F29D696}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F2C8E0B5-D69E-42FC-A0A4-20379F29D696}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -463,8 +463,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -486,6 +494,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -570,7 +584,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -643,17 +657,37 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1616,7 +1650,7 @@
         <v>20</v>
       </c>
       <c r="AZ4" s="17">
-        <f t="shared" ref="AZ4:AZ62" si="6">S4+AD4+AO4+H4</f>
+        <f t="shared" ref="AZ4:AZ61" si="6">S4+AD4+AO4+H4</f>
         <v>24.876199999999997</v>
       </c>
       <c r="BA4" s="17">
@@ -1678,7 +1712,7 @@
       <c r="C5" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="28" t="s">
         <v>118</v>
       </c>
       <c r="E5" s="3" t="s">
@@ -1852,7 +1886,7 @@
       <c r="C6" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="28" t="s">
         <v>118</v>
       </c>
       <c r="E6" s="3" t="s">
@@ -2208,7 +2242,7 @@
       <c r="C8" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="28" t="s">
         <v>118</v>
       </c>
       <c r="E8" s="3" t="s">
@@ -2382,7 +2416,7 @@
       <c r="C9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="28" t="s">
         <v>118</v>
       </c>
       <c r="E9" s="3" t="s">
@@ -2557,7 +2591,7 @@
       <c r="C10" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="28" t="s">
         <v>118</v>
       </c>
       <c r="E10" s="3" t="s">
@@ -2732,7 +2766,7 @@
       <c r="C11" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="28" t="s">
         <v>118</v>
       </c>
       <c r="E11" s="3" t="s">
@@ -3252,7 +3286,7 @@
       <c r="C14" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="28" t="s">
         <v>118</v>
       </c>
       <c r="E14" s="3" t="s">
@@ -3423,7 +3457,7 @@
       <c r="C15" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="29" t="s">
         <v>118</v>
       </c>
       <c r="E15" s="3" t="s">
@@ -3763,7 +3797,7 @@
       <c r="C17" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="28" t="s">
         <v>118</v>
       </c>
       <c r="E17" s="3" t="s">
@@ -3938,7 +3972,7 @@
       <c r="C18" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="29" t="s">
         <v>118</v>
       </c>
       <c r="E18" s="3" t="s">
@@ -4278,7 +4312,7 @@
       <c r="C20" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="28" t="s">
         <v>118</v>
       </c>
       <c r="E20" s="3" t="s">
@@ -4453,7 +4487,7 @@
       <c r="C21" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="28" t="s">
         <v>118</v>
       </c>
       <c r="E21" s="3" t="s">
@@ -4627,7 +4661,7 @@
       <c r="C22" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="29" t="s">
         <v>118</v>
       </c>
       <c r="E22" s="3" t="s">
@@ -4981,7 +5015,7 @@
       <c r="C24" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="28" t="s">
         <v>118</v>
       </c>
       <c r="E24" s="3" t="s">
@@ -5156,7 +5190,7 @@
       <c r="C25" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="28" t="s">
         <v>118</v>
       </c>
       <c r="E25" s="3" t="s">
@@ -5676,7 +5710,7 @@
       <c r="C28" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="28" t="s">
         <v>118</v>
       </c>
       <c r="E28" s="3" t="s">
@@ -5847,7 +5881,7 @@
       <c r="C29" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="28" t="s">
         <v>118</v>
       </c>
       <c r="E29" s="3" t="s">
@@ -6022,7 +6056,7 @@
       <c r="C30" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="29" t="s">
         <v>118</v>
       </c>
       <c r="E30" s="3" t="s">
@@ -6191,7 +6225,7 @@
       <c r="C31" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="28" t="s">
         <v>118</v>
       </c>
       <c r="E31" s="3" t="s">
@@ -6362,7 +6396,7 @@
       <c r="C32" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="30" t="s">
         <v>118</v>
       </c>
       <c r="E32" s="3" t="s">
@@ -6535,7 +6569,7 @@
       <c r="C33" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="28" t="s">
         <v>118</v>
       </c>
       <c r="E33" s="3" t="s">
@@ -6708,7 +6742,7 @@
       <c r="C34" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="28" t="s">
         <v>118</v>
       </c>
       <c r="E34" s="3" t="s">
@@ -6877,7 +6911,7 @@
       <c r="C35" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="28" t="s">
         <v>118</v>
       </c>
       <c r="E35" s="3" t="s">
@@ -7048,7 +7082,7 @@
       <c r="C36" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="28" t="s">
         <v>118</v>
       </c>
       <c r="E36" s="3" t="s">
@@ -7219,7 +7253,7 @@
       <c r="C37" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D37" s="28" t="s">
         <v>118</v>
       </c>
       <c r="E37" s="3" t="s">
@@ -7561,7 +7595,7 @@
       <c r="C39" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="28" t="s">
         <v>118</v>
       </c>
       <c r="E39" s="3" t="s">
@@ -7732,7 +7766,7 @@
       <c r="C40" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D40" s="28" t="s">
         <v>118</v>
       </c>
       <c r="E40" s="3" t="s">
@@ -7907,7 +7941,7 @@
       <c r="C41" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D41" s="29" t="s">
         <v>118</v>
       </c>
       <c r="E41" s="3" t="s">
@@ -8076,7 +8110,7 @@
       <c r="C42" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D42" s="28" t="s">
         <v>118</v>
       </c>
       <c r="E42" s="3" t="s">
@@ -8768,7 +8802,7 @@
       <c r="C46" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D46" s="28" t="s">
         <v>118</v>
       </c>
       <c r="E46" s="3" t="s">
@@ -8939,7 +8973,7 @@
       <c r="C47" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D47" s="28" t="s">
         <v>118</v>
       </c>
       <c r="E47" s="3" t="s">
@@ -9286,7 +9320,7 @@
       <c r="C49" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="D49" s="28" t="s">
         <v>119</v>
       </c>
       <c r="E49" s="3" t="s">
@@ -9462,7 +9496,7 @@
       <c r="C50" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D50" s="28" t="s">
         <v>119</v>
       </c>
       <c r="E50" s="3" t="s">
@@ -9632,7 +9666,7 @@
       <c r="C51" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D51" s="28" t="s">
         <v>119</v>
       </c>
       <c r="E51" s="3" t="s">
@@ -9801,7 +9835,7 @@
       <c r="C52" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D52" s="29" t="s">
         <v>118</v>
       </c>
       <c r="E52" s="3" t="s">
@@ -9970,7 +10004,7 @@
       <c r="C53" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="D53" s="29" t="s">
         <v>118</v>
       </c>
       <c r="E53" s="3" t="s">
@@ -10308,7 +10342,7 @@
       <c r="C55" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D55" s="28" t="s">
         <v>119</v>
       </c>
       <c r="E55" s="3" t="s">
@@ -10813,13 +10847,13 @@
       <c r="A58" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="B58" s="16" t="s">
+      <c r="B58" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C58" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="D58" s="28" t="s">
         <v>119</v>
       </c>
       <c r="E58" s="16" t="s">
@@ -10969,13 +11003,13 @@
       <c r="A59" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="B59" s="16" t="s">
+      <c r="B59" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C59" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="D59" s="28" t="s">
         <v>119</v>
       </c>
       <c r="E59" s="16" t="s">
@@ -11181,7 +11215,7 @@
         <f>759+12</f>
         <v>771</v>
       </c>
-      <c r="AD60" s="29">
+      <c r="AD60" s="16">
         <v>0</v>
       </c>
       <c r="AH60">
@@ -11228,7 +11262,7 @@
       <c r="C61" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="D61" s="24" t="s">
+      <c r="D61" s="2" t="s">
         <v>118</v>
       </c>
       <c r="E61" s="16" t="s">
@@ -11299,13 +11333,13 @@
       <c r="C62" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="D62" s="24" t="s">
+      <c r="D62" s="2" t="s">
         <v>119</v>
       </c>
       <c r="E62" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="H62" s="28">
+      <c r="H62" s="23">
         <v>3.18</v>
       </c>
       <c r="S62" s="3">

--- a/CEO Review.xlsx
+++ b/CEO Review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://peoplestronghrservices-my.sharepoint.com/personal/baljeet_singh_taggd_in/Documents/Desktop/Clude Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2474" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA4947A4-870C-4BD8-A9E1-37F51554CF8B}"/>
+  <xr:revisionPtr revIDLastSave="2497" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{836A6335-CE60-40DE-9782-A9B60D704CF9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{F2C8E0B5-D69E-42FC-A0A4-20379F29D696}"/>
   </bookViews>
@@ -700,6 +700,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -715,7 +716,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1108,86 +1108,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:93" x14ac:dyDescent="0.35">
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
-      <c r="U1" s="36" t="s">
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="U1" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="V1" s="37"/>
-      <c r="W1" s="37"/>
-      <c r="X1" s="37"/>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="37"/>
-      <c r="AA1" s="37"/>
-      <c r="AB1" s="37"/>
-      <c r="AC1" s="37"/>
-      <c r="AD1" s="37"/>
-      <c r="AE1" s="37"/>
-      <c r="AF1" s="37"/>
-      <c r="AG1" s="37"/>
-      <c r="AI1" s="33" t="s">
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
+      <c r="X1" s="38"/>
+      <c r="Y1" s="38"/>
+      <c r="Z1" s="38"/>
+      <c r="AA1" s="38"/>
+      <c r="AB1" s="38"/>
+      <c r="AC1" s="38"/>
+      <c r="AD1" s="38"/>
+      <c r="AE1" s="38"/>
+      <c r="AF1" s="38"/>
+      <c r="AG1" s="38"/>
+      <c r="AI1" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="AJ1" s="34"/>
-      <c r="AK1" s="34"/>
-      <c r="AL1" s="34"/>
-      <c r="AM1" s="34"/>
-      <c r="AN1" s="34"/>
-      <c r="AO1" s="34"/>
-      <c r="AP1" s="34"/>
-      <c r="AQ1" s="34"/>
-      <c r="AR1" s="34"/>
-      <c r="AS1" s="34"/>
-      <c r="AT1" s="34"/>
-      <c r="AU1" s="34"/>
-      <c r="AW1" s="36" t="s">
+      <c r="AJ1" s="35"/>
+      <c r="AK1" s="35"/>
+      <c r="AL1" s="35"/>
+      <c r="AM1" s="35"/>
+      <c r="AN1" s="35"/>
+      <c r="AO1" s="35"/>
+      <c r="AP1" s="35"/>
+      <c r="AQ1" s="35"/>
+      <c r="AR1" s="35"/>
+      <c r="AS1" s="35"/>
+      <c r="AT1" s="35"/>
+      <c r="AU1" s="35"/>
+      <c r="AW1" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="AX1" s="37"/>
-      <c r="AY1" s="37"/>
-      <c r="AZ1" s="37"/>
-      <c r="BA1" s="37"/>
-      <c r="BB1" s="37"/>
-      <c r="BC1" s="37"/>
-      <c r="BD1" s="37"/>
-      <c r="BE1" s="37"/>
-      <c r="BF1" s="37"/>
-      <c r="BG1" s="37"/>
-      <c r="BH1" s="37"/>
-      <c r="BI1" s="37"/>
-      <c r="BK1" s="34" t="s">
+      <c r="AX1" s="38"/>
+      <c r="AY1" s="38"/>
+      <c r="AZ1" s="38"/>
+      <c r="BA1" s="38"/>
+      <c r="BB1" s="38"/>
+      <c r="BC1" s="38"/>
+      <c r="BD1" s="38"/>
+      <c r="BE1" s="38"/>
+      <c r="BF1" s="38"/>
+      <c r="BG1" s="38"/>
+      <c r="BH1" s="38"/>
+      <c r="BI1" s="38"/>
+      <c r="BK1" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="BL1" s="34"/>
-      <c r="BM1" s="34"/>
-      <c r="BN1" s="34"/>
-      <c r="BO1" s="34"/>
-      <c r="BP1" s="34"/>
-      <c r="BQ1" s="34"/>
-      <c r="BR1" s="34"/>
-      <c r="BS1" s="34"/>
-      <c r="BT1" s="34"/>
-      <c r="BU1" s="34"/>
-      <c r="BV1" s="34"/>
-      <c r="BW1" s="34"/>
-      <c r="BY1" s="35" t="s">
+      <c r="BL1" s="35"/>
+      <c r="BM1" s="35"/>
+      <c r="BN1" s="35"/>
+      <c r="BO1" s="35"/>
+      <c r="BP1" s="35"/>
+      <c r="BQ1" s="35"/>
+      <c r="BR1" s="35"/>
+      <c r="BS1" s="35"/>
+      <c r="BT1" s="35"/>
+      <c r="BU1" s="35"/>
+      <c r="BV1" s="35"/>
+      <c r="BW1" s="35"/>
+      <c r="BY1" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="BZ1" s="35"/>
-      <c r="CA1" s="35"/>
+      <c r="BZ1" s="36"/>
+      <c r="CA1" s="36"/>
       <c r="CC1" s="19" t="s">
         <v>79</v>
       </c>
@@ -1477,15 +1477,15 @@
       <c r="G3" s="14">
         <v>475</v>
       </c>
-      <c r="H3" s="17">
-        <v>475</v>
+      <c r="H3" s="7">
+        <v>475.01369999999997</v>
       </c>
       <c r="I3" s="3">
         <v>289.89295097999286</v>
       </c>
       <c r="J3" s="4">
         <f>IFERROR(I3/H3,0)</f>
-        <v>0.61030094943156388</v>
+        <v>0.61028334757501279</v>
       </c>
       <c r="K3" s="3">
         <v>107620.37733721343</v>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="BL3" s="17">
         <f>V3+AJ3+AX3+H3</f>
-        <v>1725</v>
+        <v>1725.0137</v>
       </c>
       <c r="BM3" s="17">
         <f>W3+AK3+AY3+I3</f>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="BN3" s="4">
         <f>IFERROR(BM3/BL3,0)</f>
-        <v>0.53857373287766341</v>
+        <v>0.53856945554343683</v>
       </c>
       <c r="BO3" s="3">
         <f t="shared" ref="BO3:BO34" si="0">AVERAGE(K3,Y3,AM3,BA3)</f>
@@ -1665,15 +1665,15 @@
       <c r="G4" s="14">
         <v>5</v>
       </c>
-      <c r="H4" s="17">
-        <v>9.876199999999999</v>
+      <c r="H4" s="7">
+        <v>12.5062</v>
       </c>
       <c r="I4" s="3">
         <v>-0.52813136392458482</v>
       </c>
       <c r="J4" s="4">
         <f t="shared" ref="J4:J61" si="2">IFERROR(I4/H4,0)</f>
-        <v>-5.3475158859134571E-2</v>
+        <v>-4.2229563250594494E-2</v>
       </c>
       <c r="K4" s="3">
         <v>173405.52273207638</v>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="BL4" s="17">
         <f t="shared" ref="BL4:BL61" si="6">V4+AJ4+AX4+H4</f>
-        <v>24.876199999999997</v>
+        <v>27.5062</v>
       </c>
       <c r="BM4" s="17">
         <f t="shared" ref="BM4:BM62" si="7">W4+AK4+AY4+I4</f>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="BN4" s="4">
         <f t="shared" ref="BN4:BN62" si="8">IFERROR(BM4/BL4,0)</f>
-        <v>-0.79845092356853997</v>
+        <v>-0.72210719273748147</v>
       </c>
       <c r="BO4" s="3">
         <f t="shared" si="0"/>
@@ -1851,15 +1851,15 @@
       <c r="G5" s="14">
         <v>24</v>
       </c>
-      <c r="H5" s="17">
-        <v>23.299676599999998</v>
+      <c r="H5" s="7">
+        <v>23.2546766</v>
       </c>
       <c r="I5" s="3">
         <v>11.183573396464103</v>
       </c>
       <c r="J5" s="4">
         <f t="shared" si="2"/>
-        <v>0.47998835299130738</v>
+        <v>0.48091717587954347</v>
       </c>
       <c r="K5" s="3">
         <v>100967.52669613245</v>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="BL5" s="17">
         <f t="shared" si="6"/>
-        <v>79.299676599999998</v>
+        <v>79.254676599999996</v>
       </c>
       <c r="BM5" s="17">
         <f t="shared" si="7"/>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="BN5" s="4">
         <f t="shared" si="8"/>
-        <v>0.34300811795234554</v>
+        <v>0.34320287447612469</v>
       </c>
       <c r="BO5" s="3">
         <f t="shared" si="0"/>
@@ -2040,7 +2040,7 @@
       <c r="G6" s="14">
         <v>56</v>
       </c>
-      <c r="H6" s="17">
+      <c r="H6" s="7">
         <v>79.400000000000006</v>
       </c>
       <c r="I6" s="3">
@@ -2235,15 +2235,15 @@
       <c r="G7" s="14">
         <v>28.499999999999996</v>
       </c>
-      <c r="H7" s="17">
-        <v>19.118500000000001</v>
+      <c r="H7" s="7">
+        <v>19.088500000000003</v>
       </c>
       <c r="I7" s="3">
         <v>0.88244783034543062</v>
       </c>
       <c r="J7" s="4">
         <f t="shared" si="2"/>
-        <v>4.6156750286132836E-2</v>
+        <v>4.6229291476304078E-2</v>
       </c>
       <c r="K7" s="3">
         <v>101311.4009425254</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="BL7" s="17">
         <f t="shared" si="6"/>
-        <v>105.4085</v>
+        <v>105.3785</v>
       </c>
       <c r="BM7" s="17">
         <f t="shared" si="7"/>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="BN7" s="4">
         <f t="shared" si="8"/>
-        <v>0.25608443029248434</v>
+        <v>0.25615733447036482</v>
       </c>
       <c r="BO7" s="3">
         <f t="shared" si="0"/>
@@ -2423,15 +2423,15 @@
       <c r="G8" s="14">
         <v>33</v>
       </c>
-      <c r="H8" s="17">
-        <v>35.332499999999996</v>
+      <c r="H8" s="7">
+        <v>38.252499999999998</v>
       </c>
       <c r="I8" s="3">
         <v>10.587499999999995</v>
       </c>
       <c r="J8" s="4">
         <f t="shared" si="2"/>
-        <v>0.29965329370975718</v>
+        <v>0.27677929547088415</v>
       </c>
       <c r="K8" s="3">
         <v>101000</v>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="BL8" s="17">
         <f t="shared" si="6"/>
-        <v>137.03249999999997</v>
+        <v>139.95249999999999</v>
       </c>
       <c r="BM8" s="17">
         <f t="shared" si="7"/>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="BN8" s="4">
         <f t="shared" si="8"/>
-        <v>0.22351631912137626</v>
+        <v>0.21885282506564721</v>
       </c>
       <c r="BO8" s="3">
         <f t="shared" si="0"/>
@@ -2612,15 +2612,15 @@
       <c r="G9" s="14">
         <v>51.75</v>
       </c>
-      <c r="H9" s="17">
-        <v>24.630000000000003</v>
+      <c r="H9" s="7">
+        <v>25.22</v>
       </c>
       <c r="I9" s="3">
         <v>-1.0278053411884613</v>
       </c>
       <c r="J9" s="4">
         <f t="shared" si="2"/>
-        <v>-4.1729814908179508E-2</v>
+        <v>-4.0753582124839864E-2</v>
       </c>
       <c r="K9" s="3">
         <v>80180.641691213954</v>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="BL9" s="17">
         <f t="shared" si="6"/>
-        <v>168.63</v>
+        <v>169.22</v>
       </c>
       <c r="BM9" s="17">
         <f t="shared" si="7"/>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="BN9" s="4">
         <f t="shared" si="8"/>
-        <v>0.34573585383911287</v>
+        <v>0.34453041622083441</v>
       </c>
       <c r="BO9" s="3">
         <f t="shared" si="0"/>
@@ -2802,15 +2802,15 @@
       <c r="G10" s="14">
         <v>10</v>
       </c>
-      <c r="H10" s="17">
-        <v>10.270737799999999</v>
+      <c r="H10" s="7">
+        <v>11.020519100000001</v>
       </c>
       <c r="I10" s="3">
         <v>3.946138567772473</v>
       </c>
       <c r="J10" s="4">
         <f t="shared" si="2"/>
-        <v>0.38421179126707655</v>
+        <v>0.35807193218080557</v>
       </c>
       <c r="K10" s="3">
         <v>105409.9872037921</v>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="BL10" s="17">
         <f t="shared" si="6"/>
-        <v>48.270737799999999</v>
+        <v>49.020519100000001</v>
       </c>
       <c r="BM10" s="17">
         <f t="shared" si="7"/>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="BN10" s="4">
         <f t="shared" si="8"/>
-        <v>0.43659910873418711</v>
+        <v>0.42992121438839753</v>
       </c>
       <c r="BO10" s="3">
         <f t="shared" si="0"/>
@@ -2992,15 +2992,15 @@
       <c r="G11" s="14">
         <v>51.5</v>
       </c>
-      <c r="H11" s="17">
-        <v>39.39</v>
+      <c r="H11" s="7">
+        <v>32.849999999999994</v>
       </c>
       <c r="I11" s="3">
         <v>15.332275115075429</v>
       </c>
       <c r="J11" s="4">
         <f t="shared" si="2"/>
-        <v>0.38924283105040441</v>
+        <v>0.4667359243554165</v>
       </c>
       <c r="K11" s="3">
         <v>92529.711095863735</v>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="BL11" s="17">
         <f t="shared" si="6"/>
-        <v>182.99</v>
+        <v>176.45</v>
       </c>
       <c r="BM11" s="17">
         <f t="shared" si="7"/>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="BN11" s="4">
         <f t="shared" si="8"/>
-        <v>0.43467830479711644</v>
+        <v>0.4507893623962842</v>
       </c>
       <c r="BO11" s="3">
         <f t="shared" si="0"/>
@@ -3181,16 +3181,15 @@
       <c r="G12" s="14">
         <v>329.30417599999998</v>
       </c>
-      <c r="H12" s="17">
-        <f>413+17</f>
-        <v>430</v>
+      <c r="H12" s="7">
+        <v>470.56917999999996</v>
       </c>
       <c r="I12" s="3">
         <v>177.45506157435264</v>
       </c>
       <c r="J12" s="4">
         <f t="shared" si="2"/>
-        <v>0.41268618970779686</v>
+        <v>0.37710727586186721</v>
       </c>
       <c r="K12" s="3">
         <v>139210.95651634005</v>
@@ -3297,7 +3296,7 @@
       </c>
       <c r="BL12" s="17">
         <f t="shared" si="6"/>
-        <v>1489.5760294000002</v>
+        <v>1530.1452094000001</v>
       </c>
       <c r="BM12" s="17">
         <f t="shared" si="7"/>
@@ -3305,7 +3304,7 @@
       </c>
       <c r="BN12" s="4">
         <f t="shared" si="8"/>
-        <v>0.30863331921022941</v>
+        <v>0.30045043525639409</v>
       </c>
       <c r="BO12" s="3">
         <f t="shared" si="0"/>
@@ -3368,15 +3367,15 @@
       <c r="G13" s="14">
         <v>27</v>
       </c>
-      <c r="H13" s="17">
-        <v>14.785</v>
+      <c r="H13" s="7">
+        <v>14.74</v>
       </c>
       <c r="I13" s="3">
         <v>5.5780109760832666</v>
       </c>
       <c r="J13" s="4">
         <f t="shared" si="2"/>
-        <v>0.3772750068368797</v>
+        <v>0.37842679620646313</v>
       </c>
       <c r="K13" s="3">
         <v>127874.84755439906</v>
@@ -3483,7 +3482,7 @@
       </c>
       <c r="BL13" s="17">
         <f t="shared" si="6"/>
-        <v>72.784999999999997</v>
+        <v>72.739999999999995</v>
       </c>
       <c r="BM13" s="17">
         <f t="shared" si="7"/>
@@ -3491,7 +3490,7 @@
       </c>
       <c r="BN13" s="4">
         <f t="shared" si="8"/>
-        <v>0.45606851957351163</v>
+        <v>0.45635066259496904</v>
       </c>
       <c r="BO13" s="3">
         <f t="shared" si="0"/>
@@ -3557,7 +3556,7 @@
       <c r="G14" s="14">
         <v>0</v>
       </c>
-      <c r="H14" s="17">
+      <c r="H14" s="7">
         <v>0.9</v>
       </c>
       <c r="I14" s="3">
@@ -3743,7 +3742,7 @@
       <c r="G15" s="14">
         <v>0</v>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="7">
         <v>0</v>
       </c>
       <c r="I15" s="3">
@@ -3927,15 +3926,15 @@
       <c r="G16" s="14">
         <v>12</v>
       </c>
-      <c r="H16" s="17">
-        <v>13.59169</v>
+      <c r="H16" s="7">
+        <v>12.019860000000001</v>
       </c>
       <c r="I16" s="3">
         <v>4.2973875819615852</v>
       </c>
       <c r="J16" s="4">
         <f t="shared" si="2"/>
-        <v>0.31617757482414516</v>
+        <v>0.35752392972643482</v>
       </c>
       <c r="K16" s="3">
         <v>84493.658345803764</v>
@@ -4042,7 +4041,7 @@
       </c>
       <c r="BL16" s="17">
         <f t="shared" si="6"/>
-        <v>40.59169</v>
+        <v>39.019860000000001</v>
       </c>
       <c r="BM16" s="17">
         <f t="shared" si="7"/>
@@ -4050,7 +4049,7 @@
       </c>
       <c r="BN16" s="4">
         <f t="shared" si="8"/>
-        <v>1.5426546725076321E-2</v>
+        <v>1.6047971531287227E-2</v>
       </c>
       <c r="BO16" s="3">
         <f t="shared" si="0"/>
@@ -4113,15 +4112,15 @@
       <c r="G17" s="14">
         <v>305</v>
       </c>
-      <c r="H17" s="17">
-        <v>380.6077823</v>
+      <c r="H17" s="7">
+        <v>349.40786230000003</v>
       </c>
       <c r="I17" s="3">
         <v>153.39413898733835</v>
       </c>
       <c r="J17" s="4">
         <f t="shared" si="2"/>
-        <v>0.40302417901279564</v>
+        <v>0.43901169818449831</v>
       </c>
       <c r="K17" s="3">
         <v>93889.935253165968</v>
@@ -4228,7 +4227,7 @@
       </c>
       <c r="BL17" s="17">
         <f t="shared" si="6"/>
-        <v>1460.6077823000001</v>
+        <v>1429.4078623</v>
       </c>
       <c r="BM17" s="17">
         <f t="shared" si="7"/>
@@ -4236,7 +4235,7 @@
       </c>
       <c r="BN17" s="4">
         <f t="shared" si="8"/>
-        <v>0.33108759375090646</v>
+        <v>0.33831429699668225</v>
       </c>
       <c r="BO17" s="3">
         <f t="shared" si="0"/>
@@ -4303,15 +4302,15 @@
       <c r="G18" s="14">
         <v>70</v>
       </c>
-      <c r="H18" s="17">
-        <v>75.491083500000002</v>
+      <c r="H18" s="7">
+        <v>69.805023500000004</v>
       </c>
       <c r="I18" s="3">
         <v>36.298225002405729</v>
       </c>
       <c r="J18" s="4">
         <f t="shared" si="2"/>
-        <v>0.48082797755056367</v>
+        <v>0.51999445286922263</v>
       </c>
       <c r="K18" s="3">
         <v>130642.86165864758</v>
@@ -4418,7 +4417,7 @@
       </c>
       <c r="BL18" s="17">
         <f t="shared" si="6"/>
-        <v>255.4910835</v>
+        <v>249.8050235</v>
       </c>
       <c r="BM18" s="17">
         <f t="shared" si="7"/>
@@ -4426,7 +4425,7 @@
       </c>
       <c r="BN18" s="4">
         <f t="shared" si="8"/>
-        <v>0.34037114238604971</v>
+        <v>0.34811866767901334</v>
       </c>
       <c r="BO18" s="3">
         <f t="shared" si="0"/>
@@ -4487,15 +4486,15 @@
       <c r="G19" s="14">
         <v>150</v>
       </c>
-      <c r="H19" s="17">
-        <v>85.987499999999997</v>
+      <c r="H19" s="7">
+        <v>89.987499999999997</v>
       </c>
       <c r="I19" s="3">
         <v>49.81770738662749</v>
       </c>
       <c r="J19" s="4">
         <f t="shared" si="2"/>
-        <v>0.5793598765707515</v>
+        <v>0.5536069719308514</v>
       </c>
       <c r="K19" s="3">
         <v>98824.569981892113</v>
@@ -4602,7 +4601,7 @@
       </c>
       <c r="BL19" s="17">
         <f t="shared" si="6"/>
-        <v>404.98750000000001</v>
+        <v>408.98750000000001</v>
       </c>
       <c r="BM19" s="17">
         <f t="shared" si="7"/>
@@ -4610,7 +4609,7 @@
       </c>
       <c r="BN19" s="4">
         <f t="shared" si="8"/>
-        <v>0.61596318840087216</v>
+        <v>0.60993891442280801</v>
       </c>
       <c r="BO19" s="3">
         <f t="shared" si="0"/>
@@ -4673,15 +4672,15 @@
       <c r="G20" s="14">
         <v>20.110000000000003</v>
       </c>
-      <c r="H20" s="17">
-        <v>27.510800000000003</v>
+      <c r="H20" s="7">
+        <v>30.900800000000004</v>
       </c>
       <c r="I20" s="3">
         <v>16.116478281603932</v>
       </c>
       <c r="J20" s="4">
         <f t="shared" si="2"/>
-        <v>0.58582368675588969</v>
+        <v>0.52155537337557378</v>
       </c>
       <c r="K20" s="3">
         <v>87648.628603046702</v>
@@ -4788,7 +4787,7 @@
       </c>
       <c r="BL20" s="17">
         <f t="shared" si="6"/>
-        <v>104.72080000000001</v>
+        <v>108.11080000000001</v>
       </c>
       <c r="BM20" s="17">
         <f t="shared" si="7"/>
@@ -4796,7 +4795,7 @@
       </c>
       <c r="BN20" s="4">
         <f t="shared" si="8"/>
-        <v>0.53213131117119894</v>
+        <v>0.51544541905986163</v>
       </c>
       <c r="BO20" s="3">
         <f t="shared" si="0"/>
@@ -4863,15 +4862,15 @@
       <c r="G21" s="14">
         <v>90</v>
       </c>
-      <c r="H21" s="17">
-        <v>108.03982999999999</v>
+      <c r="H21" s="7">
+        <v>117.64298275000002</v>
       </c>
       <c r="I21" s="3">
         <v>9.4148827127914245</v>
       </c>
       <c r="J21" s="4">
         <f t="shared" si="2"/>
-        <v>8.7142702027496938E-2</v>
+        <v>8.0029275803034872E-2</v>
       </c>
       <c r="K21" s="3">
         <v>92605.584307238096</v>
@@ -4978,7 +4977,7 @@
       </c>
       <c r="BL21" s="17">
         <f t="shared" si="6"/>
-        <v>378.03982999999999</v>
+        <v>387.64298274999999</v>
       </c>
       <c r="BM21" s="17">
         <f t="shared" si="7"/>
@@ -4986,7 +4985,7 @@
       </c>
       <c r="BN21" s="4">
         <f t="shared" si="8"/>
-        <v>-0.12180579843927269</v>
+        <v>-0.11878828041289215</v>
       </c>
       <c r="BO21" s="3">
         <f t="shared" si="0"/>
@@ -5052,15 +5051,15 @@
       <c r="G22" s="14">
         <v>15</v>
       </c>
-      <c r="H22" s="17">
-        <v>4.6449999999999996</v>
+      <c r="H22" s="7">
+        <v>2.2600000000000002</v>
       </c>
       <c r="I22" s="3">
         <v>2.5832903000433043</v>
       </c>
       <c r="J22" s="4">
         <f t="shared" si="2"/>
-        <v>0.556144305714382</v>
+        <v>1.1430488053288956</v>
       </c>
       <c r="K22" s="3">
         <v>103085.48499783476</v>
@@ -5167,7 +5166,7 @@
       </c>
       <c r="BL22" s="17">
         <f t="shared" si="6"/>
-        <v>79.644999999999996</v>
+        <v>77.260000000000005</v>
       </c>
       <c r="BM22" s="17">
         <f t="shared" si="7"/>
@@ -5175,7 +5174,7 @@
       </c>
       <c r="BN22" s="4">
         <f t="shared" si="8"/>
-        <v>0.88868916178273849</v>
+        <v>0.916122809865211</v>
       </c>
       <c r="BO22" s="3">
         <f t="shared" si="0"/>
@@ -5241,15 +5240,15 @@
       <c r="G23" s="14">
         <v>4</v>
       </c>
-      <c r="H23" s="17">
-        <v>2.68445</v>
+      <c r="H23" s="7">
+        <v>2.3909400000000001</v>
       </c>
       <c r="I23" s="3">
         <v>-0.61992166626462764</v>
       </c>
       <c r="J23" s="4">
         <f t="shared" si="2"/>
-        <v>-0.23093060636801863</v>
+        <v>-0.25927947429238191</v>
       </c>
       <c r="K23" s="3">
         <v>110145.72220882092</v>
@@ -5356,7 +5355,7 @@
       </c>
       <c r="BL23" s="17">
         <f t="shared" si="6"/>
-        <v>5.18445</v>
+        <v>4.8909400000000005</v>
       </c>
       <c r="BM23" s="17">
         <f t="shared" si="7"/>
@@ -5364,7 +5363,7 @@
       </c>
       <c r="BN23" s="4">
         <f t="shared" si="8"/>
-        <v>-1.7406568035062346</v>
+        <v>-1.8451152876416184</v>
       </c>
       <c r="BO23" s="3">
         <f t="shared" si="0"/>
@@ -5434,7 +5433,7 @@
       <c r="G24" s="14">
         <v>32</v>
       </c>
-      <c r="H24" s="17">
+      <c r="H24" s="7">
         <v>8.9005700000000001</v>
       </c>
       <c r="I24" s="3">
@@ -5624,15 +5623,15 @@
       <c r="G25" s="14">
         <v>21</v>
       </c>
-      <c r="H25" s="17">
-        <v>30.495699999999999</v>
+      <c r="H25" s="7">
+        <v>28.573790000000002</v>
       </c>
       <c r="I25" s="3">
         <v>15.513742816992021</v>
       </c>
       <c r="J25" s="4">
         <f t="shared" si="2"/>
-        <v>0.5087190265182312</v>
+        <v>0.54293612492399568</v>
       </c>
       <c r="K25" s="3">
         <v>99879.714553386511</v>
@@ -5739,7 +5738,7 @@
       </c>
       <c r="BL25" s="17">
         <f t="shared" si="6"/>
-        <v>95.995699999999999</v>
+        <v>94.073790000000002</v>
       </c>
       <c r="BM25" s="17">
         <f t="shared" si="7"/>
@@ -5747,7 +5746,7 @@
       </c>
       <c r="BN25" s="4">
         <f t="shared" si="8"/>
-        <v>0.32890310829616004</v>
+        <v>0.33562253751088045</v>
       </c>
       <c r="BO25" s="3">
         <f t="shared" si="0"/>
@@ -5814,15 +5813,15 @@
       <c r="G26" s="14">
         <v>48</v>
       </c>
-      <c r="H26" s="17">
-        <v>58.223479999999995</v>
+      <c r="H26" s="7">
+        <v>76.052480000000003</v>
       </c>
       <c r="I26" s="3">
         <v>-7.3742335619042478</v>
       </c>
       <c r="J26" s="4">
         <f t="shared" si="2"/>
-        <v>-0.12665394720316012</v>
+        <v>-9.6962433860200842E-2</v>
       </c>
       <c r="K26" s="3">
         <v>117138.77421768615</v>
@@ -5929,7 +5928,7 @@
       </c>
       <c r="BL26" s="17">
         <f t="shared" si="6"/>
-        <v>202.22348</v>
+        <v>220.05248</v>
       </c>
       <c r="BM26" s="17">
         <f t="shared" si="7"/>
@@ -5937,7 +5936,7 @@
       </c>
       <c r="BN26" s="4">
         <f t="shared" si="8"/>
-        <v>-0.39484380506253919</v>
+        <v>-0.3628529354278956</v>
       </c>
       <c r="BO26" s="3">
         <f t="shared" si="0"/>
@@ -6005,7 +6004,7 @@
       <c r="G27" s="14">
         <v>18</v>
       </c>
-      <c r="H27" s="17">
+      <c r="H27" s="7">
         <v>0</v>
       </c>
       <c r="I27" s="3">
@@ -6189,7 +6188,7 @@
       <c r="G28" s="14">
         <v>33</v>
       </c>
-      <c r="H28" s="17">
+      <c r="H28" s="7">
         <v>33.69</v>
       </c>
       <c r="I28" s="3">
@@ -6375,7 +6374,7 @@
       <c r="G29" s="14">
         <v>12</v>
       </c>
-      <c r="H29" s="17">
+      <c r="H29" s="7">
         <v>38.650710000000004</v>
       </c>
       <c r="I29" s="3">
@@ -6565,7 +6564,7 @@
       <c r="G30" s="14">
         <v>3</v>
       </c>
-      <c r="H30" s="17">
+      <c r="H30" s="7">
         <v>1.8</v>
       </c>
       <c r="I30" s="3">
@@ -6749,15 +6748,15 @@
       <c r="G31" s="14">
         <v>100</v>
       </c>
-      <c r="H31" s="17">
-        <v>83.5</v>
+      <c r="H31" s="7">
+        <v>85.5</v>
       </c>
       <c r="I31" s="3">
         <v>6.6859393757712553</v>
       </c>
       <c r="J31" s="4">
         <f t="shared" si="2"/>
-        <v>8.0071130248757547E-2</v>
+        <v>7.8198121354049771E-2</v>
       </c>
       <c r="K31" s="3">
         <v>92547.060993046674</v>
@@ -6864,7 +6863,7 @@
       </c>
       <c r="BL31" s="17">
         <f t="shared" si="6"/>
-        <v>463.5</v>
+        <v>465.5</v>
       </c>
       <c r="BM31" s="17">
         <f t="shared" si="7"/>
@@ -6872,7 +6871,7 @@
       </c>
       <c r="BN31" s="4">
         <f t="shared" si="8"/>
-        <v>0.28737764685181538</v>
+        <v>0.28614294160218351</v>
       </c>
       <c r="BO31" s="3">
         <f t="shared" si="0"/>
@@ -6935,15 +6934,15 @@
       <c r="G32" s="14">
         <v>62.730000000000004</v>
       </c>
-      <c r="H32" s="17">
-        <v>83.07</v>
+      <c r="H32" s="7">
+        <v>81.44</v>
       </c>
       <c r="I32" s="3">
         <v>45.251880147597902</v>
       </c>
       <c r="J32" s="4">
         <f t="shared" si="2"/>
-        <v>0.54474395266158548</v>
+        <v>0.55564685839388384</v>
       </c>
       <c r="K32" s="3">
         <v>87949.115935818816</v>
@@ -7050,7 +7049,7 @@
       </c>
       <c r="BL32" s="17">
         <f t="shared" si="6"/>
-        <v>266.31</v>
+        <v>264.68</v>
       </c>
       <c r="BM32" s="17">
         <f t="shared" si="7"/>
@@ -7058,7 +7057,7 @@
       </c>
       <c r="BN32" s="4">
         <f t="shared" si="8"/>
-        <v>0.38936609453145204</v>
+        <v>0.3917639588736247</v>
       </c>
       <c r="BO32" s="3">
         <f t="shared" si="0"/>
@@ -7123,7 +7122,7 @@
       <c r="G33" s="14">
         <v>3.5</v>
       </c>
-      <c r="H33" s="17">
+      <c r="H33" s="7">
         <v>0</v>
       </c>
       <c r="I33" s="3">
@@ -7311,15 +7310,15 @@
       <c r="G34" s="14">
         <v>0</v>
       </c>
-      <c r="H34" s="17">
-        <v>3.22</v>
+      <c r="H34" s="7">
+        <v>3.2240000000000002</v>
       </c>
       <c r="I34" s="3">
         <v>3.22</v>
       </c>
       <c r="J34" s="4">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.99875930521091816</v>
       </c>
       <c r="K34" s="3">
         <v>0</v>
@@ -7426,7 +7425,7 @@
       </c>
       <c r="BL34" s="17">
         <f t="shared" si="6"/>
-        <v>3.22</v>
+        <v>3.2240000000000002</v>
       </c>
       <c r="BM34" s="17">
         <f t="shared" si="7"/>
@@ -7434,7 +7433,7 @@
       </c>
       <c r="BN34" s="4">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0.99875930521091816</v>
       </c>
       <c r="BO34" s="3">
         <f t="shared" si="0"/>
@@ -7495,7 +7494,7 @@
       <c r="G35" s="14">
         <v>8.6</v>
       </c>
-      <c r="H35" s="17">
+      <c r="H35" s="7">
         <v>8.59</v>
       </c>
       <c r="I35" s="3">
@@ -7681,15 +7680,15 @@
       <c r="G36" s="14">
         <v>23.61</v>
       </c>
-      <c r="H36" s="17">
-        <v>11.866775000000001</v>
+      <c r="H36" s="7">
+        <v>15.336774999999999</v>
       </c>
       <c r="I36" s="3">
         <v>-1.3090076277194189</v>
       </c>
       <c r="J36" s="4">
         <f t="shared" si="2"/>
-        <v>-0.11030862451840696</v>
+        <v>-8.5350905110065114E-2</v>
       </c>
       <c r="K36" s="3">
         <v>82348.641423246372</v>
@@ -7796,7 +7795,7 @@
       </c>
       <c r="BL36" s="17">
         <f t="shared" si="6"/>
-        <v>88.575775000000007</v>
+        <v>92.045775000000006</v>
       </c>
       <c r="BM36" s="17">
         <f t="shared" si="7"/>
@@ -7804,7 +7803,7 @@
       </c>
       <c r="BN36" s="4">
         <f t="shared" si="8"/>
-        <v>0.36036839306013962</v>
+        <v>0.34678299683832842</v>
       </c>
       <c r="BO36" s="3">
         <f t="shared" si="10"/>
@@ -7867,15 +7866,15 @@
       <c r="G37" s="14">
         <v>112</v>
       </c>
-      <c r="H37" s="17">
-        <v>94.38</v>
+      <c r="H37" s="7">
+        <v>99.82</v>
       </c>
       <c r="I37" s="3">
         <v>-20.774374589761095</v>
       </c>
       <c r="J37" s="4">
         <f t="shared" si="2"/>
-        <v>-0.22011416179022139</v>
+        <v>-0.20811835894370964</v>
       </c>
       <c r="K37" s="3">
         <v>94388.83163095171</v>
@@ -7982,7 +7981,7 @@
       </c>
       <c r="BL37" s="17">
         <f t="shared" si="6"/>
-        <v>408.38</v>
+        <v>413.82</v>
       </c>
       <c r="BM37" s="17">
         <f t="shared" si="7"/>
@@ -7990,7 +7989,7 @@
       </c>
       <c r="BN37" s="4">
         <f t="shared" si="8"/>
-        <v>-0.21250749482338188</v>
+        <v>-0.20971391120770552</v>
       </c>
       <c r="BO37" s="3">
         <f t="shared" si="10"/>
@@ -8053,15 +8052,15 @@
       <c r="G38" s="14">
         <v>46</v>
       </c>
-      <c r="H38" s="17">
-        <v>54.4</v>
+      <c r="H38" s="7">
+        <v>39.759039999999999</v>
       </c>
       <c r="I38" s="3">
         <v>19.183197784832394</v>
       </c>
       <c r="J38" s="4">
         <f t="shared" si="2"/>
-        <v>0.35263231222118374</v>
+        <v>0.48248644295315973</v>
       </c>
       <c r="K38" s="3">
         <v>100619.43490047885</v>
@@ -8168,7 +8167,7 @@
       </c>
       <c r="BL38" s="17">
         <f t="shared" si="6"/>
-        <v>236.4</v>
+        <v>221.75904</v>
       </c>
       <c r="BM38" s="17">
         <f t="shared" si="7"/>
@@ -8176,7 +8175,7 @@
       </c>
       <c r="BN38" s="4">
         <f t="shared" si="8"/>
-        <v>0.35942364837047097</v>
+        <v>0.38315349162216494</v>
       </c>
       <c r="BO38" s="3">
         <f t="shared" si="10"/>
@@ -8239,15 +8238,15 @@
       <c r="G39" s="14">
         <v>15.5</v>
       </c>
-      <c r="H39" s="17">
-        <v>17.672502000000001</v>
+      <c r="H39" s="7">
+        <v>17.535019999999999</v>
       </c>
       <c r="I39" s="3">
         <v>9.259929066798664</v>
       </c>
       <c r="J39" s="4">
         <f t="shared" si="2"/>
-        <v>0.52397385875518154</v>
+        <v>0.52808203622229488</v>
       </c>
       <c r="K39" s="3">
         <v>93473.032591125986</v>
@@ -8354,7 +8353,7 @@
       </c>
       <c r="BL39" s="17">
         <f t="shared" si="6"/>
-        <v>67.672502000000009</v>
+        <v>67.535020000000003</v>
       </c>
       <c r="BM39" s="17">
         <f t="shared" si="7"/>
@@ -8362,7 +8361,7 @@
       </c>
       <c r="BN39" s="4">
         <f t="shared" si="8"/>
-        <v>0.46545402425396115</v>
+        <v>0.46640155562601798</v>
       </c>
       <c r="BO39" s="3">
         <f t="shared" si="10"/>
@@ -8425,15 +8424,15 @@
       <c r="G40" s="14">
         <v>12</v>
       </c>
-      <c r="H40" s="17">
-        <v>19.601610399999998</v>
+      <c r="H40" s="7">
+        <v>18.1816104</v>
       </c>
       <c r="I40" s="3">
         <v>7.2548821293751615</v>
       </c>
       <c r="J40" s="4">
         <f t="shared" si="2"/>
-        <v>0.37011663742562512</v>
+        <v>0.39902307715135954</v>
       </c>
       <c r="K40" s="3">
         <v>102889.40225520697</v>
@@ -8540,7 +8539,7 @@
       </c>
       <c r="BL40" s="17">
         <f t="shared" si="6"/>
-        <v>65.601610399999998</v>
+        <v>64.181610399999997</v>
       </c>
       <c r="BM40" s="17">
         <f t="shared" si="7"/>
@@ -8548,7 +8547,7 @@
       </c>
       <c r="BN40" s="4">
         <f t="shared" si="8"/>
-        <v>0.19070688600524363</v>
+        <v>0.19492622198699466</v>
       </c>
       <c r="BO40" s="3">
         <f t="shared" si="10"/>
@@ -8615,7 +8614,7 @@
       <c r="G41" s="14">
         <v>0</v>
       </c>
-      <c r="H41" s="17">
+      <c r="H41" s="7">
         <v>0</v>
       </c>
       <c r="I41" s="3">
@@ -8799,7 +8798,7 @@
       <c r="G42" s="14">
         <v>28.5</v>
       </c>
-      <c r="H42" s="17">
+      <c r="H42" s="7">
         <v>30.11</v>
       </c>
       <c r="I42" s="3">
@@ -8985,15 +8984,15 @@
       <c r="G43" s="14">
         <v>0</v>
       </c>
-      <c r="H43" s="17">
-        <v>1</v>
+      <c r="H43" s="7">
+        <v>2.2999999999999998</v>
       </c>
       <c r="I43" s="3">
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="J43" s="4">
         <f t="shared" si="2"/>
-        <v>9.9999999999999978E-2</v>
+        <v>4.3478260869565209E-2</v>
       </c>
       <c r="K43" s="3">
         <v>90000</v>
@@ -9100,7 +9099,7 @@
       </c>
       <c r="BL43" s="17">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="BM43" s="17">
         <f t="shared" si="7"/>
@@ -9108,7 +9107,7 @@
       </c>
       <c r="BN43" s="4">
         <f t="shared" si="8"/>
-        <v>0.77500000000000002</v>
+        <v>0.58490566037735847</v>
       </c>
       <c r="BO43" s="3">
         <f t="shared" si="10"/>
@@ -9169,15 +9168,15 @@
       <c r="G44" s="14">
         <v>20</v>
       </c>
-      <c r="H44" s="17">
-        <v>19.856249999999999</v>
+      <c r="H44" s="7">
+        <v>19.899999999999999</v>
       </c>
       <c r="I44" s="3">
         <v>4.3001544268574143</v>
       </c>
       <c r="J44" s="4">
         <f t="shared" si="2"/>
-        <v>0.21656427708441495</v>
+        <v>0.21608816215363894</v>
       </c>
       <c r="K44" s="3">
         <v>112725.33024016366</v>
@@ -9284,7 +9283,7 @@
       </c>
       <c r="BL44" s="17">
         <f t="shared" si="6"/>
-        <v>66.856250000000003</v>
+        <v>66.900000000000006</v>
       </c>
       <c r="BM44" s="17">
         <f t="shared" si="7"/>
@@ -9292,7 +9291,7 @@
       </c>
       <c r="BN44" s="4">
         <f t="shared" si="8"/>
-        <v>-5.2292739292330638E-4</v>
+        <v>-5.2258541873137217E-4</v>
       </c>
       <c r="BO44" s="3">
         <f t="shared" si="10"/>
@@ -9362,15 +9361,15 @@
       <c r="G45" s="14">
         <v>33.580799999999996</v>
       </c>
-      <c r="H45" s="17">
-        <v>26.142800000000001</v>
+      <c r="H45" s="7">
+        <v>21.72</v>
       </c>
       <c r="I45" s="3">
         <v>12.264640410293163</v>
       </c>
       <c r="J45" s="4">
         <f t="shared" si="2"/>
-        <v>0.46914027611017806</v>
+        <v>0.56467036879802779</v>
       </c>
       <c r="K45" s="3">
         <v>115651.32991422365</v>
@@ -9477,7 +9476,7 @@
       </c>
       <c r="BL45" s="17">
         <f t="shared" si="6"/>
-        <v>142.73480000000001</v>
+        <v>138.31200000000001</v>
       </c>
       <c r="BM45" s="17">
         <f t="shared" si="7"/>
@@ -9485,7 +9484,7 @@
       </c>
       <c r="BN45" s="4">
         <f t="shared" si="8"/>
-        <v>0.5819093435116075</v>
+        <v>0.6005170467078822</v>
       </c>
       <c r="BO45" s="3">
         <f t="shared" si="10"/>
@@ -9551,15 +9550,15 @@
       <c r="G46" s="14">
         <v>19.099999999999998</v>
       </c>
-      <c r="H46" s="17">
-        <v>24.310000000000002</v>
+      <c r="H46" s="7">
+        <v>26.685100000000002</v>
       </c>
       <c r="I46" s="3">
         <v>10.068902406452644</v>
       </c>
       <c r="J46" s="4">
         <f t="shared" si="2"/>
-        <v>0.41418767611898982</v>
+        <v>0.37732301570736637</v>
       </c>
       <c r="K46" s="3">
         <v>74953.145229196627</v>
@@ -9666,7 +9665,7 @@
       </c>
       <c r="BL46" s="17">
         <f t="shared" si="6"/>
-        <v>87.460000000000008</v>
+        <v>89.835099999999997</v>
       </c>
       <c r="BM46" s="17">
         <f t="shared" si="7"/>
@@ -9674,7 +9673,7 @@
       </c>
       <c r="BN46" s="4">
         <f t="shared" si="8"/>
-        <v>0.29983169846497087</v>
+        <v>0.29190461576540078</v>
       </c>
       <c r="BO46" s="3">
         <f t="shared" si="10"/>
@@ -9737,7 +9736,7 @@
       <c r="G47" s="14">
         <v>12</v>
       </c>
-      <c r="H47" s="17">
+      <c r="H47" s="7">
         <v>14.6951</v>
       </c>
       <c r="I47" s="3">
@@ -9921,15 +9920,15 @@
       <c r="G48" s="14">
         <v>137.5</v>
       </c>
-      <c r="H48" s="17">
-        <v>157</v>
+      <c r="H48" s="7">
+        <v>180.4</v>
       </c>
       <c r="I48" s="3">
         <v>79.417552917788299</v>
       </c>
       <c r="J48" s="4">
         <f t="shared" si="2"/>
-        <v>0.50584428610056242</v>
+        <v>0.44023033768175329</v>
       </c>
       <c r="K48" s="3">
         <v>104841.14470569149</v>
@@ -10036,7 +10035,7 @@
       </c>
       <c r="BL48" s="17">
         <f t="shared" si="6"/>
-        <v>569.5</v>
+        <v>592.9</v>
       </c>
       <c r="BM48" s="17">
         <f t="shared" si="7"/>
@@ -10044,7 +10043,7 @@
       </c>
       <c r="BN48" s="4">
         <f t="shared" si="8"/>
-        <v>0.41421506153905124</v>
+        <v>0.39786722473686909</v>
       </c>
       <c r="BO48" s="3">
         <f t="shared" si="10"/>
@@ -10114,15 +10113,15 @@
       <c r="G49" s="14">
         <v>81.63</v>
       </c>
-      <c r="H49" s="17">
-        <v>72</v>
+      <c r="H49" s="7">
+        <v>72.691798554999991</v>
       </c>
       <c r="I49" s="3">
         <v>14.43</v>
       </c>
       <c r="J49" s="4">
         <f t="shared" si="2"/>
-        <v>0.20041666666666666</v>
+        <v>0.19850932686831224</v>
       </c>
       <c r="K49" s="3">
         <v>101000</v>
@@ -10229,7 +10228,7 @@
       </c>
       <c r="BL49" s="17">
         <f t="shared" si="6"/>
-        <v>433.27</v>
+        <v>433.96179855499997</v>
       </c>
       <c r="BM49" s="17">
         <f t="shared" si="7"/>
@@ -10237,7 +10236,7 @@
       </c>
       <c r="BN49" s="4">
         <f t="shared" si="8"/>
-        <v>0.42864495580123235</v>
+        <v>0.42796163307093965</v>
       </c>
       <c r="BO49" s="3">
         <f t="shared" si="10"/>
@@ -10305,15 +10304,15 @@
       <c r="G50" s="14">
         <v>21.75</v>
       </c>
-      <c r="H50" s="17">
-        <v>22.341290000000001</v>
+      <c r="H50" s="7">
+        <v>22.31129</v>
       </c>
       <c r="I50" s="3">
         <v>18.301290000000002</v>
       </c>
       <c r="J50" s="4">
         <f t="shared" si="2"/>
-        <v>0.81916890206429449</v>
+        <v>0.82027036536211051</v>
       </c>
       <c r="K50" s="3">
         <v>101000</v>
@@ -10421,7 +10420,7 @@
       </c>
       <c r="BL50" s="17">
         <f t="shared" si="6"/>
-        <v>92.691290000000009</v>
+        <v>92.661290000000008</v>
       </c>
       <c r="BM50" s="17">
         <f t="shared" si="7"/>
@@ -10429,7 +10428,7 @@
       </c>
       <c r="BN50" s="4">
         <f t="shared" si="8"/>
-        <v>0.8125821746574029</v>
+        <v>0.81284525609345593</v>
       </c>
       <c r="BO50" s="3">
         <f t="shared" si="10"/>
@@ -10490,15 +10489,15 @@
       <c r="G51" s="14">
         <v>57</v>
       </c>
-      <c r="H51" s="17">
-        <v>0</v>
+      <c r="H51" s="7">
+        <v>0.99424999999999997</v>
       </c>
       <c r="I51" s="3">
         <v>-19.03593710853351</v>
       </c>
       <c r="J51" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-19.14602676241741</v>
       </c>
       <c r="K51" s="3">
         <v>105755.2061585195</v>
@@ -10605,7 +10604,7 @@
       </c>
       <c r="BL51" s="17">
         <f t="shared" si="6"/>
-        <v>284.10000000000002</v>
+        <v>285.09425000000005</v>
       </c>
       <c r="BM51" s="17">
         <f t="shared" si="7"/>
@@ -10613,7 +10612,7 @@
       </c>
       <c r="BN51" s="4">
         <f t="shared" si="8"/>
-        <v>0.71188127572441362</v>
+        <v>0.70939863021897454</v>
       </c>
       <c r="BO51" s="3">
         <f t="shared" si="10"/>
@@ -10674,15 +10673,15 @@
       <c r="G52" s="14">
         <v>8</v>
       </c>
-      <c r="H52" s="17">
-        <v>6</v>
+      <c r="H52" s="7">
+        <v>1.2</v>
       </c>
       <c r="I52" s="3">
         <v>-2.3648496895126332</v>
       </c>
       <c r="J52" s="4">
         <f t="shared" si="2"/>
-        <v>-0.3941416149187722</v>
+        <v>-1.970708074593861</v>
       </c>
       <c r="K52" s="3">
         <v>139414.16149187722</v>
@@ -10789,7 +10788,7 @@
       </c>
       <c r="BL52" s="17">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>23.2</v>
       </c>
       <c r="BM52" s="17">
         <f t="shared" si="7"/>
@@ -10797,7 +10796,7 @@
       </c>
       <c r="BN52" s="4">
         <f t="shared" si="8"/>
-        <v>-0.28460191660372597</v>
+        <v>-0.34348507176311754</v>
       </c>
       <c r="BO52" s="3">
         <f t="shared" si="10"/>
@@ -10858,7 +10857,7 @@
       <c r="G53" s="14">
         <v>1</v>
       </c>
-      <c r="H53" s="17">
+      <c r="H53" s="7">
         <v>0</v>
       </c>
       <c r="I53" s="3">
@@ -11042,7 +11041,7 @@
       <c r="G54" s="14">
         <v>0</v>
       </c>
-      <c r="H54" s="17">
+      <c r="H54" s="7">
         <v>0</v>
       </c>
       <c r="I54" s="3">
@@ -11226,15 +11225,15 @@
       <c r="G55" s="14">
         <v>60.514180000000003</v>
       </c>
-      <c r="H55" s="17">
-        <v>32.5</v>
+      <c r="H55" s="7">
+        <v>33.948900000000002</v>
       </c>
       <c r="I55" s="3">
         <v>2.2736636198644078E-2</v>
       </c>
       <c r="J55" s="4">
         <f t="shared" si="2"/>
-        <v>6.9958880611212552E-4</v>
+        <v>6.6973116061622249E-4</v>
       </c>
       <c r="K55" s="3">
         <v>50745.724005939614</v>
@@ -11341,7 +11340,7 @@
       </c>
       <c r="BL55" s="17">
         <f t="shared" si="6"/>
-        <v>506.24518</v>
+        <v>507.69407999999999</v>
       </c>
       <c r="BM55" s="17">
         <f t="shared" si="7"/>
@@ -11349,7 +11348,7 @@
       </c>
       <c r="BN55" s="4">
         <f t="shared" si="8"/>
-        <v>0.72414111189296504</v>
+        <v>0.72207449717683181</v>
       </c>
       <c r="BO55" s="3">
         <f t="shared" si="10"/>
@@ -11410,15 +11409,15 @@
       <c r="G56" s="14">
         <v>36.664500000000004</v>
       </c>
-      <c r="H56" s="17">
-        <v>3.7710600000000003</v>
+      <c r="H56" s="7">
+        <v>3.7510600000000003</v>
       </c>
       <c r="I56" s="3">
         <v>1.3470600000000004</v>
       </c>
       <c r="J56" s="4">
         <f t="shared" si="2"/>
-        <v>0.3572099091502125</v>
+        <v>0.35911449030407411</v>
       </c>
       <c r="K56" s="3">
         <v>101000</v>
@@ -11525,7 +11524,7 @@
       </c>
       <c r="BL56" s="17">
         <f t="shared" si="6"/>
-        <v>100.27106000000001</v>
+        <v>100.25106</v>
       </c>
       <c r="BM56" s="17">
         <f t="shared" si="7"/>
@@ -11533,7 +11532,7 @@
       </c>
       <c r="BN56" s="4">
         <f t="shared" si="8"/>
-        <v>0.89604976750021381</v>
+        <v>0.89622852865595637</v>
       </c>
       <c r="BO56" s="3">
         <f t="shared" si="10"/>
@@ -11598,7 +11597,7 @@
       <c r="G57" s="14">
         <v>17.4129</v>
       </c>
-      <c r="H57" s="17">
+      <c r="H57" s="7">
         <v>0</v>
       </c>
       <c r="I57" s="3">
@@ -11781,7 +11780,7 @@
       <c r="G58" s="3">
         <v>0</v>
       </c>
-      <c r="H58" s="17">
+      <c r="H58" s="7">
         <v>4</v>
       </c>
       <c r="I58" s="3">
@@ -11952,7 +11951,7 @@
       <c r="G59" s="3">
         <v>0</v>
       </c>
-      <c r="H59" s="17">
+      <c r="H59" s="7">
         <v>5.25</v>
       </c>
       <c r="I59" s="3">
@@ -12126,7 +12125,7 @@
       <c r="G60" s="14">
         <v>217</v>
       </c>
-      <c r="H60" s="17">
+      <c r="H60" s="7">
         <v>0</v>
       </c>
       <c r="I60" s="3">
@@ -12224,15 +12223,15 @@
         <v>122</v>
       </c>
       <c r="G61" s="28"/>
-      <c r="H61" s="17">
-        <v>25</v>
+      <c r="H61" s="7">
+        <v>23</v>
       </c>
       <c r="I61" s="3">
         <v>6.1704803999999989</v>
       </c>
       <c r="J61" s="4">
         <f t="shared" si="2"/>
-        <v>0.24681921599999995</v>
+        <v>0.26828175652173908</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -12267,7 +12266,7 @@
       </c>
       <c r="BL61" s="17">
         <f t="shared" si="6"/>
-        <v>54.36</v>
+        <v>52.36</v>
       </c>
       <c r="BM61" s="17">
         <f t="shared" si="7"/>
@@ -12275,7 +12274,7 @@
       </c>
       <c r="BN61" s="4">
         <f t="shared" si="8"/>
-        <v>0.4372523988226637</v>
+        <v>0.45395417112299463</v>
       </c>
       <c r="BO61" s="3">
         <f t="shared" si="10"/>
@@ -12299,7 +12298,7 @@
         <v>95</v>
       </c>
       <c r="G62" s="8"/>
-      <c r="H62" s="17">
+      <c r="H62" s="7">
         <v>3.18</v>
       </c>
       <c r="I62" s="8"/>
@@ -12378,54 +12377,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" x14ac:dyDescent="0.35">
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
-      <c r="T1" s="34"/>
-      <c r="V1" s="33" t="s">
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="V1" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="W1" s="34"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="34"/>
-      <c r="Z1" s="34"/>
-      <c r="AA1" s="34"/>
-      <c r="AB1" s="34"/>
-      <c r="AC1" s="34"/>
-      <c r="AD1" s="34"/>
-      <c r="AE1" s="34"/>
-      <c r="AF1" s="34"/>
-      <c r="AG1" s="34"/>
-      <c r="AH1" s="34"/>
-      <c r="AI1" s="34"/>
-      <c r="AK1" s="33" t="s">
+      <c r="W1" s="35"/>
+      <c r="X1" s="35"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="35"/>
+      <c r="AA1" s="35"/>
+      <c r="AB1" s="35"/>
+      <c r="AC1" s="35"/>
+      <c r="AD1" s="35"/>
+      <c r="AE1" s="35"/>
+      <c r="AF1" s="35"/>
+      <c r="AG1" s="35"/>
+      <c r="AH1" s="35"/>
+      <c r="AI1" s="35"/>
+      <c r="AK1" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="AL1" s="34"/>
-      <c r="AM1" s="34"/>
-      <c r="AN1" s="34"/>
-      <c r="AO1" s="34"/>
-      <c r="AP1" s="34"/>
-      <c r="AQ1" s="34"/>
-      <c r="AR1" s="34"/>
-      <c r="AS1" s="34"/>
-      <c r="AT1" s="34"/>
-      <c r="AU1" s="34"/>
-      <c r="AV1" s="34"/>
-      <c r="AW1" s="34"/>
-      <c r="AX1" s="34"/>
+      <c r="AL1" s="35"/>
+      <c r="AM1" s="35"/>
+      <c r="AN1" s="35"/>
+      <c r="AO1" s="35"/>
+      <c r="AP1" s="35"/>
+      <c r="AQ1" s="35"/>
+      <c r="AR1" s="35"/>
+      <c r="AS1" s="35"/>
+      <c r="AT1" s="35"/>
+      <c r="AU1" s="35"/>
+      <c r="AV1" s="35"/>
+      <c r="AW1" s="35"/>
+      <c r="AX1" s="35"/>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -12659,7 +12658,7 @@
         <v>188</v>
       </c>
       <c r="AL3" s="17">
-        <v>188</v>
+        <v>178.9</v>
       </c>
       <c r="AM3" s="3"/>
       <c r="AN3" s="4"/>
@@ -12760,7 +12759,7 @@
         <v>2</v>
       </c>
       <c r="AL4" s="17">
-        <v>1.02</v>
+        <v>3</v>
       </c>
       <c r="AM4" s="3"/>
       <c r="AN4" s="4"/>
@@ -12861,7 +12860,7 @@
         <v>8</v>
       </c>
       <c r="AL5" s="17">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="AM5" s="3"/>
       <c r="AN5" s="4"/>
@@ -13063,7 +13062,7 @@
         <v>10.199999999999999</v>
       </c>
       <c r="AL7" s="17">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="AM7" s="3"/>
       <c r="AN7" s="4"/>
@@ -13467,7 +13466,7 @@
         <v>17.166666666666668</v>
       </c>
       <c r="AL11" s="17">
-        <v>13.3</v>
+        <v>10.82</v>
       </c>
       <c r="AM11" s="3"/>
       <c r="AN11" s="4"/>
@@ -13568,8 +13567,7 @@
         <v>103.101392</v>
       </c>
       <c r="AL12" s="17">
-        <f>115.71541+9</f>
-        <v>124.71541000000001</v>
+        <v>144</v>
       </c>
       <c r="AM12" s="3"/>
       <c r="AN12" s="4"/>
@@ -13670,7 +13668,7 @@
         <v>9</v>
       </c>
       <c r="AL13" s="17">
-        <v>6</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="AM13" s="3"/>
       <c r="AN13" s="4"/>
@@ -13969,7 +13967,7 @@
         <v>5</v>
       </c>
       <c r="AL16" s="17">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="AM16" s="3"/>
       <c r="AN16" s="4"/>
@@ -14070,7 +14068,7 @@
         <v>100</v>
       </c>
       <c r="AL17" s="17">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="AM17" s="3"/>
       <c r="AN17" s="4"/>
@@ -14171,7 +14169,7 @@
         <v>30</v>
       </c>
       <c r="AL18" s="17">
-        <v>45</v>
+        <v>49.19</v>
       </c>
       <c r="AM18" s="3"/>
       <c r="AN18" s="4"/>
@@ -14272,7 +14270,7 @@
         <v>50</v>
       </c>
       <c r="AL19" s="17">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AM19" s="3"/>
       <c r="AN19" s="4"/>
@@ -14373,7 +14371,7 @@
         <v>6.703333333333334</v>
       </c>
       <c r="AL20" s="17">
-        <v>6.44</v>
+        <v>6.83</v>
       </c>
       <c r="AM20" s="3"/>
       <c r="AN20" s="4"/>
@@ -14474,7 +14472,7 @@
         <v>30</v>
       </c>
       <c r="AL21" s="17">
-        <v>52.88</v>
+        <v>56.88</v>
       </c>
       <c r="AM21" s="3"/>
       <c r="AN21" s="4"/>
@@ -14672,7 +14670,7 @@
         <v>1.3333333333333333</v>
       </c>
       <c r="AL23" s="17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM23" s="3"/>
       <c r="AN23" s="4"/>
@@ -15573,7 +15571,7 @@
         <v>20.91</v>
       </c>
       <c r="AL32" s="17">
-        <v>21.5</v>
+        <v>21.75</v>
       </c>
       <c r="AM32" s="3"/>
       <c r="AN32" s="4"/>
@@ -15971,7 +15969,7 @@
         <v>7.87</v>
       </c>
       <c r="AL36" s="17">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="AM36" s="3"/>
       <c r="AN36" s="4"/>
@@ -16072,7 +16070,7 @@
         <v>36</v>
       </c>
       <c r="AL37" s="17">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="AM37" s="3"/>
       <c r="AN37" s="4"/>
@@ -16173,7 +16171,7 @@
         <v>17</v>
       </c>
       <c r="AL38" s="17">
-        <v>24.4</v>
+        <v>15.5</v>
       </c>
       <c r="AM38" s="3"/>
       <c r="AN38" s="4"/>
@@ -16375,7 +16373,7 @@
         <v>5</v>
       </c>
       <c r="AL40" s="17">
-        <v>9</v>
+        <v>7.9</v>
       </c>
       <c r="AM40" s="3"/>
       <c r="AN40" s="4"/>
@@ -16672,7 +16670,7 @@
         <v>0</v>
       </c>
       <c r="AL43" s="17">
-        <v>1</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="AM43" s="3"/>
       <c r="AN43" s="4"/>
@@ -16773,7 +16771,7 @@
         <v>6</v>
       </c>
       <c r="AL44" s="17">
-        <v>9</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="AM44" s="3"/>
       <c r="AN44" s="4"/>
@@ -16874,7 +16872,7 @@
         <v>11.1936</v>
       </c>
       <c r="AL45" s="17">
-        <v>9.0863999999999994</v>
+        <v>8</v>
       </c>
       <c r="AM45" s="3"/>
       <c r="AN45" s="4"/>
@@ -16975,7 +16973,7 @@
         <v>6.3666666666666663</v>
       </c>
       <c r="AL46" s="17">
-        <v>5.0999999999999996</v>
+        <v>5.8000000000000007</v>
       </c>
       <c r="AM46" s="3"/>
       <c r="AN46" s="4"/>
@@ -17177,7 +17175,7 @@
         <v>45.833333333333336</v>
       </c>
       <c r="AL48" s="17">
-        <v>45.8</v>
+        <v>45</v>
       </c>
       <c r="AM48" s="3"/>
       <c r="AN48" s="4"/>
@@ -17379,7 +17377,7 @@
         <v>7.25</v>
       </c>
       <c r="AL50" s="17">
-        <v>3.83</v>
+        <v>6.7</v>
       </c>
       <c r="AM50" s="3"/>
       <c r="AN50" s="4"/>
@@ -17577,7 +17575,7 @@
         <v>5</v>
       </c>
       <c r="AL52" s="17">
-        <v>5</v>
+        <v>0.2</v>
       </c>
       <c r="AM52" s="3"/>
       <c r="AN52" s="4"/>
@@ -17951,7 +17949,9 @@
       <c r="AH56" s="30"/>
       <c r="AI56" s="30"/>
       <c r="AK56" s="14"/>
-      <c r="AL56" s="17"/>
+      <c r="AL56" s="17">
+        <v>0</v>
+      </c>
       <c r="AM56" s="3"/>
       <c r="AN56" s="4"/>
       <c r="AO56" s="3"/>
@@ -18047,7 +18047,7 @@
         <v>7</v>
       </c>
       <c r="AL57" s="17">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM57" s="3"/>
       <c r="AN57" s="4"/>
@@ -18515,7 +18515,7 @@
         <v>0</v>
       </c>
       <c r="AL62" s="17">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AM62" s="3"/>
       <c r="AN62" s="4"/>
@@ -18647,7 +18647,7 @@
     <row r="66" spans="8:20" x14ac:dyDescent="0.35">
       <c r="H66" s="18"/>
       <c r="I66" s="18"/>
-      <c r="J66" s="38"/>
+      <c r="J66" s="33"/>
       <c r="T66" s="18"/>
     </row>
   </sheetData>
